--- a/universities_wise/arizona_state_university/asu_aerospace_mechanical_faculty.xlsx
+++ b/universities_wise/arizona_state_university/asu_aerospace_mechanical_faculty.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Faculty A-Z" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Field Matched A-Z" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,12 +18,19 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="10"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -43,14 +51,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -466,12 +477,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Lin Li</t>
+          <t>Aditi Chattopadhyay</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Regents Professor</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -484,35 +495,39 @@
           <t>Arizona State University</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Lin.Li.10@asu.edu</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>aditi@asu.edu</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>inverse problems, multiscale modeling, optimization, transition</t>
+        </is>
+      </c>
       <c r="G2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>https://search.asu.edu/profile/linli25</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Lin%20Li%20Arizona%20State%20University</t>
+        <v>1</v>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/chattopa</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Aditi%20Chattopadhyay%20Arizona%20State%20University</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Kunal Garg</t>
+          <t>Aikaterini Stefanaki</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Associate Teaching Professor</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -525,27 +540,23 @@
           <t>Arizona State University</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>kgarg24@asu.edu</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>optimization</t>
-        </is>
-      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>astefan9@asu.edu</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="b">
-        <v>1</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>https://search.asu.edu/profile/kgarg24</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Kunal%20Garg%20Arizona%20State%20University</t>
+        <v>0</v>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/astefan9</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Aikaterini%20Stefanaki%20Arizona%20State%20University</t>
         </is>
       </c>
     </row>
@@ -570,7 +581,7 @@
           <t>Arizona State University</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>Alberto.Scotti@asu.edu</t>
         </is>
@@ -583,12 +594,12 @@
       <c r="G4" t="b">
         <v>1</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="1" t="inlineStr">
         <is>
           <t>https://search.asu.edu/profile/adscotti</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="1" t="inlineStr">
         <is>
           <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Alberto%20Scotti%20Arizona%20State%20University</t>
         </is>
@@ -597,12 +608,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Zhe Xu</t>
+          <t>Beomjin Kwon</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -615,35 +626,39 @@
           <t>Arizona State University</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>xzhe1@asu.edu</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>kwon@asu.edu</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>data-driven modeling, heat transfer, transport phenomena</t>
+        </is>
+      </c>
       <c r="G5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>https://search.asu.edu/profile/xzhe1</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Zhe%20Xu%20Arizona%20State%20University</t>
+        <v>1</v>
+      </c>
+      <c r="H5" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/bkwon2</t>
+        </is>
+      </c>
+      <c r="I5" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Beomjin%20Kwon%20Arizona%20State%20University</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Aikaterini Stefanaki</t>
+          <t>Cindy (Xiangjia) Li</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Associate Teaching Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -656,35 +671,35 @@
           <t>Arizona State University</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>astefan9@asu.edu</t>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>xiangjia.li@asu.edu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="b">
         <v>0</v>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>https://search.asu.edu/profile/astefan9</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Aikaterini%20Stefanaki%20Arizona%20State%20University</t>
+      <c r="H6" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/xiangji5</t>
+        </is>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Cindy%20%28Xiangjia%29%20Li%20Arizona%20State%20University</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ronald Calhoun</t>
+          <t>Derrick Speaks</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Assistant Teaching Professor</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -697,39 +712,35 @@
           <t>Arizona State University</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Ronald.Calhoun@asu.edu</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>fluid dynamics</t>
-        </is>
-      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>Derrick.Speaks@asu.edu</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="b">
-        <v>1</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>https://search.asu.edu/profile/rcalhou</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ronald%20Calhoun%20Arizona%20State%20University</t>
+        <v>0</v>
+      </c>
+      <c r="H7" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/dspeaks2</t>
+        </is>
+      </c>
+      <c r="I7" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Derrick%20Speaks%20Arizona%20State%20University</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Wonmo Kang</t>
+          <t>Erik Andersen</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Faculty Associate</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -742,23 +753,23 @@
           <t>Arizona State University</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Wonmo.Kang@asu.edu</t>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>Erik.J.Andersen@asu.edu</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="b">
         <v>0</v>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>https://search.asu.edu/profile/wkang16</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Wonmo%20Kang%20Arizona%20State%20University</t>
+      <c r="H8" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/ejande22</t>
+        </is>
+      </c>
+      <c r="I8" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Erik%20Andersen%20Arizona%20State%20University</t>
         </is>
       </c>
     </row>
@@ -783,7 +794,7 @@
           <t>Arizona State University</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="1" t="inlineStr">
         <is>
           <t>Gokul.Pathikonda@asu.edu</t>
         </is>
@@ -796,12 +807,12 @@
       <c r="G9" t="b">
         <v>1</v>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="1" t="inlineStr">
         <is>
           <t>https://search.asu.edu/profile/gpathiko</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="1" t="inlineStr">
         <is>
           <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Gokul%20Pathikonda%20Arizona%20State%20University</t>
         </is>
@@ -810,12 +821,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Yongming Liu</t>
+          <t>Hamidreza Marvi</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -828,34 +839,30 @@
           <t>Arizona State University</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Yongming.Liu@asu.edu</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>uncertainty quantification</t>
-        </is>
-      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>hmarvi@asu.edu</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="b">
-        <v>1</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>https://search.asu.edu/profile/yliu35</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Yongming%20Liu%20Arizona%20State%20University</t>
+        <v>0</v>
+      </c>
+      <c r="H10" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/hmarvi</t>
+        </is>
+      </c>
+      <c r="I10" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Hamidreza%20Marvi%20Arizona%20State%20University</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Liping Wang</t>
+          <t>Houlong Zhuang</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -873,39 +880,39 @@
           <t>Arizona State University</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Liping.Wang@asu.edu</t>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>zhuanghl@asu.edu</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>heat transfer</t>
+          <t>computational physics</t>
         </is>
       </c>
       <c r="G11" t="b">
         <v>1</v>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>https://search.asu.edu/profile/lwang78</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Liping%20Wang%20Arizona%20State%20University</t>
+      <c r="H11" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/hzhuang7</t>
+        </is>
+      </c>
+      <c r="I11" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Houlong%20Zhuang%20Arizona%20State%20University</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Qiong Nian</t>
+          <t>Huan Wu</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -918,30 +925,34 @@
           <t>Arizona State University</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Qiong.Nian@asu.edu</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
+      <c r="E12" s="1" t="inlineStr">
+        <is>
+          <t>huanwu@asu.edu</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>computational physics</t>
+        </is>
+      </c>
       <c r="G12" t="b">
-        <v>0</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://search.asu.edu/profile/qnian</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Qiong%20Nian%20Arizona%20State%20University</t>
+        <v>1</v>
+      </c>
+      <c r="H12" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/huanwu</t>
+        </is>
+      </c>
+      <c r="I12" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Huan%20Wu%20Arizona%20State%20University</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Hyunglae Lee</t>
+          <t>Huei-Ping Huang</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -959,35 +970,39 @@
           <t>Arizona State University</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Hyunglae.Lee@asu.edu</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t>Huei-Ping.Huang@asu.edu</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>fluid dynamics, numerical simulation</t>
+        </is>
+      </c>
       <c r="G13" t="b">
-        <v>0</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://search.asu.edu/profile/hlee234</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Hyunglae%20Lee%20Arizona%20State%20University</t>
+        <v>1</v>
+      </c>
+      <c r="H13" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/hhuang38</t>
+        </is>
+      </c>
+      <c r="I13" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Huei-Ping%20Huang%20Arizona%20State%20University</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Patrick Phelan</t>
+          <t>Hyunglae Lee</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1000,35 +1015,35 @@
           <t>Arizona State University</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>phelan@asu.edu</t>
+      <c r="E14" s="1" t="inlineStr">
+        <is>
+          <t>Hyunglae.Lee@asu.edu</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="b">
         <v>0</v>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>https://search.asu.edu/profile/pphelan</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Patrick%20Phelan%20Arizona%20State%20University</t>
+      <c r="H14" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/hlee234</t>
+        </is>
+      </c>
+      <c r="I14" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Hyunglae%20Lee%20Arizona%20State%20University</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Beomjin Kwon</t>
+          <t>Ivy Chang</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Assistant Teaching Professor</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1041,27 +1056,23 @@
           <t>Arizona State University</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>kwon@asu.edu</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>data-driven modeling, heat transfer, transport phenomena</t>
-        </is>
-      </c>
+      <c r="E15" s="1" t="inlineStr">
+        <is>
+          <t>Ivy.Chang@asu.edu</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="b">
-        <v>1</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>https://search.asu.edu/profile/bkwon2</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Beomjin%20Kwon%20Arizona%20State%20University</t>
+        <v>0</v>
+      </c>
+      <c r="H15" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/iychang</t>
+        </is>
+      </c>
+      <c r="I15" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ivy%20Chang%20Arizona%20State%20University</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1097,7 @@
           <t>Arizona State University</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="1" t="inlineStr">
         <is>
           <t>Jagannathan.Rajagopalan@asu.edu</t>
         </is>
@@ -1099,12 +1110,12 @@
       <c r="G16" t="b">
         <v>1</v>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H16" s="1" t="inlineStr">
         <is>
           <t>https://search.asu.edu/profile/jrajago1</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I16" s="1" t="inlineStr">
         <is>
           <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Jagannathan%20Rajagopalan%20Arizona%20State%20University</t>
         </is>
@@ -1113,12 +1124,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T.-W. Lee</t>
+          <t>James Middleton</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Professor</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1131,27 +1142,23 @@
           <t>Arizona State University</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>ATTWL@asu.edu</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>aerospace propulsion, propulsion</t>
-        </is>
-      </c>
+      <c r="E17" s="1" t="inlineStr">
+        <is>
+          <t>jimbo@asu.edu</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>https://search.asu.edu/profile/attwl</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=T.-W.%20Lee%20Arizona%20State%20University</t>
+        <v>0</v>
+      </c>
+      <c r="H17" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/jimbo</t>
+        </is>
+      </c>
+      <c r="I17" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=James%20Middleton%20Arizona%20State%20University</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1183,7 @@
           <t>Arizona State University</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="1" t="inlineStr">
         <is>
           <t>joswald1@asu.edu</t>
         </is>
@@ -1189,12 +1196,12 @@
       <c r="G18" t="b">
         <v>1</v>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H18" s="1" t="inlineStr">
         <is>
           <t>https://search.asu.edu/profile/joswald1</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I18" s="1" t="inlineStr">
         <is>
           <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Jay%20Oswald%20Arizona%20State%20University</t>
         </is>
@@ -1203,12 +1210,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Raghavendra Murthy</t>
+          <t>Jeonglae Kim</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Associate Teaching Professor</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1221,39 +1228,39 @@
           <t>Arizona State University</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>rnmurthy@asu.edu</t>
+      <c r="E19" s="1" t="inlineStr">
+        <is>
+          <t>jeokim@asu.edu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>optimization, reduced-order modeling</t>
+          <t>aeroacoustics, flow control, optimization, turbulence, turbulent flows</t>
         </is>
       </c>
       <c r="G19" t="b">
         <v>1</v>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>https://search.asu.edu/profile/rnmurthy</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Raghavendra%20Murthy%20Arizona%20State%20University</t>
+      <c r="H19" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/jkim520</t>
+        </is>
+      </c>
+      <c r="I19" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Jeonglae%20Kim%20Arizona%20State%20University</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Srinivas Chakravarthi Kosaraju</t>
+          <t>Jiefeng Sun</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Teaching Professor</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1266,35 +1273,35 @@
           <t>Arizona State University</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Srinivas.Kosaraju@asu.edu</t>
+      <c r="E20" s="1" t="inlineStr">
+        <is>
+          <t>Jiefeng.Sun@asu.edu</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="b">
         <v>0</v>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>https://search.asu.edu/profile/skosara2</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Srinivas%20Chakravarthi%20Kosaraju%20Arizona%20State%20University</t>
+      <c r="H20" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/jsun165</t>
+        </is>
+      </c>
+      <c r="I20" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Jiefeng%20Sun%20Arizona%20State%20University</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Huei-Ping Huang</t>
+          <t>Joshua Wilbur</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Associate Teaching Professor</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1307,39 +1314,35 @@
           <t>Arizona State University</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Huei-Ping.Huang@asu.edu</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>fluid dynamics, numerical simulation</t>
-        </is>
-      </c>
+      <c r="E21" s="1" t="inlineStr">
+        <is>
+          <t>Joshua.Wilbur@asu.edu</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="b">
-        <v>1</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>https://search.asu.edu/profile/hhuang38</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Huei-Ping%20Huang%20Arizona%20State%20University</t>
+        <v>0</v>
+      </c>
+      <c r="H21" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/jdwilbu1</t>
+        </is>
+      </c>
+      <c r="I21" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Joshua%20Wilbur%20Arizona%20State%20University</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Erik Andersen</t>
+          <t>Kangping Chen</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Faculty Associate</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1352,35 +1355,39 @@
           <t>Arizona State University</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Erik.J.Andersen@asu.edu</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
+      <c r="E22" s="1" t="inlineStr">
+        <is>
+          <t>k.p.chen@asu.edu</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>computational fluid dynamics, drag reduction, fluid dynamics, fluid mechanics, multiphase flow</t>
+        </is>
+      </c>
       <c r="G22" t="b">
-        <v>0</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>https://search.asu.edu/profile/ejande22</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Erik%20Andersen%20Arizona%20State%20University</t>
+        <v>1</v>
+      </c>
+      <c r="H22" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/asuchen</t>
+        </is>
+      </c>
+      <c r="I22" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Kangping%20Chen%20Arizona%20State%20University</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sridhar Seetharaman</t>
+          <t>Kiran Ramesh</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1393,35 +1400,39 @@
           <t>Arizona State University</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>seetharaman@asu.edu</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
+      <c r="E23" s="1" t="inlineStr">
+        <is>
+          <t>Kiran.Ramesh@asu.edu</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>aerodynamics, flow control, fluid dynamics, turbulence, vortex dynamics</t>
+        </is>
+      </c>
       <c r="G23" t="b">
-        <v>0</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>https://search.asu.edu/profile/sseeth11</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Sridhar%20Seetharaman%20Arizona%20State%20University</t>
+        <v>1</v>
+      </c>
+      <c r="H23" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/kramesh2</t>
+        </is>
+      </c>
+      <c r="I23" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Kiran%20Ramesh%20Arizona%20State%20University</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Aditi Chattopadhyay</t>
+          <t>Konrad Rykaczewski</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Regents Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1434,39 +1445,35 @@
           <t>Arizona State University</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>aditi@asu.edu</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>inverse problems, multiscale modeling, optimization, transition</t>
-        </is>
-      </c>
+      <c r="E24" s="1" t="inlineStr">
+        <is>
+          <t>konradr@asu.edu</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="b">
-        <v>1</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>https://search.asu.edu/profile/chattopa</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Aditi%20Chattopadhyay%20Arizona%20State%20University</t>
+        <v>0</v>
+      </c>
+      <c r="H24" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/krykacze</t>
+        </is>
+      </c>
+      <c r="I24" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Konrad%20Rykaczewski%20Arizona%20State%20University</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Mohamed Houssem Kasbaoui</t>
+          <t>Kunal Garg</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1479,39 +1486,39 @@
           <t>Arizona State University</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>houssem.kasbaoui@asu.edu</t>
+      <c r="E25" s="1" t="inlineStr">
+        <is>
+          <t>kgarg24@asu.edu</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>cfd, computational fluid dynamics, dns, fluid dynamics, multiphase flow</t>
+          <t>optimization</t>
         </is>
       </c>
       <c r="G25" t="b">
         <v>1</v>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>https://search.asu.edu/profile/mkasbaou</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Mohamed%20Houssem%20Kasbaoui%20Arizona%20State%20University</t>
+      <c r="H25" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/kgarg24</t>
+        </is>
+      </c>
+      <c r="I25" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Kunal%20Garg%20Arizona%20State%20University</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Jiefeng Sun</t>
+          <t>Leila Ladani</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Professor</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1524,35 +1531,35 @@
           <t>Arizona State University</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Jiefeng.Sun@asu.edu</t>
+      <c r="E26" s="1" t="inlineStr">
+        <is>
+          <t>ladani@asu.edu</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="b">
         <v>0</v>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>https://search.asu.edu/profile/jsun165</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Jiefeng%20Sun%20Arizona%20State%20University</t>
+      <c r="H26" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/ljannesa</t>
+        </is>
+      </c>
+      <c r="I26" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Leila%20Ladani%20Arizona%20State%20University</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Yi Ren</t>
+          <t>Leixin Ma</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1565,39 +1572,39 @@
           <t>Arizona State University</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>yiren@asu.edu</t>
+      <c r="E27" s="1" t="inlineStr">
+        <is>
+          <t>Leixin.Ma@asu.edu</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>optimization</t>
+          <t>aerodynamics, fluid-structure interaction, physics-informed machine learning</t>
         </is>
       </c>
       <c r="G27" t="b">
         <v>1</v>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>https://search.asu.edu/profile/yren32</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Yi%20Ren%20Arizona%20State%20University</t>
+      <c r="H27" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/leixinma</t>
+        </is>
+      </c>
+      <c r="I27" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Leixin%20Ma%20Arizona%20State%20University</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Derrick Speaks</t>
+          <t>Lin Li</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Assistant Teaching Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1610,35 +1617,35 @@
           <t>Arizona State University</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Derrick.Speaks@asu.edu</t>
+      <c r="E28" s="1" t="inlineStr">
+        <is>
+          <t>Lin.Li.10@asu.edu</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="b">
         <v>0</v>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>https://search.asu.edu/profile/dspeaks2</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Derrick%20Speaks%20Arizona%20State%20University</t>
+      <c r="H28" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/linli25</t>
+        </is>
+      </c>
+      <c r="I28" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Lin%20Li%20Arizona%20State%20University</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Werner Dahm</t>
+          <t>Liping Wang</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SUM/WTR Faculty Research</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1651,39 +1658,39 @@
           <t>Arizona State University</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Werner.Dahm@asu.edu</t>
+      <c r="E29" s="1" t="inlineStr">
+        <is>
+          <t>Liping.Wang@asu.edu</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>combustion, computational physics, fluid dynamics, heat transfer, propulsion, turbulence</t>
+          <t>heat transfer</t>
         </is>
       </c>
       <c r="G29" t="b">
         <v>1</v>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>https://search.asu.edu/profile/wdahm</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Werner%20Dahm%20Arizona%20State%20University</t>
+      <c r="H29" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/lwang78</t>
+        </is>
+      </c>
+      <c r="I29" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Liping%20Wang%20Arizona%20State%20University</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Leixin Ma</t>
+          <t>Marc Mignolet</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Professor</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1696,34 +1703,30 @@
           <t>Arizona State University</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Leixin.Ma@asu.edu</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>aerodynamics, fluid-structure interaction, physics-informed machine learning</t>
-        </is>
-      </c>
+      <c r="E30" s="1" t="inlineStr">
+        <is>
+          <t>marc.mignolet@asu.edu</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="b">
-        <v>1</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>https://search.asu.edu/profile/leixinma</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Leixin%20Ma%20Arizona%20State%20University</t>
+        <v>0</v>
+      </c>
+      <c r="H30" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/marc03</t>
+        </is>
+      </c>
+      <c r="I30" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Marc%20Mignolet%20Arizona%20State%20University</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Leila Ladani</t>
+          <t>Marcus Herrmann</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1741,35 +1744,39 @@
           <t>Arizona State University</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>ladani@asu.edu</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
+      <c r="E31" s="1" t="inlineStr">
+        <is>
+          <t>Marcus.Herrmann@asu.edu</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>fluid mechanics, multiphase flow, numerical simulation, turbulence</t>
+        </is>
+      </c>
       <c r="G31" t="b">
-        <v>0</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>https://search.asu.edu/profile/ljannesa</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Leila%20Ladani%20Arizona%20State%20University</t>
+        <v>1</v>
+      </c>
+      <c r="H31" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/mherrma1</t>
+        </is>
+      </c>
+      <c r="I31" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Marcus%20Herrmann%20Arizona%20State%20University</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Spring Berman</t>
+          <t>Matthew Peet</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1782,9 +1789,9 @@
           <t>Arizona State University</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Spring.Berman@asu.edu</t>
+      <c r="E32" s="1" t="inlineStr">
+        <is>
+          <t>mpeet@asu.edu</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1795,26 +1802,26 @@
       <c r="G32" t="b">
         <v>1</v>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>https://search.asu.edu/profile/smberma2</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Spring%20Berman%20Arizona%20State%20University</t>
+      <c r="H32" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/mpeet</t>
+        </is>
+      </c>
+      <c r="I32" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Matthew%20Peet%20Arizona%20State%20University</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Huan Wu</t>
+          <t>Minglei Qu</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1827,34 +1834,34 @@
           <t>Arizona State University</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>huanwu@asu.edu</t>
+      <c r="E33" s="1" t="inlineStr">
+        <is>
+          <t>minglei.qu@asu.edu</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>computational physics</t>
+          <t>instability</t>
         </is>
       </c>
       <c r="G33" t="b">
         <v>1</v>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>https://search.asu.edu/profile/huanwu</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Huan%20Wu%20Arizona%20State%20University</t>
+      <c r="H33" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/mingleiq</t>
+        </is>
+      </c>
+      <c r="I33" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Minglei%20Qu%20Arizona%20State%20University</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Matthew Peet</t>
+          <t>Mohamed Houssem Kasbaoui</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1872,39 +1879,39 @@
           <t>Arizona State University</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>mpeet@asu.edu</t>
+      <c r="E34" s="1" t="inlineStr">
+        <is>
+          <t>houssem.kasbaoui@asu.edu</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>optimization</t>
+          <t>cfd, computational fluid dynamics, dns, fluid dynamics, multiphase flow</t>
         </is>
       </c>
       <c r="G34" t="b">
         <v>1</v>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>https://search.asu.edu/profile/mpeet</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Matthew%20Peet%20Arizona%20State%20University</t>
+      <c r="H34" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/mkasbaou</t>
+        </is>
+      </c>
+      <c r="I34" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Mohamed%20Houssem%20Kasbaoui%20Arizona%20State%20University</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Wanxin Jin</t>
+          <t>Patrick Phelan</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Professor</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1917,23 +1924,23 @@
           <t>Arizona State University</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>wjin@asu.edu</t>
+      <c r="E35" s="1" t="inlineStr">
+        <is>
+          <t>phelan@asu.edu</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="b">
         <v>0</v>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>https://search.asu.edu/profile/wjin34</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Wanxin%20Jin%20Arizona%20State%20University</t>
+      <c r="H35" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/pphelan</t>
+        </is>
+      </c>
+      <c r="I35" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Patrick%20Phelan%20Arizona%20State%20University</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1965,7 @@
           <t>Arizona State University</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" s="1" t="inlineStr">
         <is>
           <t>pperalta@asu.edu</t>
         </is>
@@ -1967,12 +1974,12 @@
       <c r="G36" t="b">
         <v>0</v>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H36" s="1" t="inlineStr">
         <is>
           <t>https://search.asu.edu/profile/pperalta</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I36" s="1" t="inlineStr">
         <is>
           <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Pedro%20Peralta%20Arizona%20State%20University</t>
         </is>
@@ -1981,12 +1988,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ivy Chang</t>
+          <t>Qiong Nian</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Assistant Teaching Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1999,35 +2006,35 @@
           <t>Arizona State University</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Ivy.Chang@asu.edu</t>
+      <c r="E37" s="1" t="inlineStr">
+        <is>
+          <t>Qiong.Nian@asu.edu</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="b">
         <v>0</v>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>https://search.asu.edu/profile/iychang</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ivy%20Chang%20Arizona%20State%20University</t>
+      <c r="H37" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/qnian</t>
+        </is>
+      </c>
+      <c r="I37" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Qiong%20Nian%20Arizona%20State%20University</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cindy (Xiangjia) Li</t>
+          <t>Raghavendra Murthy</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Associate Teaching Professor</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2040,35 +2047,39 @@
           <t>Arizona State University</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>xiangjia.li@asu.edu</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
+      <c r="E38" s="1" t="inlineStr">
+        <is>
+          <t>rnmurthy@asu.edu</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>optimization, reduced-order modeling</t>
+        </is>
+      </c>
       <c r="G38" t="b">
-        <v>0</v>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>https://search.asu.edu/profile/xiangji5</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Cindy%20%28Xiangjia%29%20Li%20Arizona%20State%20University</t>
+        <v>1</v>
+      </c>
+      <c r="H38" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/rnmurthy</t>
+        </is>
+      </c>
+      <c r="I38" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Raghavendra%20Murthy%20Arizona%20State%20University</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Kangping Chen</t>
+          <t>Ricardo Cruz Lozano</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Assistant Teaching Professor</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2081,34 +2092,30 @@
           <t>Arizona State University</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>k.p.chen@asu.edu</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>computational fluid dynamics, drag reduction, fluid dynamics, fluid mechanics, multiphase flow</t>
-        </is>
-      </c>
+      <c r="E39" s="1" t="inlineStr">
+        <is>
+          <t>Ricardo.Cruz.Lozano@asu.edu</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="b">
-        <v>1</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>https://search.asu.edu/profile/asuchen</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Kangping%20Chen%20Arizona%20State%20University</t>
+        <v>0</v>
+      </c>
+      <c r="H39" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/rcruzloz</t>
+        </is>
+      </c>
+      <c r="I39" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ricardo%20Cruz%20Lozano%20Arizona%20State%20University</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Hamidreza Marvi</t>
+          <t>Robert Wang</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2126,35 +2133,39 @@
           <t>Arizona State University</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>hmarvi@asu.edu</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
+      <c r="E40" s="1" t="inlineStr">
+        <is>
+          <t>rywang@asu.edu</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>heat transfer</t>
+        </is>
+      </c>
       <c r="G40" t="b">
-        <v>0</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>https://search.asu.edu/profile/hmarvi</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Hamidreza%20Marvi%20Arizona%20State%20University</t>
+        <v>1</v>
+      </c>
+      <c r="H40" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/rywang</t>
+        </is>
+      </c>
+      <c r="I40" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Robert%20Wang%20Arizona%20State%20University</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Minglei Qu</t>
+          <t>Ronald Calhoun</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2167,39 +2178,39 @@
           <t>Arizona State University</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>minglei.qu@asu.edu</t>
+      <c r="E41" s="1" t="inlineStr">
+        <is>
+          <t>Ronald.Calhoun@asu.edu</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>instability</t>
+          <t>fluid dynamics</t>
         </is>
       </c>
       <c r="G41" t="b">
         <v>1</v>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>https://search.asu.edu/profile/mingleiq</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Minglei%20Qu%20Arizona%20State%20University</t>
+      <c r="H41" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/rcalhou</t>
+        </is>
+      </c>
+      <c r="I41" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ronald%20Calhoun%20Arizona%20State%20University</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Marcus Herrmann</t>
+          <t>Ryan Milcarek</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2212,39 +2223,39 @@
           <t>Arizona State University</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Marcus.Herrmann@asu.edu</t>
+      <c r="E42" s="1" t="inlineStr">
+        <is>
+          <t>Ryan.Milcarek@asu.edu</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>fluid mechanics, multiphase flow, numerical simulation, turbulence</t>
+          <t>combustion, transition</t>
         </is>
       </c>
       <c r="G42" t="b">
         <v>1</v>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>https://search.asu.edu/profile/mherrma1</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Marcus%20Herrmann%20Arizona%20State%20University</t>
+      <c r="H42" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/rjmilcar</t>
+        </is>
+      </c>
+      <c r="I42" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ryan%20Milcarek%20Arizona%20State%20University</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Ricardo Cruz Lozano</t>
+          <t>Spring Berman</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Assistant Teaching Professor</t>
+          <t>Professor</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2257,35 +2268,39 @@
           <t>Arizona State University</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Ricardo.Cruz.Lozano@asu.edu</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
+      <c r="E43" s="1" t="inlineStr">
+        <is>
+          <t>Spring.Berman@asu.edu</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>optimization</t>
+        </is>
+      </c>
       <c r="G43" t="b">
-        <v>0</v>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>https://search.asu.edu/profile/rcruzloz</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ricardo%20Cruz%20Lozano%20Arizona%20State%20University</t>
+        <v>1</v>
+      </c>
+      <c r="H43" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/smberma2</t>
+        </is>
+      </c>
+      <c r="I43" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Spring%20Berman%20Arizona%20State%20University</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Ryan Milcarek</t>
+          <t>Sridhar Seetharaman</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Professor</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2298,39 +2313,35 @@
           <t>Arizona State University</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Ryan.Milcarek@asu.edu</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>combustion, transition</t>
-        </is>
-      </c>
+      <c r="E44" s="1" t="inlineStr">
+        <is>
+          <t>seetharaman@asu.edu</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" t="b">
-        <v>1</v>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>https://search.asu.edu/profile/rjmilcar</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ryan%20Milcarek%20Arizona%20State%20University</t>
+        <v>0</v>
+      </c>
+      <c r="H44" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/sseeth11</t>
+        </is>
+      </c>
+      <c r="I44" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Sridhar%20Seetharaman%20Arizona%20State%20University</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Konrad Rykaczewski</t>
+          <t>Srinivas Chakravarthi Kosaraju</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Teaching Professor</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2343,30 +2354,30 @@
           <t>Arizona State University</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>konradr@asu.edu</t>
+      <c r="E45" s="1" t="inlineStr">
+        <is>
+          <t>Srinivas.Kosaraju@asu.edu</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="b">
         <v>0</v>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>https://search.asu.edu/profile/krykacze</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Konrad%20Rykaczewski%20Arizona%20State%20University</t>
+      <c r="H45" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/skosara2</t>
+        </is>
+      </c>
+      <c r="I45" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Srinivas%20Chakravarthi%20Kosaraju%20Arizona%20State%20University</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Kiran Ramesh</t>
+          <t>T.-W. Lee</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2384,39 +2395,39 @@
           <t>Arizona State University</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Kiran.Ramesh@asu.edu</t>
+      <c r="E46" s="1" t="inlineStr">
+        <is>
+          <t>ATTWL@asu.edu</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>aerodynamics, flow control, fluid dynamics, turbulence, vortex dynamics</t>
+          <t>aerospace propulsion, propulsion</t>
         </is>
       </c>
       <c r="G46" t="b">
         <v>1</v>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>https://search.asu.edu/profile/kramesh2</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Kiran%20Ramesh%20Arizona%20State%20University</t>
+      <c r="H46" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/attwl</t>
+        </is>
+      </c>
+      <c r="I46" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=T.-W.%20Lee%20Arizona%20State%20University</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Joshua Wilbur</t>
+          <t>Tianyu Yang</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Associate Teaching Professor</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2429,35 +2440,39 @@
           <t>Arizona State University</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Joshua.Wilbur@asu.edu</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
+      <c r="E47" s="1" t="inlineStr">
+        <is>
+          <t>Tianyu.Yang@asu.edu</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>heat transfer</t>
+        </is>
+      </c>
       <c r="G47" t="b">
-        <v>0</v>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>https://search.asu.edu/profile/jdwilbu1</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Joshua%20Wilbur%20Arizona%20State%20University</t>
+        <v>1</v>
+      </c>
+      <c r="H47" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/tyang123</t>
+        </is>
+      </c>
+      <c r="I47" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Tianyu%20Yang%20Arizona%20State%20University</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Houlong Zhuang</t>
+          <t>Wanxin Jin</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2470,39 +2485,35 @@
           <t>Arizona State University</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>zhuanghl@asu.edu</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>computational physics</t>
-        </is>
-      </c>
+      <c r="E48" s="1" t="inlineStr">
+        <is>
+          <t>wjin@asu.edu</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
       <c r="G48" t="b">
-        <v>1</v>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>https://search.asu.edu/profile/hzhuang7</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Houlong%20Zhuang%20Arizona%20State%20University</t>
+        <v>0</v>
+      </c>
+      <c r="H48" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/wjin34</t>
+        </is>
+      </c>
+      <c r="I48" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Wanxin%20Jin%20Arizona%20State%20University</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Tianyu Yang</t>
+          <t>Werner Dahm</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>SUM/WTR Faculty Research</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2515,39 +2526,39 @@
           <t>Arizona State University</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Tianyu.Yang@asu.edu</t>
+      <c r="E49" s="1" t="inlineStr">
+        <is>
+          <t>Werner.Dahm@asu.edu</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>heat transfer</t>
+          <t>combustion, computational physics, fluid dynamics, heat transfer, propulsion, turbulence</t>
         </is>
       </c>
       <c r="G49" t="b">
         <v>1</v>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>https://search.asu.edu/profile/tyang123</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Tianyu%20Yang%20Arizona%20State%20University</t>
+      <c r="H49" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/wdahm</t>
+        </is>
+      </c>
+      <c r="I49" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Werner%20Dahm%20Arizona%20State%20University</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Yulia Peet</t>
+          <t>Wonmo Kang</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2560,39 +2571,35 @@
           <t>Arizona State University</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>ypeet@asu.edu</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>fluid mechanics, high-performance computing, turbulence</t>
-        </is>
-      </c>
+      <c r="E50" s="1" t="inlineStr">
+        <is>
+          <t>Wonmo.Kang@asu.edu</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
       <c r="G50" t="b">
-        <v>1</v>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>https://search.asu.edu/profile/ypeet</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Yulia%20Peet%20Arizona%20State%20University</t>
+        <v>0</v>
+      </c>
+      <c r="H50" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/wkang16</t>
+        </is>
+      </c>
+      <c r="I50" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Wonmo%20Kang%20Arizona%20State%20University</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Marc Mignolet</t>
+          <t>Yi Ren</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2605,35 +2612,39 @@
           <t>Arizona State University</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>marc.mignolet@asu.edu</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr"/>
+      <c r="E51" s="1" t="inlineStr">
+        <is>
+          <t>yiren@asu.edu</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>optimization</t>
+        </is>
+      </c>
       <c r="G51" t="b">
-        <v>0</v>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>https://search.asu.edu/profile/marc03</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Marc%20Mignolet%20Arizona%20State%20University</t>
+        <v>1</v>
+      </c>
+      <c r="H51" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/yren32</t>
+        </is>
+      </c>
+      <c r="I51" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Yi%20Ren%20Arizona%20State%20University</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Robert Wang</t>
+          <t>Yongming Liu</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Professor</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2646,34 +2657,34 @@
           <t>Arizona State University</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>rywang@asu.edu</t>
+      <c r="E52" s="1" t="inlineStr">
+        <is>
+          <t>Yongming.Liu@asu.edu</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>heat transfer</t>
+          <t>uncertainty quantification</t>
         </is>
       </c>
       <c r="G52" t="b">
         <v>1</v>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>https://search.asu.edu/profile/rywang</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Robert%20Wang%20Arizona%20State%20University</t>
+      <c r="H52" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/yliu35</t>
+        </is>
+      </c>
+      <c r="I52" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Yongming%20Liu%20Arizona%20State%20University</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>James Middleton</t>
+          <t>Yulia Peet</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2691,72 +2702,1736 @@
           <t>Arizona State University</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>jimbo@asu.edu</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr"/>
+      <c r="E53" s="1" t="inlineStr">
+        <is>
+          <t>ypeet@asu.edu</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>fluid mechanics, high-performance computing, turbulence</t>
+        </is>
+      </c>
       <c r="G53" t="b">
-        <v>0</v>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>https://search.asu.edu/profile/jimbo</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=James%20Middleton%20Arizona%20State%20University</t>
+        <v>1</v>
+      </c>
+      <c r="H53" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/ypeet</t>
+        </is>
+      </c>
+      <c r="I53" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Yulia%20Peet%20Arizona%20State%20University</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>Zhe Xu</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Assistant Professor</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Aerospace &amp; Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Arizona State University</t>
+        </is>
+      </c>
+      <c r="E54" s="1" t="inlineStr">
+        <is>
+          <t>xzhe1@asu.edu</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="b">
+        <v>0</v>
+      </c>
+      <c r="H54" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/xzhe1</t>
+        </is>
+      </c>
+      <c r="I54" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Zhe%20Xu%20Arizona%20State%20University</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId159"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Job Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Matched Fields</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Is Field Match</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Profile URL</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Google Scholar URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Aditi Chattopadhyay</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Regents Professor</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Aerospace &amp; Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Arizona State University</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>aditi@asu.edu</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>inverse problems, multiscale modeling, optimization, transition</t>
+        </is>
+      </c>
+      <c r="G2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/chattopa</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Aditi%20Chattopadhyay%20Arizona%20State%20University</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Alberto Scotti</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Aerospace &amp; Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Arizona State University</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>Alberto.Scotti@asu.edu</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>applied mathematics, fluid mechanics, turbulent mixing</t>
+        </is>
+      </c>
+      <c r="G3" t="b">
+        <v>1</v>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/adscotti</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Alberto%20Scotti%20Arizona%20State%20University</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Beomjin Kwon</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Aerospace &amp; Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Arizona State University</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>kwon@asu.edu</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>data-driven modeling, heat transfer, transport phenomena</t>
+        </is>
+      </c>
+      <c r="G4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/bkwon2</t>
+        </is>
+      </c>
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Beomjin%20Kwon%20Arizona%20State%20University</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gokul Pathikonda</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Assistant Professor</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Aerospace &amp; Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Arizona State University</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>Gokul.Pathikonda@asu.edu</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>aerodynamics, reacting flows, turbulence, turbulent mixing</t>
+        </is>
+      </c>
+      <c r="G5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/gpathiko</t>
+        </is>
+      </c>
+      <c r="I5" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Gokul%20Pathikonda%20Arizona%20State%20University</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Houlong Zhuang</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Aerospace &amp; Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Arizona State University</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>zhuanghl@asu.edu</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>computational physics</t>
+        </is>
+      </c>
+      <c r="G6" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/hzhuang7</t>
+        </is>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Houlong%20Zhuang%20Arizona%20State%20University</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Huan Wu</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Faculty</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Aerospace &amp; Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Arizona State University</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>huanwu@asu.edu</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>computational physics</t>
+        </is>
+      </c>
+      <c r="G7" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/huanwu</t>
+        </is>
+      </c>
+      <c r="I7" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Huan%20Wu%20Arizona%20State%20University</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Huei-Ping Huang</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Aerospace &amp; Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Arizona State University</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>Huei-Ping.Huang@asu.edu</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>fluid dynamics, numerical simulation</t>
+        </is>
+      </c>
+      <c r="G8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/hhuang38</t>
+        </is>
+      </c>
+      <c r="I8" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Huei-Ping%20Huang%20Arizona%20State%20University</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Jagannathan Rajagopalan</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Aerospace &amp; Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Arizona State University</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>Jagannathan.Rajagopalan@asu.edu</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>optimization</t>
+        </is>
+      </c>
+      <c r="G9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/jrajago1</t>
+        </is>
+      </c>
+      <c r="I9" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Jagannathan%20Rajagopalan%20Arizona%20State%20University</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Jay Oswald</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Aerospace &amp; Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Arizona State University</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>joswald1@asu.edu</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>finite element</t>
+        </is>
+      </c>
+      <c r="G10" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/joswald1</t>
+        </is>
+      </c>
+      <c r="I10" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Jay%20Oswald%20Arizona%20State%20University</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Jeonglae Kim</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Assistant Professor</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Aerospace &amp; Mechanical Engineering</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Arizona State University</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Aerospace &amp; Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Arizona State University</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
         <is>
           <t>jeokim@asu.edu</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>aeroacoustics, flow control, optimization, turbulence, turbulent flows</t>
         </is>
       </c>
-      <c r="G54" t="b">
-        <v>1</v>
-      </c>
-      <c r="H54" t="inlineStr">
+      <c r="G11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" s="1" t="inlineStr">
         <is>
           <t>https://search.asu.edu/profile/jkim520</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="I11" s="1" t="inlineStr">
         <is>
           <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Jeonglae%20Kim%20Arizona%20State%20University</t>
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Kangping Chen</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Aerospace &amp; Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Arizona State University</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="inlineStr">
+        <is>
+          <t>k.p.chen@asu.edu</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>computational fluid dynamics, drag reduction, fluid dynamics, fluid mechanics, multiphase flow</t>
+        </is>
+      </c>
+      <c r="G12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/asuchen</t>
+        </is>
+      </c>
+      <c r="I12" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Kangping%20Chen%20Arizona%20State%20University</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Kiran Ramesh</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Aerospace &amp; Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Arizona State University</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t>Kiran.Ramesh@asu.edu</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>aerodynamics, flow control, fluid dynamics, turbulence, vortex dynamics</t>
+        </is>
+      </c>
+      <c r="G13" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/kramesh2</t>
+        </is>
+      </c>
+      <c r="I13" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Kiran%20Ramesh%20Arizona%20State%20University</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Kunal Garg</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Assistant Professor</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Aerospace &amp; Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Arizona State University</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="inlineStr">
+        <is>
+          <t>kgarg24@asu.edu</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>optimization</t>
+        </is>
+      </c>
+      <c r="G14" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/kgarg24</t>
+        </is>
+      </c>
+      <c r="I14" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Kunal%20Garg%20Arizona%20State%20University</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Leixin Ma</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Assistant Professor</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Aerospace &amp; Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Arizona State University</t>
+        </is>
+      </c>
+      <c r="E15" s="1" t="inlineStr">
+        <is>
+          <t>Leixin.Ma@asu.edu</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>aerodynamics, fluid-structure interaction, physics-informed machine learning</t>
+        </is>
+      </c>
+      <c r="G15" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/leixinma</t>
+        </is>
+      </c>
+      <c r="I15" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Leixin%20Ma%20Arizona%20State%20University</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Liping Wang</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Aerospace &amp; Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Arizona State University</t>
+        </is>
+      </c>
+      <c r="E16" s="1" t="inlineStr">
+        <is>
+          <t>Liping.Wang@asu.edu</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>heat transfer</t>
+        </is>
+      </c>
+      <c r="G16" t="b">
+        <v>1</v>
+      </c>
+      <c r="H16" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/lwang78</t>
+        </is>
+      </c>
+      <c r="I16" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Liping%20Wang%20Arizona%20State%20University</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Marcus Herrmann</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Aerospace &amp; Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Arizona State University</t>
+        </is>
+      </c>
+      <c r="E17" s="1" t="inlineStr">
+        <is>
+          <t>Marcus.Herrmann@asu.edu</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>fluid mechanics, multiphase flow, numerical simulation, turbulence</t>
+        </is>
+      </c>
+      <c r="G17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H17" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/mherrma1</t>
+        </is>
+      </c>
+      <c r="I17" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Marcus%20Herrmann%20Arizona%20State%20University</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Matthew Peet</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Aerospace &amp; Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Arizona State University</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="inlineStr">
+        <is>
+          <t>mpeet@asu.edu</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>optimization</t>
+        </is>
+      </c>
+      <c r="G18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/mpeet</t>
+        </is>
+      </c>
+      <c r="I18" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Matthew%20Peet%20Arizona%20State%20University</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Minglei Qu</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Assistant Professor</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Aerospace &amp; Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Arizona State University</t>
+        </is>
+      </c>
+      <c r="E19" s="1" t="inlineStr">
+        <is>
+          <t>minglei.qu@asu.edu</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>instability</t>
+        </is>
+      </c>
+      <c r="G19" t="b">
+        <v>1</v>
+      </c>
+      <c r="H19" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/mingleiq</t>
+        </is>
+      </c>
+      <c r="I19" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Minglei%20Qu%20Arizona%20State%20University</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Mohamed Houssem Kasbaoui</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Aerospace &amp; Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Arizona State University</t>
+        </is>
+      </c>
+      <c r="E20" s="1" t="inlineStr">
+        <is>
+          <t>houssem.kasbaoui@asu.edu</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>cfd, computational fluid dynamics, dns, fluid dynamics, multiphase flow</t>
+        </is>
+      </c>
+      <c r="G20" t="b">
+        <v>1</v>
+      </c>
+      <c r="H20" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/mkasbaou</t>
+        </is>
+      </c>
+      <c r="I20" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Mohamed%20Houssem%20Kasbaoui%20Arizona%20State%20University</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Raghavendra Murthy</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Associate Teaching Professor</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Aerospace &amp; Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Arizona State University</t>
+        </is>
+      </c>
+      <c r="E21" s="1" t="inlineStr">
+        <is>
+          <t>rnmurthy@asu.edu</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>optimization, reduced-order modeling</t>
+        </is>
+      </c>
+      <c r="G21" t="b">
+        <v>1</v>
+      </c>
+      <c r="H21" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/rnmurthy</t>
+        </is>
+      </c>
+      <c r="I21" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Raghavendra%20Murthy%20Arizona%20State%20University</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Robert Wang</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Aerospace &amp; Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Arizona State University</t>
+        </is>
+      </c>
+      <c r="E22" s="1" t="inlineStr">
+        <is>
+          <t>rywang@asu.edu</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>heat transfer</t>
+        </is>
+      </c>
+      <c r="G22" t="b">
+        <v>1</v>
+      </c>
+      <c r="H22" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/rywang</t>
+        </is>
+      </c>
+      <c r="I22" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Robert%20Wang%20Arizona%20State%20University</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Ronald Calhoun</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Aerospace &amp; Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Arizona State University</t>
+        </is>
+      </c>
+      <c r="E23" s="1" t="inlineStr">
+        <is>
+          <t>Ronald.Calhoun@asu.edu</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>fluid dynamics</t>
+        </is>
+      </c>
+      <c r="G23" t="b">
+        <v>1</v>
+      </c>
+      <c r="H23" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/rcalhou</t>
+        </is>
+      </c>
+      <c r="I23" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ronald%20Calhoun%20Arizona%20State%20University</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Ryan Milcarek</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Aerospace &amp; Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Arizona State University</t>
+        </is>
+      </c>
+      <c r="E24" s="1" t="inlineStr">
+        <is>
+          <t>Ryan.Milcarek@asu.edu</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>combustion, transition</t>
+        </is>
+      </c>
+      <c r="G24" t="b">
+        <v>1</v>
+      </c>
+      <c r="H24" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/rjmilcar</t>
+        </is>
+      </c>
+      <c r="I24" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ryan%20Milcarek%20Arizona%20State%20University</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Spring Berman</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Aerospace &amp; Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Arizona State University</t>
+        </is>
+      </c>
+      <c r="E25" s="1" t="inlineStr">
+        <is>
+          <t>Spring.Berman@asu.edu</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>optimization</t>
+        </is>
+      </c>
+      <c r="G25" t="b">
+        <v>1</v>
+      </c>
+      <c r="H25" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/smberma2</t>
+        </is>
+      </c>
+      <c r="I25" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Spring%20Berman%20Arizona%20State%20University</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>T.-W. Lee</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Aerospace &amp; Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Arizona State University</t>
+        </is>
+      </c>
+      <c r="E26" s="1" t="inlineStr">
+        <is>
+          <t>ATTWL@asu.edu</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>aerospace propulsion, propulsion</t>
+        </is>
+      </c>
+      <c r="G26" t="b">
+        <v>1</v>
+      </c>
+      <c r="H26" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/attwl</t>
+        </is>
+      </c>
+      <c r="I26" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=T.-W.%20Lee%20Arizona%20State%20University</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Tianyu Yang</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Assistant Professor</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Aerospace &amp; Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Arizona State University</t>
+        </is>
+      </c>
+      <c r="E27" s="1" t="inlineStr">
+        <is>
+          <t>Tianyu.Yang@asu.edu</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>heat transfer</t>
+        </is>
+      </c>
+      <c r="G27" t="b">
+        <v>1</v>
+      </c>
+      <c r="H27" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/tyang123</t>
+        </is>
+      </c>
+      <c r="I27" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Tianyu%20Yang%20Arizona%20State%20University</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Werner Dahm</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SUM/WTR Faculty Research</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Aerospace &amp; Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Arizona State University</t>
+        </is>
+      </c>
+      <c r="E28" s="1" t="inlineStr">
+        <is>
+          <t>Werner.Dahm@asu.edu</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>combustion, computational physics, fluid dynamics, heat transfer, propulsion, turbulence</t>
+        </is>
+      </c>
+      <c r="G28" t="b">
+        <v>1</v>
+      </c>
+      <c r="H28" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/wdahm</t>
+        </is>
+      </c>
+      <c r="I28" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Werner%20Dahm%20Arizona%20State%20University</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Yi Ren</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Aerospace &amp; Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Arizona State University</t>
+        </is>
+      </c>
+      <c r="E29" s="1" t="inlineStr">
+        <is>
+          <t>yiren@asu.edu</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>optimization</t>
+        </is>
+      </c>
+      <c r="G29" t="b">
+        <v>1</v>
+      </c>
+      <c r="H29" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/yren32</t>
+        </is>
+      </c>
+      <c r="I29" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Yi%20Ren%20Arizona%20State%20University</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Yongming Liu</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Aerospace &amp; Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Arizona State University</t>
+        </is>
+      </c>
+      <c r="E30" s="1" t="inlineStr">
+        <is>
+          <t>Yongming.Liu@asu.edu</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>uncertainty quantification</t>
+        </is>
+      </c>
+      <c r="G30" t="b">
+        <v>1</v>
+      </c>
+      <c r="H30" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/yliu35</t>
+        </is>
+      </c>
+      <c r="I30" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Yongming%20Liu%20Arizona%20State%20University</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Yulia Peet</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Aerospace &amp; Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Arizona State University</t>
+        </is>
+      </c>
+      <c r="E31" s="1" t="inlineStr">
+        <is>
+          <t>ypeet@asu.edu</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>fluid mechanics, high-performance computing, turbulence</t>
+        </is>
+      </c>
+      <c r="G31" t="b">
+        <v>1</v>
+      </c>
+      <c r="H31" s="1" t="inlineStr">
+        <is>
+          <t>https://search.asu.edu/profile/ypeet</t>
+        </is>
+      </c>
+      <c r="I31" s="1" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Yulia%20Peet%20Arizona%20State%20University</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId90"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/universities_wise/arizona_state_university/asu_aerospace_mechanical_faculty.xlsx
+++ b/universities_wise/arizona_state_university/asu_aerospace_mechanical_faculty.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Field Matched Faculty (A-Z)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Active Faculty (A-Z)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Field Matched (Max Keywords)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Faculty (Max Keywords)" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -455,18 +455,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
-    <col width="65" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="44" customWidth="1" min="8" max="8"/>
-    <col width="29" customWidth="1" min="9" max="9"/>
+    <col width="49" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="65" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="49" customWidth="1" min="10" max="10"/>
+    <col width="32" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -497,20 +499,30 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Matched Count</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Matched Fields</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Is Field Match</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Scholar ID</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Profile URL</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Google Scholar URL</t>
         </is>
@@ -519,12 +531,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Aditi Chattopadhyay</t>
+          <t>Werner Dahm</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Regents Professor</t>
+          <t>SUM/WTR Faculty Research</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -538,35 +550,39 @@
         </is>
       </c>
       <c r="E2" s="3">
-        <f>HYPERLINK("mailto:aditi@asu.edu", "aditi@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>inverse problems, multiscale modeling, optimization, transition</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H2" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/chattopa", "https://search.asu.edu/profile/chattopa")</f>
-        <v/>
-      </c>
-      <c r="I2" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Aditi%20Chattopadhyay%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:Werner.Dahm@asu.edu", "Werner.Dahm@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>combustion, computational physics, fluid dynamics, heat transfer, propulsion, turbulence</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/wdahm", "https://search.asu.edu/profile/wdahm")</f>
+        <v/>
+      </c>
+      <c r="K2" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Werner%20Dahm%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Alberto Scotti</t>
+          <t>Jeonglae Kim</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Professor</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -580,30 +596,34 @@
         </is>
       </c>
       <c r="E3" s="3">
-        <f>HYPERLINK("mailto:Alberto.Scotti@asu.edu", "Alberto.Scotti@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>applied mathematics, fluid mechanics, turbulent mixing</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H3" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/adscotti", "https://search.asu.edu/profile/adscotti")</f>
-        <v/>
-      </c>
-      <c r="I3" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Alberto%20Scotti%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:jeokim@asu.edu", "jeokim@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>aeroacoustics, flow control, optimization, turbulence, turbulent flows</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/jkim520", "https://search.asu.edu/profile/jkim520")</f>
+        <v/>
+      </c>
+      <c r="K3" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Jeonglae%20Kim%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Beomjin Kwon</t>
+          <t>Kangping Chen</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -622,35 +642,43 @@
         </is>
       </c>
       <c r="E4" s="3">
-        <f>HYPERLINK("mailto:kwon@asu.edu", "kwon@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>data-driven modeling, heat transfer, transport phenomena</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H4" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/bkwon2", "https://search.asu.edu/profile/bkwon2")</f>
-        <v/>
-      </c>
-      <c r="I4" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Beomjin%20Kwon%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:k.p.chen@asu.edu", "k.p.chen@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>computational fluid dynamics, drag reduction, fluid dynamics, fluid mechanics, multiphase flow</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>xT-lX9sAAAAJ</t>
+        </is>
+      </c>
+      <c r="J4" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/asuchen", "https://search.asu.edu/profile/asuchen")</f>
+        <v/>
+      </c>
+      <c r="K4" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=xT-lX9sAAAAJ", "Scholar (xT-lX9sAAAAJ)")</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Gokul Pathikonda</t>
+          <t>Kiran Ramesh</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -664,30 +692,38 @@
         </is>
       </c>
       <c r="E5" s="3">
-        <f>HYPERLINK("mailto:Gokul.Pathikonda@asu.edu", "Gokul.Pathikonda@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>aerodynamics, reacting flows, turbulence, turbulent mixing</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H5" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/gpathiko", "https://search.asu.edu/profile/gpathiko")</f>
-        <v/>
-      </c>
-      <c r="I5" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Gokul%20Pathikonda%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:Kiran.Ramesh@asu.edu", "Kiran.Ramesh@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>aerodynamics, flow control, fluid dynamics, turbulence, vortex dynamics</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>DKc-AgcAAAAJ</t>
+        </is>
+      </c>
+      <c r="J5" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/kramesh2", "https://search.asu.edu/profile/kramesh2")</f>
+        <v/>
+      </c>
+      <c r="K5" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=DKc-AgcAAAAJ", "Scholar (DKc-AgcAAAAJ)")</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Houlong Zhuang</t>
+          <t>Mohamed Houssem Kasbaoui</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -706,35 +742,39 @@
         </is>
       </c>
       <c r="E6" s="3">
-        <f>HYPERLINK("mailto:zhuanghl@asu.edu", "zhuanghl@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>computational physics</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H6" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/hzhuang7", "https://search.asu.edu/profile/hzhuang7")</f>
-        <v/>
-      </c>
-      <c r="I6" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Houlong%20Zhuang%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:houssem.kasbaoui@asu.edu", "houssem.kasbaoui@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>cfd, computational fluid dynamics, dns, fluid dynamics, multiphase flow</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/mkasbaou", "https://search.asu.edu/profile/mkasbaou")</f>
+        <v/>
+      </c>
+      <c r="K6" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Mohamed%20Houssem%20Kasbaoui%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Huan Wu</t>
+          <t>Aditi Chattopadhyay</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Regents Professor</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -748,35 +788,43 @@
         </is>
       </c>
       <c r="E7" s="3">
-        <f>HYPERLINK("mailto:huanwu@asu.edu", "huanwu@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>computational physics</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H7" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/huanwu", "https://search.asu.edu/profile/huanwu")</f>
-        <v/>
-      </c>
-      <c r="I7" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Huan%20Wu%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:aditi@asu.edu", "aditi@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>inverse problems, multiscale modeling, optimization, transition</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>w3fU9E0AAAAJ</t>
+        </is>
+      </c>
+      <c r="J7" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/chattopa", "https://search.asu.edu/profile/chattopa")</f>
+        <v/>
+      </c>
+      <c r="K7" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=w3fU9E0AAAAJ", "Scholar (w3fU9E0AAAAJ)")</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Huei-Ping Huang</t>
+          <t>Gokul Pathikonda</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -790,35 +838,39 @@
         </is>
       </c>
       <c r="E8" s="3">
-        <f>HYPERLINK("mailto:Huei-Ping.Huang@asu.edu", "Huei-Ping.Huang@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>fluid dynamics, numerical simulation</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H8" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/hhuang38", "https://search.asu.edu/profile/hhuang38")</f>
-        <v/>
-      </c>
-      <c r="I8" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Huei-Ping%20Huang%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:Gokul.Pathikonda@asu.edu", "Gokul.Pathikonda@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>aerodynamics, reacting flows, turbulence, turbulent mixing</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/gpathiko", "https://search.asu.edu/profile/gpathiko")</f>
+        <v/>
+      </c>
+      <c r="K8" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Gokul%20Pathikonda%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Jagannathan Rajagopalan</t>
+          <t>Marcus Herrmann</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Professor</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -832,35 +884,43 @@
         </is>
       </c>
       <c r="E9" s="3">
-        <f>HYPERLINK("mailto:Jagannathan.Rajagopalan@asu.edu", "Jagannathan.Rajagopalan@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>optimization</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H9" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/jrajago1", "https://search.asu.edu/profile/jrajago1")</f>
-        <v/>
-      </c>
-      <c r="I9" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Jagannathan%20Rajagopalan%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:Marcus.Herrmann@asu.edu", "Marcus.Herrmann@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>fluid mechanics, multiphase flow, numerical simulation, turbulence</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>yv6aCW8AAAAJ</t>
+        </is>
+      </c>
+      <c r="J9" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/mherrma1", "https://search.asu.edu/profile/mherrma1")</f>
+        <v/>
+      </c>
+      <c r="K9" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=yv6aCW8AAAAJ", "Scholar (yv6aCW8AAAAJ)")</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Jay Oswald</t>
+          <t>Alberto Scotti</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Professor</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -874,35 +934,43 @@
         </is>
       </c>
       <c r="E10" s="3">
-        <f>HYPERLINK("mailto:joswald1@asu.edu", "joswald1@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>finite element</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H10" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/joswald1", "https://search.asu.edu/profile/joswald1")</f>
-        <v/>
-      </c>
-      <c r="I10" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Jay%20Oswald%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:Alberto.Scotti@asu.edu", "Alberto.Scotti@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>applied mathematics, fluid mechanics, turbulent mixing</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>HRx2lJQAAAAJ</t>
+        </is>
+      </c>
+      <c r="J10" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/adscotti", "https://search.asu.edu/profile/adscotti")</f>
+        <v/>
+      </c>
+      <c r="K10" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=HRx2lJQAAAAJ", "Scholar (HRx2lJQAAAAJ)")</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Jeonglae Kim</t>
+          <t>Beomjin Kwon</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -916,35 +984,43 @@
         </is>
       </c>
       <c r="E11" s="3">
-        <f>HYPERLINK("mailto:jeokim@asu.edu", "jeokim@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>aeroacoustics, flow control, optimization, turbulence, turbulent flows</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H11" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/jkim520", "https://search.asu.edu/profile/jkim520")</f>
-        <v/>
-      </c>
-      <c r="I11" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Jeonglae%20Kim%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:kwon@asu.edu", "kwon@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>data-driven modeling, heat transfer, transport phenomena</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>fs2d97sAAAAJ</t>
+        </is>
+      </c>
+      <c r="J11" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/bkwon2", "https://search.asu.edu/profile/bkwon2")</f>
+        <v/>
+      </c>
+      <c r="K11" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=fs2d97sAAAAJ", "Scholar (fs2d97sAAAAJ)")</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Kangping Chen</t>
+          <t>Leixin Ma</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -958,35 +1034,43 @@
         </is>
       </c>
       <c r="E12" s="3">
-        <f>HYPERLINK("mailto:k.p.chen@asu.edu", "k.p.chen@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>computational fluid dynamics, drag reduction, fluid dynamics, fluid mechanics, multiphase flow</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H12" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/asuchen", "https://search.asu.edu/profile/asuchen")</f>
-        <v/>
-      </c>
-      <c r="I12" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Kangping%20Chen%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:Leixin.Ma@asu.edu", "Leixin.Ma@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>aerodynamics, fluid-structure interaction, physics-informed machine learning</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2xQTOc0AAAAJ</t>
+        </is>
+      </c>
+      <c r="J12" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/leixinma", "https://search.asu.edu/profile/leixinma")</f>
+        <v/>
+      </c>
+      <c r="K12" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=2xQTOc0AAAAJ", "Scholar (2xQTOc0AAAAJ)")</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Kiran Ramesh</t>
+          <t>Yulia Peet</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Professor</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1000,35 +1084,43 @@
         </is>
       </c>
       <c r="E13" s="3">
-        <f>HYPERLINK("mailto:Kiran.Ramesh@asu.edu", "Kiran.Ramesh@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>aerodynamics, flow control, fluid dynamics, turbulence, vortex dynamics</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H13" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/kramesh2", "https://search.asu.edu/profile/kramesh2")</f>
-        <v/>
-      </c>
-      <c r="I13" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Kiran%20Ramesh%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:ypeet@asu.edu", "ypeet@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>fluid mechanics, high-performance computing, turbulence</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>_6o8MrUAAAAJ</t>
+        </is>
+      </c>
+      <c r="J13" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/ypeet", "https://search.asu.edu/profile/ypeet")</f>
+        <v/>
+      </c>
+      <c r="K13" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=_6o8MrUAAAAJ", "Scholar (_6o8MrUAAAAJ)")</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Kunal Garg</t>
+          <t>Huei-Ping Huang</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1042,35 +1134,39 @@
         </is>
       </c>
       <c r="E14" s="3">
-        <f>HYPERLINK("mailto:kgarg24@asu.edu", "kgarg24@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>optimization</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H14" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/kgarg24", "https://search.asu.edu/profile/kgarg24")</f>
-        <v/>
-      </c>
-      <c r="I14" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Kunal%20Garg%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:Huei-Ping.Huang@asu.edu", "Huei-Ping.Huang@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>fluid dynamics, numerical simulation</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/hhuang38", "https://search.asu.edu/profile/hhuang38")</f>
+        <v/>
+      </c>
+      <c r="K14" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Huei-Ping%20Huang%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Leixin Ma</t>
+          <t>Raghavendra Murthy</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Associate Teaching Professor</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1084,30 +1180,34 @@
         </is>
       </c>
       <c r="E15" s="3">
-        <f>HYPERLINK("mailto:Leixin.Ma@asu.edu", "Leixin.Ma@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>aerodynamics, fluid-structure interaction, physics-informed machine learning</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H15" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/leixinma", "https://search.asu.edu/profile/leixinma")</f>
-        <v/>
-      </c>
-      <c r="I15" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Leixin%20Ma%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:rnmurthy@asu.edu", "rnmurthy@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>optimization, reduced-order modeling</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/rnmurthy", "https://search.asu.edu/profile/rnmurthy")</f>
+        <v/>
+      </c>
+      <c r="K15" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Raghavendra%20Murthy%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Liping Wang</t>
+          <t>Ryan Milcarek</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1126,35 +1226,43 @@
         </is>
       </c>
       <c r="E16" s="3">
-        <f>HYPERLINK("mailto:Liping.Wang@asu.edu", "Liping.Wang@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>heat transfer</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H16" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/lwang78", "https://search.asu.edu/profile/lwang78")</f>
-        <v/>
-      </c>
-      <c r="I16" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Liping%20Wang%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:Ryan.Milcarek@asu.edu", "Ryan.Milcarek@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>combustion, transition</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>m-Pb6g2pm2UC</t>
+        </is>
+      </c>
+      <c r="J16" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/rjmilcar", "https://search.asu.edu/profile/rjmilcar")</f>
+        <v/>
+      </c>
+      <c r="K16" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=m-Pb6g2pm2UC", "Scholar (m-Pb6g2pm2UC)")</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Marcus Herrmann</t>
+          <t>T.-W. Lee</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1168,30 +1276,34 @@
         </is>
       </c>
       <c r="E17" s="3">
-        <f>HYPERLINK("mailto:Marcus.Herrmann@asu.edu", "Marcus.Herrmann@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>fluid mechanics, multiphase flow, numerical simulation, turbulence</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H17" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/mherrma1", "https://search.asu.edu/profile/mherrma1")</f>
-        <v/>
-      </c>
-      <c r="I17" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Marcus%20Herrmann%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:ATTWL@asu.edu", "ATTWL@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>aerospace propulsion, propulsion</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/attwl", "https://search.asu.edu/profile/attwl")</f>
+        <v/>
+      </c>
+      <c r="K17" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=T.-W.%20Lee%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Matthew Peet</t>
+          <t>Houlong Zhuang</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1210,35 +1322,43 @@
         </is>
       </c>
       <c r="E18" s="3">
-        <f>HYPERLINK("mailto:mpeet@asu.edu", "mpeet@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>optimization</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H18" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/mpeet", "https://search.asu.edu/profile/mpeet")</f>
-        <v/>
-      </c>
-      <c r="I18" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Matthew%20Peet%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:zhuanghl@asu.edu", "zhuanghl@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>computational physics</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>4yYKCpUAAAAJ</t>
+        </is>
+      </c>
+      <c r="J18" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/hzhuang7", "https://search.asu.edu/profile/hzhuang7")</f>
+        <v/>
+      </c>
+      <c r="K18" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=4yYKCpUAAAAJ", "Scholar (4yYKCpUAAAAJ)")</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Minglei Qu</t>
+          <t>Huan Wu</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1252,30 +1372,38 @@
         </is>
       </c>
       <c r="E19" s="3">
-        <f>HYPERLINK("mailto:minglei.qu@asu.edu", "minglei.qu@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>instability</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H19" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/mingleiq", "https://search.asu.edu/profile/mingleiq")</f>
-        <v/>
-      </c>
-      <c r="I19" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Minglei%20Qu%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:huanwu@asu.edu", "huanwu@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>computational physics</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>8CS4X9IAAAAJ</t>
+        </is>
+      </c>
+      <c r="J19" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/huanwu", "https://search.asu.edu/profile/huanwu")</f>
+        <v/>
+      </c>
+      <c r="K19" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=8CS4X9IAAAAJ", "Scholar (8CS4X9IAAAAJ)")</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Mohamed Houssem Kasbaoui</t>
+          <t>Jagannathan Rajagopalan</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1294,35 +1422,43 @@
         </is>
       </c>
       <c r="E20" s="3">
-        <f>HYPERLINK("mailto:houssem.kasbaoui@asu.edu", "houssem.kasbaoui@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>cfd, computational fluid dynamics, dns, fluid dynamics, multiphase flow</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H20" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/mkasbaou", "https://search.asu.edu/profile/mkasbaou")</f>
-        <v/>
-      </c>
-      <c r="I20" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Mohamed%20Houssem%20Kasbaoui%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:Jagannathan.Rajagopalan@asu.edu", "Jagannathan.Rajagopalan@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>optimization</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>ClqRIhIAAAAJ</t>
+        </is>
+      </c>
+      <c r="J20" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/jrajago1", "https://search.asu.edu/profile/jrajago1")</f>
+        <v/>
+      </c>
+      <c r="K20" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=ClqRIhIAAAAJ", "Scholar (ClqRIhIAAAAJ)")</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Raghavendra Murthy</t>
+          <t>Jay Oswald</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Associate Teaching Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1336,35 +1472,39 @@
         </is>
       </c>
       <c r="E21" s="3">
-        <f>HYPERLINK("mailto:rnmurthy@asu.edu", "rnmurthy@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>optimization, reduced-order modeling</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H21" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/rnmurthy", "https://search.asu.edu/profile/rnmurthy")</f>
-        <v/>
-      </c>
-      <c r="I21" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Raghavendra%20Murthy%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:joswald1@asu.edu", "joswald1@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>finite element</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/joswald1", "https://search.asu.edu/profile/joswald1")</f>
+        <v/>
+      </c>
+      <c r="K21" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Jay%20Oswald%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Robert Wang</t>
+          <t>Kunal Garg</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1378,30 +1518,38 @@
         </is>
       </c>
       <c r="E22" s="3">
-        <f>HYPERLINK("mailto:rywang@asu.edu", "rywang@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>heat transfer</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H22" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/rywang", "https://search.asu.edu/profile/rywang")</f>
-        <v/>
-      </c>
-      <c r="I22" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Robert%20Wang%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:kgarg24@asu.edu", "kgarg24@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>optimization</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>vs3pl-8AAAAJ</t>
+        </is>
+      </c>
+      <c r="J22" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/kgarg24", "https://search.asu.edu/profile/kgarg24")</f>
+        <v/>
+      </c>
+      <c r="K22" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=vs3pl-8AAAAJ", "Scholar (vs3pl-8AAAAJ)")</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Ronald Calhoun</t>
+          <t>Liping Wang</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1420,30 +1568,34 @@
         </is>
       </c>
       <c r="E23" s="3">
-        <f>HYPERLINK("mailto:Ronald.Calhoun@asu.edu", "Ronald.Calhoun@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>fluid dynamics</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H23" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/rcalhou", "https://search.asu.edu/profile/rcalhou")</f>
-        <v/>
-      </c>
-      <c r="I23" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ronald%20Calhoun%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:Liping.Wang@asu.edu", "Liping.Wang@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>heat transfer</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/lwang78", "https://search.asu.edu/profile/lwang78")</f>
+        <v/>
+      </c>
+      <c r="K23" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Liping%20Wang%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Ryan Milcarek</t>
+          <t>Matthew Peet</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1462,35 +1614,39 @@
         </is>
       </c>
       <c r="E24" s="3">
-        <f>HYPERLINK("mailto:Ryan.Milcarek@asu.edu", "Ryan.Milcarek@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>combustion, transition</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H24" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/rjmilcar", "https://search.asu.edu/profile/rjmilcar")</f>
-        <v/>
-      </c>
-      <c r="I24" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ryan%20Milcarek%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:mpeet@asu.edu", "mpeet@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>optimization</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/mpeet", "https://search.asu.edu/profile/mpeet")</f>
+        <v/>
+      </c>
+      <c r="K24" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Matthew%20Peet%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Spring Berman</t>
+          <t>Minglei Qu</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Professor</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1504,30 +1660,38 @@
         </is>
       </c>
       <c r="E25" s="3">
-        <f>HYPERLINK("mailto:Spring.Berman@asu.edu", "Spring.Berman@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>optimization</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H25" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/smberma2", "https://search.asu.edu/profile/smberma2")</f>
-        <v/>
-      </c>
-      <c r="I25" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Spring%20Berman%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:minglei.qu@asu.edu", "minglei.qu@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>instability</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>9LWNC50AAAAJ</t>
+        </is>
+      </c>
+      <c r="J25" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/mingleiq", "https://search.asu.edu/profile/mingleiq")</f>
+        <v/>
+      </c>
+      <c r="K25" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=9LWNC50AAAAJ", "Scholar (9LWNC50AAAAJ)")</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>T.-W. Lee</t>
+          <t>Robert Wang</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1546,35 +1710,43 @@
         </is>
       </c>
       <c r="E26" s="3">
-        <f>HYPERLINK("mailto:ATTWL@asu.edu", "ATTWL@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>aerospace propulsion, propulsion</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H26" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/attwl", "https://search.asu.edu/profile/attwl")</f>
-        <v/>
-      </c>
-      <c r="I26" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=T.-W.%20Lee%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:rywang@asu.edu", "rywang@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>heat transfer</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>LaUdx9gAAAAJ</t>
+        </is>
+      </c>
+      <c r="J26" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/rywang", "https://search.asu.edu/profile/rywang")</f>
+        <v/>
+      </c>
+      <c r="K26" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=LaUdx9gAAAAJ", "Scholar (LaUdx9gAAAAJ)")</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Tianyu Yang</t>
+          <t>Ronald Calhoun</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1588,35 +1760,39 @@
         </is>
       </c>
       <c r="E27" s="3">
-        <f>HYPERLINK("mailto:Tianyu.Yang@asu.edu", "Tianyu.Yang@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>heat transfer</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H27" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/tyang123", "https://search.asu.edu/profile/tyang123")</f>
-        <v/>
-      </c>
-      <c r="I27" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Tianyu%20Yang%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:Ronald.Calhoun@asu.edu", "Ronald.Calhoun@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>fluid dynamics</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/rcalhou", "https://search.asu.edu/profile/rcalhou")</f>
+        <v/>
+      </c>
+      <c r="K27" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ronald%20Calhoun%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Werner Dahm</t>
+          <t>Spring Berman</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>SUM/WTR Faculty Research</t>
+          <t>Professor</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1630,35 +1806,43 @@
         </is>
       </c>
       <c r="E28" s="3">
-        <f>HYPERLINK("mailto:Werner.Dahm@asu.edu", "Werner.Dahm@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>combustion, computational physics, fluid dynamics, heat transfer, propulsion, turbulence</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H28" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/wdahm", "https://search.asu.edu/profile/wdahm")</f>
-        <v/>
-      </c>
-      <c r="I28" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Werner%20Dahm%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:Spring.Berman@asu.edu", "Spring.Berman@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>optimization</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>KKup0OgAAAAJ</t>
+        </is>
+      </c>
+      <c r="J28" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/smberma2", "https://search.asu.edu/profile/smberma2")</f>
+        <v/>
+      </c>
+      <c r="K28" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=KKup0OgAAAAJ", "Scholar (KKup0OgAAAAJ)")</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Yi Ren</t>
+          <t>Tianyu Yang</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1672,35 +1856,43 @@
         </is>
       </c>
       <c r="E29" s="3">
-        <f>HYPERLINK("mailto:yiren@asu.edu", "yiren@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>optimization</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H29" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/yren32", "https://search.asu.edu/profile/yren32")</f>
-        <v/>
-      </c>
-      <c r="I29" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Yi%20Ren%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:Tianyu.Yang@asu.edu", "Tianyu.Yang@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>heat transfer</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>OmBV67MAAAAJ</t>
+        </is>
+      </c>
+      <c r="J29" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/tyang123", "https://search.asu.edu/profile/tyang123")</f>
+        <v/>
+      </c>
+      <c r="K29" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=OmBV67MAAAAJ", "Scholar (OmBV67MAAAAJ)")</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Yongming Liu</t>
+          <t>Yi Ren</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1714,30 +1906,34 @@
         </is>
       </c>
       <c r="E30" s="3">
-        <f>HYPERLINK("mailto:Yongming.Liu@asu.edu", "Yongming.Liu@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>uncertainty quantification</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H30" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/yliu35", "https://search.asu.edu/profile/yliu35")</f>
-        <v/>
-      </c>
-      <c r="I30" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Yongming%20Liu%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:yiren@asu.edu", "yiren@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>optimization</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/yren32", "https://search.asu.edu/profile/yren32")</f>
+        <v/>
+      </c>
+      <c r="K30" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Yi%20Ren%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Yulia Peet</t>
+          <t>Yongming Liu</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1756,118 +1952,122 @@
         </is>
       </c>
       <c r="E31" s="3">
-        <f>HYPERLINK("mailto:ypeet@asu.edu", "ypeet@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>fluid mechanics, high-performance computing, turbulence</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H31" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/ypeet", "https://search.asu.edu/profile/ypeet")</f>
-        <v/>
-      </c>
-      <c r="I31" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Yulia%20Peet%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:Yongming.Liu@asu.edu", "Yongming.Liu@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>uncertainty quantification</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/yliu35", "https://search.asu.edu/profile/yliu35")</f>
+        <v/>
+      </c>
+      <c r="K31" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Yongming%20Liu%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId63"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId69"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId75"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId81"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId87"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId90"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1879,18 +2079,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:K54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
-    <col width="65" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="44" customWidth="1" min="8" max="8"/>
-    <col width="29" customWidth="1" min="9" max="9"/>
+    <col width="49" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="65" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="49" customWidth="1" min="10" max="10"/>
+    <col width="32" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1921,20 +2123,30 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Matched Count</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Matched Fields</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Is Field Match</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Scholar ID</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Profile URL</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Google Scholar URL</t>
         </is>
@@ -1943,12 +2155,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Aditi Chattopadhyay</t>
+          <t>Werner Dahm</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Regents Professor</t>
+          <t>SUM/WTR Faculty Research</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -1962,35 +2174,39 @@
         </is>
       </c>
       <c r="E2" s="3">
-        <f>HYPERLINK("mailto:aditi@asu.edu", "aditi@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>inverse problems, multiscale modeling, optimization, transition</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H2" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/chattopa", "https://search.asu.edu/profile/chattopa")</f>
-        <v/>
-      </c>
-      <c r="I2" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Aditi%20Chattopadhyay%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:Werner.Dahm@asu.edu", "Werner.Dahm@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>combustion, computational physics, fluid dynamics, heat transfer, propulsion, turbulence</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/wdahm", "https://search.asu.edu/profile/wdahm")</f>
+        <v/>
+      </c>
+      <c r="K2" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Werner%20Dahm%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Aikaterini Stefanaki</t>
+          <t>Jeonglae Kim</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Associate Teaching Professor</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -2004,31 +2220,39 @@
         </is>
       </c>
       <c r="E3" s="3">
-        <f>HYPERLINK("mailto:astefan9@asu.edu", "astefan9@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H3" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/astefan9", "https://search.asu.edu/profile/astefan9")</f>
-        <v/>
-      </c>
-      <c r="I3" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Aikaterini%20Stefanaki%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:jeokim@asu.edu", "jeokim@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>aeroacoustics, flow control, optimization, turbulence, turbulent flows</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/jkim520", "https://search.asu.edu/profile/jkim520")</f>
+        <v/>
+      </c>
+      <c r="K3" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Jeonglae%20Kim%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Alberto Scotti</t>
+          <t>Kangping Chen</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -2042,30 +2266,38 @@
         </is>
       </c>
       <c r="E4" s="3">
-        <f>HYPERLINK("mailto:Alberto.Scotti@asu.edu", "Alberto.Scotti@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>applied mathematics, fluid mechanics, turbulent mixing</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H4" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/adscotti", "https://search.asu.edu/profile/adscotti")</f>
-        <v/>
-      </c>
-      <c r="I4" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Alberto%20Scotti%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:k.p.chen@asu.edu", "k.p.chen@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>computational fluid dynamics, drag reduction, fluid dynamics, fluid mechanics, multiphase flow</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>xT-lX9sAAAAJ</t>
+        </is>
+      </c>
+      <c r="J4" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/asuchen", "https://search.asu.edu/profile/asuchen")</f>
+        <v/>
+      </c>
+      <c r="K4" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=xT-lX9sAAAAJ", "Scholar (xT-lX9sAAAAJ)")</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Beomjin Kwon</t>
+          <t>Kiran Ramesh</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -2084,30 +2316,38 @@
         </is>
       </c>
       <c r="E5" s="3">
-        <f>HYPERLINK("mailto:kwon@asu.edu", "kwon@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>data-driven modeling, heat transfer, transport phenomena</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H5" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/bkwon2", "https://search.asu.edu/profile/bkwon2")</f>
-        <v/>
-      </c>
-      <c r="I5" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Beomjin%20Kwon%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:Kiran.Ramesh@asu.edu", "Kiran.Ramesh@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>aerodynamics, flow control, fluid dynamics, turbulence, vortex dynamics</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>DKc-AgcAAAAJ</t>
+        </is>
+      </c>
+      <c r="J5" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/kramesh2", "https://search.asu.edu/profile/kramesh2")</f>
+        <v/>
+      </c>
+      <c r="K5" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=DKc-AgcAAAAJ", "Scholar (DKc-AgcAAAAJ)")</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Cindy (Xiangjia) Li</t>
+          <t>Mohamed Houssem Kasbaoui</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -2126,31 +2366,39 @@
         </is>
       </c>
       <c r="E6" s="3">
-        <f>HYPERLINK("mailto:xiangjia.li@asu.edu", "xiangjia.li@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H6" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/xiangji5", "https://search.asu.edu/profile/xiangji5")</f>
-        <v/>
-      </c>
-      <c r="I6" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Cindy%20%28Xiangjia%29%20Li%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:houssem.kasbaoui@asu.edu", "houssem.kasbaoui@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>cfd, computational fluid dynamics, dns, fluid dynamics, multiphase flow</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/mkasbaou", "https://search.asu.edu/profile/mkasbaou")</f>
+        <v/>
+      </c>
+      <c r="K6" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Mohamed%20Houssem%20Kasbaoui%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Derrick Speaks</t>
+          <t>Aditi Chattopadhyay</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Assistant Teaching Professor</t>
+          <t>Regents Professor</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -2164,31 +2412,43 @@
         </is>
       </c>
       <c r="E7" s="3">
-        <f>HYPERLINK("mailto:Derrick.Speaks@asu.edu", "Derrick.Speaks@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H7" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/dspeaks2", "https://search.asu.edu/profile/dspeaks2")</f>
-        <v/>
-      </c>
-      <c r="I7" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Derrick%20Speaks%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:aditi@asu.edu", "aditi@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>inverse problems, multiscale modeling, optimization, transition</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>w3fU9E0AAAAJ</t>
+        </is>
+      </c>
+      <c r="J7" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/chattopa", "https://search.asu.edu/profile/chattopa")</f>
+        <v/>
+      </c>
+      <c r="K7" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=w3fU9E0AAAAJ", "Scholar (w3fU9E0AAAAJ)")</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Erik Andersen</t>
+          <t>Gokul Pathikonda</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Faculty Associate</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -2202,31 +2462,39 @@
         </is>
       </c>
       <c r="E8" s="3">
-        <f>HYPERLINK("mailto:Erik.J.Andersen@asu.edu", "Erik.J.Andersen@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/ejande22", "https://search.asu.edu/profile/ejande22")</f>
-        <v/>
-      </c>
-      <c r="I8" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Erik%20Andersen%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:Gokul.Pathikonda@asu.edu", "Gokul.Pathikonda@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>aerodynamics, reacting flows, turbulence, turbulent mixing</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/gpathiko", "https://search.asu.edu/profile/gpathiko")</f>
+        <v/>
+      </c>
+      <c r="K8" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Gokul%20Pathikonda%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Gokul Pathikonda</t>
+          <t>Marcus Herrmann</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Professor</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -2240,35 +2508,43 @@
         </is>
       </c>
       <c r="E9" s="3">
-        <f>HYPERLINK("mailto:Gokul.Pathikonda@asu.edu", "Gokul.Pathikonda@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>aerodynamics, reacting flows, turbulence, turbulent mixing</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H9" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/gpathiko", "https://search.asu.edu/profile/gpathiko")</f>
-        <v/>
-      </c>
-      <c r="I9" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Gokul%20Pathikonda%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:Marcus.Herrmann@asu.edu", "Marcus.Herrmann@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>fluid mechanics, multiphase flow, numerical simulation, turbulence</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>yv6aCW8AAAAJ</t>
+        </is>
+      </c>
+      <c r="J9" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/mherrma1", "https://search.asu.edu/profile/mherrma1")</f>
+        <v/>
+      </c>
+      <c r="K9" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=yv6aCW8AAAAJ", "Scholar (yv6aCW8AAAAJ)")</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Hamidreza Marvi</t>
+          <t>Alberto Scotti</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Professor</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -2282,26 +2558,38 @@
         </is>
       </c>
       <c r="E10" s="3">
-        <f>HYPERLINK("mailto:hmarvi@asu.edu", "hmarvi@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H10" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/hmarvi", "https://search.asu.edu/profile/hmarvi")</f>
-        <v/>
-      </c>
-      <c r="I10" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Hamidreza%20Marvi%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:Alberto.Scotti@asu.edu", "Alberto.Scotti@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>applied mathematics, fluid mechanics, turbulent mixing</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>HRx2lJQAAAAJ</t>
+        </is>
+      </c>
+      <c r="J10" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/adscotti", "https://search.asu.edu/profile/adscotti")</f>
+        <v/>
+      </c>
+      <c r="K10" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=HRx2lJQAAAAJ", "Scholar (HRx2lJQAAAAJ)")</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Houlong Zhuang</t>
+          <t>Beomjin Kwon</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -2320,35 +2608,43 @@
         </is>
       </c>
       <c r="E11" s="3">
-        <f>HYPERLINK("mailto:zhuanghl@asu.edu", "zhuanghl@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>computational physics</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H11" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/hzhuang7", "https://search.asu.edu/profile/hzhuang7")</f>
-        <v/>
-      </c>
-      <c r="I11" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Houlong%20Zhuang%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:kwon@asu.edu", "kwon@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>data-driven modeling, heat transfer, transport phenomena</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>fs2d97sAAAAJ</t>
+        </is>
+      </c>
+      <c r="J11" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/bkwon2", "https://search.asu.edu/profile/bkwon2")</f>
+        <v/>
+      </c>
+      <c r="K11" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=fs2d97sAAAAJ", "Scholar (fs2d97sAAAAJ)")</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Huan Wu</t>
+          <t>Leixin Ma</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -2362,35 +2658,43 @@
         </is>
       </c>
       <c r="E12" s="3">
-        <f>HYPERLINK("mailto:huanwu@asu.edu", "huanwu@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>computational physics</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H12" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/huanwu", "https://search.asu.edu/profile/huanwu")</f>
-        <v/>
-      </c>
-      <c r="I12" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Huan%20Wu%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:Leixin.Ma@asu.edu", "Leixin.Ma@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>aerodynamics, fluid-structure interaction, physics-informed machine learning</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2xQTOc0AAAAJ</t>
+        </is>
+      </c>
+      <c r="J12" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/leixinma", "https://search.asu.edu/profile/leixinma")</f>
+        <v/>
+      </c>
+      <c r="K12" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=2xQTOc0AAAAJ", "Scholar (2xQTOc0AAAAJ)")</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Huei-Ping Huang</t>
+          <t>Yulia Peet</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Professor</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -2404,30 +2708,38 @@
         </is>
       </c>
       <c r="E13" s="3">
-        <f>HYPERLINK("mailto:Huei-Ping.Huang@asu.edu", "Huei-Ping.Huang@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>fluid dynamics, numerical simulation</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H13" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/hhuang38", "https://search.asu.edu/profile/hhuang38")</f>
-        <v/>
-      </c>
-      <c r="I13" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Huei-Ping%20Huang%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:ypeet@asu.edu", "ypeet@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>fluid mechanics, high-performance computing, turbulence</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>_6o8MrUAAAAJ</t>
+        </is>
+      </c>
+      <c r="J13" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/ypeet", "https://search.asu.edu/profile/ypeet")</f>
+        <v/>
+      </c>
+      <c r="K13" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=_6o8MrUAAAAJ", "Scholar (_6o8MrUAAAAJ)")</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Hyunglae Lee</t>
+          <t>Huei-Ping Huang</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -2446,31 +2758,39 @@
         </is>
       </c>
       <c r="E14" s="3">
-        <f>HYPERLINK("mailto:Hyunglae.Lee@asu.edu", "Hyunglae.Lee@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F14" s="2" t="inlineStr"/>
-      <c r="G14" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/hlee234", "https://search.asu.edu/profile/hlee234")</f>
-        <v/>
-      </c>
-      <c r="I14" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Hyunglae%20Lee%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:Huei-Ping.Huang@asu.edu", "Huei-Ping.Huang@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>fluid dynamics, numerical simulation</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/hhuang38", "https://search.asu.edu/profile/hhuang38")</f>
+        <v/>
+      </c>
+      <c r="K14" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Huei-Ping%20Huang%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Ivy Chang</t>
+          <t>Raghavendra Murthy</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Assistant Teaching Professor</t>
+          <t>Associate Teaching Professor</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -2484,26 +2804,34 @@
         </is>
       </c>
       <c r="E15" s="3">
-        <f>HYPERLINK("mailto:Ivy.Chang@asu.edu", "Ivy.Chang@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F15" s="2" t="inlineStr"/>
-      <c r="G15" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H15" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/iychang", "https://search.asu.edu/profile/iychang")</f>
-        <v/>
-      </c>
-      <c r="I15" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ivy%20Chang%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:rnmurthy@asu.edu", "rnmurthy@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>optimization, reduced-order modeling</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/rnmurthy", "https://search.asu.edu/profile/rnmurthy")</f>
+        <v/>
+      </c>
+      <c r="K15" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Raghavendra%20Murthy%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Jagannathan Rajagopalan</t>
+          <t>Ryan Milcarek</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -2522,35 +2850,43 @@
         </is>
       </c>
       <c r="E16" s="3">
-        <f>HYPERLINK("mailto:Jagannathan.Rajagopalan@asu.edu", "Jagannathan.Rajagopalan@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>optimization</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H16" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/jrajago1", "https://search.asu.edu/profile/jrajago1")</f>
-        <v/>
-      </c>
-      <c r="I16" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Jagannathan%20Rajagopalan%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:Ryan.Milcarek@asu.edu", "Ryan.Milcarek@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>combustion, transition</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>m-Pb6g2pm2UC</t>
+        </is>
+      </c>
+      <c r="J16" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/rjmilcar", "https://search.asu.edu/profile/rjmilcar")</f>
+        <v/>
+      </c>
+      <c r="K16" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=m-Pb6g2pm2UC", "Scholar (m-Pb6g2pm2UC)")</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>James Middleton</t>
+          <t>T.-W. Lee</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2564,26 +2900,34 @@
         </is>
       </c>
       <c r="E17" s="3">
-        <f>HYPERLINK("mailto:jimbo@asu.edu", "jimbo@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F17" s="2" t="inlineStr"/>
-      <c r="G17" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H17" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/jimbo", "https://search.asu.edu/profile/jimbo")</f>
-        <v/>
-      </c>
-      <c r="I17" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=James%20Middleton%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:ATTWL@asu.edu", "ATTWL@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>aerospace propulsion, propulsion</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/attwl", "https://search.asu.edu/profile/attwl")</f>
+        <v/>
+      </c>
+      <c r="K17" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=T.-W.%20Lee%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Jay Oswald</t>
+          <t>Houlong Zhuang</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -2602,35 +2946,43 @@
         </is>
       </c>
       <c r="E18" s="3">
-        <f>HYPERLINK("mailto:joswald1@asu.edu", "joswald1@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>finite element</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H18" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/joswald1", "https://search.asu.edu/profile/joswald1")</f>
-        <v/>
-      </c>
-      <c r="I18" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Jay%20Oswald%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:zhuanghl@asu.edu", "zhuanghl@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>computational physics</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>4yYKCpUAAAAJ</t>
+        </is>
+      </c>
+      <c r="J18" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/hzhuang7", "https://search.asu.edu/profile/hzhuang7")</f>
+        <v/>
+      </c>
+      <c r="K18" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=4yYKCpUAAAAJ", "Scholar (4yYKCpUAAAAJ)")</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Jeonglae Kim</t>
+          <t>Huan Wu</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Faculty</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -2644,35 +2996,43 @@
         </is>
       </c>
       <c r="E19" s="3">
-        <f>HYPERLINK("mailto:jeokim@asu.edu", "jeokim@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>aeroacoustics, flow control, optimization, turbulence, turbulent flows</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H19" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/jkim520", "https://search.asu.edu/profile/jkim520")</f>
-        <v/>
-      </c>
-      <c r="I19" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Jeonglae%20Kim%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:huanwu@asu.edu", "huanwu@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>computational physics</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>8CS4X9IAAAAJ</t>
+        </is>
+      </c>
+      <c r="J19" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/huanwu", "https://search.asu.edu/profile/huanwu")</f>
+        <v/>
+      </c>
+      <c r="K19" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=8CS4X9IAAAAJ", "Scholar (8CS4X9IAAAAJ)")</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Jiefeng Sun</t>
+          <t>Jagannathan Rajagopalan</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2686,31 +3046,43 @@
         </is>
       </c>
       <c r="E20" s="3">
-        <f>HYPERLINK("mailto:Jiefeng.Sun@asu.edu", "Jiefeng.Sun@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/jsun165", "https://search.asu.edu/profile/jsun165")</f>
-        <v/>
-      </c>
-      <c r="I20" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Jiefeng%20Sun%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:Jagannathan.Rajagopalan@asu.edu", "Jagannathan.Rajagopalan@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>optimization</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>ClqRIhIAAAAJ</t>
+        </is>
+      </c>
+      <c r="J20" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/jrajago1", "https://search.asu.edu/profile/jrajago1")</f>
+        <v/>
+      </c>
+      <c r="K20" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=ClqRIhIAAAAJ", "Scholar (ClqRIhIAAAAJ)")</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Joshua Wilbur</t>
+          <t>Jay Oswald</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Associate Teaching Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2724,31 +3096,39 @@
         </is>
       </c>
       <c r="E21" s="3">
-        <f>HYPERLINK("mailto:Joshua.Wilbur@asu.edu", "Joshua.Wilbur@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H21" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/jdwilbu1", "https://search.asu.edu/profile/jdwilbu1")</f>
-        <v/>
-      </c>
-      <c r="I21" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Joshua%20Wilbur%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:joswald1@asu.edu", "joswald1@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>finite element</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/joswald1", "https://search.asu.edu/profile/joswald1")</f>
+        <v/>
+      </c>
+      <c r="K21" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Jay%20Oswald%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Kangping Chen</t>
+          <t>Kunal Garg</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2762,30 +3142,38 @@
         </is>
       </c>
       <c r="E22" s="3">
-        <f>HYPERLINK("mailto:k.p.chen@asu.edu", "k.p.chen@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>computational fluid dynamics, drag reduction, fluid dynamics, fluid mechanics, multiphase flow</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H22" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/asuchen", "https://search.asu.edu/profile/asuchen")</f>
-        <v/>
-      </c>
-      <c r="I22" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Kangping%20Chen%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:kgarg24@asu.edu", "kgarg24@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>optimization</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>vs3pl-8AAAAJ</t>
+        </is>
+      </c>
+      <c r="J22" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/kgarg24", "https://search.asu.edu/profile/kgarg24")</f>
+        <v/>
+      </c>
+      <c r="K22" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=vs3pl-8AAAAJ", "Scholar (vs3pl-8AAAAJ)")</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Kiran Ramesh</t>
+          <t>Liping Wang</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -2804,30 +3192,34 @@
         </is>
       </c>
       <c r="E23" s="3">
-        <f>HYPERLINK("mailto:Kiran.Ramesh@asu.edu", "Kiran.Ramesh@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>aerodynamics, flow control, fluid dynamics, turbulence, vortex dynamics</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H23" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/kramesh2", "https://search.asu.edu/profile/kramesh2")</f>
-        <v/>
-      </c>
-      <c r="I23" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Kiran%20Ramesh%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:Liping.Wang@asu.edu", "Liping.Wang@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>heat transfer</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/lwang78", "https://search.asu.edu/profile/lwang78")</f>
+        <v/>
+      </c>
+      <c r="K23" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Liping%20Wang%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Konrad Rykaczewski</t>
+          <t>Matthew Peet</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -2846,26 +3238,34 @@
         </is>
       </c>
       <c r="E24" s="3">
-        <f>HYPERLINK("mailto:konradr@asu.edu", "konradr@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/krykacze", "https://search.asu.edu/profile/krykacze")</f>
-        <v/>
-      </c>
-      <c r="I24" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Konrad%20Rykaczewski%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:mpeet@asu.edu", "mpeet@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>optimization</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/mpeet", "https://search.asu.edu/profile/mpeet")</f>
+        <v/>
+      </c>
+      <c r="K24" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Matthew%20Peet%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Kunal Garg</t>
+          <t>Minglei Qu</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -2884,35 +3284,43 @@
         </is>
       </c>
       <c r="E25" s="3">
-        <f>HYPERLINK("mailto:kgarg24@asu.edu", "kgarg24@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>optimization</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H25" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/kgarg24", "https://search.asu.edu/profile/kgarg24")</f>
-        <v/>
-      </c>
-      <c r="I25" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Kunal%20Garg%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:minglei.qu@asu.edu", "minglei.qu@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>instability</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>9LWNC50AAAAJ</t>
+        </is>
+      </c>
+      <c r="J25" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/mingleiq", "https://search.asu.edu/profile/mingleiq")</f>
+        <v/>
+      </c>
+      <c r="K25" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=9LWNC50AAAAJ", "Scholar (9LWNC50AAAAJ)")</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Leila Ladani</t>
+          <t>Robert Wang</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2926,31 +3334,43 @@
         </is>
       </c>
       <c r="E26" s="3">
-        <f>HYPERLINK("mailto:ladani@asu.edu", "ladani@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F26" s="2" t="inlineStr"/>
-      <c r="G26" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H26" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/ljannesa", "https://search.asu.edu/profile/ljannesa")</f>
-        <v/>
-      </c>
-      <c r="I26" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Leila%20Ladani%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:rywang@asu.edu", "rywang@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>heat transfer</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>LaUdx9gAAAAJ</t>
+        </is>
+      </c>
+      <c r="J26" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/rywang", "https://search.asu.edu/profile/rywang")</f>
+        <v/>
+      </c>
+      <c r="K26" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=LaUdx9gAAAAJ", "Scholar (LaUdx9gAAAAJ)")</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Leixin Ma</t>
+          <t>Ronald Calhoun</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2964,35 +3384,39 @@
         </is>
       </c>
       <c r="E27" s="3">
-        <f>HYPERLINK("mailto:Leixin.Ma@asu.edu", "Leixin.Ma@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>aerodynamics, fluid-structure interaction, physics-informed machine learning</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H27" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/leixinma", "https://search.asu.edu/profile/leixinma")</f>
-        <v/>
-      </c>
-      <c r="I27" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Leixin%20Ma%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:Ronald.Calhoun@asu.edu", "Ronald.Calhoun@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>fluid dynamics</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/rcalhou", "https://search.asu.edu/profile/rcalhou")</f>
+        <v/>
+      </c>
+      <c r="K27" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ronald%20Calhoun%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Lin Li</t>
+          <t>Spring Berman</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Professor</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -3006,31 +3430,43 @@
         </is>
       </c>
       <c r="E28" s="3">
-        <f>HYPERLINK("mailto:Lin.Li.10@asu.edu", "Lin.Li.10@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F28" s="2" t="inlineStr"/>
-      <c r="G28" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H28" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/linli25", "https://search.asu.edu/profile/linli25")</f>
-        <v/>
-      </c>
-      <c r="I28" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Lin%20Li%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:Spring.Berman@asu.edu", "Spring.Berman@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>optimization</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>KKup0OgAAAAJ</t>
+        </is>
+      </c>
+      <c r="J28" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/smberma2", "https://search.asu.edu/profile/smberma2")</f>
+        <v/>
+      </c>
+      <c r="K28" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=KKup0OgAAAAJ", "Scholar (KKup0OgAAAAJ)")</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Liping Wang</t>
+          <t>Tianyu Yang</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -3044,35 +3480,43 @@
         </is>
       </c>
       <c r="E29" s="3">
-        <f>HYPERLINK("mailto:Liping.Wang@asu.edu", "Liping.Wang@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
+        <f>HYPERLINK("mailto:Tianyu.Yang@asu.edu", "Tianyu.Yang@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>heat transfer</t>
         </is>
       </c>
-      <c r="G29" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H29" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/lwang78", "https://search.asu.edu/profile/lwang78")</f>
-        <v/>
-      </c>
-      <c r="I29" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Liping%20Wang%20Arizona%20State%20University", "Google Scholar Profile")</f>
+      <c r="H29" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>OmBV67MAAAAJ</t>
+        </is>
+      </c>
+      <c r="J29" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/tyang123", "https://search.asu.edu/profile/tyang123")</f>
+        <v/>
+      </c>
+      <c r="K29" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=OmBV67MAAAAJ", "Scholar (OmBV67MAAAAJ)")</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Marc Mignolet</t>
+          <t>Yi Ren</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -3086,26 +3530,34 @@
         </is>
       </c>
       <c r="E30" s="3">
-        <f>HYPERLINK("mailto:marc.mignolet@asu.edu", "marc.mignolet@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F30" s="2" t="inlineStr"/>
-      <c r="G30" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H30" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/marc03", "https://search.asu.edu/profile/marc03")</f>
-        <v/>
-      </c>
-      <c r="I30" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Marc%20Mignolet%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:yiren@asu.edu", "yiren@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>optimization</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/yren32", "https://search.asu.edu/profile/yren32")</f>
+        <v/>
+      </c>
+      <c r="K30" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Yi%20Ren%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Marcus Herrmann</t>
+          <t>Yongming Liu</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -3124,35 +3576,39 @@
         </is>
       </c>
       <c r="E31" s="3">
-        <f>HYPERLINK("mailto:Marcus.Herrmann@asu.edu", "Marcus.Herrmann@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>fluid mechanics, multiphase flow, numerical simulation, turbulence</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H31" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/mherrma1", "https://search.asu.edu/profile/mherrma1")</f>
-        <v/>
-      </c>
-      <c r="I31" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Marcus%20Herrmann%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:Yongming.Liu@asu.edu", "Yongming.Liu@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>uncertainty quantification</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/yliu35", "https://search.asu.edu/profile/yliu35")</f>
+        <v/>
+      </c>
+      <c r="K31" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Yongming%20Liu%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Matthew Peet</t>
+          <t>Aikaterini Stefanaki</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Associate Teaching Professor</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -3166,35 +3622,35 @@
         </is>
       </c>
       <c r="E32" s="3">
-        <f>HYPERLINK("mailto:mpeet@asu.edu", "mpeet@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>optimization</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H32" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/mpeet", "https://search.asu.edu/profile/mpeet")</f>
-        <v/>
-      </c>
-      <c r="I32" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Matthew%20Peet%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:astefan9@asu.edu", "astefan9@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/astefan9", "https://search.asu.edu/profile/astefan9")</f>
+        <v/>
+      </c>
+      <c r="K32" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Aikaterini%20Stefanaki%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Minglei Qu</t>
+          <t>Cindy (Xiangjia) Li</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -3208,35 +3664,39 @@
         </is>
       </c>
       <c r="E33" s="3">
-        <f>HYPERLINK("mailto:minglei.qu@asu.edu", "minglei.qu@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>instability</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H33" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/mingleiq", "https://search.asu.edu/profile/mingleiq")</f>
-        <v/>
-      </c>
-      <c r="I33" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Minglei%20Qu%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:xiangjia.li@asu.edu", "xiangjia.li@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>tGQzHJIAAAAJ</t>
+        </is>
+      </c>
+      <c r="J33" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/xiangji5", "https://search.asu.edu/profile/xiangji5")</f>
+        <v/>
+      </c>
+      <c r="K33" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=tGQzHJIAAAAJ", "Scholar (tGQzHJIAAAAJ)")</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Mohamed Houssem Kasbaoui</t>
+          <t>Derrick Speaks</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Assistant Teaching Professor</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3250,35 +3710,35 @@
         </is>
       </c>
       <c r="E34" s="3">
-        <f>HYPERLINK("mailto:houssem.kasbaoui@asu.edu", "houssem.kasbaoui@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>cfd, computational fluid dynamics, dns, fluid dynamics, multiphase flow</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H34" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/mkasbaou", "https://search.asu.edu/profile/mkasbaou")</f>
-        <v/>
-      </c>
-      <c r="I34" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Mohamed%20Houssem%20Kasbaoui%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:Derrick.Speaks@asu.edu", "Derrick.Speaks@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/dspeaks2", "https://search.asu.edu/profile/dspeaks2")</f>
+        <v/>
+      </c>
+      <c r="K34" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Derrick%20Speaks%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Patrick Phelan</t>
+          <t>Erik Andersen</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Professor</t>
+          <t>Faculty Associate</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3292,31 +3752,35 @@
         </is>
       </c>
       <c r="E35" s="3">
-        <f>HYPERLINK("mailto:phelan@asu.edu", "phelan@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F35" s="2" t="inlineStr"/>
-      <c r="G35" s="2" t="b">
+        <f>HYPERLINK("mailto:Erik.J.Andersen@asu.edu", "Erik.J.Andersen@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F35" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H35" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/pphelan", "https://search.asu.edu/profile/pphelan")</f>
-        <v/>
-      </c>
-      <c r="I35" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Patrick%20Phelan%20Arizona%20State%20University", "Google Scholar Profile")</f>
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/ejande22", "https://search.asu.edu/profile/ejande22")</f>
+        <v/>
+      </c>
+      <c r="K35" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Erik%20Andersen%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Pedro Peralta</t>
+          <t>Hamidreza Marvi</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3330,26 +3794,34 @@
         </is>
       </c>
       <c r="E36" s="3">
-        <f>HYPERLINK("mailto:pperalta@asu.edu", "pperalta@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F36" s="2" t="inlineStr"/>
-      <c r="G36" s="2" t="b">
+        <f>HYPERLINK("mailto:hmarvi@asu.edu", "hmarvi@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F36" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H36" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/pperalta", "https://search.asu.edu/profile/pperalta")</f>
-        <v/>
-      </c>
-      <c r="I36" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Pedro%20Peralta%20Arizona%20State%20University", "Google Scholar Profile")</f>
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>00Fepb0AAAAJ</t>
+        </is>
+      </c>
+      <c r="J36" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/hmarvi", "https://search.asu.edu/profile/hmarvi")</f>
+        <v/>
+      </c>
+      <c r="K36" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=00Fepb0AAAAJ", "Scholar (00Fepb0AAAAJ)")</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Qiong Nian</t>
+          <t>Hyunglae Lee</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -3368,31 +3840,35 @@
         </is>
       </c>
       <c r="E37" s="3">
-        <f>HYPERLINK("mailto:Qiong.Nian@asu.edu", "Qiong.Nian@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F37" s="2" t="inlineStr"/>
-      <c r="G37" s="2" t="b">
+        <f>HYPERLINK("mailto:Hyunglae.Lee@asu.edu", "Hyunglae.Lee@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F37" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H37" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/qnian", "https://search.asu.edu/profile/qnian")</f>
-        <v/>
-      </c>
-      <c r="I37" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Qiong%20Nian%20Arizona%20State%20University", "Google Scholar Profile")</f>
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/hlee234", "https://search.asu.edu/profile/hlee234")</f>
+        <v/>
+      </c>
+      <c r="K37" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Hyunglae%20Lee%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Raghavendra Murthy</t>
+          <t>Ivy Chang</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Associate Teaching Professor</t>
+          <t>Assistant Teaching Professor</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3406,35 +3882,35 @@
         </is>
       </c>
       <c r="E38" s="3">
-        <f>HYPERLINK("mailto:rnmurthy@asu.edu", "rnmurthy@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>optimization, reduced-order modeling</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H38" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/rnmurthy", "https://search.asu.edu/profile/rnmurthy")</f>
-        <v/>
-      </c>
-      <c r="I38" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Raghavendra%20Murthy%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:Ivy.Chang@asu.edu", "Ivy.Chang@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/iychang", "https://search.asu.edu/profile/iychang")</f>
+        <v/>
+      </c>
+      <c r="K38" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ivy%20Chang%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Ricardo Cruz Lozano</t>
+          <t>James Middleton</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Assistant Teaching Professor</t>
+          <t>Professor</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3448,31 +3924,35 @@
         </is>
       </c>
       <c r="E39" s="3">
-        <f>HYPERLINK("mailto:Ricardo.Cruz.Lozano@asu.edu", "Ricardo.Cruz.Lozano@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F39" s="2" t="inlineStr"/>
-      <c r="G39" s="2" t="b">
+        <f>HYPERLINK("mailto:jimbo@asu.edu", "jimbo@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F39" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H39" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/rcruzloz", "https://search.asu.edu/profile/rcruzloz")</f>
-        <v/>
-      </c>
-      <c r="I39" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ricardo%20Cruz%20Lozano%20Arizona%20State%20University", "Google Scholar Profile")</f>
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/jimbo", "https://search.asu.edu/profile/jimbo")</f>
+        <v/>
+      </c>
+      <c r="K39" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=James%20Middleton%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Robert Wang</t>
+          <t>Jiefeng Sun</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3486,35 +3966,39 @@
         </is>
       </c>
       <c r="E40" s="3">
-        <f>HYPERLINK("mailto:rywang@asu.edu", "rywang@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>heat transfer</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H40" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/rywang", "https://search.asu.edu/profile/rywang")</f>
-        <v/>
-      </c>
-      <c r="I40" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Robert%20Wang%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:Jiefeng.Sun@asu.edu", "Jiefeng.Sun@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>fjUoHOsAAAAJ</t>
+        </is>
+      </c>
+      <c r="J40" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/jsun165", "https://search.asu.edu/profile/jsun165")</f>
+        <v/>
+      </c>
+      <c r="K40" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=fjUoHOsAAAAJ", "Scholar (fjUoHOsAAAAJ)")</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Ronald Calhoun</t>
+          <t>Joshua Wilbur</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Associate Teaching Professor</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3528,30 +4012,30 @@
         </is>
       </c>
       <c r="E41" s="3">
-        <f>HYPERLINK("mailto:Ronald.Calhoun@asu.edu", "Ronald.Calhoun@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>fluid dynamics</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H41" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/rcalhou", "https://search.asu.edu/profile/rcalhou")</f>
-        <v/>
-      </c>
-      <c r="I41" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ronald%20Calhoun%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:Joshua.Wilbur@asu.edu", "Joshua.Wilbur@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/jdwilbu1", "https://search.asu.edu/profile/jdwilbu1")</f>
+        <v/>
+      </c>
+      <c r="K41" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Joshua%20Wilbur%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Ryan Milcarek</t>
+          <t>Konrad Rykaczewski</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -3570,30 +4054,34 @@
         </is>
       </c>
       <c r="E42" s="3">
-        <f>HYPERLINK("mailto:Ryan.Milcarek@asu.edu", "Ryan.Milcarek@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>combustion, transition</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H42" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/rjmilcar", "https://search.asu.edu/profile/rjmilcar")</f>
-        <v/>
-      </c>
-      <c r="I42" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ryan%20Milcarek%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:konradr@asu.edu", "konradr@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>SWeAf4UAAAAJ</t>
+        </is>
+      </c>
+      <c r="J42" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/krykacze", "https://search.asu.edu/profile/krykacze")</f>
+        <v/>
+      </c>
+      <c r="K42" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=SWeAf4UAAAAJ", "Scholar (SWeAf4UAAAAJ)")</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Spring Berman</t>
+          <t>Leila Ladani</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -3612,35 +4100,35 @@
         </is>
       </c>
       <c r="E43" s="3">
-        <f>HYPERLINK("mailto:Spring.Berman@asu.edu", "Spring.Berman@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>optimization</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H43" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/smberma2", "https://search.asu.edu/profile/smberma2")</f>
-        <v/>
-      </c>
-      <c r="I43" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Spring%20Berman%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:ladani@asu.edu", "ladani@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/ljannesa", "https://search.asu.edu/profile/ljannesa")</f>
+        <v/>
+      </c>
+      <c r="K43" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Leila%20Ladani%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Sridhar Seetharaman</t>
+          <t>Lin Li</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3654,31 +4142,35 @@
         </is>
       </c>
       <c r="E44" s="3">
-        <f>HYPERLINK("mailto:seetharaman@asu.edu", "seetharaman@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F44" s="2" t="inlineStr"/>
-      <c r="G44" s="2" t="b">
+        <f>HYPERLINK("mailto:Lin.Li.10@asu.edu", "Lin.Li.10@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F44" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H44" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/sseeth11", "https://search.asu.edu/profile/sseeth11")</f>
-        <v/>
-      </c>
-      <c r="I44" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Sridhar%20Seetharaman%20Arizona%20State%20University", "Google Scholar Profile")</f>
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/linli25", "https://search.asu.edu/profile/linli25")</f>
+        <v/>
+      </c>
+      <c r="K44" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Lin%20Li%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Srinivas Chakravarthi Kosaraju</t>
+          <t>Marc Mignolet</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Teaching Professor</t>
+          <t>Professor</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3692,31 +4184,35 @@
         </is>
       </c>
       <c r="E45" s="3">
-        <f>HYPERLINK("mailto:Srinivas.Kosaraju@asu.edu", "Srinivas.Kosaraju@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F45" s="2" t="inlineStr"/>
-      <c r="G45" s="2" t="b">
+        <f>HYPERLINK("mailto:marc.mignolet@asu.edu", "marc.mignolet@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F45" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H45" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/skosara2", "https://search.asu.edu/profile/skosara2")</f>
-        <v/>
-      </c>
-      <c r="I45" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Srinivas%20Chakravarthi%20Kosaraju%20Arizona%20State%20University", "Google Scholar Profile")</f>
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/marc03", "https://search.asu.edu/profile/marc03")</f>
+        <v/>
+      </c>
+      <c r="K45" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Marc%20Mignolet%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>T.-W. Lee</t>
+          <t>Patrick Phelan</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Professor</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3730,35 +4226,35 @@
         </is>
       </c>
       <c r="E46" s="3">
-        <f>HYPERLINK("mailto:ATTWL@asu.edu", "ATTWL@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>aerospace propulsion, propulsion</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H46" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/attwl", "https://search.asu.edu/profile/attwl")</f>
-        <v/>
-      </c>
-      <c r="I46" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=T.-W.%20Lee%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:phelan@asu.edu", "phelan@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/pphelan", "https://search.asu.edu/profile/pphelan")</f>
+        <v/>
+      </c>
+      <c r="K46" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Patrick%20Phelan%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Tianyu Yang</t>
+          <t>Pedro Peralta</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Professor</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3772,35 +4268,35 @@
         </is>
       </c>
       <c r="E47" s="3">
-        <f>HYPERLINK("mailto:Tianyu.Yang@asu.edu", "Tianyu.Yang@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>heat transfer</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H47" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/tyang123", "https://search.asu.edu/profile/tyang123")</f>
-        <v/>
-      </c>
-      <c r="I47" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Tianyu%20Yang%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:pperalta@asu.edu", "pperalta@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/pperalta", "https://search.asu.edu/profile/pperalta")</f>
+        <v/>
+      </c>
+      <c r="K47" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Pedro%20Peralta%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Wanxin Jin</t>
+          <t>Qiong Nian</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3814,31 +4310,35 @@
         </is>
       </c>
       <c r="E48" s="3">
-        <f>HYPERLINK("mailto:wjin@asu.edu", "wjin@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F48" s="2" t="inlineStr"/>
-      <c r="G48" s="2" t="b">
+        <f>HYPERLINK("mailto:Qiong.Nian@asu.edu", "Qiong.Nian@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F48" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H48" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/wjin34", "https://search.asu.edu/profile/wjin34")</f>
-        <v/>
-      </c>
-      <c r="I48" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Wanxin%20Jin%20Arizona%20State%20University", "Google Scholar Profile")</f>
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/qnian", "https://search.asu.edu/profile/qnian")</f>
+        <v/>
+      </c>
+      <c r="K48" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Qiong%20Nian%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Werner Dahm</t>
+          <t>Ricardo Cruz Lozano</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>SUM/WTR Faculty Research</t>
+          <t>Assistant Teaching Professor</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -3852,35 +4352,35 @@
         </is>
       </c>
       <c r="E49" s="3">
-        <f>HYPERLINK("mailto:Werner.Dahm@asu.edu", "Werner.Dahm@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>combustion, computational physics, fluid dynamics, heat transfer, propulsion, turbulence</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H49" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/wdahm", "https://search.asu.edu/profile/wdahm")</f>
-        <v/>
-      </c>
-      <c r="I49" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Werner%20Dahm%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:Ricardo.Cruz.Lozano@asu.edu", "Ricardo.Cruz.Lozano@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/rcruzloz", "https://search.asu.edu/profile/rcruzloz")</f>
+        <v/>
+      </c>
+      <c r="K49" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ricardo%20Cruz%20Lozano%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Wonmo Kang</t>
+          <t>Sridhar Seetharaman</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Professor</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -3894,31 +4394,35 @@
         </is>
       </c>
       <c r="E50" s="3">
-        <f>HYPERLINK("mailto:Wonmo.Kang@asu.edu", "Wonmo.Kang@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F50" s="2" t="inlineStr"/>
-      <c r="G50" s="2" t="b">
+        <f>HYPERLINK("mailto:seetharaman@asu.edu", "seetharaman@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F50" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H50" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/wkang16", "https://search.asu.edu/profile/wkang16")</f>
-        <v/>
-      </c>
-      <c r="I50" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Wonmo%20Kang%20Arizona%20State%20University", "Google Scholar Profile")</f>
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/sseeth11", "https://search.asu.edu/profile/sseeth11")</f>
+        <v/>
+      </c>
+      <c r="K50" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Sridhar%20Seetharaman%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Yi Ren</t>
+          <t>Srinivas Chakravarthi Kosaraju</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Teaching Professor</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -3932,35 +4436,35 @@
         </is>
       </c>
       <c r="E51" s="3">
-        <f>HYPERLINK("mailto:yiren@asu.edu", "yiren@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>optimization</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H51" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/yren32", "https://search.asu.edu/profile/yren32")</f>
-        <v/>
-      </c>
-      <c r="I51" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Yi%20Ren%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:Srinivas.Kosaraju@asu.edu", "Srinivas.Kosaraju@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/skosara2", "https://search.asu.edu/profile/skosara2")</f>
+        <v/>
+      </c>
+      <c r="K51" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Srinivas%20Chakravarthi%20Kosaraju%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Yongming Liu</t>
+          <t>Wanxin Jin</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Professor</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3974,35 +4478,39 @@
         </is>
       </c>
       <c r="E52" s="3">
-        <f>HYPERLINK("mailto:Yongming.Liu@asu.edu", "Yongming.Liu@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>uncertainty quantification</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H52" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/yliu35", "https://search.asu.edu/profile/yliu35")</f>
-        <v/>
-      </c>
-      <c r="I52" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Yongming%20Liu%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:wjin@asu.edu", "wjin@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>SoEC4h4AAAAJ</t>
+        </is>
+      </c>
+      <c r="J52" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/wjin34", "https://search.asu.edu/profile/wjin34")</f>
+        <v/>
+      </c>
+      <c r="K52" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=SoEC4h4AAAAJ", "Scholar (SoEC4h4AAAAJ)")</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Yulia Peet</t>
+          <t>Wonmo Kang</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4016,23 +4524,27 @@
         </is>
       </c>
       <c r="E53" s="3">
-        <f>HYPERLINK("mailto:ypeet@asu.edu", "ypeet@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>fluid mechanics, high-performance computing, turbulence</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H53" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/ypeet", "https://search.asu.edu/profile/ypeet")</f>
-        <v/>
-      </c>
-      <c r="I53" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Yulia%20Peet%20Arizona%20State%20University", "Google Scholar Profile")</f>
+        <f>HYPERLINK("mailto:Wonmo.Kang@asu.edu", "Wonmo.Kang@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>bHyyOTAAAAAJ</t>
+        </is>
+      </c>
+      <c r="J53" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/wkang16", "https://search.asu.edu/profile/wkang16")</f>
+        <v/>
+      </c>
+      <c r="K53" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=bHyyOTAAAAAJ", "Scholar (bHyyOTAAAAAJ)")</f>
         <v/>
       </c>
     </row>
@@ -4061,180 +4573,184 @@
         <f>HYPERLINK("mailto:xzhe1@asu.edu", "xzhe1@asu.edu")</f>
         <v/>
       </c>
-      <c r="F54" s="2" t="inlineStr"/>
-      <c r="G54" s="2" t="b">
+      <c r="F54" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H54" s="3">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/xzhe1", "https://search.asu.edu/profile/xzhe1")</f>
         <v/>
       </c>
-      <c r="I54" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Zhe%20Xu%20Arizona%20State%20University", "Google Scholar Profile")</f>
+      <c r="K54" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Zhe%20Xu%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId63"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId69"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId75"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId81"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId87"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId93"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId96"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId99"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId105"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId108"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId111"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId114"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId117"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId123"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId126"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="rId129"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId132"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId135"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId138"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId141"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId144"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId147"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId150"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J52" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K52" r:id="rId153"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J53" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K53" r:id="rId156"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K54" r:id="rId159"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/universities_wise/arizona_state_university/asu_aerospace_mechanical_faculty.xlsx
+++ b/universities_wise/arizona_state_university/asu_aerospace_mechanical_faculty.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -465,10 +465,13 @@
     <col width="49" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="49" customWidth="1" min="10" max="10"/>
-    <col width="32" customWidth="1" min="11" max="11"/>
+    <col width="65" customWidth="1" min="8" max="8"/>
+    <col width="65" customWidth="1" min="9" max="9"/>
+    <col width="65" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="49" customWidth="1" min="13" max="13"/>
+    <col width="32" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -509,20 +512,35 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Research Interests</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Expertise Areas</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Research / Bio Summary</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Is Field Match</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Scholar ID</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Profile URL</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Google Scholar URL</t>
         </is>
@@ -531,12 +549,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Werner Dahm</t>
+          <t>Jeonglae Kim</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUM/WTR Faculty Research</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -550,7 +568,7 @@
         </is>
       </c>
       <c r="E2" s="3">
-        <f>HYPERLINK("mailto:Werner.Dahm@asu.edu", "Werner.Dahm@asu.edu")</f>
+        <f>HYPERLINK("mailto:jeokim@asu.edu", "jeokim@asu.edu")</f>
         <v/>
       </c>
       <c r="F2" s="2" t="n">
@@ -558,31 +576,38 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>combustion, computational physics, fluid dynamics, heat transfer, propulsion, turbulence</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="b">
-        <v>1</v>
-      </c>
+          <t>aeroacoustics, flow control, high-performance computing, optimization, turbulence, turbulent flows</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/wdahm", "https://search.asu.edu/profile/wdahm")</f>
-        <v/>
-      </c>
-      <c r="K2" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Werner%20Dahm%20Arizona%20State%20University", "Google Scholar Search")</f>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Kim's research interests include large-eddy simulation of high-speed turbulent flows with multi-physics, aeroacoustics, flow control and optimization.</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/jkim520", "https://search.asu.edu/profile/jkim520")</f>
+        <v/>
+      </c>
+      <c r="N2" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Jeonglae%20Kim%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Jeonglae Kim</t>
+          <t>Werner Dahm</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>SUM/WTR Faculty Research</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -596,27 +621,42 @@
         </is>
       </c>
       <c r="E3" s="3">
-        <f>HYPERLINK("mailto:jeokim@asu.edu", "jeokim@asu.edu")</f>
+        <f>HYPERLINK("mailto:Werner.Dahm@asu.edu", "Werner.Dahm@asu.edu")</f>
         <v/>
       </c>
       <c r="F3" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>aeroacoustics, flow control, optimization, turbulence, turbulent flows</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/jkim520", "https://search.asu.edu/profile/jkim520")</f>
-        <v/>
-      </c>
-      <c r="K3" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Jeonglae%20Kim%20Arizona%20State%20University", "Google Scholar Search")</f>
+          <t>combustion, computational physics, fluid dynamics, heat transfer, propulsion, turbulence</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Dahm specializes in fluid dynamics, thermodynamics, combustion, heat transfer, thermal sciences, propulsion, fuel efficiency, emissions, powertrains, and other areas relevant to a broad range of automotive, aerospace, and industrial applications. He is an author of over 200 refereed technical articles, conference papers, and technical publications, a holder of six U.S. and international patents, and has given over 260 technical presentations, including over 190 invited, plenary, and keynote lectures worldwide, on topics dealing with mechanical and aerospace engineering and defense science.</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Aerospace Engineering, Applied Research, Computational Modeling, Computational Physics, Mechanical Engineering, Propulsion</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Werner J.A. Dahm has since 2010 been the ASU Foundation Professor of Mechanical and Aerospace Engineering, and also Professor Emeritus of Engineering at the University of Michigan where served for the previous 25 years.</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/wdahm", "https://search.asu.edu/profile/wdahm")</f>
+        <v/>
+      </c>
+      <c r="N3" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Werner%20Dahm%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
     </row>
@@ -653,19 +693,26 @@
           <t>computational fluid dynamics, drag reduction, fluid dynamics, fluid mechanics, multiphase flow</t>
         </is>
       </c>
-      <c r="H4" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Chen’s research interests include multiphase flows, drag reduction, airplane de-icing, interfacial instabilities and flow in porous media.</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>xT-lX9sAAAAJ</t>
         </is>
       </c>
-      <c r="J4" s="3">
+      <c r="M4" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/asuchen", "https://search.asu.edu/profile/asuchen")</f>
         <v/>
       </c>
-      <c r="K4" s="3">
+      <c r="N4" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=xT-lX9sAAAAJ", "Scholar (xT-lX9sAAAAJ)")</f>
         <v/>
       </c>
@@ -703,19 +750,30 @@
           <t>aerodynamics, flow control, fluid dynamics, turbulence, vortex dynamics</t>
         </is>
       </c>
-      <c r="H5" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Unsteady aerodynamics, vortex dynamics, flow control, turbulence, separated flows</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Ramesh's expertise is in unsteady fluid dynamics, vortex dynamics, turbulence and flow control.</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>DKc-AgcAAAAJ</t>
         </is>
       </c>
-      <c r="J5" s="3">
+      <c r="M5" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/kramesh2", "https://search.asu.edu/profile/kramesh2")</f>
         <v/>
       </c>
-      <c r="K5" s="3">
+      <c r="N5" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=DKc-AgcAAAAJ", "Scholar (DKc-AgcAAAAJ)")</f>
         <v/>
       </c>
@@ -753,15 +811,22 @@
           <t>cfd, computational fluid dynamics, dns, fluid dynamics, multiphase flow</t>
         </is>
       </c>
-      <c r="H6" s="2" t="b">
-        <v>1</v>
-      </c>
+      <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="3">
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Kasbaoui's research interests include computational fluid dynamics, numerical methods, and massively parallel simulations of multiphase and particle-laden flows for environmental and aerospace applications.</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/mkasbaou", "https://search.asu.edu/profile/mkasbaou")</f>
         <v/>
       </c>
-      <c r="K6" s="3">
+      <c r="N6" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Mohamed%20Houssem%20Kasbaoui%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
@@ -799,19 +864,26 @@
           <t>inverse problems, multiscale modeling, optimization, transition</t>
         </is>
       </c>
-      <c r="H7" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Chattopadhyay is the director of Adaptive Intelligent Materials and Systems (AIMS) Center at ASU. Her research focuses on structural health monitoring and damage prognosis, and multidisciplinary design optimization.</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>w3fU9E0AAAAJ</t>
         </is>
       </c>
-      <c r="J7" s="3">
+      <c r="M7" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/chattopa", "https://search.asu.edu/profile/chattopa")</f>
         <v/>
       </c>
-      <c r="K7" s="3">
+      <c r="N7" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=w3fU9E0AAAAJ", "Scholar (w3fU9E0AAAAJ)")</f>
         <v/>
       </c>
@@ -849,15 +921,30 @@
           <t>aerodynamics, reacting flows, turbulence, turbulent mixing</t>
         </is>
       </c>
-      <c r="H8" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="3">
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Aerodynamics, Aerospace Engineering, Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Aerodynamics, Aerospace Engineering, Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Pathikonda studies turbulent fluid flows to understand natural and engineering phenomena using lab experiments. His expertise is in complex (reacting) mixing, high Re-flows, laser-based &amp; spectroscopic techniques, etc.</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/gpathiko", "https://search.asu.edu/profile/gpathiko")</f>
         <v/>
       </c>
-      <c r="K8" s="3">
+      <c r="N8" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Gokul%20Pathikonda%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
@@ -895,19 +982,26 @@
           <t>fluid mechanics, multiphase flow, numerical simulation, turbulence</t>
         </is>
       </c>
-      <c r="H9" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Herrmann's research interests include fluid mechanics, modeling and numerical simulation of multiphase flows with a focus on turbulent atomization processes, and numerical methods for discontinuous interfaces.</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>yv6aCW8AAAAJ</t>
         </is>
       </c>
-      <c r="J9" s="3">
+      <c r="M9" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/mherrma1", "https://search.asu.edu/profile/mherrma1")</f>
         <v/>
       </c>
-      <c r="K9" s="3">
+      <c r="N9" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=yv6aCW8AAAAJ", "Scholar (yv6aCW8AAAAJ)")</f>
         <v/>
       </c>
@@ -945,19 +1039,34 @@
           <t>applied mathematics, fluid mechanics, turbulent mixing</t>
         </is>
       </c>
-      <c r="H10" s="2" t="b">
-        <v>1</v>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Modeling and Simulation, Oceanography, Earth Systems and Climate Science, Modeling, Modeling, Simulation and Cyberinfrastructure, Applied Mathematics</t>
+        </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>Modeling and Simulation, Oceanography, Earth Systems and Climate Science, Modeling, Modeling, Simulation and Cyberinfrastructure, Applied Mathematics</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Scotti's main focus is theoretical, experimental and computational aspects of environmental fluid mechanics.</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>HRx2lJQAAAAJ</t>
         </is>
       </c>
-      <c r="J10" s="3">
+      <c r="M10" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/adscotti", "https://search.asu.edu/profile/adscotti")</f>
         <v/>
       </c>
-      <c r="K10" s="3">
+      <c r="N10" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=HRx2lJQAAAAJ", "Scholar (HRx2lJQAAAAJ)")</f>
         <v/>
       </c>
@@ -995,19 +1104,30 @@
           <t>data-driven modeling, heat transfer, transport phenomena</t>
         </is>
       </c>
-      <c r="H11" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Transport phenomena in heat transfer systems Additive manufacturing Data-driven modeling and design</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Kwon aims to improve the energy conversion and transport systems through the fundamental insights into transport physics, and by exploiting additive manufacturing and data-driven approaches.</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>fs2d97sAAAAJ</t>
         </is>
       </c>
-      <c r="J11" s="3">
+      <c r="M11" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/bkwon2", "https://search.asu.edu/profile/bkwon2")</f>
         <v/>
       </c>
-      <c r="K11" s="3">
+      <c r="N11" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=fs2d97sAAAAJ", "Scholar (fs2d97sAAAAJ)")</f>
         <v/>
       </c>
@@ -1045,19 +1165,34 @@
           <t>aerodynamics, fluid-structure interaction, physics-informed machine learning</t>
         </is>
       </c>
-      <c r="H12" s="2" t="b">
-        <v>1</v>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Aerodynamics, Dynamical Systems, Machine Learning, Mechanics of Composite Materials</t>
+        </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
+          <t>Aerodynamics, Dynamical Systems, Machine Learning, Mechanics of Composite Materials</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Leixin Ma's career goal is a data-driven and physically consistent approach to modeling and designing programmable smart structures and robots, especially under complex fluid flow conditions.</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
           <t>2xQTOc0AAAAJ</t>
         </is>
       </c>
-      <c r="J12" s="3">
+      <c r="M12" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/leixinma", "https://search.asu.edu/profile/leixinma")</f>
         <v/>
       </c>
-      <c r="K12" s="3">
+      <c r="N12" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=2xQTOc0AAAAJ", "Scholar (2xQTOc0AAAAJ)")</f>
         <v/>
       </c>
@@ -1095,19 +1230,26 @@
           <t>fluid mechanics, high-performance computing, turbulence</t>
         </is>
       </c>
-      <c r="H13" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Yulia Peet is an associate professor of aerospace and mechanical engineering in the School for Engineering of Matter, Transport and Energy with the Ira A. Fulton Schools of Engineering at Arizona State University. Her Ph.D. degree is in Aeronautics and Astronautics from Stanford (2006), M.S. and B.S. degrees are from Moscow Institute of Physics and Technology (1999 and 1997). Her previous appoi...</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>_6o8MrUAAAAJ</t>
         </is>
       </c>
-      <c r="J13" s="3">
+      <c r="M13" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/ypeet", "https://search.asu.edu/profile/ypeet")</f>
         <v/>
       </c>
-      <c r="K13" s="3">
+      <c r="N13" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=_6o8MrUAAAAJ", "Scholar (_6o8MrUAAAAJ)")</f>
         <v/>
       </c>
@@ -1145,15 +1287,22 @@
           <t>fluid dynamics, numerical simulation</t>
         </is>
       </c>
-      <c r="H14" s="2" t="b">
-        <v>1</v>
-      </c>
+      <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="3">
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Huang's research interests are geophysical and environmental fluid dynamics, numerical simulation of atmospheric and oceanic flows, Earth system remote sensing, and climate change.</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/hhuang38", "https://search.asu.edu/profile/hhuang38")</f>
         <v/>
       </c>
-      <c r="K14" s="3">
+      <c r="N14" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Huei-Ping%20Huang%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
@@ -1191,15 +1340,22 @@
           <t>optimization, reduced-order modeling</t>
         </is>
       </c>
-      <c r="H15" s="2" t="b">
-        <v>1</v>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Structural Dynamics, Rotordynamics, Vibration Analysis, Reduced-Order Modeling, Optimization</t>
+        </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="3">
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/rnmurthy", "https://search.asu.edu/profile/rnmurthy")</f>
         <v/>
       </c>
-      <c r="K15" s="3">
+      <c r="N15" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Raghavendra%20Murthy%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
@@ -1237,19 +1393,34 @@
           <t>combustion, transition</t>
         </is>
       </c>
-      <c r="H16" s="2" t="b">
-        <v>1</v>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Energy management and efficiency, energy transition, energy storage, solid oxide fuel cells, partial oxidation, cogeneration, combustion, and synthesis of hydrogen</t>
+        </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>Ceramics, Electrochemistry, Energy, Energy and Sustainability, Energy Conservation, Energy Economics, Energy Efficiency Technologies, Thin Film Materials</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Milcarek's current research focuses on energy management and efficiency, energy system modeling, energy transition, energy storage, solid oxide fuel cells fabrication and testing, partial oxidation and synthesis of hydrogen.</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>m-Pb6g2pm2UC</t>
         </is>
       </c>
-      <c r="J16" s="3">
+      <c r="M16" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/rjmilcar", "https://search.asu.edu/profile/rjmilcar")</f>
         <v/>
       </c>
-      <c r="K16" s="3">
+      <c r="N16" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=m-Pb6g2pm2UC", "Scholar (m-Pb6g2pm2UC)")</f>
         <v/>
       </c>
@@ -1287,15 +1458,22 @@
           <t>aerospace propulsion, propulsion</t>
         </is>
       </c>
-      <c r="H17" s="2" t="b">
-        <v>1</v>
-      </c>
+      <c r="H17" s="2" t="inlineStr"/>
       <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="3">
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Lee's areas of expertise include energy system analysis, thermal and fluid process characterization, and fuel property measurements for energy systems.</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/attwl", "https://search.asu.edu/profile/attwl")</f>
         <v/>
       </c>
-      <c r="K17" s="3">
+      <c r="N17" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=T.-W.%20Lee%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
@@ -1333,19 +1511,34 @@
           <t>computational physics</t>
         </is>
       </c>
-      <c r="H18" s="2" t="b">
-        <v>1</v>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Quantum simulations Machine learning Quantum computing</t>
+        </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
+          <t>Artificial Photosynthesis, Chemistry, Computational Physics, Machine Learning, Materials Science, Metals, Nanoscience, Semiconductors</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Houlong Zhuang is an associate professor in the School for Engineering of Matter, Transport and Energy at ASU. He received his doctorate in materials science and engineering at Cornell University. Prior to ASU, Dr. Zhuang was a postdoctoral researcher at Princeton University. Dr. Zhuang’s current research interests are quantum mechanical simulations, machine learning, and quantum computing.</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
           <t>4yYKCpUAAAAJ</t>
         </is>
       </c>
-      <c r="J18" s="3">
+      <c r="M18" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/hzhuang7", "https://search.asu.edu/profile/hzhuang7")</f>
         <v/>
       </c>
-      <c r="K18" s="3">
+      <c r="N18" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=4yYKCpUAAAAJ", "Scholar (4yYKCpUAAAAJ)")</f>
         <v/>
       </c>
@@ -1383,19 +1576,34 @@
           <t>computational physics</t>
         </is>
       </c>
-      <c r="H19" s="2" t="b">
-        <v>1</v>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Aerospace Engineering, Computational Physics, Energy, Material Physics, Materials Science, Mechanical Engineering, Modeling and Simulation, Theoretical Solid State Physics</t>
+        </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
+          <t>Aerospace Engineering, Computational Physics, Energy, Material Physics, Materials Science, Mechanical Engineering, Modeling and Simulation, Theoretical Solid State Physics</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Wu’s research focuses on electron, phonon, and magnon transport, exploring nanoscale energy transport and conversion through first-principles approaches, as well as material thermal and electrical transport properties.</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
           <t>8CS4X9IAAAAJ</t>
         </is>
       </c>
-      <c r="J19" s="3">
+      <c r="M19" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/huanwu", "https://search.asu.edu/profile/huanwu")</f>
         <v/>
       </c>
-      <c r="K19" s="3">
+      <c r="N19" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=8CS4X9IAAAAJ", "Scholar (8CS4X9IAAAAJ)")</f>
         <v/>
       </c>
@@ -1433,19 +1641,34 @@
           <t>optimization</t>
         </is>
       </c>
-      <c r="H20" s="2" t="b">
-        <v>1</v>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Synthesis of nanocrystalline materials with tailored microstructures, Mechanics of nanostructured metal and alloy films, MEMS for in situ materials testing, Polymer based micro devices for cell mechanics and biohybrid platforms</t>
+        </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>Thin Film Materials, Materials Science, Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Rajagopalan's research focuses on the mechanics of nanoscale materials, cells and biological systems.</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
           <t>ClqRIhIAAAAJ</t>
         </is>
       </c>
-      <c r="J20" s="3">
+      <c r="M20" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/jrajago1", "https://search.asu.edu/profile/jrajago1")</f>
         <v/>
       </c>
-      <c r="K20" s="3">
+      <c r="N20" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=ClqRIhIAAAAJ", "Scholar (ClqRIhIAAAAJ)")</f>
         <v/>
       </c>
@@ -1483,15 +1706,26 @@
           <t>finite element</t>
         </is>
       </c>
-      <c r="H21" s="2" t="b">
-        <v>1</v>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Development of computational mechanics: finite element methods, molecular dynamics, multiscale methods, failure analysis, and material design.</t>
+        </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="3">
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Oswald develops computational and AI-driven methods for advanced manufacturing, including laser welding, automated inspection, robotics, and computational mechanics.</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/joswald1", "https://search.asu.edu/profile/joswald1")</f>
         <v/>
       </c>
-      <c r="K21" s="3">
+      <c r="N21" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Jay%20Oswald%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
@@ -1529,19 +1763,34 @@
           <t>optimization</t>
         </is>
       </c>
-      <c r="H22" s="2" t="b">
-        <v>1</v>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Distributed multi-agent motion planning and control, Provably safe control design using machine learning-based certificates, Foundation models in complex robotic tasks, Failure prediction from limited demonstrations, Human-robot interaction.</t>
+        </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>Control Systems, Dynamical Systems, Machine Learning, Nonlinear Dynamical Systems, Robotics</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Garg's research interests include control synthesis for multi-agent coordination using control theory and machine learning.</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
           <t>vs3pl-8AAAAJ</t>
         </is>
       </c>
-      <c r="J22" s="3">
+      <c r="M22" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/kgarg24", "https://search.asu.edu/profile/kgarg24")</f>
         <v/>
       </c>
-      <c r="K22" s="3">
+      <c r="N22" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=vs3pl-8AAAAJ", "Scholar (vs3pl-8AAAAJ)")</f>
         <v/>
       </c>
@@ -1579,15 +1828,26 @@
           <t>heat transfer</t>
         </is>
       </c>
-      <c r="H23" s="2" t="b">
-        <v>1</v>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Nanoscale heat transfer, metamaterials, plasmonics, and nanophotonics with an emphasis on solar thermal energy harvesting using plasmonic-enhanced light trapping for photovolatics, as well as near-field enhancement and spectral control of radiation for thermophotovoltaic energy conversion. Other research interests involve electronic cooling, MEMS, and bio-sensing.</t>
+        </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="3">
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Wang research interests include selective control of thermal emission/absorption using meta-materials for energy harvesting and near-field radiation heat transfer enhancement between meta-materials for thermophotovoltaics.</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/lwang78", "https://search.asu.edu/profile/lwang78")</f>
         <v/>
       </c>
-      <c r="K23" s="3">
+      <c r="N23" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Liping%20Wang%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
@@ -1625,15 +1885,30 @@
           <t>optimization</t>
         </is>
       </c>
-      <c r="H24" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="3">
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>The intersection of computer science and control including convex optimization, artificial intelligence, and manipulation of delayed and PDE systems. The understanding and regulation of complex dynamical systems such as the motion of plasma in nuclear fusion reactors, autoregulation in the human immune response, and the motion of spacecraft in orbit.</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Control Systems, Dynamical Systems Theory, Aerospace Engineering, Algorithm Development, Dynamical Systems, Nonlinear Dynamical Systems, Mathematical and System Dynamics Modeling, Immunology</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Peet's current research interests are in the role of computation as it is applied to the understanding and control of complex and large-scale systems.</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/mpeet", "https://search.asu.edu/profile/mpeet")</f>
         <v/>
       </c>
-      <c r="K24" s="3">
+      <c r="N24" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Matthew%20Peet%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
@@ -1671,19 +1946,30 @@
           <t>instability</t>
         </is>
       </c>
-      <c r="H25" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Metal additive manufacturing, in-situ synchrotron X-ray and neutron characterization, non-equilibrium phase transformation, metal matrix composites. Selected Publications M. Qu , J. Yuan, Q. Guo, A. Nabaa, L. I. Escano, J. Huang, Q. Li, L. Chen. Achieving uniformly refined grain structure in metal additive manufacturing: Experimental demonstration and analytical model development. Additive Manufacturing 108 (2025) 104805. M. Qu , D. Yu, J. Yuan, L. Chen, K. An, Y. Chen. Multi-stage load partitioning in additively manufactured Al6061+TiC nanocomposite characterized by in-situ neutron diffraction. Additive Manufacturing, 96 (2024) 104584. M. Qu , J. Yuan, A. Nabaa, J. Huang, C. A. Chuang, L. Chen. Melting and solidification dynamics during laser additive manufacturing of reaction-based metal matrix composites uncovered by in-situ synchrotron X-ray diffraction. Acta Materialia , 271 (2024) 119875. M. Qu , Q. Guo, L. I. Escano, A. Nabaa, S. M. H. Hojjatzadeh, Z. A. Young, L. Chen. Controlling process instability for defect lean metal additive manufacturing. Nature Communications , 13 (2022) 1079. M. Qu , Q. Guo, L. I. Escano, A. Nabaa, K. Fezzaa, L. Chen. Nanoparticle-enabled increase of energy efficiency during laser metal additive manufacturing. Additive Manufacturing , 60 (2022) 103242. M. Qu , Q.Guo, L. I. Escano, J. Yuan, S. J. Clark, K. Fezzaa, L. Chen. Controlling melt flow by nanoparticles to eliminate surface wave induced surface fluctuation. Additive Manufacturing , 59 (2022) 103081.</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Minglei Qu is an Assistant Professor of Mechanical Engineering and a graduate faculty of Materials Science and Engineering in the School for Engineering of Matter, Transport and Energy at ASU. His research lies at the intersection of metal additive manufacturing, in-situ characterization, and materials science. By utilizing advanced in-situ characterization tools, including synchrotron X-ray im...</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>9LWNC50AAAAJ</t>
         </is>
       </c>
-      <c r="J25" s="3">
+      <c r="M25" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/mingleiq", "https://search.asu.edu/profile/mingleiq")</f>
         <v/>
       </c>
-      <c r="K25" s="3">
+      <c r="N25" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=9LWNC50AAAAJ", "Scholar (9LWNC50AAAAJ)")</f>
         <v/>
       </c>
@@ -1721,19 +2007,34 @@
           <t>heat transfer</t>
         </is>
       </c>
-      <c r="H26" s="2" t="b">
-        <v>1</v>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>My research group is an interdisciplinary nanoengineering team that focuses on manipulating material properties for thermal energy applications. Some of our focus areas are thermoelectric power generation, thermal storage media, heat transfer, and phonon optics. To achieve our objectives, we custom-design materials using colloidal nanoparticles, chemical precursors, and nanocomposites.</t>
+        </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
+          <t>Mechanical Engineering, Energy, Renewable Energy, Energy and Sustainability, Clean Energy, Energy Efficiency Technologies, Materials Science and Engineering, Chemical Engineering, Nanoengineering, Nanoscience, Nanotechnology, Solid State Physics, Thin Film Materials, Semiconductors, Chemistry, Physics</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Wang's research interests include thermal energy conversion, storage, and transport in nanostructured materials; thermoelectric power generation; thermal storage media; heat transfer, and phonon optics</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
           <t>LaUdx9gAAAAJ</t>
         </is>
       </c>
-      <c r="J26" s="3">
+      <c r="M26" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/rywang", "https://search.asu.edu/profile/rywang")</f>
         <v/>
       </c>
-      <c r="K26" s="3">
+      <c r="N26" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=LaUdx9gAAAAJ", "Scholar (LaUdx9gAAAAJ)")</f>
         <v/>
       </c>
@@ -1771,15 +2072,22 @@
           <t>fluid dynamics</t>
         </is>
       </c>
-      <c r="H27" s="2" t="b">
-        <v>1</v>
-      </c>
+      <c r="H27" s="2" t="inlineStr"/>
       <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="3">
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>Calhoun’s research interests are in fluid dynamics; atmospheric sciences; boundary layer; wind energy and remote sensing.</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/rcalhou", "https://search.asu.edu/profile/rcalhou")</f>
         <v/>
       </c>
-      <c r="K27" s="3">
+      <c r="N27" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ronald%20Calhoun%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
@@ -1817,19 +2125,34 @@
           <t>optimization</t>
         </is>
       </c>
-      <c r="H28" s="2" t="b">
-        <v>1</v>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Modeling, analysis, control, and optimization of multi-robot systems including robotic swarms; analysis of collective behaviors in biology and biologically-inspired control of distributed systems</t>
+        </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
+          <t>Systems and Control Theory, Mechanical Engineering, Autonomous Technologies, Robotics</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Berman directs the Autonomous Collective Systems Laboratory at ASU, which models and analyzes behaviors in biological and engineered collectives and designs control strategies for multi-robot systems.</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
           <t>KKup0OgAAAAJ</t>
         </is>
       </c>
-      <c r="J28" s="3">
+      <c r="M28" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/smberma2", "https://search.asu.edu/profile/smberma2")</f>
         <v/>
       </c>
-      <c r="K28" s="3">
+      <c r="N28" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=KKup0OgAAAAJ", "Scholar (KKup0OgAAAAJ)")</f>
         <v/>
       </c>
@@ -1867,20 +2190,23 @@
           <t>heat transfer</t>
         </is>
       </c>
-      <c r="H29" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>OmBV67MAAAAJ</t>
-        </is>
-      </c>
-      <c r="J29" s="3">
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>Yang studies heat transfer, thermal management of electronics, and biomedical devices. She has published multiple research papers in major scientific journals.</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/tyang123", "https://search.asu.edu/profile/tyang123")</f>
         <v/>
       </c>
-      <c r="K29" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=OmBV67MAAAAJ", "Scholar (OmBV67MAAAAJ)")</f>
+      <c r="N29" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Tianyu%20Yang%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
     </row>
@@ -1917,15 +2243,22 @@
           <t>optimization</t>
         </is>
       </c>
-      <c r="H30" s="2" t="b">
-        <v>1</v>
-      </c>
+      <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="3">
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>Ren’s current research interests include optimization, product/configuration design, human-computer interaction and machine learning.</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/yren32", "https://search.asu.edu/profile/yren32")</f>
         <v/>
       </c>
-      <c r="K30" s="3">
+      <c r="N30" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Yi%20Ren%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
@@ -1963,15 +2296,26 @@
           <t>uncertainty quantification</t>
         </is>
       </c>
-      <c r="H31" s="2" t="b">
-        <v>1</v>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Yongming Liu is a professor of aerospace and mechanical engineering with the School for Engineering of Matter, Transport and Energy at Arizona State University. Fatigue and fracture of engineering materials and structures, probabilistic computational mechanics, risk assessment and management, multi-physics damage modeling and structural durability, multi-scale uncertainty quantification and propagation, imaging-based experimental testing, diagnostics and prognostics</t>
+        </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="3">
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>Liu heads the Prognostic Analysis and Reliability Assessment Laboratory (PARA). He joined ASU in 2012.</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/yliu35", "https://search.asu.edu/profile/yliu35")</f>
         <v/>
       </c>
-      <c r="K31" s="3">
+      <c r="N31" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Yongming%20Liu%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
@@ -1979,95 +2323,95 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N7" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N8" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N11" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N12" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId63"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId69"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId75"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N28" r:id="rId81"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId87"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="rId90"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2079,7 +2423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K54"/>
+  <dimension ref="A1:N54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2089,10 +2433,13 @@
     <col width="49" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="49" customWidth="1" min="10" max="10"/>
-    <col width="32" customWidth="1" min="11" max="11"/>
+    <col width="65" customWidth="1" min="8" max="8"/>
+    <col width="65" customWidth="1" min="9" max="9"/>
+    <col width="65" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="49" customWidth="1" min="13" max="13"/>
+    <col width="32" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2133,20 +2480,35 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Research Interests</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Expertise Areas</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Research / Bio Summary</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Is Field Match</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Scholar ID</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Profile URL</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Google Scholar URL</t>
         </is>
@@ -2155,12 +2517,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Werner Dahm</t>
+          <t>Jeonglae Kim</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUM/WTR Faculty Research</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -2174,7 +2536,7 @@
         </is>
       </c>
       <c r="E2" s="3">
-        <f>HYPERLINK("mailto:Werner.Dahm@asu.edu", "Werner.Dahm@asu.edu")</f>
+        <f>HYPERLINK("mailto:jeokim@asu.edu", "jeokim@asu.edu")</f>
         <v/>
       </c>
       <c r="F2" s="2" t="n">
@@ -2182,31 +2544,38 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>combustion, computational physics, fluid dynamics, heat transfer, propulsion, turbulence</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="b">
-        <v>1</v>
-      </c>
+          <t>aeroacoustics, flow control, high-performance computing, optimization, turbulence, turbulent flows</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/wdahm", "https://search.asu.edu/profile/wdahm")</f>
-        <v/>
-      </c>
-      <c r="K2" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Werner%20Dahm%20Arizona%20State%20University", "Google Scholar Search")</f>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Kim's research interests include large-eddy simulation of high-speed turbulent flows with multi-physics, aeroacoustics, flow control and optimization.</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/jkim520", "https://search.asu.edu/profile/jkim520")</f>
+        <v/>
+      </c>
+      <c r="N2" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Jeonglae%20Kim%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Jeonglae Kim</t>
+          <t>Werner Dahm</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>SUM/WTR Faculty Research</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -2220,27 +2589,42 @@
         </is>
       </c>
       <c r="E3" s="3">
-        <f>HYPERLINK("mailto:jeokim@asu.edu", "jeokim@asu.edu")</f>
+        <f>HYPERLINK("mailto:Werner.Dahm@asu.edu", "Werner.Dahm@asu.edu")</f>
         <v/>
       </c>
       <c r="F3" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>aeroacoustics, flow control, optimization, turbulence, turbulent flows</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/jkim520", "https://search.asu.edu/profile/jkim520")</f>
-        <v/>
-      </c>
-      <c r="K3" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Jeonglae%20Kim%20Arizona%20State%20University", "Google Scholar Search")</f>
+          <t>combustion, computational physics, fluid dynamics, heat transfer, propulsion, turbulence</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Dahm specializes in fluid dynamics, thermodynamics, combustion, heat transfer, thermal sciences, propulsion, fuel efficiency, emissions, powertrains, and other areas relevant to a broad range of automotive, aerospace, and industrial applications. He is an author of over 200 refereed technical articles, conference papers, and technical publications, a holder of six U.S. and international patents, and has given over 260 technical presentations, including over 190 invited, plenary, and keynote lectures worldwide, on topics dealing with mechanical and aerospace engineering and defense science.</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Aerospace Engineering, Applied Research, Computational Modeling, Computational Physics, Mechanical Engineering, Propulsion</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Werner J.A. Dahm has since 2010 been the ASU Foundation Professor of Mechanical and Aerospace Engineering, and also Professor Emeritus of Engineering at the University of Michigan where served for the previous 25 years.</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/wdahm", "https://search.asu.edu/profile/wdahm")</f>
+        <v/>
+      </c>
+      <c r="N3" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Werner%20Dahm%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
     </row>
@@ -2277,19 +2661,26 @@
           <t>computational fluid dynamics, drag reduction, fluid dynamics, fluid mechanics, multiphase flow</t>
         </is>
       </c>
-      <c r="H4" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Chen’s research interests include multiphase flows, drag reduction, airplane de-icing, interfacial instabilities and flow in porous media.</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>xT-lX9sAAAAJ</t>
         </is>
       </c>
-      <c r="J4" s="3">
+      <c r="M4" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/asuchen", "https://search.asu.edu/profile/asuchen")</f>
         <v/>
       </c>
-      <c r="K4" s="3">
+      <c r="N4" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=xT-lX9sAAAAJ", "Scholar (xT-lX9sAAAAJ)")</f>
         <v/>
       </c>
@@ -2327,19 +2718,30 @@
           <t>aerodynamics, flow control, fluid dynamics, turbulence, vortex dynamics</t>
         </is>
       </c>
-      <c r="H5" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Unsteady aerodynamics, vortex dynamics, flow control, turbulence, separated flows</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Ramesh's expertise is in unsteady fluid dynamics, vortex dynamics, turbulence and flow control.</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>DKc-AgcAAAAJ</t>
         </is>
       </c>
-      <c r="J5" s="3">
+      <c r="M5" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/kramesh2", "https://search.asu.edu/profile/kramesh2")</f>
         <v/>
       </c>
-      <c r="K5" s="3">
+      <c r="N5" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=DKc-AgcAAAAJ", "Scholar (DKc-AgcAAAAJ)")</f>
         <v/>
       </c>
@@ -2377,15 +2779,22 @@
           <t>cfd, computational fluid dynamics, dns, fluid dynamics, multiphase flow</t>
         </is>
       </c>
-      <c r="H6" s="2" t="b">
-        <v>1</v>
-      </c>
+      <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="3">
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Kasbaoui's research interests include computational fluid dynamics, numerical methods, and massively parallel simulations of multiphase and particle-laden flows for environmental and aerospace applications.</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/mkasbaou", "https://search.asu.edu/profile/mkasbaou")</f>
         <v/>
       </c>
-      <c r="K6" s="3">
+      <c r="N6" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Mohamed%20Houssem%20Kasbaoui%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
@@ -2423,19 +2832,26 @@
           <t>inverse problems, multiscale modeling, optimization, transition</t>
         </is>
       </c>
-      <c r="H7" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Chattopadhyay is the director of Adaptive Intelligent Materials and Systems (AIMS) Center at ASU. Her research focuses on structural health monitoring and damage prognosis, and multidisciplinary design optimization.</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>w3fU9E0AAAAJ</t>
         </is>
       </c>
-      <c r="J7" s="3">
+      <c r="M7" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/chattopa", "https://search.asu.edu/profile/chattopa")</f>
         <v/>
       </c>
-      <c r="K7" s="3">
+      <c r="N7" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=w3fU9E0AAAAJ", "Scholar (w3fU9E0AAAAJ)")</f>
         <v/>
       </c>
@@ -2473,15 +2889,30 @@
           <t>aerodynamics, reacting flows, turbulence, turbulent mixing</t>
         </is>
       </c>
-      <c r="H8" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="3">
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Aerodynamics, Aerospace Engineering, Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Aerodynamics, Aerospace Engineering, Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Pathikonda studies turbulent fluid flows to understand natural and engineering phenomena using lab experiments. His expertise is in complex (reacting) mixing, high Re-flows, laser-based &amp; spectroscopic techniques, etc.</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/gpathiko", "https://search.asu.edu/profile/gpathiko")</f>
         <v/>
       </c>
-      <c r="K8" s="3">
+      <c r="N8" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Gokul%20Pathikonda%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
@@ -2519,19 +2950,26 @@
           <t>fluid mechanics, multiphase flow, numerical simulation, turbulence</t>
         </is>
       </c>
-      <c r="H9" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Herrmann's research interests include fluid mechanics, modeling and numerical simulation of multiphase flows with a focus on turbulent atomization processes, and numerical methods for discontinuous interfaces.</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>yv6aCW8AAAAJ</t>
         </is>
       </c>
-      <c r="J9" s="3">
+      <c r="M9" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/mherrma1", "https://search.asu.edu/profile/mherrma1")</f>
         <v/>
       </c>
-      <c r="K9" s="3">
+      <c r="N9" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=yv6aCW8AAAAJ", "Scholar (yv6aCW8AAAAJ)")</f>
         <v/>
       </c>
@@ -2569,19 +3007,34 @@
           <t>applied mathematics, fluid mechanics, turbulent mixing</t>
         </is>
       </c>
-      <c r="H10" s="2" t="b">
-        <v>1</v>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Modeling and Simulation, Oceanography, Earth Systems and Climate Science, Modeling, Modeling, Simulation and Cyberinfrastructure, Applied Mathematics</t>
+        </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>Modeling and Simulation, Oceanography, Earth Systems and Climate Science, Modeling, Modeling, Simulation and Cyberinfrastructure, Applied Mathematics</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Scotti's main focus is theoretical, experimental and computational aspects of environmental fluid mechanics.</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>HRx2lJQAAAAJ</t>
         </is>
       </c>
-      <c r="J10" s="3">
+      <c r="M10" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/adscotti", "https://search.asu.edu/profile/adscotti")</f>
         <v/>
       </c>
-      <c r="K10" s="3">
+      <c r="N10" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=HRx2lJQAAAAJ", "Scholar (HRx2lJQAAAAJ)")</f>
         <v/>
       </c>
@@ -2619,19 +3072,30 @@
           <t>data-driven modeling, heat transfer, transport phenomena</t>
         </is>
       </c>
-      <c r="H11" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Transport phenomena in heat transfer systems Additive manufacturing Data-driven modeling and design</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Kwon aims to improve the energy conversion and transport systems through the fundamental insights into transport physics, and by exploiting additive manufacturing and data-driven approaches.</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>fs2d97sAAAAJ</t>
         </is>
       </c>
-      <c r="J11" s="3">
+      <c r="M11" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/bkwon2", "https://search.asu.edu/profile/bkwon2")</f>
         <v/>
       </c>
-      <c r="K11" s="3">
+      <c r="N11" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=fs2d97sAAAAJ", "Scholar (fs2d97sAAAAJ)")</f>
         <v/>
       </c>
@@ -2669,19 +3133,34 @@
           <t>aerodynamics, fluid-structure interaction, physics-informed machine learning</t>
         </is>
       </c>
-      <c r="H12" s="2" t="b">
-        <v>1</v>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Aerodynamics, Dynamical Systems, Machine Learning, Mechanics of Composite Materials</t>
+        </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
+          <t>Aerodynamics, Dynamical Systems, Machine Learning, Mechanics of Composite Materials</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Leixin Ma's career goal is a data-driven and physically consistent approach to modeling and designing programmable smart structures and robots, especially under complex fluid flow conditions.</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
           <t>2xQTOc0AAAAJ</t>
         </is>
       </c>
-      <c r="J12" s="3">
+      <c r="M12" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/leixinma", "https://search.asu.edu/profile/leixinma")</f>
         <v/>
       </c>
-      <c r="K12" s="3">
+      <c r="N12" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=2xQTOc0AAAAJ", "Scholar (2xQTOc0AAAAJ)")</f>
         <v/>
       </c>
@@ -2719,19 +3198,26 @@
           <t>fluid mechanics, high-performance computing, turbulence</t>
         </is>
       </c>
-      <c r="H13" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Yulia Peet is an associate professor of aerospace and mechanical engineering in the School for Engineering of Matter, Transport and Energy with the Ira A. Fulton Schools of Engineering at Arizona State University. Her Ph.D. degree is in Aeronautics and Astronautics from Stanford (2006), M.S. and B.S. degrees are from Moscow Institute of Physics and Technology (1999 and 1997). Her previous appoi...</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>_6o8MrUAAAAJ</t>
         </is>
       </c>
-      <c r="J13" s="3">
+      <c r="M13" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/ypeet", "https://search.asu.edu/profile/ypeet")</f>
         <v/>
       </c>
-      <c r="K13" s="3">
+      <c r="N13" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=_6o8MrUAAAAJ", "Scholar (_6o8MrUAAAAJ)")</f>
         <v/>
       </c>
@@ -2769,15 +3255,22 @@
           <t>fluid dynamics, numerical simulation</t>
         </is>
       </c>
-      <c r="H14" s="2" t="b">
-        <v>1</v>
-      </c>
+      <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="3">
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Huang's research interests are geophysical and environmental fluid dynamics, numerical simulation of atmospheric and oceanic flows, Earth system remote sensing, and climate change.</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/hhuang38", "https://search.asu.edu/profile/hhuang38")</f>
         <v/>
       </c>
-      <c r="K14" s="3">
+      <c r="N14" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Huei-Ping%20Huang%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
@@ -2815,15 +3308,22 @@
           <t>optimization, reduced-order modeling</t>
         </is>
       </c>
-      <c r="H15" s="2" t="b">
-        <v>1</v>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Structural Dynamics, Rotordynamics, Vibration Analysis, Reduced-Order Modeling, Optimization</t>
+        </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="3">
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/rnmurthy", "https://search.asu.edu/profile/rnmurthy")</f>
         <v/>
       </c>
-      <c r="K15" s="3">
+      <c r="N15" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Raghavendra%20Murthy%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
@@ -2861,19 +3361,34 @@
           <t>combustion, transition</t>
         </is>
       </c>
-      <c r="H16" s="2" t="b">
-        <v>1</v>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Energy management and efficiency, energy transition, energy storage, solid oxide fuel cells, partial oxidation, cogeneration, combustion, and synthesis of hydrogen</t>
+        </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>Ceramics, Electrochemistry, Energy, Energy and Sustainability, Energy Conservation, Energy Economics, Energy Efficiency Technologies, Thin Film Materials</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Milcarek's current research focuses on energy management and efficiency, energy system modeling, energy transition, energy storage, solid oxide fuel cells fabrication and testing, partial oxidation and synthesis of hydrogen.</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>m-Pb6g2pm2UC</t>
         </is>
       </c>
-      <c r="J16" s="3">
+      <c r="M16" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/rjmilcar", "https://search.asu.edu/profile/rjmilcar")</f>
         <v/>
       </c>
-      <c r="K16" s="3">
+      <c r="N16" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=m-Pb6g2pm2UC", "Scholar (m-Pb6g2pm2UC)")</f>
         <v/>
       </c>
@@ -2911,15 +3426,22 @@
           <t>aerospace propulsion, propulsion</t>
         </is>
       </c>
-      <c r="H17" s="2" t="b">
-        <v>1</v>
-      </c>
+      <c r="H17" s="2" t="inlineStr"/>
       <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="3">
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Lee's areas of expertise include energy system analysis, thermal and fluid process characterization, and fuel property measurements for energy systems.</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/attwl", "https://search.asu.edu/profile/attwl")</f>
         <v/>
       </c>
-      <c r="K17" s="3">
+      <c r="N17" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=T.-W.%20Lee%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
@@ -2957,19 +3479,34 @@
           <t>computational physics</t>
         </is>
       </c>
-      <c r="H18" s="2" t="b">
-        <v>1</v>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Quantum simulations Machine learning Quantum computing</t>
+        </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
+          <t>Artificial Photosynthesis, Chemistry, Computational Physics, Machine Learning, Materials Science, Metals, Nanoscience, Semiconductors</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Houlong Zhuang is an associate professor in the School for Engineering of Matter, Transport and Energy at ASU. He received his doctorate in materials science and engineering at Cornell University. Prior to ASU, Dr. Zhuang was a postdoctoral researcher at Princeton University. Dr. Zhuang’s current research interests are quantum mechanical simulations, machine learning, and quantum computing.</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
           <t>4yYKCpUAAAAJ</t>
         </is>
       </c>
-      <c r="J18" s="3">
+      <c r="M18" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/hzhuang7", "https://search.asu.edu/profile/hzhuang7")</f>
         <v/>
       </c>
-      <c r="K18" s="3">
+      <c r="N18" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=4yYKCpUAAAAJ", "Scholar (4yYKCpUAAAAJ)")</f>
         <v/>
       </c>
@@ -3007,19 +3544,34 @@
           <t>computational physics</t>
         </is>
       </c>
-      <c r="H19" s="2" t="b">
-        <v>1</v>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Aerospace Engineering, Computational Physics, Energy, Material Physics, Materials Science, Mechanical Engineering, Modeling and Simulation, Theoretical Solid State Physics</t>
+        </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
+          <t>Aerospace Engineering, Computational Physics, Energy, Material Physics, Materials Science, Mechanical Engineering, Modeling and Simulation, Theoretical Solid State Physics</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Wu’s research focuses on electron, phonon, and magnon transport, exploring nanoscale energy transport and conversion through first-principles approaches, as well as material thermal and electrical transport properties.</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
           <t>8CS4X9IAAAAJ</t>
         </is>
       </c>
-      <c r="J19" s="3">
+      <c r="M19" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/huanwu", "https://search.asu.edu/profile/huanwu")</f>
         <v/>
       </c>
-      <c r="K19" s="3">
+      <c r="N19" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=8CS4X9IAAAAJ", "Scholar (8CS4X9IAAAAJ)")</f>
         <v/>
       </c>
@@ -3057,19 +3609,34 @@
           <t>optimization</t>
         </is>
       </c>
-      <c r="H20" s="2" t="b">
-        <v>1</v>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Synthesis of nanocrystalline materials with tailored microstructures, Mechanics of nanostructured metal and alloy films, MEMS for in situ materials testing, Polymer based micro devices for cell mechanics and biohybrid platforms</t>
+        </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>Thin Film Materials, Materials Science, Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Rajagopalan's research focuses on the mechanics of nanoscale materials, cells and biological systems.</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
           <t>ClqRIhIAAAAJ</t>
         </is>
       </c>
-      <c r="J20" s="3">
+      <c r="M20" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/jrajago1", "https://search.asu.edu/profile/jrajago1")</f>
         <v/>
       </c>
-      <c r="K20" s="3">
+      <c r="N20" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=ClqRIhIAAAAJ", "Scholar (ClqRIhIAAAAJ)")</f>
         <v/>
       </c>
@@ -3107,15 +3674,26 @@
           <t>finite element</t>
         </is>
       </c>
-      <c r="H21" s="2" t="b">
-        <v>1</v>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Development of computational mechanics: finite element methods, molecular dynamics, multiscale methods, failure analysis, and material design.</t>
+        </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="3">
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Oswald develops computational and AI-driven methods for advanced manufacturing, including laser welding, automated inspection, robotics, and computational mechanics.</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/joswald1", "https://search.asu.edu/profile/joswald1")</f>
         <v/>
       </c>
-      <c r="K21" s="3">
+      <c r="N21" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Jay%20Oswald%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
@@ -3153,19 +3731,34 @@
           <t>optimization</t>
         </is>
       </c>
-      <c r="H22" s="2" t="b">
-        <v>1</v>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Distributed multi-agent motion planning and control, Provably safe control design using machine learning-based certificates, Foundation models in complex robotic tasks, Failure prediction from limited demonstrations, Human-robot interaction.</t>
+        </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>Control Systems, Dynamical Systems, Machine Learning, Nonlinear Dynamical Systems, Robotics</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Garg's research interests include control synthesis for multi-agent coordination using control theory and machine learning.</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
           <t>vs3pl-8AAAAJ</t>
         </is>
       </c>
-      <c r="J22" s="3">
+      <c r="M22" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/kgarg24", "https://search.asu.edu/profile/kgarg24")</f>
         <v/>
       </c>
-      <c r="K22" s="3">
+      <c r="N22" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=vs3pl-8AAAAJ", "Scholar (vs3pl-8AAAAJ)")</f>
         <v/>
       </c>
@@ -3203,15 +3796,26 @@
           <t>heat transfer</t>
         </is>
       </c>
-      <c r="H23" s="2" t="b">
-        <v>1</v>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Nanoscale heat transfer, metamaterials, plasmonics, and nanophotonics with an emphasis on solar thermal energy harvesting using plasmonic-enhanced light trapping for photovolatics, as well as near-field enhancement and spectral control of radiation for thermophotovoltaic energy conversion. Other research interests involve electronic cooling, MEMS, and bio-sensing.</t>
+        </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="3">
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Wang research interests include selective control of thermal emission/absorption using meta-materials for energy harvesting and near-field radiation heat transfer enhancement between meta-materials for thermophotovoltaics.</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/lwang78", "https://search.asu.edu/profile/lwang78")</f>
         <v/>
       </c>
-      <c r="K23" s="3">
+      <c r="N23" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Liping%20Wang%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
@@ -3249,15 +3853,30 @@
           <t>optimization</t>
         </is>
       </c>
-      <c r="H24" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="3">
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>The intersection of computer science and control including convex optimization, artificial intelligence, and manipulation of delayed and PDE systems. The understanding and regulation of complex dynamical systems such as the motion of plasma in nuclear fusion reactors, autoregulation in the human immune response, and the motion of spacecraft in orbit.</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Control Systems, Dynamical Systems Theory, Aerospace Engineering, Algorithm Development, Dynamical Systems, Nonlinear Dynamical Systems, Mathematical and System Dynamics Modeling, Immunology</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Peet's current research interests are in the role of computation as it is applied to the understanding and control of complex and large-scale systems.</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/mpeet", "https://search.asu.edu/profile/mpeet")</f>
         <v/>
       </c>
-      <c r="K24" s="3">
+      <c r="N24" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Matthew%20Peet%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
@@ -3295,19 +3914,30 @@
           <t>instability</t>
         </is>
       </c>
-      <c r="H25" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Metal additive manufacturing, in-situ synchrotron X-ray and neutron characterization, non-equilibrium phase transformation, metal matrix composites. Selected Publications M. Qu , J. Yuan, Q. Guo, A. Nabaa, L. I. Escano, J. Huang, Q. Li, L. Chen. Achieving uniformly refined grain structure in metal additive manufacturing: Experimental demonstration and analytical model development. Additive Manufacturing 108 (2025) 104805. M. Qu , D. Yu, J. Yuan, L. Chen, K. An, Y. Chen. Multi-stage load partitioning in additively manufactured Al6061+TiC nanocomposite characterized by in-situ neutron diffraction. Additive Manufacturing, 96 (2024) 104584. M. Qu , J. Yuan, A. Nabaa, J. Huang, C. A. Chuang, L. Chen. Melting and solidification dynamics during laser additive manufacturing of reaction-based metal matrix composites uncovered by in-situ synchrotron X-ray diffraction. Acta Materialia , 271 (2024) 119875. M. Qu , Q. Guo, L. I. Escano, A. Nabaa, S. M. H. Hojjatzadeh, Z. A. Young, L. Chen. Controlling process instability for defect lean metal additive manufacturing. Nature Communications , 13 (2022) 1079. M. Qu , Q. Guo, L. I. Escano, A. Nabaa, K. Fezzaa, L. Chen. Nanoparticle-enabled increase of energy efficiency during laser metal additive manufacturing. Additive Manufacturing , 60 (2022) 103242. M. Qu , Q.Guo, L. I. Escano, J. Yuan, S. J. Clark, K. Fezzaa, L. Chen. Controlling melt flow by nanoparticles to eliminate surface wave induced surface fluctuation. Additive Manufacturing , 59 (2022) 103081.</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Minglei Qu is an Assistant Professor of Mechanical Engineering and a graduate faculty of Materials Science and Engineering in the School for Engineering of Matter, Transport and Energy at ASU. His research lies at the intersection of metal additive manufacturing, in-situ characterization, and materials science. By utilizing advanced in-situ characterization tools, including synchrotron X-ray im...</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>9LWNC50AAAAJ</t>
         </is>
       </c>
-      <c r="J25" s="3">
+      <c r="M25" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/mingleiq", "https://search.asu.edu/profile/mingleiq")</f>
         <v/>
       </c>
-      <c r="K25" s="3">
+      <c r="N25" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=9LWNC50AAAAJ", "Scholar (9LWNC50AAAAJ)")</f>
         <v/>
       </c>
@@ -3345,19 +3975,34 @@
           <t>heat transfer</t>
         </is>
       </c>
-      <c r="H26" s="2" t="b">
-        <v>1</v>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>My research group is an interdisciplinary nanoengineering team that focuses on manipulating material properties for thermal energy applications. Some of our focus areas are thermoelectric power generation, thermal storage media, heat transfer, and phonon optics. To achieve our objectives, we custom-design materials using colloidal nanoparticles, chemical precursors, and nanocomposites.</t>
+        </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
+          <t>Mechanical Engineering, Energy, Renewable Energy, Energy and Sustainability, Clean Energy, Energy Efficiency Technologies, Materials Science and Engineering, Chemical Engineering, Nanoengineering, Nanoscience, Nanotechnology, Solid State Physics, Thin Film Materials, Semiconductors, Chemistry, Physics</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Wang's research interests include thermal energy conversion, storage, and transport in nanostructured materials; thermoelectric power generation; thermal storage media; heat transfer, and phonon optics</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
           <t>LaUdx9gAAAAJ</t>
         </is>
       </c>
-      <c r="J26" s="3">
+      <c r="M26" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/rywang", "https://search.asu.edu/profile/rywang")</f>
         <v/>
       </c>
-      <c r="K26" s="3">
+      <c r="N26" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=LaUdx9gAAAAJ", "Scholar (LaUdx9gAAAAJ)")</f>
         <v/>
       </c>
@@ -3395,15 +4040,22 @@
           <t>fluid dynamics</t>
         </is>
       </c>
-      <c r="H27" s="2" t="b">
-        <v>1</v>
-      </c>
+      <c r="H27" s="2" t="inlineStr"/>
       <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="3">
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>Calhoun’s research interests are in fluid dynamics; atmospheric sciences; boundary layer; wind energy and remote sensing.</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/rcalhou", "https://search.asu.edu/profile/rcalhou")</f>
         <v/>
       </c>
-      <c r="K27" s="3">
+      <c r="N27" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ronald%20Calhoun%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
@@ -3441,19 +4093,34 @@
           <t>optimization</t>
         </is>
       </c>
-      <c r="H28" s="2" t="b">
-        <v>1</v>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Modeling, analysis, control, and optimization of multi-robot systems including robotic swarms; analysis of collective behaviors in biology and biologically-inspired control of distributed systems</t>
+        </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
+          <t>Systems and Control Theory, Mechanical Engineering, Autonomous Technologies, Robotics</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Berman directs the Autonomous Collective Systems Laboratory at ASU, which models and analyzes behaviors in biological and engineered collectives and designs control strategies for multi-robot systems.</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
           <t>KKup0OgAAAAJ</t>
         </is>
       </c>
-      <c r="J28" s="3">
+      <c r="M28" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/smberma2", "https://search.asu.edu/profile/smberma2")</f>
         <v/>
       </c>
-      <c r="K28" s="3">
+      <c r="N28" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=KKup0OgAAAAJ", "Scholar (KKup0OgAAAAJ)")</f>
         <v/>
       </c>
@@ -3491,20 +4158,23 @@
           <t>heat transfer</t>
         </is>
       </c>
-      <c r="H29" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>OmBV67MAAAAJ</t>
-        </is>
-      </c>
-      <c r="J29" s="3">
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>Yang studies heat transfer, thermal management of electronics, and biomedical devices. She has published multiple research papers in major scientific journals.</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/tyang123", "https://search.asu.edu/profile/tyang123")</f>
         <v/>
       </c>
-      <c r="K29" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=OmBV67MAAAAJ", "Scholar (OmBV67MAAAAJ)")</f>
+      <c r="N29" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Tianyu%20Yang%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
     </row>
@@ -3541,15 +4211,22 @@
           <t>optimization</t>
         </is>
       </c>
-      <c r="H30" s="2" t="b">
-        <v>1</v>
-      </c>
+      <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="3">
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>Ren’s current research interests include optimization, product/configuration design, human-computer interaction and machine learning.</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/yren32", "https://search.asu.edu/profile/yren32")</f>
         <v/>
       </c>
-      <c r="K30" s="3">
+      <c r="N30" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Yi%20Ren%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
@@ -3587,15 +4264,26 @@
           <t>uncertainty quantification</t>
         </is>
       </c>
-      <c r="H31" s="2" t="b">
-        <v>1</v>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Yongming Liu is a professor of aerospace and mechanical engineering with the School for Engineering of Matter, Transport and Energy at Arizona State University. Fatigue and fracture of engineering materials and structures, probabilistic computational mechanics, risk assessment and management, multi-physics damage modeling and structural durability, multi-scale uncertainty quantification and propagation, imaging-based experimental testing, diagnostics and prognostics</t>
+        </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="3">
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>Liu heads the Prognostic Analysis and Reliability Assessment Laboratory (PARA). He joined ASU in 2012.</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/yliu35", "https://search.asu.edu/profile/yliu35")</f>
         <v/>
       </c>
-      <c r="K31" s="3">
+      <c r="N31" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Yongming%20Liu%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
@@ -3629,15 +4317,18 @@
         <v>0</v>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="b">
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="3">
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/astefan9", "https://search.asu.edu/profile/astefan9")</f>
         <v/>
       </c>
-      <c r="K32" s="3">
+      <c r="N32" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Aikaterini%20Stefanaki%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
@@ -3671,19 +4362,34 @@
         <v>0</v>
       </c>
       <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="b">
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Biomimetic Additive Manufacturing (3D Printing); Bioinspired Material and Structure Design; Stereolithography; Photopolymerization based 3D Printing; Multi-material and Multi-scale 3D printing; Biofabrication; Biomaterial; Ceramic Printing; Nanocomposite Printing; Physical Field Assisted Printing; 4D Printing; Flexible Sensor; Biomedical Device; Tissue Repair and Regeneration.</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Ceramic Technology, Mechanics of Composite Materials, Mechanical Engineering, Biomimicry, 3D Printing, Additive Manufacturing, Manufacturing Engineering</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>Xiangjia (Cindy) Li is an Associate Professor at Arizona State University. Her research focuses on multiscale, multimaterial additive manufacturing and bioinspired design for functional materials and devices.</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="L33" s="2" t="inlineStr">
         <is>
           <t>tGQzHJIAAAAJ</t>
         </is>
       </c>
-      <c r="J33" s="3">
+      <c r="M33" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/xiangji5", "https://search.asu.edu/profile/xiangji5")</f>
         <v/>
       </c>
-      <c r="K33" s="3">
+      <c r="N33" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=tGQzHJIAAAAJ", "Scholar (tGQzHJIAAAAJ)")</f>
         <v/>
       </c>
@@ -3717,15 +4423,18 @@
         <v>0</v>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="b">
+      <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="3">
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/dspeaks2", "https://search.asu.edu/profile/dspeaks2")</f>
         <v/>
       </c>
-      <c r="K34" s="3">
+      <c r="N34" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Derrick%20Speaks%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
@@ -3759,15 +4468,18 @@
         <v>0</v>
       </c>
       <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="b">
+      <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="3">
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/ejande22", "https://search.asu.edu/profile/ejande22")</f>
         <v/>
       </c>
-      <c r="K35" s="3">
+      <c r="N35" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Erik%20Andersen%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
@@ -3801,19 +4513,30 @@
         <v>0</v>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="b">
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Bio-inspired robotics Soft robotics Magnetic micro-robotics Mechanics of animal locomotion</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>Marvi would like to develop bio-inspired robotic systems and programmable interfacial structures for search and rescue, exploratory and medical applications.</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="L36" s="2" t="inlineStr">
         <is>
           <t>00Fepb0AAAAJ</t>
         </is>
       </c>
-      <c r="J36" s="3">
+      <c r="M36" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/hmarvi", "https://search.asu.edu/profile/hmarvi")</f>
         <v/>
       </c>
-      <c r="K36" s="3">
+      <c r="N36" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=00Fepb0AAAAJ", "Scholar (00Fepb0AAAAJ)")</f>
         <v/>
       </c>
@@ -3847,15 +4570,22 @@
         <v>0</v>
       </c>
       <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="b">
+      <c r="H37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>Lee's research interests include physical human-robot interaction, neuromuscular control of human movement, robot-aided neurorehabilitation, bio-inspired robotics and system identification for physiological systems.</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="3">
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/hlee234", "https://search.asu.edu/profile/hlee234")</f>
         <v/>
       </c>
-      <c r="K37" s="3">
+      <c r="N37" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Hyunglae%20Lee%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
@@ -3889,15 +4619,18 @@
         <v>0</v>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="b">
+      <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="3">
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/iychang", "https://search.asu.edu/profile/iychang")</f>
         <v/>
       </c>
-      <c r="K38" s="3">
+      <c r="N38" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ivy%20Chang%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
@@ -3931,15 +4664,26 @@
         <v>0</v>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="b">
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Student learning of mathematical concepts. Motivation and mathematics learning. Teacher change. Applications of technology to mathematics teaching and learning.</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>Middleton’s research interests focus in the following areas where he has published extensively: children’s mathematical thinking; teacher and student motivation in mathematics; and teacher change in mathematics.</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="3">
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/jimbo", "https://search.asu.edu/profile/jimbo")</f>
         <v/>
       </c>
-      <c r="K39" s="3">
+      <c r="N39" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=James%20Middleton%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
@@ -3973,19 +4717,34 @@
         <v>0</v>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="b">
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Hire students to conduct research https://sunroboticslab.github.io</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Autonomous Technologies, Control Systems, Mechanical Engineering, Robotics</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>Sun's research focuses on the design, dynamics, and control of soft robots and artificial muscles</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="L40" s="2" t="inlineStr">
         <is>
           <t>fjUoHOsAAAAJ</t>
         </is>
       </c>
-      <c r="J40" s="3">
+      <c r="M40" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/jsun165", "https://search.asu.edu/profile/jsun165")</f>
         <v/>
       </c>
-      <c r="K40" s="3">
+      <c r="N40" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=fjUoHOsAAAAJ", "Scholar (fjUoHOsAAAAJ)")</f>
         <v/>
       </c>
@@ -4019,15 +4778,18 @@
         <v>0</v>
       </c>
       <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="b">
+      <c r="H41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="3">
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/jdwilbu1", "https://search.asu.edu/profile/jdwilbu1")</f>
         <v/>
       </c>
-      <c r="K41" s="3">
+      <c r="N41" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Joshua%20Wilbur%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
@@ -4061,19 +4823,26 @@
         <v>0</v>
       </c>
       <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="b">
+      <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>Rykaczewski's research focuses on development of soft thermal materials and system as well as studying human thermal exposure in extreme heat.</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="I42" s="2" t="inlineStr">
+      <c r="L42" s="2" t="inlineStr">
         <is>
           <t>SWeAf4UAAAAJ</t>
         </is>
       </c>
-      <c r="J42" s="3">
+      <c r="M42" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/krykacze", "https://search.asu.edu/profile/krykacze")</f>
         <v/>
       </c>
-      <c r="K42" s="3">
+      <c r="N42" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=SWeAf4UAAAAJ", "Scholar (SWeAf4UAAAAJ)")</f>
         <v/>
       </c>
@@ -4107,15 +4876,30 @@
         <v>0</v>
       </c>
       <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="b">
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Manufacturing process simulation and modeling and experiments Additive manufacturing Micro/nano manufacturing Microelectronic packaging Application of AI in manufacturing Mechanic of metallic materials Materials characterization Fatigue and damage modeling and simulation</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>Additive Manufacturing, Manufacturing Engineering</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Ladani is a Professor of Mechanical and Aerospace Engineering at Arizona State University.</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="3">
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/ljannesa", "https://search.asu.edu/profile/ljannesa")</f>
         <v/>
       </c>
-      <c r="K43" s="3">
+      <c r="N43" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Leila%20Ladani%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
@@ -4149,15 +4933,22 @@
         <v>0</v>
       </c>
       <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="b">
+      <c r="H44" s="2" t="inlineStr"/>
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>Li uses multiscale material mechanics models, computational and data tools to explore advanced materials for extreme environments.</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="3">
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/linli25", "https://search.asu.edu/profile/linli25")</f>
         <v/>
       </c>
-      <c r="K44" s="3">
+      <c r="N44" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Lin%20Li%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
@@ -4191,15 +4982,22 @@
         <v>0</v>
       </c>
       <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="b">
+      <c r="H45" s="2" t="inlineStr"/>
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>Mignolet's research interests include structural dynamics, vibrations, modeling of uncertainty in structures and stochastic multiscale analyses.</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="3">
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/marc03", "https://search.asu.edu/profile/marc03")</f>
         <v/>
       </c>
-      <c r="K45" s="3">
+      <c r="N45" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Marc%20Mignolet%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
@@ -4233,15 +5031,30 @@
         <v>0</v>
       </c>
       <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="b">
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Thermal engineering, sustainable energy systems, energy management, sustainable cooling systems.</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Building Technology, Solar Energy Systems, Energy Efficiency Technologies, Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>Phelan researches and teaches in the area of sustainable energy, thermal transport and thermal management.</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="3">
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/pphelan", "https://search.asu.edu/profile/pphelan")</f>
         <v/>
       </c>
-      <c r="K46" s="3">
+      <c r="N46" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Patrick%20Phelan%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
@@ -4275,15 +5088,22 @@
         <v>0</v>
       </c>
       <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="b">
+      <c r="H47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>Peralta's research focuses on mechanics of materials, fatigue and fracture of metallic alloys, dynamic and shock loading of metallic and intermetallic materials.</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="3">
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/pperalta", "https://search.asu.edu/profile/pperalta")</f>
         <v/>
       </c>
-      <c r="K47" s="3">
+      <c r="N47" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Pedro%20Peralta%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
@@ -4317,15 +5137,30 @@
         <v>0</v>
       </c>
       <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="b">
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Nanomanufacturing, additive manufacturing, laser-based material processing, laser matter interaction and physics simulation; inkjet printing of functional materials; and 2D materials fabrication for energy storage and bio-sensors.</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Additive Manufacturing, Manufacturing Engineering, Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>Nian's research interests include additive manufacturing, laser-based manufacturing and material processing, laser matter interaction and physics simulation, and functional materials for energy storage and bio-sensors.</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="3">
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/qnian", "https://search.asu.edu/profile/qnian")</f>
         <v/>
       </c>
-      <c r="K48" s="3">
+      <c r="N48" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Qiong%20Nian%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
@@ -4359,15 +5194,18 @@
         <v>0</v>
       </c>
       <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="b">
+      <c r="H49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="3">
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/rcruzloz", "https://search.asu.edu/profile/rcruzloz")</f>
         <v/>
       </c>
-      <c r="K49" s="3">
+      <c r="N49" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ricardo%20Cruz%20Lozano%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
@@ -4401,15 +5239,22 @@
         <v>0</v>
       </c>
       <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="b">
+      <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>Seetharaman's is the director of EPIXC. His research and teaching interests lie in metals and ceramics. He is also engaged in developing materials for harsh conditions.</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="3">
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/sseeth11", "https://search.asu.edu/profile/sseeth11")</f>
         <v/>
       </c>
-      <c r="K50" s="3">
+      <c r="N50" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Sridhar%20Seetharaman%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
@@ -4443,15 +5288,18 @@
         <v>0</v>
       </c>
       <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="b">
+      <c r="H51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="3">
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/skosara2", "https://search.asu.edu/profile/skosara2")</f>
         <v/>
       </c>
-      <c r="K51" s="3">
+      <c r="N51" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Srinivas%20Chakravarthi%20Kosaraju%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
@@ -4485,19 +5333,30 @@
         <v>0</v>
       </c>
       <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="b">
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>https://irislab.tech/</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>Jin's research includes robotics, control and machine learning, with a focus on the autonomy of robots interacting with humans and objects.</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="I52" s="2" t="inlineStr">
+      <c r="L52" s="2" t="inlineStr">
         <is>
           <t>SoEC4h4AAAAJ</t>
         </is>
       </c>
-      <c r="J52" s="3">
+      <c r="M52" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/wjin34", "https://search.asu.edu/profile/wjin34")</f>
         <v/>
       </c>
-      <c r="K52" s="3">
+      <c r="N52" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=SoEC4h4AAAAJ", "Scholar (SoEC4h4AAAAJ)")</f>
         <v/>
       </c>
@@ -4531,19 +5390,34 @@
         <v>0</v>
       </c>
       <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="b">
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>Mechanics of Composite Materials, Micro and Nanoscale Bioengineering, Nanotechnology, Thin Film Materials</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>Mechanics of Composite Materials, Micro and Nanoscale Bioengineering, Nanotechnology, Thin Film Materials</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>Kang's current research interests include functional materials for energy/manufacturing applications and biomaterials/biomechanics for injury and wound healing mechanisms.</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="I53" s="2" t="inlineStr">
+      <c r="L53" s="2" t="inlineStr">
         <is>
           <t>bHyyOTAAAAAJ</t>
         </is>
       </c>
-      <c r="J53" s="3">
+      <c r="M53" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/wkang16", "https://search.asu.edu/profile/wkang16")</f>
         <v/>
       </c>
-      <c r="K53" s="3">
+      <c r="N53" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=bHyyOTAAAAAJ", "Scholar (bHyyOTAAAAAJ)")</f>
         <v/>
       </c>
@@ -4577,15 +5451,30 @@
         <v>0</v>
       </c>
       <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="b">
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>The research interests include control theory, machine learning, formal methods and autonomous systems.</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence, Control Systems, Electric Power and Energy Systems, Machine Learning, Robotics, Systems and Control Theory</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>My research interests include control theory, formal methods, and machine learning (including reinforcement learning), with applications on autonomous systems and cyber-physical systems.</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="3">
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/xzhe1", "https://search.asu.edu/profile/xzhe1")</f>
         <v/>
       </c>
-      <c r="K54" s="3">
+      <c r="N54" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Zhe%20Xu%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
@@ -4593,164 +5482,164 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N7" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N8" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N11" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N12" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId63"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId69"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId75"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N28" r:id="rId81"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId87"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N32" r:id="rId93"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N33" r:id="rId96"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N34" r:id="rId99"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N35" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N36" r:id="rId105"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N37" r:id="rId108"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N38" r:id="rId111"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N39" r:id="rId114"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N40" r:id="rId117"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N41" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N42" r:id="rId123"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N43" r:id="rId126"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N44" r:id="rId129"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M45" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N45" r:id="rId132"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N46" r:id="rId135"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M47" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N47" r:id="rId138"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M48" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N48" r:id="rId141"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M49" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N49" r:id="rId144"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M50" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N50" r:id="rId147"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M51" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N51" r:id="rId150"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J52" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K52" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M52" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N52" r:id="rId153"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J53" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K53" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M53" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N53" r:id="rId156"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K54" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M54" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N54" r:id="rId159"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/universities_wise/arizona_state_university/asu_aerospace_mechanical_faculty.xlsx
+++ b/universities_wise/arizona_state_university/asu_aerospace_mechanical_faculty.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:O31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -472,6 +472,7 @@
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="49" customWidth="1" min="13" max="13"/>
     <col width="32" customWidth="1" min="14" max="14"/>
+    <col width="49" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -545,6 +546,11 @@
           <t>Google Scholar URL</t>
         </is>
       </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Directory URL</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -598,6 +604,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Jeonglae%20Kim%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
+      <c r="O2" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -659,6 +669,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Werner%20Dahm%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
+      <c r="O3" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -716,6 +730,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=xT-lX9sAAAAJ", "Scholar (xT-lX9sAAAAJ)")</f>
         <v/>
       </c>
+      <c r="O4" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -775,6 +793,10 @@
       </c>
       <c r="N5" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=DKc-AgcAAAAJ", "Scholar (DKc-AgcAAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="O5" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
     </row>
@@ -830,6 +852,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Mohamed%20Houssem%20Kasbaoui%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
+      <c r="O6" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -887,6 +913,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=w3fU9E0AAAAJ", "Scholar (w3fU9E0AAAAJ)")</f>
         <v/>
       </c>
+      <c r="O7" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -948,6 +978,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Gokul%20Pathikonda%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
+      <c r="O8" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1005,6 +1039,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=yv6aCW8AAAAJ", "Scholar (yv6aCW8AAAAJ)")</f>
         <v/>
       </c>
+      <c r="O9" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1070,6 +1108,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=HRx2lJQAAAAJ", "Scholar (HRx2lJQAAAAJ)")</f>
         <v/>
       </c>
+      <c r="O10" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1131,6 +1173,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=fs2d97sAAAAJ", "Scholar (fs2d97sAAAAJ)")</f>
         <v/>
       </c>
+      <c r="O11" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1194,6 +1240,10 @@
       </c>
       <c r="N12" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=2xQTOc0AAAAJ", "Scholar (2xQTOc0AAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="O12" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
     </row>
@@ -1253,6 +1303,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=_6o8MrUAAAAJ", "Scholar (_6o8MrUAAAAJ)")</f>
         <v/>
       </c>
+      <c r="O13" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1306,6 +1360,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Huei-Ping%20Huang%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
+      <c r="O14" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1359,6 +1417,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Raghavendra%20Murthy%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
+      <c r="O15" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1411,17 +1473,17 @@
       <c r="K16" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>m-Pb6g2pm2UC</t>
-        </is>
-      </c>
+      <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/rjmilcar", "https://search.asu.edu/profile/rjmilcar")</f>
         <v/>
       </c>
       <c r="N16" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=m-Pb6g2pm2UC", "Scholar (m-Pb6g2pm2UC)")</f>
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ryan%20Milcarek%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="O16" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
     </row>
@@ -1477,6 +1539,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=T.-W.%20Lee%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
+      <c r="O17" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1542,6 +1608,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=4yYKCpUAAAAJ", "Scholar (4yYKCpUAAAAJ)")</f>
         <v/>
       </c>
+      <c r="O18" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1607,6 +1677,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=8CS4X9IAAAAJ", "Scholar (8CS4X9IAAAAJ)")</f>
         <v/>
       </c>
+      <c r="O19" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1670,6 +1744,10 @@
       </c>
       <c r="N20" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=ClqRIhIAAAAJ", "Scholar (ClqRIhIAAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="O20" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
     </row>
@@ -1729,6 +1807,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Jay%20Oswald%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
+      <c r="O21" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1792,6 +1874,10 @@
       </c>
       <c r="N22" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=vs3pl-8AAAAJ", "Scholar (vs3pl-8AAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="O22" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
     </row>
@@ -1851,6 +1937,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Liping%20Wang%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
+      <c r="O23" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1912,6 +2002,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Matthew%20Peet%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
+      <c r="O24" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1973,6 +2067,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=9LWNC50AAAAJ", "Scholar (9LWNC50AAAAJ)")</f>
         <v/>
       </c>
+      <c r="O25" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2036,6 +2134,10 @@
       </c>
       <c r="N26" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=LaUdx9gAAAAJ", "Scholar (LaUdx9gAAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="O26" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
     </row>
@@ -2091,6 +2193,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ronald%20Calhoun%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
+      <c r="O27" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2154,6 +2260,10 @@
       </c>
       <c r="N28" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=KKup0OgAAAAJ", "Scholar (KKup0OgAAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="O28" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
     </row>
@@ -2209,6 +2319,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Tianyu%20Yang%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
+      <c r="O29" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2262,6 +2376,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Yi%20Ren%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
+      <c r="O30" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2317,6 +2435,10 @@
       </c>
       <c r="N31" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Yongming%20Liu%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="O31" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
     </row>
@@ -2325,93 +2447,123 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N7" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N8" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N11" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N12" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N28" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N7" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N8" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N11" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N12" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N28" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId120"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2423,7 +2575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N54"/>
+  <dimension ref="A1:O54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2440,6 +2592,7 @@
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="49" customWidth="1" min="13" max="13"/>
     <col width="32" customWidth="1" min="14" max="14"/>
+    <col width="49" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2513,6 +2666,11 @@
           <t>Google Scholar URL</t>
         </is>
       </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Directory URL</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -2566,6 +2724,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Jeonglae%20Kim%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
+      <c r="O2" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -2627,6 +2789,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Werner%20Dahm%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
+      <c r="O3" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -2684,6 +2850,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=xT-lX9sAAAAJ", "Scholar (xT-lX9sAAAAJ)")</f>
         <v/>
       </c>
+      <c r="O4" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -2743,6 +2913,10 @@
       </c>
       <c r="N5" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=DKc-AgcAAAAJ", "Scholar (DKc-AgcAAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="O5" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
     </row>
@@ -2798,6 +2972,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Mohamed%20Houssem%20Kasbaoui%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
+      <c r="O6" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2855,6 +3033,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=w3fU9E0AAAAJ", "Scholar (w3fU9E0AAAAJ)")</f>
         <v/>
       </c>
+      <c r="O7" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2916,6 +3098,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Gokul%20Pathikonda%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
+      <c r="O8" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2973,6 +3159,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=yv6aCW8AAAAJ", "Scholar (yv6aCW8AAAAJ)")</f>
         <v/>
       </c>
+      <c r="O9" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -3038,6 +3228,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=HRx2lJQAAAAJ", "Scholar (HRx2lJQAAAAJ)")</f>
         <v/>
       </c>
+      <c r="O10" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -3099,6 +3293,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=fs2d97sAAAAJ", "Scholar (fs2d97sAAAAJ)")</f>
         <v/>
       </c>
+      <c r="O11" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3162,6 +3360,10 @@
       </c>
       <c r="N12" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=2xQTOc0AAAAJ", "Scholar (2xQTOc0AAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="O12" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
     </row>
@@ -3221,6 +3423,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=_6o8MrUAAAAJ", "Scholar (_6o8MrUAAAAJ)")</f>
         <v/>
       </c>
+      <c r="O13" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3274,6 +3480,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Huei-Ping%20Huang%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
+      <c r="O14" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3327,6 +3537,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Raghavendra%20Murthy%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
+      <c r="O15" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3379,17 +3593,17 @@
       <c r="K16" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>m-Pb6g2pm2UC</t>
-        </is>
-      </c>
+      <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/rjmilcar", "https://search.asu.edu/profile/rjmilcar")</f>
         <v/>
       </c>
       <c r="N16" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=m-Pb6g2pm2UC", "Scholar (m-Pb6g2pm2UC)")</f>
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ryan%20Milcarek%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="O16" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
     </row>
@@ -3445,6 +3659,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=T.-W.%20Lee%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
+      <c r="O17" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3510,6 +3728,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=4yYKCpUAAAAJ", "Scholar (4yYKCpUAAAAJ)")</f>
         <v/>
       </c>
+      <c r="O18" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -3575,6 +3797,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=8CS4X9IAAAAJ", "Scholar (8CS4X9IAAAAJ)")</f>
         <v/>
       </c>
+      <c r="O19" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -3638,6 +3864,10 @@
       </c>
       <c r="N20" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=ClqRIhIAAAAJ", "Scholar (ClqRIhIAAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="O20" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
     </row>
@@ -3697,6 +3927,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Jay%20Oswald%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
+      <c r="O21" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -3760,6 +3994,10 @@
       </c>
       <c r="N22" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=vs3pl-8AAAAJ", "Scholar (vs3pl-8AAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="O22" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
     </row>
@@ -3819,6 +4057,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Liping%20Wang%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
+      <c r="O23" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -3880,6 +4122,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Matthew%20Peet%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
+      <c r="O24" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -3941,6 +4187,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=9LWNC50AAAAJ", "Scholar (9LWNC50AAAAJ)")</f>
         <v/>
       </c>
+      <c r="O25" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -4004,6 +4254,10 @@
       </c>
       <c r="N26" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=LaUdx9gAAAAJ", "Scholar (LaUdx9gAAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="O26" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
     </row>
@@ -4059,6 +4313,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ronald%20Calhoun%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
+      <c r="O27" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -4122,6 +4380,10 @@
       </c>
       <c r="N28" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=KKup0OgAAAAJ", "Scholar (KKup0OgAAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="O28" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
     </row>
@@ -4177,6 +4439,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Tianyu%20Yang%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
+      <c r="O29" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -4230,6 +4496,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Yi%20Ren%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
+      <c r="O30" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -4285,6 +4555,10 @@
       </c>
       <c r="N31" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Yongming%20Liu%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="O31" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
     </row>
@@ -4332,6 +4606,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Aikaterini%20Stefanaki%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
+      <c r="O32" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -4391,6 +4669,10 @@
       </c>
       <c r="N33" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=tGQzHJIAAAAJ", "Scholar (tGQzHJIAAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="O33" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
     </row>
@@ -4438,6 +4720,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Derrick%20Speaks%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
+      <c r="O34" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -4483,6 +4769,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Erik%20Andersen%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
+      <c r="O35" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -4538,6 +4828,10 @@
       </c>
       <c r="N36" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=00Fepb0AAAAJ", "Scholar (00Fepb0AAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="O36" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
     </row>
@@ -4587,6 +4881,10 @@
       </c>
       <c r="N37" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Hyunglae%20Lee%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="O37" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
     </row>
@@ -4634,6 +4932,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ivy%20Chang%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
+      <c r="O38" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -4687,6 +4989,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=James%20Middleton%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
+      <c r="O39" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -4746,6 +5052,10 @@
       </c>
       <c r="N40" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=fjUoHOsAAAAJ", "Scholar (fjUoHOsAAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="O40" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
     </row>
@@ -4793,6 +5103,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Joshua%20Wilbur%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
+      <c r="O41" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -4846,6 +5160,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=SWeAf4UAAAAJ", "Scholar (SWeAf4UAAAAJ)")</f>
         <v/>
       </c>
+      <c r="O42" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -4901,6 +5219,10 @@
       </c>
       <c r="N43" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Leila%20Ladani%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="O43" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
     </row>
@@ -4952,6 +5274,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Lin%20Li%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
+      <c r="O44" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -5001,6 +5327,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Marc%20Mignolet%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
+      <c r="O45" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -5056,6 +5386,10 @@
       </c>
       <c r="N46" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Patrick%20Phelan%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="O46" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
     </row>
@@ -5107,6 +5441,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Pedro%20Peralta%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
+      <c r="O47" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -5162,6 +5500,10 @@
       </c>
       <c r="N48" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Qiong%20Nian%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="O48" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
     </row>
@@ -5209,6 +5551,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ricardo%20Cruz%20Lozano%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
+      <c r="O49" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -5256,6 +5602,10 @@
       </c>
       <c r="N50" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Sridhar%20Seetharaman%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="O50" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
     </row>
@@ -5303,6 +5653,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Srinivas%20Chakravarthi%20Kosaraju%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
+      <c r="O51" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -5360,6 +5714,10 @@
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=SoEC4h4AAAAJ", "Scholar (SoEC4h4AAAAJ)")</f>
         <v/>
       </c>
+      <c r="O52" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -5419,6 +5777,10 @@
       </c>
       <c r="N53" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=bHyyOTAAAAAJ", "Scholar (bHyyOTAAAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="O53" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
     </row>
@@ -5476,6 +5838,10 @@
       </c>
       <c r="N54" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Zhe%20Xu%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="O54" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
     </row>
@@ -5484,162 +5850,215 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N7" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N8" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N11" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N12" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N28" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N32" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N33" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N34" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N35" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N36" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N37" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N38" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N39" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N40" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N41" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N42" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N43" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N44" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M45" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N45" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N46" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M47" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N47" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M48" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N48" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M49" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N49" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M50" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N50" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M51" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N51" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M52" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N52" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M53" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N53" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M54" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N54" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N7" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N8" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N11" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N12" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N28" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N32" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N33" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N34" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N35" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N36" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N37" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N38" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N39" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N40" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N41" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N42" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N43" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N44" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M45" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N45" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N46" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M47" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N47" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M48" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N48" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M49" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N49" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M50" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N50" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M51" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N51" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M52" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N52" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O52" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M53" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N53" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O53" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M54" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N54" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O54" r:id="rId212"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/universities_wise/arizona_state_university/asu_aerospace_mechanical_faculty.xlsx
+++ b/universities_wise/arizona_state_university/asu_aerospace_mechanical_faculty.xlsx
@@ -455,11 +455,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:R43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="49" customWidth="1" min="5" max="5"/>
@@ -468,11 +468,14 @@
     <col width="65" customWidth="1" min="8" max="8"/>
     <col width="65" customWidth="1" min="9" max="9"/>
     <col width="65" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="65" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="12" max="12"/>
     <col width="49" customWidth="1" min="13" max="13"/>
-    <col width="32" customWidth="1" min="14" max="14"/>
-    <col width="49" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="49" customWidth="1" min="16" max="16"/>
+    <col width="32" customWidth="1" min="17" max="17"/>
+    <col width="49" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -528,25 +531,40 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>Education / Degrees</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Office Location</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Lab / Personal Website</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>Is Field Match</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Scholar ID</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Profile URL</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Google Scholar URL</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Directory URL</t>
         </is>
@@ -555,12 +573,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Jeonglae Kim</t>
+          <t>Liping Wang</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -574,37 +592,55 @@
         </is>
       </c>
       <c r="E2" s="3">
-        <f>HYPERLINK("mailto:jeokim@asu.edu", "jeokim@asu.edu")</f>
+        <f>HYPERLINK("mailto:Liping.Wang@asu.edu", "Liping.Wang@asu.edu")</f>
         <v/>
       </c>
       <c r="F2" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>aeroacoustics, flow control, high-performance computing, optimization, turbulence, turbulent flows</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr"/>
+          <t>aerospace, guidance, heat transfer, materials, metamaterials, radiation, thermal</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Nanoscale heat transfer, metamaterials, plasmonics, and nanophotonics with an emphasis on solar thermal energy harvesting using plasmonic-enhanced light trapping for photovolatics, as well as near-field enhancement and spectral control of radiation for thermophotovoltaic energy conversion. Other research interests involve electronic cooling, MEMS, and bio-sensing.</t>
+        </is>
+      </c>
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Kim's research interests include large-eddy simulation of high-speed turbulent flows with multi-physics, aeroacoustics, flow control and optimization.</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+          <t>Wang research interests include selective control of thermal emission/absorption using meta-materials for energy harvesting and near-field radiation heat transfer enhancement between meta-materials for thermophotovoltaics.</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D. Mechanical Engineering, Georgia Institute of Technology 2011 | M.S. Refrigeration and Cryogenic Engineering, Shanghai Institute of Technical Physics, Chinese  Academy of Sciences 2007 | B.E. Thermal Science and Energy Engineering, University of Science and Technology of China 2004</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>ENGRC 327 (Tempe, AZ 85287-6106)</t>
+        </is>
+      </c>
       <c r="M2" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/jkim520", "https://search.asu.edu/profile/jkim520")</f>
-        <v/>
-      </c>
-      <c r="N2" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Jeonglae%20Kim%20Arizona%20State%20University", "Google Scholar Search")</f>
-        <v/>
-      </c>
-      <c r="O2" s="3">
+        <f>HYPERLINK("http://faculty.engineering.asu.edu/lpwang", "http://faculty.engineering.asu.edu/lpwang")</f>
+        <v/>
+      </c>
+      <c r="N2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O2" s="2" t="inlineStr"/>
+      <c r="P2" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/lwang78", "https://search.asu.edu/profile/lwang78")</f>
+        <v/>
+      </c>
+      <c r="Q2" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Liping%20Wang%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="R2" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -612,12 +648,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Werner Dahm</t>
+          <t>Mohamed Houssem Kasbaoui</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>SUM/WTR Faculty Research</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -631,45 +667,51 @@
         </is>
       </c>
       <c r="E3" s="3">
-        <f>HYPERLINK("mailto:Werner.Dahm@asu.edu", "Werner.Dahm@asu.edu")</f>
+        <f>HYPERLINK("mailto:houssem.kasbaoui@asu.edu", "houssem.kasbaoui@asu.edu")</f>
         <v/>
       </c>
       <c r="F3" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>combustion, computational physics, fluid dynamics, heat transfer, propulsion, turbulence</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Dr. Dahm specializes in fluid dynamics, thermodynamics, combustion, heat transfer, thermal sciences, propulsion, fuel efficiency, emissions, powertrains, and other areas relevant to a broad range of automotive, aerospace, and industrial applications. He is an author of over 200 refereed technical articles, conference papers, and technical publications, a holder of six U.S. and international patents, and has given over 260 technical presentations, including over 190 invited, plenary, and keynote lectures worldwide, on topics dealing with mechanical and aerospace engineering and defense science.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Aerospace Engineering, Applied Research, Computational Modeling, Computational Physics, Mechanical Engineering, Propulsion</t>
-        </is>
-      </c>
+          <t>aerospace, cfd, computational fluid dynamics, dns, fluid dynamics, multiphase flow, turbulent</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Werner J.A. Dahm has since 2010 been the ASU Foundation Professor of Mechanical and Aerospace Engineering, and also Professor Emeritus of Engineering at the University of Michigan where served for the previous 25 years.</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
+          <t>Kasbaoui's research interests include computational fluid dynamics, numerical methods, and massively parallel simulations of multiphase and particle-laden flows for environmental and aerospace applications.</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D.  Aerospace Engineering, Cornell University, 2017 | M.Sc.  Aerospace Engineering, Cornell University, 2015 | M.Sc.  Theoretical Physics, Université Paris-Sud, 2014 | Diplôme d'Ingénieur , Ecole Centrale Paris, 2013 | B.Sc.  Theoretical Physics, Université Paris-Sud, 2011</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Campus: Tempe</t>
+        </is>
+      </c>
       <c r="M3" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/wdahm", "https://search.asu.edu/profile/wdahm")</f>
-        <v/>
-      </c>
-      <c r="N3" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Werner%20Dahm%20Arizona%20State%20University", "Google Scholar Search")</f>
-        <v/>
-      </c>
-      <c r="O3" s="3">
+        <f>HYPERLINK("https://kasbaoui.bitbucket.io", "https://kasbaoui.bitbucket.io")</f>
+        <v/>
+      </c>
+      <c r="N3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O3" s="2" t="inlineStr"/>
+      <c r="P3" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/mkasbaou", "https://search.asu.edu/profile/mkasbaou")</f>
+        <v/>
+      </c>
+      <c r="Q3" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Mohamed%20Houssem%20Kasbaoui%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="R3" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -677,7 +719,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Kangping Chen</t>
+          <t>Jay Oswald</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -696,41 +738,55 @@
         </is>
       </c>
       <c r="E4" s="3">
-        <f>HYPERLINK("mailto:k.p.chen@asu.edu", "k.p.chen@asu.edu")</f>
+        <f>HYPERLINK("mailto:joswald1@asu.edu", "joswald1@asu.edu")</f>
         <v/>
       </c>
       <c r="F4" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>computational fluid dynamics, drag reduction, fluid dynamics, fluid mechanics, multiphase flow</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
+          <t>estimation, finite element, materials, robot, robotics, solid mechanics</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Development of computational mechanics: finite element methods, molecular dynamics, multiscale methods, failure analysis, and material design.</t>
+        </is>
+      </c>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Chen’s research interests include multiphase flows, drag reduction, airplane de-icing, interfacial instabilities and flow in porous media.</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="b">
-        <v>1</v>
+          <t>Dr. Oswald develops computational and AI-driven methods for advanced manufacturing, including laser welding, automated inspection, robotics, and computational mechanics.</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D. Mechanical Engineering, Northwestern University, Evanston, IL 2011 | M.S. Mechanical Engineering, Case Western Reserve University, Cleveland, OH 2005 | B.S. Mechanical Engineering, Case Western Reserve University, Cleveland, OH 2004</t>
+        </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>xT-lX9sAAAAJ</t>
+          <t>ENGRC 353 (Tempe, AZ 85287-6106)</t>
         </is>
       </c>
       <c r="M4" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/asuchen", "https://search.asu.edu/profile/asuchen")</f>
-        <v/>
-      </c>
-      <c r="N4" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=xT-lX9sAAAAJ", "Scholar (xT-lX9sAAAAJ)")</f>
-        <v/>
-      </c>
-      <c r="O4" s="3">
+        <f>HYPERLINK("http://sparky.fulton.asu.edu/oswald/", "http://sparky.fulton.asu.edu/oswald/")</f>
+        <v/>
+      </c>
+      <c r="N4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O4" s="2" t="inlineStr"/>
+      <c r="P4" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/joswald1", "https://search.asu.edu/profile/joswald1")</f>
+        <v/>
+      </c>
+      <c r="Q4" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Jay%20Oswald%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="R4" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -738,12 +794,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Kiran Ramesh</t>
+          <t>Jiefeng Sun</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -757,45 +813,63 @@
         </is>
       </c>
       <c r="E5" s="3">
-        <f>HYPERLINK("mailto:Kiran.Ramesh@asu.edu", "Kiran.Ramesh@asu.edu")</f>
+        <f>HYPERLINK("mailto:Jiefeng.Sun@asu.edu", "Jiefeng.Sun@asu.edu")</f>
         <v/>
       </c>
       <c r="F5" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>aerodynamics, flow control, fluid dynamics, turbulence, vortex dynamics</t>
+          <t>aerospace, autonomous, materials, robot, robotics, smart materials</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Unsteady aerodynamics, vortex dynamics, flow control, turbulence, separated flows</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr"/>
+          <t>Hire students to conduct research https://sunroboticslab.github.io</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Autonomous Technologies, Control Systems, Mechanical Engineering, Robotics</t>
+        </is>
+      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Ramesh's expertise is in unsteady fluid dynamics, vortex dynamics, turbulence and flow control.</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="b">
-        <v>1</v>
+          <t>Sun's research focuses on the design, dynamics, and control of soft robots and artificial muscles</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D. in Robotics and Control, Colorado State University, 2022 M.S. in Mechanical Engineering, Dalian University of Technology, 2017 B.S. in Mechanical Engineering, Lanzhou University of Technology, 2014</t>
+        </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>DKc-AgcAAAAJ</t>
+          <t>Campus: Tempe</t>
         </is>
       </c>
       <c r="M5" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/kramesh2", "https://search.asu.edu/profile/kramesh2")</f>
-        <v/>
-      </c>
-      <c r="N5" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=DKc-AgcAAAAJ", "Scholar (DKc-AgcAAAAJ)")</f>
-        <v/>
-      </c>
-      <c r="O5" s="3">
+        <f>HYPERLINK("https://sunroboticslab.github.io", "https://sunroboticslab.github.io")</f>
+        <v/>
+      </c>
+      <c r="N5" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>fjUoHOsAAAAJ</t>
+        </is>
+      </c>
+      <c r="P5" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/jsun165", "https://search.asu.edu/profile/jsun165")</f>
+        <v/>
+      </c>
+      <c r="Q5" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=fjUoHOsAAAAJ", "Scholar (fjUoHOsAAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="R5" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -803,7 +877,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Mohamed Houssem Kasbaoui</t>
+          <t>Kangping Chen</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -822,37 +896,48 @@
         </is>
       </c>
       <c r="E6" s="3">
-        <f>HYPERLINK("mailto:houssem.kasbaoui@asu.edu", "houssem.kasbaoui@asu.edu")</f>
+        <f>HYPERLINK("mailto:k.p.chen@asu.edu", "k.p.chen@asu.edu")</f>
         <v/>
       </c>
       <c r="F6" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>cfd, computational fluid dynamics, dns, fluid dynamics, multiphase flow</t>
+          <t>aerospace, computational fluid dynamics, fluid dynamics, fluid mechanics, guidance, multiphase flow</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Kasbaoui's research interests include computational fluid dynamics, numerical methods, and massively parallel simulations of multiphase and particle-laden flows for environmental and aerospace applications.</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="b">
-        <v>1</v>
+          <t>Chen’s research interests include multiphase flows, drag reduction, airplane de-icing, interfacial instabilities and flow in porous media.</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D. Fluid Mechanics, University of Minnesota 1990 | B.S. Mechanics, Peking University, China 1982</t>
+        </is>
       </c>
       <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/mkasbaou", "https://search.asu.edu/profile/mkasbaou")</f>
-        <v/>
-      </c>
-      <c r="N6" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Mohamed%20Houssem%20Kasbaoui%20Arizona%20State%20University", "Google Scholar Search")</f>
-        <v/>
-      </c>
-      <c r="O6" s="3">
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>xT-lX9sAAAAJ</t>
+        </is>
+      </c>
+      <c r="P6" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/asuchen", "https://search.asu.edu/profile/asuchen")</f>
+        <v/>
+      </c>
+      <c r="Q6" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=xT-lX9sAAAAJ", "Scholar (xT-lX9sAAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="R6" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -860,12 +945,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Aditi Chattopadhyay</t>
+          <t>Kiran Ramesh</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Regents Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -879,41 +964,52 @@
         </is>
       </c>
       <c r="E7" s="3">
-        <f>HYPERLINK("mailto:aditi@asu.edu", "aditi@asu.edu")</f>
+        <f>HYPERLINK("mailto:Kiran.Ramesh@asu.edu", "Kiran.Ramesh@asu.edu")</f>
         <v/>
       </c>
       <c r="F7" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>inverse problems, multiscale modeling, optimization, transition</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr"/>
+          <t>aerodynamics, aerospace, flow control, fluid dynamics, turbulence, vortex dynamics</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Unsteady aerodynamics, vortex dynamics, flow control, turbulence, separated flows</t>
+        </is>
+      </c>
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Chattopadhyay is the director of Adaptive Intelligent Materials and Systems (AIMS) Center at ASU. Her research focuses on structural health monitoring and damage prognosis, and multidisciplinary design optimization.</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>w3fU9E0AAAAJ</t>
-        </is>
-      </c>
-      <c r="M7" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/chattopa", "https://search.asu.edu/profile/chattopa")</f>
-        <v/>
-      </c>
-      <c r="N7" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=w3fU9E0AAAAJ", "Scholar (w3fU9E0AAAAJ)")</f>
-        <v/>
-      </c>
-      <c r="O7" s="3">
+          <t>Ramesh's expertise is in unsteady fluid dynamics, vortex dynamics, turbulence and flow control.</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>PhD North Carolina State University</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>DKc-AgcAAAAJ</t>
+        </is>
+      </c>
+      <c r="P7" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/kramesh2", "https://search.asu.edu/profile/kramesh2")</f>
+        <v/>
+      </c>
+      <c r="Q7" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=DKc-AgcAAAAJ", "Scholar (DKc-AgcAAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="R7" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -921,7 +1017,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Gokul Pathikonda</t>
+          <t>Leixin Ma</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -940,45 +1036,59 @@
         </is>
       </c>
       <c r="E8" s="3">
-        <f>HYPERLINK("mailto:Gokul.Pathikonda@asu.edu", "Gokul.Pathikonda@asu.edu")</f>
+        <f>HYPERLINK("mailto:Leixin.Ma@asu.edu", "Leixin.Ma@asu.edu")</f>
         <v/>
       </c>
       <c r="F8" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>aerodynamics, reacting flows, turbulence, turbulent mixing</t>
+          <t>aerodynamics, aerospace, fluid-structure interaction, fluids, materials, robot</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Aerodynamics, Aerospace Engineering, Mechanical Engineering</t>
+          <t>Aerodynamics, Dynamical Systems, Machine Learning, Mechanics of Composite Materials</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Aerodynamics, Aerospace Engineering, Mechanical Engineering</t>
+          <t>Aerodynamics, Dynamical Systems, Machine Learning, Mechanics of Composite Materials</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Dr. Pathikonda studies turbulent fluid flows to understand natural and engineering phenomena using lab experiments. His expertise is in complex (reacting) mixing, high Re-flows, laser-based &amp; spectroscopic techniques, etc.</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="b">
-        <v>1</v>
+          <t>Leixin Ma's career goal is a data-driven and physically consistent approach to modeling and designing programmable smart structures and robots, especially under complex fluid flow conditions.</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D. in Mechanical Engineering, Massachusetts Institute of Technology, 2021 S.M. in Mechanical Engineering, Massachusetts Institute of Technology, 2017 B.S.E. in Naval Architecture and Ocean Engineering, Shanghai Jiao Tong University, 2015</t>
+        </is>
       </c>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/gpathiko", "https://search.asu.edu/profile/gpathiko")</f>
-        <v/>
-      </c>
-      <c r="N8" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Gokul%20Pathikonda%20Arizona%20State%20University", "Google Scholar Search")</f>
-        <v/>
-      </c>
-      <c r="O8" s="3">
+        <f>HYPERLINK("https://sites.google.com/view/oasislabasu", "https://sites.google.com/view/oasislabasu")</f>
+        <v/>
+      </c>
+      <c r="N8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>2xQTOc0AAAAJ</t>
+        </is>
+      </c>
+      <c r="P8" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/leixinma", "https://search.asu.edu/profile/leixinma")</f>
+        <v/>
+      </c>
+      <c r="Q8" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=2xQTOc0AAAAJ", "Scholar (2xQTOc0AAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="R8" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -986,12 +1096,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Marcus Herrmann</t>
+          <t>Gokul Pathikonda</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Professor</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1005,41 +1115,59 @@
         </is>
       </c>
       <c r="E9" s="3">
-        <f>HYPERLINK("mailto:Marcus.Herrmann@asu.edu", "Marcus.Herrmann@asu.edu")</f>
+        <f>HYPERLINK("mailto:Gokul.Pathikonda@asu.edu", "Gokul.Pathikonda@asu.edu")</f>
         <v/>
       </c>
       <c r="F9" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>fluid mechanics, multiphase flow, numerical simulation, turbulence</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr"/>
+          <t>aerodynamics, aerospace, reacting flow, turbulence, turbulent</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Aerodynamics, Aerospace Engineering, Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Aerodynamics, Aerospace Engineering, Mechanical Engineering</t>
+        </is>
+      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Herrmann's research interests include fluid mechanics, modeling and numerical simulation of multiphase flows with a focus on turbulent atomization processes, and numerical methods for discontinuous interfaces.</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="b">
-        <v>1</v>
+          <t>Dr. Pathikonda studies turbulent fluid flows to understand natural and engineering phenomena using lab experiments. His expertise is in complex (reacting) mixing, high Re-flows, laser-based &amp; spectroscopic techniques, etc.</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>Ph. D. Theoretical and Applied Mechanics, University of Illinois, Urbana Champaign, 2017 | MS Aerospace Engineering, University of Illinois, Urbana Champaign, 2013 | B. Tech. Mechanical Engineering, National Institute of Technology, Warangal, 2009</t>
+        </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>yv6aCW8AAAAJ</t>
+          <t>551 E Tyler Mall ERC 479 (Tempe, AZ 85281)</t>
         </is>
       </c>
       <c r="M9" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/mherrma1", "https://search.asu.edu/profile/mherrma1")</f>
-        <v/>
-      </c>
-      <c r="N9" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=yv6aCW8AAAAJ", "Scholar (yv6aCW8AAAAJ)")</f>
-        <v/>
-      </c>
-      <c r="O9" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/cmat/", "https://faculty.engineering.asu.edu/cmat/")</f>
+        <v/>
+      </c>
+      <c r="N9" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O9" s="2" t="inlineStr"/>
+      <c r="P9" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/gpathiko", "https://search.asu.edu/profile/gpathiko")</f>
+        <v/>
+      </c>
+      <c r="Q9" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Gokul%20Pathikonda%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="R9" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1047,12 +1175,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Alberto Scotti</t>
+          <t>Kunal Garg</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Professor</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1066,49 +1194,63 @@
         </is>
       </c>
       <c r="E10" s="3">
-        <f>HYPERLINK("mailto:Alberto.Scotti@asu.edu", "Alberto.Scotti@asu.edu")</f>
+        <f>HYPERLINK("mailto:kgarg24@asu.edu", "kgarg24@asu.edu")</f>
         <v/>
       </c>
       <c r="F10" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>applied mathematics, fluid mechanics, turbulent mixing</t>
+          <t>aerospace, control theory, motion planning, robot, robotics</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Modeling and Simulation, Oceanography, Earth Systems and Climate Science, Modeling, Modeling, Simulation and Cyberinfrastructure, Applied Mathematics</t>
+          <t>Distributed multi-agent motion planning and control, Provably safe control design using machine learning-based certificates, Foundation models in complex robotic tasks, Failure prediction from limited demonstrations, Human-robot interaction.</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Modeling and Simulation, Oceanography, Earth Systems and Climate Science, Modeling, Modeling, Simulation and Cyberinfrastructure, Applied Mathematics</t>
+          <t>Control Systems, Dynamical Systems, Machine Learning, Nonlinear Dynamical Systems, Robotics</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Scotti's main focus is theoretical, experimental and computational aspects of environmental fluid mechanics.</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="b">
-        <v>1</v>
+          <t>Garg's research interests include control synthesis for multi-agent coordination using control theory and machine learning.</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>PhD. Aerospace Engineering, University of Michigan, Ann Arbor, 2021 MS. Aerospace Engineering, University of Michigan, Ann Arbor, 2019 BTech. Aerospace Engineering, Indian Institute of Technology, Bombay, 2016</t>
+        </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>HRx2lJQAAAAJ</t>
+          <t>551 E Tyler Mall ERC 475 (Tempe, AZ 85281)</t>
         </is>
       </c>
       <c r="M10" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/adscotti", "https://search.asu.edu/profile/adscotti")</f>
-        <v/>
-      </c>
-      <c r="N10" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=HRx2lJQAAAAJ", "Scholar (HRx2lJQAAAAJ)")</f>
-        <v/>
-      </c>
-      <c r="O10" s="3">
+        <f>HYPERLINK("https://sites.google.com/asu.edu/kunalgarg/", "https://sites.google.com/asu.edu/kunalgarg/")</f>
+        <v/>
+      </c>
+      <c r="N10" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>vs3pl-8AAAAJ</t>
+        </is>
+      </c>
+      <c r="P10" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/kgarg24", "https://search.asu.edu/profile/kgarg24")</f>
+        <v/>
+      </c>
+      <c r="Q10" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=vs3pl-8AAAAJ", "Scholar (vs3pl-8AAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="R10" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1116,12 +1258,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Beomjin Kwon</t>
+          <t>Marcus Herrmann</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Professor</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1135,45 +1277,48 @@
         </is>
       </c>
       <c r="E11" s="3">
-        <f>HYPERLINK("mailto:kwon@asu.edu", "kwon@asu.edu")</f>
+        <f>HYPERLINK("mailto:Marcus.Herrmann@asu.edu", "Marcus.Herrmann@asu.edu")</f>
         <v/>
       </c>
       <c r="F11" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>data-driven modeling, heat transfer, transport phenomena</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Transport phenomena in heat transfer systems Additive manufacturing Data-driven modeling and design</t>
-        </is>
-      </c>
+          <t>aerospace, fluid mechanics, multiphase flow, turbulence, turbulent</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>Kwon aims to improve the energy conversion and transport systems through the fundamental insights into transport physics, and by exploiting additive manufacturing and data-driven approaches.</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>fs2d97sAAAAJ</t>
-        </is>
-      </c>
-      <c r="M11" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/bkwon2", "https://search.asu.edu/profile/bkwon2")</f>
-        <v/>
-      </c>
-      <c r="N11" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=fs2d97sAAAAJ", "Scholar (fs2d97sAAAAJ)")</f>
-        <v/>
-      </c>
-      <c r="O11" s="3">
+          <t>Herrmann's research interests include fluid mechanics, modeling and numerical simulation of multiphase flows with a focus on turbulent atomization processes, and numerical methods for discontinuous interfaces.</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>PhD in Mechanical Engineering, University of Technology (RWTH) Aachen, Germany 2001 | Diploma. Mechanical and Aerospace Engineering, University of Technology (RWTH) Aachen, Germany 1995</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>yv6aCW8AAAAJ</t>
+        </is>
+      </c>
+      <c r="P11" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/mherrma1", "https://search.asu.edu/profile/mherrma1")</f>
+        <v/>
+      </c>
+      <c r="Q11" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=yv6aCW8AAAAJ", "Scholar (yv6aCW8AAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="R11" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1181,12 +1326,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Leixin Ma</t>
+          <t>Spring Berman</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Professor</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1200,49 +1345,59 @@
         </is>
       </c>
       <c r="E12" s="3">
-        <f>HYPERLINK("mailto:Leixin.Ma@asu.edu", "Leixin.Ma@asu.edu")</f>
+        <f>HYPERLINK("mailto:Spring.Berman@asu.edu", "Spring.Berman@asu.edu")</f>
         <v/>
       </c>
       <c r="F12" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>aerodynamics, fluid-structure interaction, physics-informed machine learning</t>
+          <t>aerospace, autonomous, control theory, robot, robotics</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Aerodynamics, Dynamical Systems, Machine Learning, Mechanics of Composite Materials</t>
+          <t>Modeling, analysis, control, and optimization of multi-robot systems including robotic swarms; analysis of collective behaviors in biology and biologically-inspired control of distributed systems</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Aerodynamics, Dynamical Systems, Machine Learning, Mechanics of Composite Materials</t>
+          <t>Systems and Control Theory, Mechanical Engineering, Autonomous Technologies, Robotics</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Leixin Ma's career goal is a data-driven and physically consistent approach to modeling and designing programmable smart structures and robots, especially under complex fluid flow conditions.</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>2xQTOc0AAAAJ</t>
-        </is>
-      </c>
+          <t>Dr. Berman directs the Autonomous Collective Systems Laboratory at ASU, which models and analyzes behaviors in biological and engineered collectives and designs control strategies for multi-robot systems.</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D. Mechanical Engineering and Applied Mechanics, University of Pennsylvania 2010 | M.S.E. Mechanical Engineering and Applied Mechanics, University of Pennsylvania 2008 | B.S.E. Mechanical and Aerospace Engineering, Princeton University 2005 | Certificate. Robotics and Intelligent Systems, Princeton University 2005</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/leixinma", "https://search.asu.edu/profile/leixinma")</f>
-        <v/>
-      </c>
-      <c r="N12" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=2xQTOc0AAAAJ", "Scholar (2xQTOc0AAAAJ)")</f>
-        <v/>
-      </c>
-      <c r="O12" s="3">
+        <f>HYPERLINK("http://faculty.engineering.asu.edu/acs/", "http://faculty.engineering.asu.edu/acs/")</f>
+        <v/>
+      </c>
+      <c r="N12" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>KKup0OgAAAAJ</t>
+        </is>
+      </c>
+      <c r="P12" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/smberma2", "https://search.asu.edu/profile/smberma2")</f>
+        <v/>
+      </c>
+      <c r="Q12" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=KKup0OgAAAAJ", "Scholar (KKup0OgAAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="R12" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1250,12 +1405,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Yulia Peet</t>
+          <t>Zhe Xu</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Professor</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1269,41 +1424,59 @@
         </is>
       </c>
       <c r="E13" s="3">
-        <f>HYPERLINK("mailto:ypeet@asu.edu", "ypeet@asu.edu")</f>
+        <f>HYPERLINK("mailto:xzhe1@asu.edu", "xzhe1@asu.edu")</f>
         <v/>
       </c>
       <c r="F13" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>fluid mechanics, high-performance computing, turbulence</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
+          <t>autonomous, control theory, energy systems, robot, robotics</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>The research interests include control theory, machine learning, formal methods and autonomous systems.</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence, Control Systems, Electric Power and Energy Systems, Machine Learning, Robotics, Systems and Control Theory</t>
+        </is>
+      </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>Yulia Peet is an associate professor of aerospace and mechanical engineering in the School for Engineering of Matter, Transport and Energy with the Ira A. Fulton Schools of Engineering at Arizona State University. Her Ph.D. degree is in Aeronautics and Astronautics from Stanford (2006), M.S. and B.S. degrees are from Moscow Institute of Physics and Technology (1999 and 1997). Her previous appoi...</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="b">
-        <v>1</v>
+          <t>My research interests include control theory, formal methods, and machine learning (including reinforcement learning), with applications on autonomous systems and cyber-physical systems.</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D Degree at the  Department of Electrical, Computer, and Systems Engineering  at  Rensselaer Polytechnic Institute  in 2018 | Master's Degree at the  School of electrical and information engineering  at  Tianjin University  in 2014 | Bachelor's Degree at the  School of electrical and information engineering  at  Tianjin University  in 2011</t>
+        </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>_6o8MrUAAAAJ</t>
+          <t>Campus: Tempe</t>
         </is>
       </c>
       <c r="M13" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/ypeet", "https://search.asu.edu/profile/ypeet")</f>
-        <v/>
-      </c>
-      <c r="N13" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=_6o8MrUAAAAJ", "Scholar (_6o8MrUAAAAJ)")</f>
-        <v/>
-      </c>
-      <c r="O13" s="3">
+        <f>HYPERLINK("https://sites.google.com/site/zhexudavid00710/research?authuser=0", "https://sites.google.com/site/zhexudavid00710/research?authuser=0")</f>
+        <v/>
+      </c>
+      <c r="N13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O13" s="2" t="inlineStr"/>
+      <c r="P13" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/xzhe1", "https://search.asu.edu/profile/xzhe1")</f>
+        <v/>
+      </c>
+      <c r="Q13" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Zhe%20Xu%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="R13" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1311,12 +1484,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Huei-Ping Huang</t>
+          <t>Jeonglae Kim</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1330,37 +1503,44 @@
         </is>
       </c>
       <c r="E14" s="3">
-        <f>HYPERLINK("mailto:Huei-Ping.Huang@asu.edu", "Huei-Ping.Huang@asu.edu")</f>
+        <f>HYPERLINK("mailto:jeokim@asu.edu", "jeokim@asu.edu")</f>
         <v/>
       </c>
       <c r="F14" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>fluid dynamics, numerical simulation</t>
+          <t>aerospace, flow control, turbulence, turbulent</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Huang's research interests are geophysical and environmental fluid dynamics, numerical simulation of atmospheric and oceanic flows, Earth system remote sensing, and climate change.</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="b">
-        <v>1</v>
+          <t>Kim's research interests include large-eddy simulation of high-speed turbulent flows with multi-physics, aeroacoustics, flow control and optimization.</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D. Theoretical and Applied Mechanics, University of Illinois at Urbana-Champaign | M.S. Mechanical and Aerospace Engineering, Seoul National University, South Korea | B.S. Mechanical and Aerospace Engineering, Seoul National University, South Korea</t>
+        </is>
       </c>
       <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/hhuang38", "https://search.asu.edu/profile/hhuang38")</f>
-        <v/>
-      </c>
-      <c r="N14" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Huei-Ping%20Huang%20Arizona%20State%20University", "Google Scholar Search")</f>
-        <v/>
-      </c>
-      <c r="O14" s="3">
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O14" s="2" t="inlineStr"/>
+      <c r="P14" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/jkim520", "https://search.asu.edu/profile/jkim520")</f>
+        <v/>
+      </c>
+      <c r="Q14" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Jeonglae%20Kim%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="R14" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1368,12 +1548,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Raghavendra Murthy</t>
+          <t>Matthew Peet</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Associate Teaching Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1387,37 +1567,55 @@
         </is>
       </c>
       <c r="E15" s="3">
-        <f>HYPERLINK("mailto:rnmurthy@asu.edu", "rnmurthy@asu.edu")</f>
+        <f>HYPERLINK("mailto:mpeet@asu.edu", "mpeet@asu.edu")</f>
         <v/>
       </c>
       <c r="F15" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>optimization, reduced-order modeling</t>
+          <t>aerospace, materials, spacecraft, system dynamics</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Structural Dynamics, Rotordynamics, Vibration Analysis, Reduced-Order Modeling, Optimization</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="b">
-        <v>1</v>
+          <t>The intersection of computer science and control including convex optimization, artificial intelligence, and manipulation of delayed and PDE systems. The understanding and regulation of complex dynamical systems such as the motion of plasma in nuclear fusion reactors, autoregulation in the human immune response, and the motion of spacecraft in orbit.</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Control Systems, Dynamical Systems Theory, Aerospace Engineering, Algorithm Development, Dynamical Systems, Nonlinear Dynamical Systems, Mathematical and System Dynamics Modeling, Immunology</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Peet's current research interests are in the role of computation as it is applied to the understanding and control of complex and large-scale systems.</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D. Aeronautics and Astronautics, Stanford University 2006 | Bachelor's degree. Physics, University of Texas-Austin 1999 | Bachelor's degree. Aerospace Engineering, University of Texas-Austin 1999</t>
+        </is>
       </c>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/rnmurthy", "https://search.asu.edu/profile/rnmurthy")</f>
-        <v/>
-      </c>
-      <c r="N15" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Raghavendra%20Murthy%20Arizona%20State%20University", "Google Scholar Search")</f>
-        <v/>
-      </c>
-      <c r="O15" s="3">
+        <f>HYPERLINK("http://control.asu.edu/", "http://control.asu.edu/")</f>
+        <v/>
+      </c>
+      <c r="N15" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O15" s="2" t="inlineStr"/>
+      <c r="P15" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/mpeet", "https://search.asu.edu/profile/mpeet")</f>
+        <v/>
+      </c>
+      <c r="Q15" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Matthew%20Peet%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="R15" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1425,7 +1623,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Ryan Milcarek</t>
+          <t>Robert Wang</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1444,45 +1642,59 @@
         </is>
       </c>
       <c r="E16" s="3">
-        <f>HYPERLINK("mailto:Ryan.Milcarek@asu.edu", "Ryan.Milcarek@asu.edu")</f>
+        <f>HYPERLINK("mailto:rywang@asu.edu", "rywang@asu.edu")</f>
         <v/>
       </c>
       <c r="F16" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>combustion, transition</t>
+          <t>composites, heat transfer, materials, thermal</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Energy management and efficiency, energy transition, energy storage, solid oxide fuel cells, partial oxidation, cogeneration, combustion, and synthesis of hydrogen</t>
+          <t>My research group is an interdisciplinary nanoengineering team that focuses on manipulating material properties for thermal energy applications. Some of our focus areas are thermoelectric power generation, thermal storage media, heat transfer, and phonon optics. To achieve our objectives, we custom-design materials using colloidal nanoparticles, chemical precursors, and nanocomposites.</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Ceramics, Electrochemistry, Energy, Energy and Sustainability, Energy Conservation, Energy Economics, Energy Efficiency Technologies, Thin Film Materials</t>
+          <t>Mechanical Engineering, Energy, Renewable Energy, Energy and Sustainability, Clean Energy, Energy Efficiency Technologies, Materials Science and Engineering, Chemical Engineering, Nanoengineering, Nanoscience, Nanotechnology, Solid State Physics, Thin Film Materials, Semiconductors, Chemistry, Physics</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Milcarek's current research focuses on energy management and efficiency, energy system modeling, energy transition, energy storage, solid oxide fuel cells fabrication and testing, partial oxidation and synthesis of hydrogen.</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="b">
-        <v>1</v>
+          <t>Wang's research interests include thermal energy conversion, storage, and transport in nanostructured materials; thermoelectric power generation; thermal storage media; heat transfer, and phonon optics</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D. Mechanical Engineering, University of California-Berkeley 2008 | M.S. Mechanical Engineering, University of California-Berkeley 2005 | B.S. Mechanical Engineering, University of California-Los Angeles 2003</t>
+        </is>
       </c>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/rjmilcar", "https://search.asu.edu/profile/rjmilcar")</f>
-        <v/>
-      </c>
-      <c r="N16" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ryan%20Milcarek%20Arizona%20State%20University", "Google Scholar Search")</f>
-        <v/>
-      </c>
-      <c r="O16" s="3">
+        <f>HYPERLINK("http://wang.faculty.asu.edu/", "http://wang.faculty.asu.edu/")</f>
+        <v/>
+      </c>
+      <c r="N16" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>LaUdx9gAAAAJ</t>
+        </is>
+      </c>
+      <c r="P16" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/rywang", "https://search.asu.edu/profile/rywang")</f>
+        <v/>
+      </c>
+      <c r="Q16" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=LaUdx9gAAAAJ", "Scholar (LaUdx9gAAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="R16" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1490,7 +1702,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>T.-W. Lee</t>
+          <t>Ryan Milcarek</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1509,37 +1721,55 @@
         </is>
       </c>
       <c r="E17" s="3">
-        <f>HYPERLINK("mailto:ATTWL@asu.edu", "ATTWL@asu.edu")</f>
+        <f>HYPERLINK("mailto:Ryan.Milcarek@asu.edu", "Ryan.Milcarek@asu.edu")</f>
         <v/>
       </c>
       <c r="F17" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>aerospace propulsion, propulsion</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr"/>
-      <c r="I17" s="2" t="inlineStr"/>
+          <t>aerospace, combustion, energy systems, materials</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Energy management and efficiency, energy transition, energy storage, solid oxide fuel cells, partial oxidation, cogeneration, combustion, and synthesis of hydrogen</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Ceramics, Electrochemistry, Energy, Energy and Sustainability, Energy Conservation, Energy Economics, Energy Efficiency Technologies, Thin Film Materials</t>
+        </is>
+      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>Lee's areas of expertise include energy system analysis, thermal and fluid process characterization, and fuel property measurements for energy systems.</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="b">
-        <v>1</v>
+          <t>Milcarek's current research focuses on energy management and efficiency, energy system modeling, energy transition, energy storage, solid oxide fuel cells fabrication and testing, partial oxidation and synthesis of hydrogen.</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D. Mechanical and Aerospace Engineering, College of Engineering and Computer Science, Syracuse University 2018 | M.S. Mechanical and Aerospace Engineering, College of Engineering and Computer Science, Syracuse University 2017 | M.S. Energy Systems Engineering, College of Engineering and Computer Science, Syracuse University 2017 | Certificate of Advanced Study (CAS) Sustainable Enterprise, Martin J. Whitman School of Management, Syracuse University 2017 | Certificate in University Teaching (CUT). Graduate School, Future Professorate Program, Syracuse University 2017 | B.S. Mechanical Engineering; minor: Mathematics (Summa Cum Laude), L.C. Smith College of Engineering and Computer Science, Syracuse University 2014</t>
+        </is>
       </c>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/attwl", "https://search.asu.edu/profile/attwl")</f>
-        <v/>
-      </c>
-      <c r="N17" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=T.-W.%20Lee%20Arizona%20State%20University", "Google Scholar Search")</f>
-        <v/>
-      </c>
-      <c r="O17" s="3">
+        <f>HYPERLINK("http://RESEARCHGATE.net/profile/Ryan_Milcarek", "http://RESEARCHGATE.net/profile/Ryan_Milcarek")</f>
+        <v/>
+      </c>
+      <c r="N17" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O17" s="2" t="inlineStr"/>
+      <c r="P17" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/rjmilcar", "https://search.asu.edu/profile/rjmilcar")</f>
+        <v/>
+      </c>
+      <c r="Q17" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ryan%20Milcarek%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="R17" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1547,7 +1777,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Houlong Zhuang</t>
+          <t>T.-W. Lee</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1566,49 +1796,48 @@
         </is>
       </c>
       <c r="E18" s="3">
-        <f>HYPERLINK("mailto:zhuanghl@asu.edu", "zhuanghl@asu.edu")</f>
+        <f>HYPERLINK("mailto:ATTWL@asu.edu", "ATTWL@asu.edu")</f>
         <v/>
       </c>
       <c r="F18" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>computational physics</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>Quantum simulations Machine learning Quantum computing</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>Artificial Photosynthesis, Chemistry, Computational Physics, Machine Learning, Materials Science, Metals, Nanoscience, Semiconductors</t>
-        </is>
-      </c>
+          <t>aerospace, energy systems, propulsion, thermal</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Dr. Houlong Zhuang is an associate professor in the School for Engineering of Matter, Transport and Energy at ASU. He received his doctorate in materials science and engineering at Cornell University. Prior to ASU, Dr. Zhuang was a postdoctoral researcher at Princeton University. Dr. Zhuang’s current research interests are quantum mechanical simulations, machine learning, and quantum computing.</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="b">
-        <v>1</v>
+          <t>Lee's areas of expertise include energy system analysis, thermal and fluid process characterization, and fuel property measurements for energy systems.</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D. Aerospace Engineering, University of Michigan-Ann Arbor | M.S.E. Aerospace Engineering, University of Michigan-Ann Arbor | B.S. Aeronautical and Astronautical Engineering, The Ohio State University-Columbus</t>
+        </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4yYKCpUAAAAJ</t>
-        </is>
-      </c>
-      <c r="M18" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/hzhuang7", "https://search.asu.edu/profile/hzhuang7")</f>
-        <v/>
-      </c>
-      <c r="N18" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=4yYKCpUAAAAJ", "Scholar (4yYKCpUAAAAJ)")</f>
-        <v/>
-      </c>
-      <c r="O18" s="3">
+          <t>ENGRC 377 (TEMPE, AZ 85287-6106)</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O18" s="2" t="inlineStr"/>
+      <c r="P18" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/attwl", "https://search.asu.edu/profile/attwl")</f>
+        <v/>
+      </c>
+      <c r="Q18" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=T.-W.%20Lee%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="R18" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1616,12 +1845,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Huan Wu</t>
+          <t>Tianyu Yang</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1635,49 +1864,44 @@
         </is>
       </c>
       <c r="E19" s="3">
-        <f>HYPERLINK("mailto:huanwu@asu.edu", "huanwu@asu.edu")</f>
+        <f>HYPERLINK("mailto:Tianyu.Yang@asu.edu", "Tianyu.Yang@asu.edu")</f>
         <v/>
       </c>
       <c r="F19" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>computational physics</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>Aerospace Engineering, Computational Physics, Energy, Material Physics, Materials Science, Mechanical Engineering, Modeling and Simulation, Theoretical Solid State Physics</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>Aerospace Engineering, Computational Physics, Energy, Material Physics, Materials Science, Mechanical Engineering, Modeling and Simulation, Theoretical Solid State Physics</t>
-        </is>
-      </c>
+          <t>autonomous, heat transfer, materials, thermal</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>Dr. Wu’s research focuses on electron, phonon, and magnon transport, exploring nanoscale energy transport and conversion through first-principles approaches, as well as material thermal and electrical transport properties.</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>8CS4X9IAAAAJ</t>
-        </is>
-      </c>
-      <c r="M19" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/huanwu", "https://search.asu.edu/profile/huanwu")</f>
-        <v/>
-      </c>
-      <c r="N19" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=8CS4X9IAAAAJ", "Scholar (8CS4X9IAAAAJ)")</f>
-        <v/>
-      </c>
-      <c r="O19" s="3">
+          <t>Yang studies heat transfer, thermal management of electronics, and biomedical devices. She has published multiple research papers in major scientific journals.</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>PhD. University of Illinois at Urbana Champaign, 2016-2021 | BS. Tsinghua University, China 2012-2016</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O19" s="2" t="inlineStr"/>
+      <c r="P19" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/tyang123", "https://search.asu.edu/profile/tyang123")</f>
+        <v/>
+      </c>
+      <c r="Q19" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Tianyu%20Yang%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="R19" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1685,12 +1909,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Jagannathan Rajagopalan</t>
+          <t>Aditi Chattopadhyay</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Regents Professor</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1704,49 +1928,52 @@
         </is>
       </c>
       <c r="E20" s="3">
-        <f>HYPERLINK("mailto:Jagannathan.Rajagopalan@asu.edu", "Jagannathan.Rajagopalan@asu.edu")</f>
+        <f>HYPERLINK("mailto:aditi@asu.edu", "aditi@asu.edu")</f>
         <v/>
       </c>
       <c r="F20" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>optimization</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>Synthesis of nanocrystalline materials with tailored microstructures, Mechanics of nanostructured metal and alloy films, MEMS for in situ materials testing, Polymer based micro devices for cell mechanics and biohybrid platforms</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>Thin Film Materials, Materials Science, Mechanical Engineering</t>
-        </is>
-      </c>
+          <t>aerospace, materials, structural health monitoring</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Rajagopalan's research focuses on the mechanics of nanoscale materials, cells and biological systems.</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="b">
-        <v>1</v>
+          <t>Chattopadhyay is the director of Adaptive Intelligent Materials and Systems (AIMS) Center at ASU. Her research focuses on structural health monitoring and damage prognosis, and multidisciplinary design optimization.</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>Ph. D. Aerospace Engineering, Georgia Institute of Technology | M.S. Aerospace Engineering, Georgia Institute of Technology | B. Tech. Aeronautical Engineering (Honors), Indian Institute of Technology, Kharagpur, India 1980</t>
+        </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>ClqRIhIAAAAJ</t>
-        </is>
-      </c>
-      <c r="M20" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/jrajago1", "https://search.asu.edu/profile/jrajago1")</f>
-        <v/>
-      </c>
-      <c r="N20" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=ClqRIhIAAAAJ", "Scholar (ClqRIhIAAAAJ)")</f>
-        <v/>
-      </c>
-      <c r="O20" s="3">
+          <t>ENGRC 427 (TEMPE, AZ 85287-6106)</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>w3fU9E0AAAAJ</t>
+        </is>
+      </c>
+      <c r="P20" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/chattopa", "https://search.asu.edu/profile/chattopa")</f>
+        <v/>
+      </c>
+      <c r="Q20" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=w3fU9E0AAAAJ", "Scholar (w3fU9E0AAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="R20" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1754,12 +1981,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Jay Oswald</t>
+          <t>Alberto Scotti</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Professor</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1773,41 +2000,60 @@
         </is>
       </c>
       <c r="E21" s="3">
-        <f>HYPERLINK("mailto:joswald1@asu.edu", "joswald1@asu.edu")</f>
+        <f>HYPERLINK("mailto:Alberto.Scotti@asu.edu", "Alberto.Scotti@asu.edu")</f>
         <v/>
       </c>
       <c r="F21" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>finite element</t>
+          <t>fluid mechanics, fluids, turbulent</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Development of computational mechanics: finite element methods, molecular dynamics, multiscale methods, failure analysis, and material design.</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr"/>
+          <t>Modeling and Simulation, Oceanography, Earth Systems and Climate Science, Modeling, Modeling, Simulation and Cyberinfrastructure, Applied Mathematics</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Modeling and Simulation, Oceanography, Earth Systems and Climate Science, Modeling, Modeling, Simulation and Cyberinfrastructure, Applied Mathematics</t>
+        </is>
+      </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>Dr. Oswald develops computational and AI-driven methods for advanced manufacturing, including laser welding, automated inspection, robotics, and computational mechanics.</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/joswald1", "https://search.asu.edu/profile/joswald1")</f>
-        <v/>
-      </c>
-      <c r="N21" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Jay%20Oswald%20Arizona%20State%20University", "Google Scholar Search")</f>
-        <v/>
-      </c>
-      <c r="O21" s="3">
+          <t>Scotti's main focus is theoretical, experimental and computational aspects of environmental fluid mechanics.</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>PhD Johns Hopkins University</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>Campus: Tempe</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>HRx2lJQAAAAJ</t>
+        </is>
+      </c>
+      <c r="P21" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/adscotti", "https://search.asu.edu/profile/adscotti")</f>
+        <v/>
+      </c>
+      <c r="Q21" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=HRx2lJQAAAAJ", "Scholar (HRx2lJQAAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="R21" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1815,12 +2061,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Kunal Garg</t>
+          <t>Beomjin Kwon</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1834,49 +2080,59 @@
         </is>
       </c>
       <c r="E22" s="3">
-        <f>HYPERLINK("mailto:kgarg24@asu.edu", "kgarg24@asu.edu")</f>
+        <f>HYPERLINK("mailto:kwon@asu.edu", "kwon@asu.edu")</f>
         <v/>
       </c>
       <c r="F22" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>optimization</t>
+          <t>aerospace, energy systems, heat transfer</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Distributed multi-agent motion planning and control, Provably safe control design using machine learning-based certificates, Foundation models in complex robotic tasks, Failure prediction from limited demonstrations, Human-robot interaction.</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>Control Systems, Dynamical Systems, Machine Learning, Nonlinear Dynamical Systems, Robotics</t>
-        </is>
-      </c>
+          <t>Transport phenomena in heat transfer systems Additive manufacturing Data-driven modeling and design</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>Garg's research interests include control synthesis for multi-agent coordination using control theory and machine learning.</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="b">
-        <v>1</v>
+          <t>Kwon aims to improve the energy conversion and transport systems through the fundamental insights into transport physics, and by exploiting additive manufacturing and data-driven approaches.</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D. Mechanical Engineering, University of Illinois at Urbana-Champaign 2013 | M.S. Mechanical Engineering, University of Illinois at Urbana-Champaign 2009 | B.S. Mechanical and Aerospace Engineering, Seoul National University 2008</t>
+        </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>vs3pl-8AAAAJ</t>
+          <t>551 E Tyler Mall ERC 363 (Tempe, AZ 85281)</t>
         </is>
       </c>
       <c r="M22" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/kgarg24", "https://search.asu.edu/profile/kgarg24")</f>
-        <v/>
-      </c>
-      <c r="N22" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=vs3pl-8AAAAJ", "Scholar (vs3pl-8AAAAJ)")</f>
-        <v/>
-      </c>
-      <c r="O22" s="3">
+        <f>HYPERLINK("http://sites.google.com/view/3denergy", "http://sites.google.com/view/3denergy")</f>
+        <v/>
+      </c>
+      <c r="N22" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>fs2d97sAAAAJ</t>
+        </is>
+      </c>
+      <c r="P22" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/bkwon2", "https://search.asu.edu/profile/bkwon2")</f>
+        <v/>
+      </c>
+      <c r="Q22" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=fs2d97sAAAAJ", "Scholar (fs2d97sAAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="R22" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1884,7 +2140,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Liping Wang</t>
+          <t>Hamidreza Marvi</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1903,41 +2159,55 @@
         </is>
       </c>
       <c r="E23" s="3">
-        <f>HYPERLINK("mailto:Liping.Wang@asu.edu", "Liping.Wang@asu.edu")</f>
+        <f>HYPERLINK("mailto:hmarvi@asu.edu", "hmarvi@asu.edu")</f>
         <v/>
       </c>
       <c r="F23" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>heat transfer</t>
+          <t>aerospace, robot, robotics</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Nanoscale heat transfer, metamaterials, plasmonics, and nanophotonics with an emphasis on solar thermal energy harvesting using plasmonic-enhanced light trapping for photovolatics, as well as near-field enhancement and spectral control of radiation for thermophotovoltaic energy conversion. Other research interests involve electronic cooling, MEMS, and bio-sensing.</t>
+          <t>Bio-inspired robotics Soft robotics Magnetic micro-robotics Mechanics of animal locomotion</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>Wang research interests include selective control of thermal emission/absorption using meta-materials for energy harvesting and near-field radiation heat transfer enhancement between meta-materials for thermophotovoltaics.</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="b">
-        <v>1</v>
+          <t>Marvi would like to develop bio-inspired robotic systems and programmable interfacial structures for search and rescue, exploratory and medical applications.</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D. Mechanical Engineering, Georgia Institute of Technology, Atlanta 2013 | M.S. Mechanical Engineering, Clemson University, SC 2009 | M.S. Biomedical Engineering, Sharif University of Technology, Tehran, Iran 2007 | B.S. Mechanical Engineering, Iran University of Science and Technology, Tehran 2004</t>
+        </is>
       </c>
       <c r="L23" s="2" t="inlineStr"/>
       <c r="M23" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/lwang78", "https://search.asu.edu/profile/lwang78")</f>
-        <v/>
-      </c>
-      <c r="N23" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Liping%20Wang%20Arizona%20State%20University", "Google Scholar Search")</f>
-        <v/>
-      </c>
-      <c r="O23" s="3">
+        <f>HYPERLINK("http://birth.asu.edu", "http://birth.asu.edu")</f>
+        <v/>
+      </c>
+      <c r="N23" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>00Fepb0AAAAJ</t>
+        </is>
+      </c>
+      <c r="P23" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/hmarvi", "https://search.asu.edu/profile/hmarvi")</f>
+        <v/>
+      </c>
+      <c r="Q23" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=00Fepb0AAAAJ", "Scholar (00Fepb0AAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="R23" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1945,7 +2215,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Matthew Peet</t>
+          <t>Hyunglae Lee</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1964,45 +2234,51 @@
         </is>
       </c>
       <c r="E24" s="3">
-        <f>HYPERLINK("mailto:mpeet@asu.edu", "mpeet@asu.edu")</f>
+        <f>HYPERLINK("mailto:Hyunglae.Lee@asu.edu", "Hyunglae.Lee@asu.edu")</f>
         <v/>
       </c>
       <c r="F24" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>optimization</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>The intersection of computer science and control including convex optimization, artificial intelligence, and manipulation of delayed and PDE systems. The understanding and regulation of complex dynamical systems such as the motion of plasma in nuclear fusion reactors, autoregulation in the human immune response, and the motion of spacecraft in orbit.</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>Control Systems, Dynamical Systems Theory, Aerospace Engineering, Algorithm Development, Dynamical Systems, Nonlinear Dynamical Systems, Mathematical and System Dynamics Modeling, Immunology</t>
-        </is>
-      </c>
+          <t>aerospace, robot, robotics</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>Peet's current research interests are in the role of computation as it is applied to the understanding and control of complex and large-scale systems.</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L24" s="2" t="inlineStr"/>
+          <t>Lee's research interests include physical human-robot interaction, neuromuscular control of human movement, robot-aided neurorehabilitation, bio-inspired robotics and system identification for physiological systems.</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>B.S. Mechanical and Aerospace Engineering, Seoul National University (2002) M.S. Mechanical and Aerospace Engineering, Seoul National University (2004) Ph.D Mechanical Engineering, Massachusetts Institute of Technology (2013)</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>Campus: Tempe</t>
+        </is>
+      </c>
       <c r="M24" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/mpeet", "https://search.asu.edu/profile/mpeet")</f>
-        <v/>
-      </c>
-      <c r="N24" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Matthew%20Peet%20Arizona%20State%20University", "Google Scholar Search")</f>
-        <v/>
-      </c>
-      <c r="O24" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/hlee", "https://faculty.engineering.asu.edu/hlee")</f>
+        <v/>
+      </c>
+      <c r="N24" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O24" s="2" t="inlineStr"/>
+      <c r="P24" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/hlee234", "https://search.asu.edu/profile/hlee234")</f>
+        <v/>
+      </c>
+      <c r="Q24" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Hyunglae%20Lee%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="R24" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2010,12 +2286,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Minglei Qu</t>
+          <t>Leila Ladani</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Professor</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2029,45 +2305,55 @@
         </is>
       </c>
       <c r="E25" s="3">
-        <f>HYPERLINK("mailto:minglei.qu@asu.edu", "minglei.qu@asu.edu")</f>
+        <f>HYPERLINK("mailto:ladani@asu.edu", "ladani@asu.edu")</f>
         <v/>
       </c>
       <c r="F25" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>instability</t>
+          <t>aerospace, materials, solid mechanics</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Metal additive manufacturing, in-situ synchrotron X-ray and neutron characterization, non-equilibrium phase transformation, metal matrix composites. Selected Publications M. Qu , J. Yuan, Q. Guo, A. Nabaa, L. I. Escano, J. Huang, Q. Li, L. Chen. Achieving uniformly refined grain structure in metal additive manufacturing: Experimental demonstration and analytical model development. Additive Manufacturing 108 (2025) 104805. M. Qu , D. Yu, J. Yuan, L. Chen, K. An, Y. Chen. Multi-stage load partitioning in additively manufactured Al6061+TiC nanocomposite characterized by in-situ neutron diffraction. Additive Manufacturing, 96 (2024) 104584. M. Qu , J. Yuan, A. Nabaa, J. Huang, C. A. Chuang, L. Chen. Melting and solidification dynamics during laser additive manufacturing of reaction-based metal matrix composites uncovered by in-situ synchrotron X-ray diffraction. Acta Materialia , 271 (2024) 119875. M. Qu , Q. Guo, L. I. Escano, A. Nabaa, S. M. H. Hojjatzadeh, Z. A. Young, L. Chen. Controlling process instability for defect lean metal additive manufacturing. Nature Communications , 13 (2022) 1079. M. Qu , Q. Guo, L. I. Escano, A. Nabaa, K. Fezzaa, L. Chen. Nanoparticle-enabled increase of energy efficiency during laser metal additive manufacturing. Additive Manufacturing , 60 (2022) 103242. M. Qu , Q.Guo, L. I. Escano, J. Yuan, S. J. Clark, K. Fezzaa, L. Chen. Controlling melt flow by nanoparticles to eliminate surface wave induced surface fluctuation. Additive Manufacturing , 59 (2022) 103081.</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr"/>
+          <t>Manufacturing process simulation and modeling and experiments Additive manufacturing Micro/nano manufacturing Microelectronic packaging Application of AI in manufacturing Mechanic of metallic materials Materials characterization Fatigue and damage modeling and simulation</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Additive Manufacturing, Manufacturing Engineering</t>
+        </is>
+      </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>Minglei Qu is an Assistant Professor of Mechanical Engineering and a graduate faculty of Materials Science and Engineering in the School for Engineering of Matter, Transport and Energy at ASU. His research lies at the intersection of metal additive manufacturing, in-situ characterization, and materials science. By utilizing advanced in-situ characterization tools, including synchrotron X-ray im...</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>9LWNC50AAAAJ</t>
-        </is>
-      </c>
+          <t>Dr. Ladani is a Professor of Mechanical and Aerospace Engineering at Arizona State University.</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>PhD. Mechanical Engineering, University of Maryland-College Park 2007 | M.S. Mechanical Engineering, University of Maryland-College Park 2005 | PhD. Student, Mechanical Engineering, Isfahan University of Technology, Iran 2001-2002 | M.S. Mechanical Engineering, Isfahan University of Technology, Iran 2001 | B.S. Mechanical Engineering, Isfahan University of Technology, Iran 1999</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/mingleiq", "https://search.asu.edu/profile/mingleiq")</f>
-        <v/>
-      </c>
-      <c r="N25" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=9LWNC50AAAAJ", "Scholar (9LWNC50AAAAJ)")</f>
-        <v/>
-      </c>
-      <c r="O25" s="3">
+        <f>HYPERLINK("https://magic.asu.edu/", "https://magic.asu.edu/")</f>
+        <v/>
+      </c>
+      <c r="N25" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O25" s="2" t="inlineStr"/>
+      <c r="P25" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/ljannesa", "https://search.asu.edu/profile/ljannesa")</f>
+        <v/>
+      </c>
+      <c r="Q25" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Leila%20Ladani%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="R25" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2075,12 +2361,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Robert Wang</t>
+          <t>Patrick Phelan</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Professor</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2094,49 +2380,56 @@
         </is>
       </c>
       <c r="E26" s="3">
-        <f>HYPERLINK("mailto:rywang@asu.edu", "rywang@asu.edu")</f>
+        <f>HYPERLINK("mailto:phelan@asu.edu", "phelan@asu.edu")</f>
         <v/>
       </c>
       <c r="F26" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>heat transfer</t>
+          <t>aerospace, energy systems, thermal</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>My research group is an interdisciplinary nanoengineering team that focuses on manipulating material properties for thermal energy applications. Some of our focus areas are thermoelectric power generation, thermal storage media, heat transfer, and phonon optics. To achieve our objectives, we custom-design materials using colloidal nanoparticles, chemical precursors, and nanocomposites.</t>
+          <t>Thermal engineering, sustainable energy systems, energy management, sustainable cooling systems.</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Mechanical Engineering, Energy, Renewable Energy, Energy and Sustainability, Clean Energy, Energy Efficiency Technologies, Materials Science and Engineering, Chemical Engineering, Nanoengineering, Nanoscience, Nanotechnology, Solid State Physics, Thin Film Materials, Semiconductors, Chemistry, Physics</t>
+          <t>Building Technology, Solar Energy Systems, Energy Efficiency Technologies, Mechanical Engineering</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>Wang's research interests include thermal energy conversion, storage, and transport in nanostructured materials; thermoelectric power generation; thermal storage media; heat transfer, and phonon optics</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="b">
-        <v>1</v>
+          <t>Phelan researches and teaches in the area of sustainable energy, thermal transport and thermal management.</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Postdoctoral Fellow, Tokyo Institute of Technology, Japan 1990-1992 | Ph.D. Mechanical Engineering, University of California, Berkeley 1990 | M.S. Mechanical Engineering, Massachusetts Institute of Technology 1987 | B. S. Mechanical Engineering, Tulane University, New Orleans, LA 1985</t>
+        </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>LaUdx9gAAAAJ</t>
-        </is>
-      </c>
-      <c r="M26" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/rywang", "https://search.asu.edu/profile/rywang")</f>
-        <v/>
-      </c>
-      <c r="N26" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=LaUdx9gAAAAJ", "Scholar (LaUdx9gAAAAJ)")</f>
-        <v/>
-      </c>
-      <c r="O26" s="3">
+          <t>ENGRC 463 (TEMPE, AZ 85287-6106)</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O26" s="2" t="inlineStr"/>
+      <c r="P26" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/pphelan", "https://search.asu.edu/profile/pphelan")</f>
+        <v/>
+      </c>
+      <c r="Q26" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Patrick%20Phelan%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="R26" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2144,12 +2437,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Ronald Calhoun</t>
+          <t>Yulia Peet</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Professor</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2163,37 +2456,51 @@
         </is>
       </c>
       <c r="E27" s="3">
-        <f>HYPERLINK("mailto:Ronald.Calhoun@asu.edu", "Ronald.Calhoun@asu.edu")</f>
+        <f>HYPERLINK("mailto:ypeet@asu.edu", "ypeet@asu.edu")</f>
         <v/>
       </c>
       <c r="F27" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>fluid dynamics</t>
+          <t>aerospace, fluid mechanics, turbulence</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr"/>
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>Calhoun’s research interests are in fluid dynamics; atmospheric sciences; boundary layer; wind energy and remote sensing.</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="b">
-        <v>1</v>
+          <t>Yulia Peet is an associate professor of aerospace and mechanical engineering in the School for Engineering of Matter, Transport and Energy with the Ira A. Fulton Schools of Engineering at Arizona State University. Her Ph.D. degree is in Aeronautics and Astronautics from Stanford (2006), M.S. and B.S. degrees are from Moscow Institute of Physics and Technology (1999 and 1997). Her previous appoi...</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D. Aeronautics and Astronautics, Stanford University 2006 | M.S. Management, State University Higher School of Economics, Moscow, Russia 2000 | M.S. Aeromechanics and Flight Engineering, Moscow Institute of Physics and Technology, Russia 1999 | B.S. Applied Mathematics and Physics, Moscow Institute of Physics and Technology, Russia 1997</t>
+        </is>
       </c>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/rcalhou", "https://search.asu.edu/profile/rcalhou")</f>
-        <v/>
-      </c>
-      <c r="N27" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ronald%20Calhoun%20Arizona%20State%20University", "Google Scholar Search")</f>
-        <v/>
-      </c>
-      <c r="O27" s="3">
+        <f>HYPERLINK("https://isim.asu.edu", "https://isim.asu.edu")</f>
+        <v/>
+      </c>
+      <c r="N27" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>_6o8MrUAAAAJ</t>
+        </is>
+      </c>
+      <c r="P27" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/ypeet", "https://search.asu.edu/profile/ypeet")</f>
+        <v/>
+      </c>
+      <c r="Q27" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=_6o8MrUAAAAJ", "Scholar (_6o8MrUAAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="R27" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2201,12 +2508,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Spring Berman</t>
+          <t>Houlong Zhuang</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2220,49 +2527,56 @@
         </is>
       </c>
       <c r="E28" s="3">
-        <f>HYPERLINK("mailto:Spring.Berman@asu.edu", "Spring.Berman@asu.edu")</f>
+        <f>HYPERLINK("mailto:zhuanghl@asu.edu", "zhuanghl@asu.edu")</f>
         <v/>
       </c>
       <c r="F28" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>optimization</t>
+          <t>aerospace, materials</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Modeling, analysis, control, and optimization of multi-robot systems including robotic swarms; analysis of collective behaviors in biology and biologically-inspired control of distributed systems</t>
+          <t>Quantum simulations Machine learning Quantum computing</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Systems and Control Theory, Mechanical Engineering, Autonomous Technologies, Robotics</t>
+          <t>Artificial Photosynthesis, Chemistry, Computational Physics, Machine Learning, Materials Science, Metals, Nanoscience, Semiconductors</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Dr. Berman directs the Autonomous Collective Systems Laboratory at ASU, which models and analyzes behaviors in biological and engineered collectives and designs control strategies for multi-robot systems.</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>KKup0OgAAAAJ</t>
-        </is>
-      </c>
-      <c r="M28" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/smberma2", "https://search.asu.edu/profile/smberma2")</f>
-        <v/>
-      </c>
-      <c r="N28" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=KKup0OgAAAAJ", "Scholar (KKup0OgAAAAJ)")</f>
-        <v/>
-      </c>
-      <c r="O28" s="3">
+          <t>Dr. Houlong Zhuang is an associate professor in the School for Engineering of Matter, Transport and Energy at ASU. He received his doctorate in materials science and engineering at Cornell University. Prior to ASU, Dr. Zhuang was a postdoctoral researcher at Princeton University. Dr. Zhuang’s current research interests are quantum mechanical simulations, machine learning, and quantum computing.</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>Postdoc, Department of Mechanical and Aerospace Engineering, Princeton University Postdoc, Center for Nanophase Materials Sciences, Oak Ridge National Laboratory Ph.D., Major: Materials Science and Engineering; Minor: Applied Engineering Physics, Cornell University M.S., Major: Materials Science and Engineering; Minor: Applied Engineering Physics, Cornell University M.Phil., Mechanical Engineering, The University of Hong Kong B.Eng., Materials Science and Engineering, Hunan University</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>4yYKCpUAAAAJ</t>
+        </is>
+      </c>
+      <c r="P28" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/hzhuang7", "https://search.asu.edu/profile/hzhuang7")</f>
+        <v/>
+      </c>
+      <c r="Q28" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=4yYKCpUAAAAJ", "Scholar (4yYKCpUAAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="R28" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2270,12 +2584,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Tianyu Yang</t>
+          <t>Huei-Ping Huang</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2289,37 +2603,51 @@
         </is>
       </c>
       <c r="E29" s="3">
-        <f>HYPERLINK("mailto:Tianyu.Yang@asu.edu", "Tianyu.Yang@asu.edu")</f>
+        <f>HYPERLINK("mailto:Huei-Ping.Huang@asu.edu", "Huei-Ping.Huang@asu.edu")</f>
         <v/>
       </c>
       <c r="F29" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>heat transfer</t>
+          <t>aerospace, fluid dynamics</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr"/>
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>Yang studies heat transfer, thermal management of electronics, and biomedical devices. She has published multiple research papers in major scientific journals.</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L29" s="2" t="inlineStr"/>
+          <t>Huang's research interests are geophysical and environmental fluid dynamics, numerical simulation of atmospheric and oceanic flows, Earth system remote sensing, and climate change.</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D. University of Illinois-Urbana-Champaign 1997 | M.S. National Taiwan University 1989 | B.S. National Central University,Taiwan 1987</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>ENGRC 359 (Tempe, AZ 85287-6106)</t>
+        </is>
+      </c>
       <c r="M29" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/tyang123", "https://search.asu.edu/profile/tyang123")</f>
-        <v/>
-      </c>
-      <c r="N29" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Tianyu%20Yang%20Arizona%20State%20University", "Google Scholar Search")</f>
-        <v/>
-      </c>
-      <c r="O29" s="3">
+        <f>HYPERLINK("http://www.public.asu.edu/~hhuang38", "http://www.public.asu.edu/~hhuang38")</f>
+        <v/>
+      </c>
+      <c r="N29" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O29" s="2" t="inlineStr"/>
+      <c r="P29" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/hhuang38", "https://search.asu.edu/profile/hhuang38")</f>
+        <v/>
+      </c>
+      <c r="Q29" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Huei-Ping%20Huang%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="R29" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2327,7 +2655,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Yi Ren</t>
+          <t>Jagannathan Rajagopalan</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -2346,37 +2674,63 @@
         </is>
       </c>
       <c r="E30" s="3">
-        <f>HYPERLINK("mailto:yiren@asu.edu", "yiren@asu.edu")</f>
+        <f>HYPERLINK("mailto:Jagannathan.Rajagopalan@asu.edu", "Jagannathan.Rajagopalan@asu.edu")</f>
         <v/>
       </c>
       <c r="F30" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>optimization</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="inlineStr"/>
+          <t>aerospace, materials</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Synthesis of nanocrystalline materials with tailored microstructures, Mechanics of nanostructured metal and alloy films, MEMS for in situ materials testing, Polymer based micro devices for cell mechanics and biohybrid platforms</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Thin Film Materials, Materials Science, Mechanical Engineering</t>
+        </is>
+      </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>Ren’s current research interests include optimization, product/configuration design, human-computer interaction and machine learning.</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L30" s="2" t="inlineStr"/>
+          <t>Rajagopalan's research focuses on the mechanics of nanoscale materials, cells and biological systems.</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D. Mechanical Science and Engineering, University of Illinois at Urbana-Champaign, Urbana, IL 2009 | M.Tech. Mechanical Engineering, Indian Institute of Technology Madras, Chennai, India 2004 | B.Tech. Mechanical Engineering, Indian Institute of Technology Madras, Chennai, India 2004</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>ENGRC 355 (Tempe, AZ 85287-6106)</t>
+        </is>
+      </c>
       <c r="M30" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/yren32", "https://search.asu.edu/profile/yren32")</f>
-        <v/>
-      </c>
-      <c r="N30" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Yi%20Ren%20Arizona%20State%20University", "Google Scholar Search")</f>
-        <v/>
-      </c>
-      <c r="O30" s="3">
+        <f>HYPERLINK("http://faculty.engineering.asu.edu/jagan/", "http://faculty.engineering.asu.edu/jagan/")</f>
+        <v/>
+      </c>
+      <c r="N30" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>ClqRIhIAAAAJ</t>
+        </is>
+      </c>
+      <c r="P30" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/jrajago1", "https://search.asu.edu/profile/jrajago1")</f>
+        <v/>
+      </c>
+      <c r="Q30" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=ClqRIhIAAAAJ", "Scholar (ClqRIhIAAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="R30" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2384,12 +2738,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Yongming Liu</t>
+          <t>Konrad Rykaczewski</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2403,41 +2757,917 @@
         </is>
       </c>
       <c r="E31" s="3">
-        <f>HYPERLINK("mailto:Yongming.Liu@asu.edu", "Yongming.Liu@asu.edu")</f>
+        <f>HYPERLINK("mailto:konradr@asu.edu", "konradr@asu.edu")</f>
         <v/>
       </c>
       <c r="F31" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>uncertainty quantification</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>Yongming Liu is a professor of aerospace and mechanical engineering with the School for Engineering of Matter, Transport and Energy at Arizona State University. Fatigue and fracture of engineering materials and structures, probabilistic computational mechanics, risk assessment and management, multi-physics damage modeling and structural durability, multi-scale uncertainty quantification and propagation, imaging-based experimental testing, diagnostics and prognostics</t>
-        </is>
-      </c>
+          <t>materials, thermal</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>Liu heads the Prognostic Analysis and Reliability Assessment Laboratory (PARA). He joined ASU in 2012.</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="b">
-        <v>1</v>
+          <t>Rykaczewski's research focuses on development of soft thermal materials and system as well as studying human thermal exposure in extreme heat.</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D. Mechanical Engineering, Georgia Institute of Technology 2009 | M.S. Mechanical Engineering, Georgia Institute of Technology 2007 | B.S. Mechanical Engineering, Georgia Institute of Technology 2005</t>
+        </is>
       </c>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="3">
+        <f>HYPERLINK("http://faculty.engineering.asu.edu/konrad/", "http://faculty.engineering.asu.edu/konrad/")</f>
+        <v/>
+      </c>
+      <c r="N31" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>SWeAf4UAAAAJ</t>
+        </is>
+      </c>
+      <c r="P31" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/krykacze", "https://search.asu.edu/profile/krykacze")</f>
+        <v/>
+      </c>
+      <c r="Q31" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=SWeAf4UAAAAJ", "Scholar (SWeAf4UAAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="R31" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Minglei Qu</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Professor</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Aerospace &amp; Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Arizona State University</t>
+        </is>
+      </c>
+      <c r="E32" s="3">
+        <f>HYPERLINK("mailto:minglei.qu@asu.edu", "minglei.qu@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>composites, materials</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Metal additive manufacturing, in-situ synchrotron X-ray and neutron characterization, non-equilibrium phase transformation, metal matrix composites. Selected Publications M. Qu , J. Yuan, Q. Guo, A. Nabaa, L. I. Escano, J. Huang, Q. Li, L. Chen. Achieving uniformly refined grain structure in metal additive manufacturing: Experimental demonstration and analytical model development. Additive Manufacturing 108 (2025) 104805. M. Qu , D. Yu, J. Yuan, L. Chen, K. An, Y. Chen. Multi-stage load partitioning in additively manufactured Al6061+TiC nanocomposite characterized by in-situ neutron diffraction. Additive Manufacturing, 96 (2024) 104584. M. Qu , J. Yuan, A. Nabaa, J. Huang, C. A. Chuang, L. Chen. Melting and solidification dynamics during laser additive manufacturing of reaction-based metal matrix composites uncovered by in-situ synchrotron X-ray diffraction. Acta Materialia , 271 (2024) 119875. M. Qu , Q. Guo, L. I. Escano, A. Nabaa, S. M. H. Hojjatzadeh, Z. A. Young, L. Chen. Controlling process instability for defect lean metal additive manufacturing. Nature Communications , 13 (2022) 1079. M. Qu , Q. Guo, L. I. Escano, A. Nabaa, K. Fezzaa, L. Chen. Nanoparticle-enabled increase of energy efficiency during laser metal additive manufacturing. Additive Manufacturing , 60 (2022) 103242. M. Qu , Q.Guo, L. I. Escano, J. Yuan, S. J. Clark, K. Fezzaa, L. Chen. Controlling melt flow by nanoparticles to eliminate surface wave induced surface fluctuation. Additive Manufacturing , 59 (2022) 103081.</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>Minglei Qu is an Assistant Professor of Mechanical Engineering and a graduate faculty of Materials Science and Engineering in the School for Engineering of Matter, Transport and Energy at ASU. His research lies at the intersection of metal additive manufacturing, in-situ characterization, and materials science. By utilizing advanced in-situ characterization tools, including synchrotron X-ray im...</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>PhD. Mechanical Engineering, University of Wisconsin-Madison 2023</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>9LWNC50AAAAJ</t>
+        </is>
+      </c>
+      <c r="P32" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/mingleiq", "https://search.asu.edu/profile/mingleiq")</f>
+        <v/>
+      </c>
+      <c r="Q32" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=9LWNC50AAAAJ", "Scholar (9LWNC50AAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="R32" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Qiong Nian</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Aerospace &amp; Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Arizona State University</t>
+        </is>
+      </c>
+      <c r="E33" s="3">
+        <f>HYPERLINK("mailto:Qiong.Nian@asu.edu", "Qiong.Nian@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>aerospace, materials</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Nanomanufacturing, additive manufacturing, laser-based material processing, laser matter interaction and physics simulation; inkjet printing of functional materials; and 2D materials fabrication for energy storage and bio-sensors.</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Additive Manufacturing, Manufacturing Engineering, Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>Nian's research interests include additive manufacturing, laser-based manufacturing and material processing, laser matter interaction and physics simulation, and functional materials for energy storage and bio-sensors.</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D. Manufacturing, Industrial Engineering, Purdue University 2015 | B.Sc. Materials Science and Engineering, University of Science and Technology of China 2009</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>Campus: Tempe</t>
+        </is>
+      </c>
+      <c r="M33" s="3">
+        <f>HYPERLINK("https://mmmplab.engineering.asu.edu/", "https://mmmplab.engineering.asu.edu/")</f>
+        <v/>
+      </c>
+      <c r="N33" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O33" s="2" t="inlineStr"/>
+      <c r="P33" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/qnian", "https://search.asu.edu/profile/qnian")</f>
+        <v/>
+      </c>
+      <c r="Q33" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Qiong%20Nian%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="R33" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Ronald Calhoun</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Aerospace &amp; Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Arizona State University</t>
+        </is>
+      </c>
+      <c r="E34" s="3">
+        <f>HYPERLINK("mailto:Ronald.Calhoun@asu.edu", "Ronald.Calhoun@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>boundary layer, fluid dynamics</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>Calhoun’s research interests are in fluid dynamics; atmospheric sciences; boundary layer; wind energy and remote sensing.</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D. Civil and Environmental Engineering, Stanford University 1998 | Engineer. Civil and Environmental Engineering, Stanford University 1993 | M.S. Civil and Environmental Engineering, Stanford University 1992 | B.S. Symbolic Systems, Stanford University 1989</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>Goldwater 466 (TEMPE, AZ 85287-6106)</t>
+        </is>
+      </c>
+      <c r="M34" s="3">
+        <f>HYPERLINK("https://windlab.engineering.asu.edu/ronald-calhoun/", "https://windlab.engineering.asu.edu/ronald-calhoun/")</f>
+        <v/>
+      </c>
+      <c r="N34" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O34" s="2" t="inlineStr"/>
+      <c r="P34" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/rcalhou", "https://search.asu.edu/profile/rcalhou")</f>
+        <v/>
+      </c>
+      <c r="Q34" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ronald%20Calhoun%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="R34" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Wanxin Jin</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Professor</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Aerospace &amp; Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Arizona State University</t>
+        </is>
+      </c>
+      <c r="E35" s="3">
+        <f>HYPERLINK("mailto:wjin@asu.edu", "wjin@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>robot, robotics</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>https://irislab.tech/</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>Jin's research includes robotics, control and machine learning, with a focus on the autonomy of robots interacting with humans and objects.</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D., Purdue University 2021 | Master of Science, Harbin Institute of Technology, 2016 | Bachelor of Engineering, Harbin Institute of Technology, 2014</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="3">
+        <f>HYPERLINK("https://irislab.tech/", "https://irislab.tech/")</f>
+        <v/>
+      </c>
+      <c r="N35" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>SoEC4h4AAAAJ</t>
+        </is>
+      </c>
+      <c r="P35" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/wjin34", "https://search.asu.edu/profile/wjin34")</f>
+        <v/>
+      </c>
+      <c r="Q35" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=SoEC4h4AAAAJ", "Scholar (SoEC4h4AAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="R35" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Yongming Liu</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Aerospace &amp; Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Arizona State University</t>
+        </is>
+      </c>
+      <c r="E36" s="3">
+        <f>HYPERLINK("mailto:Yongming.Liu@asu.edu", "Yongming.Liu@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>aerospace, materials</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Yongming Liu is a professor of aerospace and mechanical engineering with the School for Engineering of Matter, Transport and Energy at Arizona State University. Fatigue and fracture of engineering materials and structures, probabilistic computational mechanics, risk assessment and management, multi-physics damage modeling and structural durability, multi-scale uncertainty quantification and propagation, imaging-based experimental testing, diagnostics and prognostics</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>Liu heads the Prognostic Analysis and Reliability Assessment Laboratory (PARA). He joined ASU in 2012.</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D. Civil Engineering, Vanderbilt University 2006 | M.S. Structural Engineering, Tongji University, Shanghai, China 2002 | B.S. Structural Engineering, Tongji University, Shanghai, China 1999</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>ENGRC 409 (Tempe, AZ 85287-6106)</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O36" s="2" t="inlineStr"/>
+      <c r="P36" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/yliu35", "https://search.asu.edu/profile/yliu35")</f>
         <v/>
       </c>
-      <c r="N31" s="3">
+      <c r="Q36" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Yongming%20Liu%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="O31" s="3">
+      <c r="R36" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Cindy (Xiangjia) Li</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Aerospace &amp; Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Arizona State University</t>
+        </is>
+      </c>
+      <c r="E37" s="3">
+        <f>HYPERLINK("mailto:xiangjia.li@asu.edu", "xiangjia.li@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Biomimetic Additive Manufacturing (3D Printing); Bioinspired Material and Structure Design; Stereolithography; Photopolymerization based 3D Printing; Multi-material and Multi-scale 3D printing; Biofabrication; Biomaterial; Ceramic Printing; Nanocomposite Printing; Physical Field Assisted Printing; 4D Printing; Flexible Sensor; Biomedical Device; Tissue Repair and Regeneration.</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Ceramic Technology, Mechanics of Composite Materials, Mechanical Engineering, Biomimicry, 3D Printing, Additive Manufacturing, Manufacturing Engineering</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>Xiangjia (Cindy) Li is an Associate Professor at Arizona State University. Her research focuses on multiscale, multimaterial additive manufacturing and bioinspired design for functional materials and devices.</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D. in Industrial and Systems Engineering, University of Southern California, 2019 M.S. in Computer Science, University of Southern California, 2019 M.S. in Manufacturing Engineering, Nanjing University of Aeronautics and Astronautics, 2014 B.E. in Mechanical Engineering and Automation, Nanjing University of Aeronautics and Astronautics, 2011</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="3">
+        <f>HYPERLINK("https://www.cindyxjli.com/", "https://www.cindyxjli.com/")</f>
+        <v/>
+      </c>
+      <c r="N37" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>tGQzHJIAAAAJ</t>
+        </is>
+      </c>
+      <c r="P37" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/xiangji5", "https://search.asu.edu/profile/xiangji5")</f>
+        <v/>
+      </c>
+      <c r="Q37" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=tGQzHJIAAAAJ", "Scholar (tGQzHJIAAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="R37" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>James Middleton</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Aerospace &amp; Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Arizona State University</t>
+        </is>
+      </c>
+      <c r="E38" s="3">
+        <f>HYPERLINK("mailto:jimbo@asu.edu", "jimbo@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>aerospace</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Student learning of mathematical concepts. Motivation and mathematics learning. Teacher change. Applications of technology to mathematics teaching and learning.</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>Middleton’s research interests focus in the following areas where he has published extensively: children’s mathematical thinking; teacher and student motivation in mathematics; and teacher change in mathematics.</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D. Educational Psychology, University of Wisconsin-Madison 1992</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O38" s="2" t="inlineStr"/>
+      <c r="P38" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/jimbo", "https://search.asu.edu/profile/jimbo")</f>
+        <v/>
+      </c>
+      <c r="Q38" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=James%20Middleton%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="R38" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Lin Li</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Aerospace &amp; Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Arizona State University</t>
+        </is>
+      </c>
+      <c r="E39" s="3">
+        <f>HYPERLINK("mailto:Lin.Li.10@asu.edu", "Lin.Li.10@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>Li uses multiscale material mechanics models, computational and data tools to explore advanced materials for extreme environments.</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>PhD The Ohio State University</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>Campus: Tempe</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O39" s="2" t="inlineStr"/>
+      <c r="P39" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/linli25", "https://search.asu.edu/profile/linli25")</f>
+        <v/>
+      </c>
+      <c r="Q39" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Lin%20Li%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="R39" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Marc Mignolet</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Aerospace &amp; Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Arizona State University</t>
+        </is>
+      </c>
+      <c r="E40" s="3">
+        <f>HYPERLINK("mailto:marc.mignolet@asu.edu", "marc.mignolet@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>aerospace</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>Mignolet's research interests include structural dynamics, vibrations, modeling of uncertainty in structures and stochastic multiscale analyses.</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D. Rice University 1987</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O40" s="2" t="inlineStr"/>
+      <c r="P40" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/marc03", "https://search.asu.edu/profile/marc03")</f>
+        <v/>
+      </c>
+      <c r="Q40" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Marc%20Mignolet%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="R40" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Pedro Peralta</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Aerospace &amp; Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Arizona State University</t>
+        </is>
+      </c>
+      <c r="E41" s="3">
+        <f>HYPERLINK("mailto:pperalta@asu.edu", "pperalta@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>Peralta's research focuses on mechanics of materials, fatigue and fracture of metallic alloys, dynamic and shock loading of metallic and intermetallic materials.</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D. Materials Science and Engineering, University of Pennsylvania | M.S. Mechanical Engineering and Applied Mechanics, University of Pennsylvania | Bachelor’s degree. Mechanical Engineering, Universidad Simón Bolívar, Caracas, Venezuela</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/pperalta/", "https://faculty.engineering.asu.edu/pperalta/")</f>
+        <v/>
+      </c>
+      <c r="N41" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O41" s="2" t="inlineStr"/>
+      <c r="P41" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/pperalta", "https://search.asu.edu/profile/pperalta")</f>
+        <v/>
+      </c>
+      <c r="Q41" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Pedro%20Peralta%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="R41" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Wonmo Kang</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Aerospace &amp; Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Arizona State University</t>
+        </is>
+      </c>
+      <c r="E42" s="3">
+        <f>HYPERLINK("mailto:Wonmo.Kang@asu.edu", "Wonmo.Kang@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Mechanics of Composite Materials, Micro and Nanoscale Bioengineering, Nanotechnology, Thin Film Materials</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Mechanics of Composite Materials, Micro and Nanoscale Bioengineering, Nanotechnology, Thin Film Materials</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>Kang's current research interests include functional materials for energy/manufacturing applications and biomaterials/biomechanics for injury and wound healing mechanisms.</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D. Mechanical Science and Engineering, University of Illinois at Urbana-Champaign 2012</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>Campus: Tempe</t>
+        </is>
+      </c>
+      <c r="M42" s="3">
+        <f>HYPERLINK("https://wonmokang3.wixsite.com/website", "https://wonmokang3.wixsite.com/website")</f>
+        <v/>
+      </c>
+      <c r="N42" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>bHyyOTAAAAAJ</t>
+        </is>
+      </c>
+      <c r="P42" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/wkang16", "https://search.asu.edu/profile/wkang16")</f>
+        <v/>
+      </c>
+      <c r="Q42" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=bHyyOTAAAAAJ", "Scholar (bHyyOTAAAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="R42" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Yi Ren</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Aerospace &amp; Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Arizona State University</t>
+        </is>
+      </c>
+      <c r="E43" s="3">
+        <f>HYPERLINK("mailto:yiren@asu.edu", "yiren@asu.edu")</f>
+        <v/>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>aerospace</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr"/>
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>Ren’s current research interests include optimization, product/configuration design, human-computer interaction and machine learning.</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D. Mechanical Engineering, University of Michigan 2011 | M.S. Mechanical Engineering, University of Michigan 2009 | B.S. Automative Engineering, Tsinghua University, China 2007</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>GWC 464 (Tempe, AZ 85287-6106)</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O43" s="2" t="inlineStr"/>
+      <c r="P43" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/yren32", "https://search.asu.edu/profile/yren32")</f>
+        <v/>
+      </c>
+      <c r="Q43" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Yi%20Ren%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="R43" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2446,124 +3676,198 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N7" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N8" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N11" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N12" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N28" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R2" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P3" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R3" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P4" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q4" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R4" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P5" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q5" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R5" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P6" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q6" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R6" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P7" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R7" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P8" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R8" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P9" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R9" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P10" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R10" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R11" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P12" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R12" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R13" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P14" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R14" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P15" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R15" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P16" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R16" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P17" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q17" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R17" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P18" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q18" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R18" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q19" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R19" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P20" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q20" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R20" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P21" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q21" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R21" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P22" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q22" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R22" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P23" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q23" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R23" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P24" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q24" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R24" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P25" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q25" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R25" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P26" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q26" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R26" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P27" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q27" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R27" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P28" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q28" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R28" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P29" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q29" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R29" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P30" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q30" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R30" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P31" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q31" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R31" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P32" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q32" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R32" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P33" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q33" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R33" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P34" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q34" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R34" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P35" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q35" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R35" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P36" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q36" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R36" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P37" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q37" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R37" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P38" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q38" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R38" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P39" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q39" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R39" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P40" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q40" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R40" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P41" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q41" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R41" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P42" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q42" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R42" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P43" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q43" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R43" r:id="rId194"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2575,7 +3879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O54"/>
+  <dimension ref="A1:R49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2588,11 +3892,14 @@
     <col width="65" customWidth="1" min="8" max="8"/>
     <col width="65" customWidth="1" min="9" max="9"/>
     <col width="65" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="65" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="12" max="12"/>
     <col width="49" customWidth="1" min="13" max="13"/>
-    <col width="32" customWidth="1" min="14" max="14"/>
-    <col width="49" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="49" customWidth="1" min="16" max="16"/>
+    <col width="32" customWidth="1" min="17" max="17"/>
+    <col width="49" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2648,25 +3955,40 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>Education / Degrees</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Office Location</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Lab / Personal Website</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>Is Field Match</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Scholar ID</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Profile URL</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Google Scholar URL</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Directory URL</t>
         </is>
@@ -2675,12 +3997,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Jeonglae Kim</t>
+          <t>Liping Wang</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -2694,37 +4016,55 @@
         </is>
       </c>
       <c r="E2" s="3">
-        <f>HYPERLINK("mailto:jeokim@asu.edu", "jeokim@asu.edu")</f>
+        <f>HYPERLINK("mailto:Liping.Wang@asu.edu", "Liping.Wang@asu.edu")</f>
         <v/>
       </c>
       <c r="F2" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>aeroacoustics, flow control, high-performance computing, optimization, turbulence, turbulent flows</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr"/>
+          <t>aerospace, guidance, heat transfer, materials, metamaterials, radiation, thermal</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Nanoscale heat transfer, metamaterials, plasmonics, and nanophotonics with an emphasis on solar thermal energy harvesting using plasmonic-enhanced light trapping for photovolatics, as well as near-field enhancement and spectral control of radiation for thermophotovoltaic energy conversion. Other research interests involve electronic cooling, MEMS, and bio-sensing.</t>
+        </is>
+      </c>
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Kim's research interests include large-eddy simulation of high-speed turbulent flows with multi-physics, aeroacoustics, flow control and optimization.</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+          <t>Wang research interests include selective control of thermal emission/absorption using meta-materials for energy harvesting and near-field radiation heat transfer enhancement between meta-materials for thermophotovoltaics.</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D. Mechanical Engineering, Georgia Institute of Technology 2011 | M.S. Refrigeration and Cryogenic Engineering, Shanghai Institute of Technical Physics, Chinese  Academy of Sciences 2007 | B.E. Thermal Science and Energy Engineering, University of Science and Technology of China 2004</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>ENGRC 327 (Tempe, AZ 85287-6106)</t>
+        </is>
+      </c>
       <c r="M2" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/jkim520", "https://search.asu.edu/profile/jkim520")</f>
-        <v/>
-      </c>
-      <c r="N2" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Jeonglae%20Kim%20Arizona%20State%20University", "Google Scholar Search")</f>
-        <v/>
-      </c>
-      <c r="O2" s="3">
+        <f>HYPERLINK("http://faculty.engineering.asu.edu/lpwang", "http://faculty.engineering.asu.edu/lpwang")</f>
+        <v/>
+      </c>
+      <c r="N2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O2" s="2" t="inlineStr"/>
+      <c r="P2" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/lwang78", "https://search.asu.edu/profile/lwang78")</f>
+        <v/>
+      </c>
+      <c r="Q2" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Liping%20Wang%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="R2" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2732,12 +4072,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Werner Dahm</t>
+          <t>Mohamed Houssem Kasbaoui</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>SUM/WTR Faculty Research</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -2751,45 +4091,51 @@
         </is>
       </c>
       <c r="E3" s="3">
-        <f>HYPERLINK("mailto:Werner.Dahm@asu.edu", "Werner.Dahm@asu.edu")</f>
+        <f>HYPERLINK("mailto:houssem.kasbaoui@asu.edu", "houssem.kasbaoui@asu.edu")</f>
         <v/>
       </c>
       <c r="F3" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>combustion, computational physics, fluid dynamics, heat transfer, propulsion, turbulence</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Dr. Dahm specializes in fluid dynamics, thermodynamics, combustion, heat transfer, thermal sciences, propulsion, fuel efficiency, emissions, powertrains, and other areas relevant to a broad range of automotive, aerospace, and industrial applications. He is an author of over 200 refereed technical articles, conference papers, and technical publications, a holder of six U.S. and international patents, and has given over 260 technical presentations, including over 190 invited, plenary, and keynote lectures worldwide, on topics dealing with mechanical and aerospace engineering and defense science.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Aerospace Engineering, Applied Research, Computational Modeling, Computational Physics, Mechanical Engineering, Propulsion</t>
-        </is>
-      </c>
+          <t>aerospace, cfd, computational fluid dynamics, dns, fluid dynamics, multiphase flow, turbulent</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Werner J.A. Dahm has since 2010 been the ASU Foundation Professor of Mechanical and Aerospace Engineering, and also Professor Emeritus of Engineering at the University of Michigan where served for the previous 25 years.</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
+          <t>Kasbaoui's research interests include computational fluid dynamics, numerical methods, and massively parallel simulations of multiphase and particle-laden flows for environmental and aerospace applications.</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D.  Aerospace Engineering, Cornell University, 2017 | M.Sc.  Aerospace Engineering, Cornell University, 2015 | M.Sc.  Theoretical Physics, Université Paris-Sud, 2014 | Diplôme d'Ingénieur , Ecole Centrale Paris, 2013 | B.Sc.  Theoretical Physics, Université Paris-Sud, 2011</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Campus: Tempe</t>
+        </is>
+      </c>
       <c r="M3" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/wdahm", "https://search.asu.edu/profile/wdahm")</f>
-        <v/>
-      </c>
-      <c r="N3" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Werner%20Dahm%20Arizona%20State%20University", "Google Scholar Search")</f>
-        <v/>
-      </c>
-      <c r="O3" s="3">
+        <f>HYPERLINK("https://kasbaoui.bitbucket.io", "https://kasbaoui.bitbucket.io")</f>
+        <v/>
+      </c>
+      <c r="N3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O3" s="2" t="inlineStr"/>
+      <c r="P3" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/mkasbaou", "https://search.asu.edu/profile/mkasbaou")</f>
+        <v/>
+      </c>
+      <c r="Q3" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Mohamed%20Houssem%20Kasbaoui%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="R3" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2797,7 +4143,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Kangping Chen</t>
+          <t>Jay Oswald</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -2816,41 +4162,55 @@
         </is>
       </c>
       <c r="E4" s="3">
-        <f>HYPERLINK("mailto:k.p.chen@asu.edu", "k.p.chen@asu.edu")</f>
+        <f>HYPERLINK("mailto:joswald1@asu.edu", "joswald1@asu.edu")</f>
         <v/>
       </c>
       <c r="F4" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>computational fluid dynamics, drag reduction, fluid dynamics, fluid mechanics, multiphase flow</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
+          <t>estimation, finite element, materials, robot, robotics, solid mechanics</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Development of computational mechanics: finite element methods, molecular dynamics, multiscale methods, failure analysis, and material design.</t>
+        </is>
+      </c>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Chen’s research interests include multiphase flows, drag reduction, airplane de-icing, interfacial instabilities and flow in porous media.</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="b">
-        <v>1</v>
+          <t>Dr. Oswald develops computational and AI-driven methods for advanced manufacturing, including laser welding, automated inspection, robotics, and computational mechanics.</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D. Mechanical Engineering, Northwestern University, Evanston, IL 2011 | M.S. Mechanical Engineering, Case Western Reserve University, Cleveland, OH 2005 | B.S. Mechanical Engineering, Case Western Reserve University, Cleveland, OH 2004</t>
+        </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>xT-lX9sAAAAJ</t>
+          <t>ENGRC 353 (Tempe, AZ 85287-6106)</t>
         </is>
       </c>
       <c r="M4" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/asuchen", "https://search.asu.edu/profile/asuchen")</f>
-        <v/>
-      </c>
-      <c r="N4" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=xT-lX9sAAAAJ", "Scholar (xT-lX9sAAAAJ)")</f>
-        <v/>
-      </c>
-      <c r="O4" s="3">
+        <f>HYPERLINK("http://sparky.fulton.asu.edu/oswald/", "http://sparky.fulton.asu.edu/oswald/")</f>
+        <v/>
+      </c>
+      <c r="N4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O4" s="2" t="inlineStr"/>
+      <c r="P4" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/joswald1", "https://search.asu.edu/profile/joswald1")</f>
+        <v/>
+      </c>
+      <c r="Q4" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Jay%20Oswald%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="R4" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2858,12 +4218,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Kiran Ramesh</t>
+          <t>Jiefeng Sun</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -2877,45 +4237,63 @@
         </is>
       </c>
       <c r="E5" s="3">
-        <f>HYPERLINK("mailto:Kiran.Ramesh@asu.edu", "Kiran.Ramesh@asu.edu")</f>
+        <f>HYPERLINK("mailto:Jiefeng.Sun@asu.edu", "Jiefeng.Sun@asu.edu")</f>
         <v/>
       </c>
       <c r="F5" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>aerodynamics, flow control, fluid dynamics, turbulence, vortex dynamics</t>
+          <t>aerospace, autonomous, materials, robot, robotics, smart materials</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Unsteady aerodynamics, vortex dynamics, flow control, turbulence, separated flows</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr"/>
+          <t>Hire students to conduct research https://sunroboticslab.github.io</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Autonomous Technologies, Control Systems, Mechanical Engineering, Robotics</t>
+        </is>
+      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Ramesh's expertise is in unsteady fluid dynamics, vortex dynamics, turbulence and flow control.</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="b">
-        <v>1</v>
+          <t>Sun's research focuses on the design, dynamics, and control of soft robots and artificial muscles</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D. in Robotics and Control, Colorado State University, 2022 M.S. in Mechanical Engineering, Dalian University of Technology, 2017 B.S. in Mechanical Engineering, Lanzhou University of Technology, 2014</t>
+        </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>DKc-AgcAAAAJ</t>
+          <t>Campus: Tempe</t>
         </is>
       </c>
       <c r="M5" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/kramesh2", "https://search.asu.edu/profile/kramesh2")</f>
-        <v/>
-      </c>
-      <c r="N5" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=DKc-AgcAAAAJ", "Scholar (DKc-AgcAAAAJ)")</f>
-        <v/>
-      </c>
-      <c r="O5" s="3">
+        <f>HYPERLINK("https://sunroboticslab.github.io", "https://sunroboticslab.github.io")</f>
+        <v/>
+      </c>
+      <c r="N5" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>fjUoHOsAAAAJ</t>
+        </is>
+      </c>
+      <c r="P5" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/jsun165", "https://search.asu.edu/profile/jsun165")</f>
+        <v/>
+      </c>
+      <c r="Q5" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=fjUoHOsAAAAJ", "Scholar (fjUoHOsAAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="R5" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2923,7 +4301,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Mohamed Houssem Kasbaoui</t>
+          <t>Kangping Chen</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -2942,37 +4320,48 @@
         </is>
       </c>
       <c r="E6" s="3">
-        <f>HYPERLINK("mailto:houssem.kasbaoui@asu.edu", "houssem.kasbaoui@asu.edu")</f>
+        <f>HYPERLINK("mailto:k.p.chen@asu.edu", "k.p.chen@asu.edu")</f>
         <v/>
       </c>
       <c r="F6" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>cfd, computational fluid dynamics, dns, fluid dynamics, multiphase flow</t>
+          <t>aerospace, computational fluid dynamics, fluid dynamics, fluid mechanics, guidance, multiphase flow</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Kasbaoui's research interests include computational fluid dynamics, numerical methods, and massively parallel simulations of multiphase and particle-laden flows for environmental and aerospace applications.</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="b">
-        <v>1</v>
+          <t>Chen’s research interests include multiphase flows, drag reduction, airplane de-icing, interfacial instabilities and flow in porous media.</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D. Fluid Mechanics, University of Minnesota 1990 | B.S. Mechanics, Peking University, China 1982</t>
+        </is>
       </c>
       <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/mkasbaou", "https://search.asu.edu/profile/mkasbaou")</f>
-        <v/>
-      </c>
-      <c r="N6" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Mohamed%20Houssem%20Kasbaoui%20Arizona%20State%20University", "Google Scholar Search")</f>
-        <v/>
-      </c>
-      <c r="O6" s="3">
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>xT-lX9sAAAAJ</t>
+        </is>
+      </c>
+      <c r="P6" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/asuchen", "https://search.asu.edu/profile/asuchen")</f>
+        <v/>
+      </c>
+      <c r="Q6" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=xT-lX9sAAAAJ", "Scholar (xT-lX9sAAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="R6" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2980,12 +4369,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Aditi Chattopadhyay</t>
+          <t>Kiran Ramesh</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Regents Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -2999,41 +4388,52 @@
         </is>
       </c>
       <c r="E7" s="3">
-        <f>HYPERLINK("mailto:aditi@asu.edu", "aditi@asu.edu")</f>
+        <f>HYPERLINK("mailto:Kiran.Ramesh@asu.edu", "Kiran.Ramesh@asu.edu")</f>
         <v/>
       </c>
       <c r="F7" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>inverse problems, multiscale modeling, optimization, transition</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr"/>
+          <t>aerodynamics, aerospace, flow control, fluid dynamics, turbulence, vortex dynamics</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Unsteady aerodynamics, vortex dynamics, flow control, turbulence, separated flows</t>
+        </is>
+      </c>
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Chattopadhyay is the director of Adaptive Intelligent Materials and Systems (AIMS) Center at ASU. Her research focuses on structural health monitoring and damage prognosis, and multidisciplinary design optimization.</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>w3fU9E0AAAAJ</t>
-        </is>
-      </c>
-      <c r="M7" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/chattopa", "https://search.asu.edu/profile/chattopa")</f>
-        <v/>
-      </c>
-      <c r="N7" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=w3fU9E0AAAAJ", "Scholar (w3fU9E0AAAAJ)")</f>
-        <v/>
-      </c>
-      <c r="O7" s="3">
+          <t>Ramesh's expertise is in unsteady fluid dynamics, vortex dynamics, turbulence and flow control.</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>PhD North Carolina State University</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>DKc-AgcAAAAJ</t>
+        </is>
+      </c>
+      <c r="P7" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/kramesh2", "https://search.asu.edu/profile/kramesh2")</f>
+        <v/>
+      </c>
+      <c r="Q7" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=DKc-AgcAAAAJ", "Scholar (DKc-AgcAAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="R7" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -3041,7 +4441,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Gokul Pathikonda</t>
+          <t>Leixin Ma</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -3060,45 +4460,59 @@
         </is>
       </c>
       <c r="E8" s="3">
-        <f>HYPERLINK("mailto:Gokul.Pathikonda@asu.edu", "Gokul.Pathikonda@asu.edu")</f>
+        <f>HYPERLINK("mailto:Leixin.Ma@asu.edu", "Leixin.Ma@asu.edu")</f>
         <v/>
       </c>
       <c r="F8" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>aerodynamics, reacting flows, turbulence, turbulent mixing</t>
+          <t>aerodynamics, aerospace, fluid-structure interaction, fluids, materials, robot</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Aerodynamics, Aerospace Engineering, Mechanical Engineering</t>
+          <t>Aerodynamics, Dynamical Systems, Machine Learning, Mechanics of Composite Materials</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Aerodynamics, Aerospace Engineering, Mechanical Engineering</t>
+          <t>Aerodynamics, Dynamical Systems, Machine Learning, Mechanics of Composite Materials</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Dr. Pathikonda studies turbulent fluid flows to understand natural and engineering phenomena using lab experiments. His expertise is in complex (reacting) mixing, high Re-flows, laser-based &amp; spectroscopic techniques, etc.</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="b">
-        <v>1</v>
+          <t>Leixin Ma's career goal is a data-driven and physically consistent approach to modeling and designing programmable smart structures and robots, especially under complex fluid flow conditions.</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D. in Mechanical Engineering, Massachusetts Institute of Technology, 2021 S.M. in Mechanical Engineering, Massachusetts Institute of Technology, 2017 B.S.E. in Naval Architecture and Ocean Engineering, Shanghai Jiao Tong University, 2015</t>
+        </is>
       </c>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/gpathiko", "https://search.asu.edu/profile/gpathiko")</f>
-        <v/>
-      </c>
-      <c r="N8" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Gokul%20Pathikonda%20Arizona%20State%20University", "Google Scholar Search")</f>
-        <v/>
-      </c>
-      <c r="O8" s="3">
+        <f>HYPERLINK("https://sites.google.com/view/oasislabasu", "https://sites.google.com/view/oasislabasu")</f>
+        <v/>
+      </c>
+      <c r="N8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>2xQTOc0AAAAJ</t>
+        </is>
+      </c>
+      <c r="P8" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/leixinma", "https://search.asu.edu/profile/leixinma")</f>
+        <v/>
+      </c>
+      <c r="Q8" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=2xQTOc0AAAAJ", "Scholar (2xQTOc0AAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="R8" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -3106,12 +4520,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Marcus Herrmann</t>
+          <t>Gokul Pathikonda</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Professor</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -3125,41 +4539,59 @@
         </is>
       </c>
       <c r="E9" s="3">
-        <f>HYPERLINK("mailto:Marcus.Herrmann@asu.edu", "Marcus.Herrmann@asu.edu")</f>
+        <f>HYPERLINK("mailto:Gokul.Pathikonda@asu.edu", "Gokul.Pathikonda@asu.edu")</f>
         <v/>
       </c>
       <c r="F9" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>fluid mechanics, multiphase flow, numerical simulation, turbulence</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr"/>
+          <t>aerodynamics, aerospace, reacting flow, turbulence, turbulent</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Aerodynamics, Aerospace Engineering, Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Aerodynamics, Aerospace Engineering, Mechanical Engineering</t>
+        </is>
+      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Herrmann's research interests include fluid mechanics, modeling and numerical simulation of multiphase flows with a focus on turbulent atomization processes, and numerical methods for discontinuous interfaces.</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="b">
-        <v>1</v>
+          <t>Dr. Pathikonda studies turbulent fluid flows to understand natural and engineering phenomena using lab experiments. His expertise is in complex (reacting) mixing, high Re-flows, laser-based &amp; spectroscopic techniques, etc.</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>Ph. D. Theoretical and Applied Mechanics, University of Illinois, Urbana Champaign, 2017 | MS Aerospace Engineering, University of Illinois, Urbana Champaign, 2013 | B. Tech. Mechanical Engineering, National Institute of Technology, Warangal, 2009</t>
+        </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>yv6aCW8AAAAJ</t>
+          <t>551 E Tyler Mall ERC 479 (Tempe, AZ 85281)</t>
         </is>
       </c>
       <c r="M9" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/mherrma1", "https://search.asu.edu/profile/mherrma1")</f>
-        <v/>
-      </c>
-      <c r="N9" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=yv6aCW8AAAAJ", "Scholar (yv6aCW8AAAAJ)")</f>
-        <v/>
-      </c>
-      <c r="O9" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/cmat/", "https://faculty.engineering.asu.edu/cmat/")</f>
+        <v/>
+      </c>
+      <c r="N9" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O9" s="2" t="inlineStr"/>
+      <c r="P9" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/gpathiko", "https://search.asu.edu/profile/gpathiko")</f>
+        <v/>
+      </c>
+      <c r="Q9" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Gokul%20Pathikonda%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="R9" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -3167,12 +4599,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Alberto Scotti</t>
+          <t>Kunal Garg</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Professor</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -3186,49 +4618,63 @@
         </is>
       </c>
       <c r="E10" s="3">
-        <f>HYPERLINK("mailto:Alberto.Scotti@asu.edu", "Alberto.Scotti@asu.edu")</f>
+        <f>HYPERLINK("mailto:kgarg24@asu.edu", "kgarg24@asu.edu")</f>
         <v/>
       </c>
       <c r="F10" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>applied mathematics, fluid mechanics, turbulent mixing</t>
+          <t>aerospace, control theory, motion planning, robot, robotics</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Modeling and Simulation, Oceanography, Earth Systems and Climate Science, Modeling, Modeling, Simulation and Cyberinfrastructure, Applied Mathematics</t>
+          <t>Distributed multi-agent motion planning and control, Provably safe control design using machine learning-based certificates, Foundation models in complex robotic tasks, Failure prediction from limited demonstrations, Human-robot interaction.</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Modeling and Simulation, Oceanography, Earth Systems and Climate Science, Modeling, Modeling, Simulation and Cyberinfrastructure, Applied Mathematics</t>
+          <t>Control Systems, Dynamical Systems, Machine Learning, Nonlinear Dynamical Systems, Robotics</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Scotti's main focus is theoretical, experimental and computational aspects of environmental fluid mechanics.</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="b">
-        <v>1</v>
+          <t>Garg's research interests include control synthesis for multi-agent coordination using control theory and machine learning.</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>PhD. Aerospace Engineering, University of Michigan, Ann Arbor, 2021 MS. Aerospace Engineering, University of Michigan, Ann Arbor, 2019 BTech. Aerospace Engineering, Indian Institute of Technology, Bombay, 2016</t>
+        </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>HRx2lJQAAAAJ</t>
+          <t>551 E Tyler Mall ERC 475 (Tempe, AZ 85281)</t>
         </is>
       </c>
       <c r="M10" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/adscotti", "https://search.asu.edu/profile/adscotti")</f>
-        <v/>
-      </c>
-      <c r="N10" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=HRx2lJQAAAAJ", "Scholar (HRx2lJQAAAAJ)")</f>
-        <v/>
-      </c>
-      <c r="O10" s="3">
+        <f>HYPERLINK("https://sites.google.com/asu.edu/kunalgarg/", "https://sites.google.com/asu.edu/kunalgarg/")</f>
+        <v/>
+      </c>
+      <c r="N10" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>vs3pl-8AAAAJ</t>
+        </is>
+      </c>
+      <c r="P10" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/kgarg24", "https://search.asu.edu/profile/kgarg24")</f>
+        <v/>
+      </c>
+      <c r="Q10" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=vs3pl-8AAAAJ", "Scholar (vs3pl-8AAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="R10" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -3236,12 +4682,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Beomjin Kwon</t>
+          <t>Marcus Herrmann</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Professor</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -3255,45 +4701,48 @@
         </is>
       </c>
       <c r="E11" s="3">
-        <f>HYPERLINK("mailto:kwon@asu.edu", "kwon@asu.edu")</f>
+        <f>HYPERLINK("mailto:Marcus.Herrmann@asu.edu", "Marcus.Herrmann@asu.edu")</f>
         <v/>
       </c>
       <c r="F11" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>data-driven modeling, heat transfer, transport phenomena</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Transport phenomena in heat transfer systems Additive manufacturing Data-driven modeling and design</t>
-        </is>
-      </c>
+          <t>aerospace, fluid mechanics, multiphase flow, turbulence, turbulent</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>Kwon aims to improve the energy conversion and transport systems through the fundamental insights into transport physics, and by exploiting additive manufacturing and data-driven approaches.</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>fs2d97sAAAAJ</t>
-        </is>
-      </c>
-      <c r="M11" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/bkwon2", "https://search.asu.edu/profile/bkwon2")</f>
-        <v/>
-      </c>
-      <c r="N11" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=fs2d97sAAAAJ", "Scholar (fs2d97sAAAAJ)")</f>
-        <v/>
-      </c>
-      <c r="O11" s="3">
+          <t>Herrmann's research interests include fluid mechanics, modeling and numerical simulation of multiphase flows with a focus on turbulent atomization processes, and numerical methods for discontinuous interfaces.</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>PhD in Mechanical Engineering, University of Technology (RWTH) Aachen, Germany 2001 | Diploma. Mechanical and Aerospace Engineering, University of Technology (RWTH) Aachen, Germany 1995</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>yv6aCW8AAAAJ</t>
+        </is>
+      </c>
+      <c r="P11" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/mherrma1", "https://search.asu.edu/profile/mherrma1")</f>
+        <v/>
+      </c>
+      <c r="Q11" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=yv6aCW8AAAAJ", "Scholar (yv6aCW8AAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="R11" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -3301,12 +4750,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Leixin Ma</t>
+          <t>Spring Berman</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Professor</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -3320,49 +4769,59 @@
         </is>
       </c>
       <c r="E12" s="3">
-        <f>HYPERLINK("mailto:Leixin.Ma@asu.edu", "Leixin.Ma@asu.edu")</f>
+        <f>HYPERLINK("mailto:Spring.Berman@asu.edu", "Spring.Berman@asu.edu")</f>
         <v/>
       </c>
       <c r="F12" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>aerodynamics, fluid-structure interaction, physics-informed machine learning</t>
+          <t>aerospace, autonomous, control theory, robot, robotics</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Aerodynamics, Dynamical Systems, Machine Learning, Mechanics of Composite Materials</t>
+          <t>Modeling, analysis, control, and optimization of multi-robot systems including robotic swarms; analysis of collective behaviors in biology and biologically-inspired control of distributed systems</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Aerodynamics, Dynamical Systems, Machine Learning, Mechanics of Composite Materials</t>
+          <t>Systems and Control Theory, Mechanical Engineering, Autonomous Technologies, Robotics</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Leixin Ma's career goal is a data-driven and physically consistent approach to modeling and designing programmable smart structures and robots, especially under complex fluid flow conditions.</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>2xQTOc0AAAAJ</t>
-        </is>
-      </c>
+          <t>Dr. Berman directs the Autonomous Collective Systems Laboratory at ASU, which models and analyzes behaviors in biological and engineered collectives and designs control strategies for multi-robot systems.</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D. Mechanical Engineering and Applied Mechanics, University of Pennsylvania 2010 | M.S.E. Mechanical Engineering and Applied Mechanics, University of Pennsylvania 2008 | B.S.E. Mechanical and Aerospace Engineering, Princeton University 2005 | Certificate. Robotics and Intelligent Systems, Princeton University 2005</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/leixinma", "https://search.asu.edu/profile/leixinma")</f>
-        <v/>
-      </c>
-      <c r="N12" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=2xQTOc0AAAAJ", "Scholar (2xQTOc0AAAAJ)")</f>
-        <v/>
-      </c>
-      <c r="O12" s="3">
+        <f>HYPERLINK("http://faculty.engineering.asu.edu/acs/", "http://faculty.engineering.asu.edu/acs/")</f>
+        <v/>
+      </c>
+      <c r="N12" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>KKup0OgAAAAJ</t>
+        </is>
+      </c>
+      <c r="P12" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/smberma2", "https://search.asu.edu/profile/smberma2")</f>
+        <v/>
+      </c>
+      <c r="Q12" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=KKup0OgAAAAJ", "Scholar (KKup0OgAAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="R12" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -3370,12 +4829,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Yulia Peet</t>
+          <t>Zhe Xu</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Professor</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -3389,41 +4848,59 @@
         </is>
       </c>
       <c r="E13" s="3">
-        <f>HYPERLINK("mailto:ypeet@asu.edu", "ypeet@asu.edu")</f>
+        <f>HYPERLINK("mailto:xzhe1@asu.edu", "xzhe1@asu.edu")</f>
         <v/>
       </c>
       <c r="F13" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>fluid mechanics, high-performance computing, turbulence</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
+          <t>autonomous, control theory, energy systems, robot, robotics</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>The research interests include control theory, machine learning, formal methods and autonomous systems.</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence, Control Systems, Electric Power and Energy Systems, Machine Learning, Robotics, Systems and Control Theory</t>
+        </is>
+      </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>Yulia Peet is an associate professor of aerospace and mechanical engineering in the School for Engineering of Matter, Transport and Energy with the Ira A. Fulton Schools of Engineering at Arizona State University. Her Ph.D. degree is in Aeronautics and Astronautics from Stanford (2006), M.S. and B.S. degrees are from Moscow Institute of Physics and Technology (1999 and 1997). Her previous appoi...</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="b">
-        <v>1</v>
+          <t>My research interests include control theory, formal methods, and machine learning (including reinforcement learning), with applications on autonomous systems and cyber-physical systems.</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D Degree at the  Department of Electrical, Computer, and Systems Engineering  at  Rensselaer Polytechnic Institute  in 2018 | Master's Degree at the  School of electrical and information engineering  at  Tianjin University  in 2014 | Bachelor's Degree at the  School of electrical and information engineering  at  Tianjin University  in 2011</t>
+        </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>_6o8MrUAAAAJ</t>
+          <t>Campus: Tempe</t>
         </is>
       </c>
       <c r="M13" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/ypeet", "https://search.asu.edu/profile/ypeet")</f>
-        <v/>
-      </c>
-      <c r="N13" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=_6o8MrUAAAAJ", "Scholar (_6o8MrUAAAAJ)")</f>
-        <v/>
-      </c>
-      <c r="O13" s="3">
+        <f>HYPERLINK("https://sites.google.com/site/zhexudavid00710/research?authuser=0", "https://sites.google.com/site/zhexudavid00710/research?authuser=0")</f>
+        <v/>
+      </c>
+      <c r="N13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O13" s="2" t="inlineStr"/>
+      <c r="P13" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/xzhe1", "https://search.asu.edu/profile/xzhe1")</f>
+        <v/>
+      </c>
+      <c r="Q13" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Zhe%20Xu%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="R13" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -3431,12 +4908,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Huei-Ping Huang</t>
+          <t>Jeonglae Kim</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -3450,37 +4927,44 @@
         </is>
       </c>
       <c r="E14" s="3">
-        <f>HYPERLINK("mailto:Huei-Ping.Huang@asu.edu", "Huei-Ping.Huang@asu.edu")</f>
+        <f>HYPERLINK("mailto:jeokim@asu.edu", "jeokim@asu.edu")</f>
         <v/>
       </c>
       <c r="F14" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>fluid dynamics, numerical simulation</t>
+          <t>aerospace, flow control, turbulence, turbulent</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Huang's research interests are geophysical and environmental fluid dynamics, numerical simulation of atmospheric and oceanic flows, Earth system remote sensing, and climate change.</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="b">
-        <v>1</v>
+          <t>Kim's research interests include large-eddy simulation of high-speed turbulent flows with multi-physics, aeroacoustics, flow control and optimization.</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D. Theoretical and Applied Mechanics, University of Illinois at Urbana-Champaign | M.S. Mechanical and Aerospace Engineering, Seoul National University, South Korea | B.S. Mechanical and Aerospace Engineering, Seoul National University, South Korea</t>
+        </is>
       </c>
       <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/hhuang38", "https://search.asu.edu/profile/hhuang38")</f>
-        <v/>
-      </c>
-      <c r="N14" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Huei-Ping%20Huang%20Arizona%20State%20University", "Google Scholar Search")</f>
-        <v/>
-      </c>
-      <c r="O14" s="3">
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O14" s="2" t="inlineStr"/>
+      <c r="P14" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/jkim520", "https://search.asu.edu/profile/jkim520")</f>
+        <v/>
+      </c>
+      <c r="Q14" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Jeonglae%20Kim%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="R14" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -3488,12 +4972,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Raghavendra Murthy</t>
+          <t>Matthew Peet</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Associate Teaching Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -3507,37 +4991,55 @@
         </is>
       </c>
       <c r="E15" s="3">
-        <f>HYPERLINK("mailto:rnmurthy@asu.edu", "rnmurthy@asu.edu")</f>
+        <f>HYPERLINK("mailto:mpeet@asu.edu", "mpeet@asu.edu")</f>
         <v/>
       </c>
       <c r="F15" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>optimization, reduced-order modeling</t>
+          <t>aerospace, materials, spacecraft, system dynamics</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Structural Dynamics, Rotordynamics, Vibration Analysis, Reduced-Order Modeling, Optimization</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="b">
-        <v>1</v>
+          <t>The intersection of computer science and control including convex optimization, artificial intelligence, and manipulation of delayed and PDE systems. The understanding and regulation of complex dynamical systems such as the motion of plasma in nuclear fusion reactors, autoregulation in the human immune response, and the motion of spacecraft in orbit.</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Control Systems, Dynamical Systems Theory, Aerospace Engineering, Algorithm Development, Dynamical Systems, Nonlinear Dynamical Systems, Mathematical and System Dynamics Modeling, Immunology</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Peet's current research interests are in the role of computation as it is applied to the understanding and control of complex and large-scale systems.</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D. Aeronautics and Astronautics, Stanford University 2006 | Bachelor's degree. Physics, University of Texas-Austin 1999 | Bachelor's degree. Aerospace Engineering, University of Texas-Austin 1999</t>
+        </is>
       </c>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/rnmurthy", "https://search.asu.edu/profile/rnmurthy")</f>
-        <v/>
-      </c>
-      <c r="N15" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Raghavendra%20Murthy%20Arizona%20State%20University", "Google Scholar Search")</f>
-        <v/>
-      </c>
-      <c r="O15" s="3">
+        <f>HYPERLINK("http://control.asu.edu/", "http://control.asu.edu/")</f>
+        <v/>
+      </c>
+      <c r="N15" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O15" s="2" t="inlineStr"/>
+      <c r="P15" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/mpeet", "https://search.asu.edu/profile/mpeet")</f>
+        <v/>
+      </c>
+      <c r="Q15" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Matthew%20Peet%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="R15" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -3545,7 +5047,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Ryan Milcarek</t>
+          <t>Robert Wang</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -3564,45 +5066,59 @@
         </is>
       </c>
       <c r="E16" s="3">
-        <f>HYPERLINK("mailto:Ryan.Milcarek@asu.edu", "Ryan.Milcarek@asu.edu")</f>
+        <f>HYPERLINK("mailto:rywang@asu.edu", "rywang@asu.edu")</f>
         <v/>
       </c>
       <c r="F16" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>combustion, transition</t>
+          <t>composites, heat transfer, materials, thermal</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Energy management and efficiency, energy transition, energy storage, solid oxide fuel cells, partial oxidation, cogeneration, combustion, and synthesis of hydrogen</t>
+          <t>My research group is an interdisciplinary nanoengineering team that focuses on manipulating material properties for thermal energy applications. Some of our focus areas are thermoelectric power generation, thermal storage media, heat transfer, and phonon optics. To achieve our objectives, we custom-design materials using colloidal nanoparticles, chemical precursors, and nanocomposites.</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Ceramics, Electrochemistry, Energy, Energy and Sustainability, Energy Conservation, Energy Economics, Energy Efficiency Technologies, Thin Film Materials</t>
+          <t>Mechanical Engineering, Energy, Renewable Energy, Energy and Sustainability, Clean Energy, Energy Efficiency Technologies, Materials Science and Engineering, Chemical Engineering, Nanoengineering, Nanoscience, Nanotechnology, Solid State Physics, Thin Film Materials, Semiconductors, Chemistry, Physics</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Milcarek's current research focuses on energy management and efficiency, energy system modeling, energy transition, energy storage, solid oxide fuel cells fabrication and testing, partial oxidation and synthesis of hydrogen.</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="b">
-        <v>1</v>
+          <t>Wang's research interests include thermal energy conversion, storage, and transport in nanostructured materials; thermoelectric power generation; thermal storage media; heat transfer, and phonon optics</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D. Mechanical Engineering, University of California-Berkeley 2008 | M.S. Mechanical Engineering, University of California-Berkeley 2005 | B.S. Mechanical Engineering, University of California-Los Angeles 2003</t>
+        </is>
       </c>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/rjmilcar", "https://search.asu.edu/profile/rjmilcar")</f>
-        <v/>
-      </c>
-      <c r="N16" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ryan%20Milcarek%20Arizona%20State%20University", "Google Scholar Search")</f>
-        <v/>
-      </c>
-      <c r="O16" s="3">
+        <f>HYPERLINK("http://wang.faculty.asu.edu/", "http://wang.faculty.asu.edu/")</f>
+        <v/>
+      </c>
+      <c r="N16" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>LaUdx9gAAAAJ</t>
+        </is>
+      </c>
+      <c r="P16" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/rywang", "https://search.asu.edu/profile/rywang")</f>
+        <v/>
+      </c>
+      <c r="Q16" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=LaUdx9gAAAAJ", "Scholar (LaUdx9gAAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="R16" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -3610,7 +5126,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>T.-W. Lee</t>
+          <t>Ryan Milcarek</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -3629,37 +5145,55 @@
         </is>
       </c>
       <c r="E17" s="3">
-        <f>HYPERLINK("mailto:ATTWL@asu.edu", "ATTWL@asu.edu")</f>
+        <f>HYPERLINK("mailto:Ryan.Milcarek@asu.edu", "Ryan.Milcarek@asu.edu")</f>
         <v/>
       </c>
       <c r="F17" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>aerospace propulsion, propulsion</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr"/>
-      <c r="I17" s="2" t="inlineStr"/>
+          <t>aerospace, combustion, energy systems, materials</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Energy management and efficiency, energy transition, energy storage, solid oxide fuel cells, partial oxidation, cogeneration, combustion, and synthesis of hydrogen</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Ceramics, Electrochemistry, Energy, Energy and Sustainability, Energy Conservation, Energy Economics, Energy Efficiency Technologies, Thin Film Materials</t>
+        </is>
+      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>Lee's areas of expertise include energy system analysis, thermal and fluid process characterization, and fuel property measurements for energy systems.</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="b">
-        <v>1</v>
+          <t>Milcarek's current research focuses on energy management and efficiency, energy system modeling, energy transition, energy storage, solid oxide fuel cells fabrication and testing, partial oxidation and synthesis of hydrogen.</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D. Mechanical and Aerospace Engineering, College of Engineering and Computer Science, Syracuse University 2018 | M.S. Mechanical and Aerospace Engineering, College of Engineering and Computer Science, Syracuse University 2017 | M.S. Energy Systems Engineering, College of Engineering and Computer Science, Syracuse University 2017 | Certificate of Advanced Study (CAS) Sustainable Enterprise, Martin J. Whitman School of Management, Syracuse University 2017 | Certificate in University Teaching (CUT). Graduate School, Future Professorate Program, Syracuse University 2017 | B.S. Mechanical Engineering; minor: Mathematics (Summa Cum Laude), L.C. Smith College of Engineering and Computer Science, Syracuse University 2014</t>
+        </is>
       </c>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/attwl", "https://search.asu.edu/profile/attwl")</f>
-        <v/>
-      </c>
-      <c r="N17" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=T.-W.%20Lee%20Arizona%20State%20University", "Google Scholar Search")</f>
-        <v/>
-      </c>
-      <c r="O17" s="3">
+        <f>HYPERLINK("http://RESEARCHGATE.net/profile/Ryan_Milcarek", "http://RESEARCHGATE.net/profile/Ryan_Milcarek")</f>
+        <v/>
+      </c>
+      <c r="N17" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O17" s="2" t="inlineStr"/>
+      <c r="P17" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/rjmilcar", "https://search.asu.edu/profile/rjmilcar")</f>
+        <v/>
+      </c>
+      <c r="Q17" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ryan%20Milcarek%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="R17" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -3667,7 +5201,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Houlong Zhuang</t>
+          <t>T.-W. Lee</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -3686,49 +5220,48 @@
         </is>
       </c>
       <c r="E18" s="3">
-        <f>HYPERLINK("mailto:zhuanghl@asu.edu", "zhuanghl@asu.edu")</f>
+        <f>HYPERLINK("mailto:ATTWL@asu.edu", "ATTWL@asu.edu")</f>
         <v/>
       </c>
       <c r="F18" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>computational physics</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>Quantum simulations Machine learning Quantum computing</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>Artificial Photosynthesis, Chemistry, Computational Physics, Machine Learning, Materials Science, Metals, Nanoscience, Semiconductors</t>
-        </is>
-      </c>
+          <t>aerospace, energy systems, propulsion, thermal</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Dr. Houlong Zhuang is an associate professor in the School for Engineering of Matter, Transport and Energy at ASU. He received his doctorate in materials science and engineering at Cornell University. Prior to ASU, Dr. Zhuang was a postdoctoral researcher at Princeton University. Dr. Zhuang’s current research interests are quantum mechanical simulations, machine learning, and quantum computing.</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="b">
-        <v>1</v>
+          <t>Lee's areas of expertise include energy system analysis, thermal and fluid process characterization, and fuel property measurements for energy systems.</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D. Aerospace Engineering, University of Michigan-Ann Arbor | M.S.E. Aerospace Engineering, University of Michigan-Ann Arbor | B.S. Aeronautical and Astronautical Engineering, The Ohio State University-Columbus</t>
+        </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4yYKCpUAAAAJ</t>
-        </is>
-      </c>
-      <c r="M18" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/hzhuang7", "https://search.asu.edu/profile/hzhuang7")</f>
-        <v/>
-      </c>
-      <c r="N18" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=4yYKCpUAAAAJ", "Scholar (4yYKCpUAAAAJ)")</f>
-        <v/>
-      </c>
-      <c r="O18" s="3">
+          <t>ENGRC 377 (TEMPE, AZ 85287-6106)</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O18" s="2" t="inlineStr"/>
+      <c r="P18" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/attwl", "https://search.asu.edu/profile/attwl")</f>
+        <v/>
+      </c>
+      <c r="Q18" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=T.-W.%20Lee%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="R18" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -3736,12 +5269,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Huan Wu</t>
+          <t>Tianyu Yang</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -3755,49 +5288,44 @@
         </is>
       </c>
       <c r="E19" s="3">
-        <f>HYPERLINK("mailto:huanwu@asu.edu", "huanwu@asu.edu")</f>
+        <f>HYPERLINK("mailto:Tianyu.Yang@asu.edu", "Tianyu.Yang@asu.edu")</f>
         <v/>
       </c>
       <c r="F19" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>computational physics</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>Aerospace Engineering, Computational Physics, Energy, Material Physics, Materials Science, Mechanical Engineering, Modeling and Simulation, Theoretical Solid State Physics</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>Aerospace Engineering, Computational Physics, Energy, Material Physics, Materials Science, Mechanical Engineering, Modeling and Simulation, Theoretical Solid State Physics</t>
-        </is>
-      </c>
+          <t>autonomous, heat transfer, materials, thermal</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>Dr. Wu’s research focuses on electron, phonon, and magnon transport, exploring nanoscale energy transport and conversion through first-principles approaches, as well as material thermal and electrical transport properties.</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>8CS4X9IAAAAJ</t>
-        </is>
-      </c>
-      <c r="M19" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/huanwu", "https://search.asu.edu/profile/huanwu")</f>
-        <v/>
-      </c>
-      <c r="N19" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=8CS4X9IAAAAJ", "Scholar (8CS4X9IAAAAJ)")</f>
-        <v/>
-      </c>
-      <c r="O19" s="3">
+          <t>Yang studies heat transfer, thermal management of electronics, and biomedical devices. She has published multiple research papers in major scientific journals.</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>PhD. University of Illinois at Urbana Champaign, 2016-2021 | BS. Tsinghua University, China 2012-2016</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O19" s="2" t="inlineStr"/>
+      <c r="P19" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/tyang123", "https://search.asu.edu/profile/tyang123")</f>
+        <v/>
+      </c>
+      <c r="Q19" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Tianyu%20Yang%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="R19" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -3805,12 +5333,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Jagannathan Rajagopalan</t>
+          <t>Aditi Chattopadhyay</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Regents Professor</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -3824,49 +5352,52 @@
         </is>
       </c>
       <c r="E20" s="3">
-        <f>HYPERLINK("mailto:Jagannathan.Rajagopalan@asu.edu", "Jagannathan.Rajagopalan@asu.edu")</f>
+        <f>HYPERLINK("mailto:aditi@asu.edu", "aditi@asu.edu")</f>
         <v/>
       </c>
       <c r="F20" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>optimization</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>Synthesis of nanocrystalline materials with tailored microstructures, Mechanics of nanostructured metal and alloy films, MEMS for in situ materials testing, Polymer based micro devices for cell mechanics and biohybrid platforms</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>Thin Film Materials, Materials Science, Mechanical Engineering</t>
-        </is>
-      </c>
+          <t>aerospace, materials, structural health monitoring</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Rajagopalan's research focuses on the mechanics of nanoscale materials, cells and biological systems.</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="b">
-        <v>1</v>
+          <t>Chattopadhyay is the director of Adaptive Intelligent Materials and Systems (AIMS) Center at ASU. Her research focuses on structural health monitoring and damage prognosis, and multidisciplinary design optimization.</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>Ph. D. Aerospace Engineering, Georgia Institute of Technology | M.S. Aerospace Engineering, Georgia Institute of Technology | B. Tech. Aeronautical Engineering (Honors), Indian Institute of Technology, Kharagpur, India 1980</t>
+        </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>ClqRIhIAAAAJ</t>
-        </is>
-      </c>
-      <c r="M20" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/jrajago1", "https://search.asu.edu/profile/jrajago1")</f>
-        <v/>
-      </c>
-      <c r="N20" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=ClqRIhIAAAAJ", "Scholar (ClqRIhIAAAAJ)")</f>
-        <v/>
-      </c>
-      <c r="O20" s="3">
+          <t>ENGRC 427 (TEMPE, AZ 85287-6106)</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>w3fU9E0AAAAJ</t>
+        </is>
+      </c>
+      <c r="P20" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/chattopa", "https://search.asu.edu/profile/chattopa")</f>
+        <v/>
+      </c>
+      <c r="Q20" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=w3fU9E0AAAAJ", "Scholar (w3fU9E0AAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="R20" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -3874,12 +5405,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Jay Oswald</t>
+          <t>Alberto Scotti</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Professor</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -3893,41 +5424,60 @@
         </is>
       </c>
       <c r="E21" s="3">
-        <f>HYPERLINK("mailto:joswald1@asu.edu", "joswald1@asu.edu")</f>
+        <f>HYPERLINK("mailto:Alberto.Scotti@asu.edu", "Alberto.Scotti@asu.edu")</f>
         <v/>
       </c>
       <c r="F21" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>finite element</t>
+          <t>fluid mechanics, fluids, turbulent</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Development of computational mechanics: finite element methods, molecular dynamics, multiscale methods, failure analysis, and material design.</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr"/>
+          <t>Modeling and Simulation, Oceanography, Earth Systems and Climate Science, Modeling, Modeling, Simulation and Cyberinfrastructure, Applied Mathematics</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Modeling and Simulation, Oceanography, Earth Systems and Climate Science, Modeling, Modeling, Simulation and Cyberinfrastructure, Applied Mathematics</t>
+        </is>
+      </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>Dr. Oswald develops computational and AI-driven methods for advanced manufacturing, including laser welding, automated inspection, robotics, and computational mechanics.</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/joswald1", "https://search.asu.edu/profile/joswald1")</f>
-        <v/>
-      </c>
-      <c r="N21" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Jay%20Oswald%20Arizona%20State%20University", "Google Scholar Search")</f>
-        <v/>
-      </c>
-      <c r="O21" s="3">
+          <t>Scotti's main focus is theoretical, experimental and computational aspects of environmental fluid mechanics.</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>PhD Johns Hopkins University</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>Campus: Tempe</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>HRx2lJQAAAAJ</t>
+        </is>
+      </c>
+      <c r="P21" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/adscotti", "https://search.asu.edu/profile/adscotti")</f>
+        <v/>
+      </c>
+      <c r="Q21" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=HRx2lJQAAAAJ", "Scholar (HRx2lJQAAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="R21" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -3935,12 +5485,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Kunal Garg</t>
+          <t>Beomjin Kwon</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -3954,49 +5504,59 @@
         </is>
       </c>
       <c r="E22" s="3">
-        <f>HYPERLINK("mailto:kgarg24@asu.edu", "kgarg24@asu.edu")</f>
+        <f>HYPERLINK("mailto:kwon@asu.edu", "kwon@asu.edu")</f>
         <v/>
       </c>
       <c r="F22" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>optimization</t>
+          <t>aerospace, energy systems, heat transfer</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Distributed multi-agent motion planning and control, Provably safe control design using machine learning-based certificates, Foundation models in complex robotic tasks, Failure prediction from limited demonstrations, Human-robot interaction.</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>Control Systems, Dynamical Systems, Machine Learning, Nonlinear Dynamical Systems, Robotics</t>
-        </is>
-      </c>
+          <t>Transport phenomena in heat transfer systems Additive manufacturing Data-driven modeling and design</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>Garg's research interests include control synthesis for multi-agent coordination using control theory and machine learning.</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="b">
-        <v>1</v>
+          <t>Kwon aims to improve the energy conversion and transport systems through the fundamental insights into transport physics, and by exploiting additive manufacturing and data-driven approaches.</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D. Mechanical Engineering, University of Illinois at Urbana-Champaign 2013 | M.S. Mechanical Engineering, University of Illinois at Urbana-Champaign 2009 | B.S. Mechanical and Aerospace Engineering, Seoul National University 2008</t>
+        </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>vs3pl-8AAAAJ</t>
+          <t>551 E Tyler Mall ERC 363 (Tempe, AZ 85281)</t>
         </is>
       </c>
       <c r="M22" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/kgarg24", "https://search.asu.edu/profile/kgarg24")</f>
-        <v/>
-      </c>
-      <c r="N22" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=vs3pl-8AAAAJ", "Scholar (vs3pl-8AAAAJ)")</f>
-        <v/>
-      </c>
-      <c r="O22" s="3">
+        <f>HYPERLINK("http://sites.google.com/view/3denergy", "http://sites.google.com/view/3denergy")</f>
+        <v/>
+      </c>
+      <c r="N22" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>fs2d97sAAAAJ</t>
+        </is>
+      </c>
+      <c r="P22" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/bkwon2", "https://search.asu.edu/profile/bkwon2")</f>
+        <v/>
+      </c>
+      <c r="Q22" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=fs2d97sAAAAJ", "Scholar (fs2d97sAAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="R22" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -4004,7 +5564,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Liping Wang</t>
+          <t>Hamidreza Marvi</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -4023,41 +5583,55 @@
         </is>
       </c>
       <c r="E23" s="3">
-        <f>HYPERLINK("mailto:Liping.Wang@asu.edu", "Liping.Wang@asu.edu")</f>
+        <f>HYPERLINK("mailto:hmarvi@asu.edu", "hmarvi@asu.edu")</f>
         <v/>
       </c>
       <c r="F23" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>heat transfer</t>
+          <t>aerospace, robot, robotics</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Nanoscale heat transfer, metamaterials, plasmonics, and nanophotonics with an emphasis on solar thermal energy harvesting using plasmonic-enhanced light trapping for photovolatics, as well as near-field enhancement and spectral control of radiation for thermophotovoltaic energy conversion. Other research interests involve electronic cooling, MEMS, and bio-sensing.</t>
+          <t>Bio-inspired robotics Soft robotics Magnetic micro-robotics Mechanics of animal locomotion</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>Wang research interests include selective control of thermal emission/absorption using meta-materials for energy harvesting and near-field radiation heat transfer enhancement between meta-materials for thermophotovoltaics.</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="b">
-        <v>1</v>
+          <t>Marvi would like to develop bio-inspired robotic systems and programmable interfacial structures for search and rescue, exploratory and medical applications.</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D. Mechanical Engineering, Georgia Institute of Technology, Atlanta 2013 | M.S. Mechanical Engineering, Clemson University, SC 2009 | M.S. Biomedical Engineering, Sharif University of Technology, Tehran, Iran 2007 | B.S. Mechanical Engineering, Iran University of Science and Technology, Tehran 2004</t>
+        </is>
       </c>
       <c r="L23" s="2" t="inlineStr"/>
       <c r="M23" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/lwang78", "https://search.asu.edu/profile/lwang78")</f>
-        <v/>
-      </c>
-      <c r="N23" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Liping%20Wang%20Arizona%20State%20University", "Google Scholar Search")</f>
-        <v/>
-      </c>
-      <c r="O23" s="3">
+        <f>HYPERLINK("http://birth.asu.edu", "http://birth.asu.edu")</f>
+        <v/>
+      </c>
+      <c r="N23" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>00Fepb0AAAAJ</t>
+        </is>
+      </c>
+      <c r="P23" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/hmarvi", "https://search.asu.edu/profile/hmarvi")</f>
+        <v/>
+      </c>
+      <c r="Q23" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=00Fepb0AAAAJ", "Scholar (00Fepb0AAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="R23" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -4065,7 +5639,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Matthew Peet</t>
+          <t>Hyunglae Lee</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -4084,45 +5658,51 @@
         </is>
       </c>
       <c r="E24" s="3">
-        <f>HYPERLINK("mailto:mpeet@asu.edu", "mpeet@asu.edu")</f>
+        <f>HYPERLINK("mailto:Hyunglae.Lee@asu.edu", "Hyunglae.Lee@asu.edu")</f>
         <v/>
       </c>
       <c r="F24" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>optimization</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>The intersection of computer science and control including convex optimization, artificial intelligence, and manipulation of delayed and PDE systems. The understanding and regulation of complex dynamical systems such as the motion of plasma in nuclear fusion reactors, autoregulation in the human immune response, and the motion of spacecraft in orbit.</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>Control Systems, Dynamical Systems Theory, Aerospace Engineering, Algorithm Development, Dynamical Systems, Nonlinear Dynamical Systems, Mathematical and System Dynamics Modeling, Immunology</t>
-        </is>
-      </c>
+          <t>aerospace, robot, robotics</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>Peet's current research interests are in the role of computation as it is applied to the understanding and control of complex and large-scale systems.</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L24" s="2" t="inlineStr"/>
+          <t>Lee's research interests include physical human-robot interaction, neuromuscular control of human movement, robot-aided neurorehabilitation, bio-inspired robotics and system identification for physiological systems.</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>B.S. Mechanical and Aerospace Engineering, Seoul National University (2002) M.S. Mechanical and Aerospace Engineering, Seoul National University (2004) Ph.D Mechanical Engineering, Massachusetts Institute of Technology (2013)</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>Campus: Tempe</t>
+        </is>
+      </c>
       <c r="M24" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/mpeet", "https://search.asu.edu/profile/mpeet")</f>
-        <v/>
-      </c>
-      <c r="N24" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Matthew%20Peet%20Arizona%20State%20University", "Google Scholar Search")</f>
-        <v/>
-      </c>
-      <c r="O24" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/hlee", "https://faculty.engineering.asu.edu/hlee")</f>
+        <v/>
+      </c>
+      <c r="N24" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O24" s="2" t="inlineStr"/>
+      <c r="P24" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/hlee234", "https://search.asu.edu/profile/hlee234")</f>
+        <v/>
+      </c>
+      <c r="Q24" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Hyunglae%20Lee%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="R24" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -4130,12 +5710,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Minglei Qu</t>
+          <t>Leila Ladani</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Professor</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -4149,45 +5729,55 @@
         </is>
       </c>
       <c r="E25" s="3">
-        <f>HYPERLINK("mailto:minglei.qu@asu.edu", "minglei.qu@asu.edu")</f>
+        <f>HYPERLINK("mailto:ladani@asu.edu", "ladani@asu.edu")</f>
         <v/>
       </c>
       <c r="F25" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>instability</t>
+          <t>aerospace, materials, solid mechanics</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Metal additive manufacturing, in-situ synchrotron X-ray and neutron characterization, non-equilibrium phase transformation, metal matrix composites. Selected Publications M. Qu , J. Yuan, Q. Guo, A. Nabaa, L. I. Escano, J. Huang, Q. Li, L. Chen. Achieving uniformly refined grain structure in metal additive manufacturing: Experimental demonstration and analytical model development. Additive Manufacturing 108 (2025) 104805. M. Qu , D. Yu, J. Yuan, L. Chen, K. An, Y. Chen. Multi-stage load partitioning in additively manufactured Al6061+TiC nanocomposite characterized by in-situ neutron diffraction. Additive Manufacturing, 96 (2024) 104584. M. Qu , J. Yuan, A. Nabaa, J. Huang, C. A. Chuang, L. Chen. Melting and solidification dynamics during laser additive manufacturing of reaction-based metal matrix composites uncovered by in-situ synchrotron X-ray diffraction. Acta Materialia , 271 (2024) 119875. M. Qu , Q. Guo, L. I. Escano, A. Nabaa, S. M. H. Hojjatzadeh, Z. A. Young, L. Chen. Controlling process instability for defect lean metal additive manufacturing. Nature Communications , 13 (2022) 1079. M. Qu , Q. Guo, L. I. Escano, A. Nabaa, K. Fezzaa, L. Chen. Nanoparticle-enabled increase of energy efficiency during laser metal additive manufacturing. Additive Manufacturing , 60 (2022) 103242. M. Qu , Q.Guo, L. I. Escano, J. Yuan, S. J. Clark, K. Fezzaa, L. Chen. Controlling melt flow by nanoparticles to eliminate surface wave induced surface fluctuation. Additive Manufacturing , 59 (2022) 103081.</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr"/>
+          <t>Manufacturing process simulation and modeling and experiments Additive manufacturing Micro/nano manufacturing Microelectronic packaging Application of AI in manufacturing Mechanic of metallic materials Materials characterization Fatigue and damage modeling and simulation</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Additive Manufacturing, Manufacturing Engineering</t>
+        </is>
+      </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>Minglei Qu is an Assistant Professor of Mechanical Engineering and a graduate faculty of Materials Science and Engineering in the School for Engineering of Matter, Transport and Energy at ASU. His research lies at the intersection of metal additive manufacturing, in-situ characterization, and materials science. By utilizing advanced in-situ characterization tools, including synchrotron X-ray im...</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>9LWNC50AAAAJ</t>
-        </is>
-      </c>
+          <t>Dr. Ladani is a Professor of Mechanical and Aerospace Engineering at Arizona State University.</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>PhD. Mechanical Engineering, University of Maryland-College Park 2007 | M.S. Mechanical Engineering, University of Maryland-College Park 2005 | PhD. Student, Mechanical Engineering, Isfahan University of Technology, Iran 2001-2002 | M.S. Mechanical Engineering, Isfahan University of Technology, Iran 2001 | B.S. Mechanical Engineering, Isfahan University of Technology, Iran 1999</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/mingleiq", "https://search.asu.edu/profile/mingleiq")</f>
-        <v/>
-      </c>
-      <c r="N25" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=9LWNC50AAAAJ", "Scholar (9LWNC50AAAAJ)")</f>
-        <v/>
-      </c>
-      <c r="O25" s="3">
+        <f>HYPERLINK("https://magic.asu.edu/", "https://magic.asu.edu/")</f>
+        <v/>
+      </c>
+      <c r="N25" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O25" s="2" t="inlineStr"/>
+      <c r="P25" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/ljannesa", "https://search.asu.edu/profile/ljannesa")</f>
+        <v/>
+      </c>
+      <c r="Q25" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Leila%20Ladani%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="R25" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -4195,12 +5785,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Robert Wang</t>
+          <t>Patrick Phelan</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Professor</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -4214,49 +5804,56 @@
         </is>
       </c>
       <c r="E26" s="3">
-        <f>HYPERLINK("mailto:rywang@asu.edu", "rywang@asu.edu")</f>
+        <f>HYPERLINK("mailto:phelan@asu.edu", "phelan@asu.edu")</f>
         <v/>
       </c>
       <c r="F26" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>heat transfer</t>
+          <t>aerospace, energy systems, thermal</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>My research group is an interdisciplinary nanoengineering team that focuses on manipulating material properties for thermal energy applications. Some of our focus areas are thermoelectric power generation, thermal storage media, heat transfer, and phonon optics. To achieve our objectives, we custom-design materials using colloidal nanoparticles, chemical precursors, and nanocomposites.</t>
+          <t>Thermal engineering, sustainable energy systems, energy management, sustainable cooling systems.</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Mechanical Engineering, Energy, Renewable Energy, Energy and Sustainability, Clean Energy, Energy Efficiency Technologies, Materials Science and Engineering, Chemical Engineering, Nanoengineering, Nanoscience, Nanotechnology, Solid State Physics, Thin Film Materials, Semiconductors, Chemistry, Physics</t>
+          <t>Building Technology, Solar Energy Systems, Energy Efficiency Technologies, Mechanical Engineering</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>Wang's research interests include thermal energy conversion, storage, and transport in nanostructured materials; thermoelectric power generation; thermal storage media; heat transfer, and phonon optics</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="b">
-        <v>1</v>
+          <t>Phelan researches and teaches in the area of sustainable energy, thermal transport and thermal management.</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Postdoctoral Fellow, Tokyo Institute of Technology, Japan 1990-1992 | Ph.D. Mechanical Engineering, University of California, Berkeley 1990 | M.S. Mechanical Engineering, Massachusetts Institute of Technology 1987 | B. S. Mechanical Engineering, Tulane University, New Orleans, LA 1985</t>
+        </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>LaUdx9gAAAAJ</t>
-        </is>
-      </c>
-      <c r="M26" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/rywang", "https://search.asu.edu/profile/rywang")</f>
-        <v/>
-      </c>
-      <c r="N26" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=LaUdx9gAAAAJ", "Scholar (LaUdx9gAAAAJ)")</f>
-        <v/>
-      </c>
-      <c r="O26" s="3">
+          <t>ENGRC 463 (TEMPE, AZ 85287-6106)</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O26" s="2" t="inlineStr"/>
+      <c r="P26" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/pphelan", "https://search.asu.edu/profile/pphelan")</f>
+        <v/>
+      </c>
+      <c r="Q26" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Patrick%20Phelan%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="R26" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -4264,12 +5861,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Ronald Calhoun</t>
+          <t>Yulia Peet</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Professor</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -4283,37 +5880,51 @@
         </is>
       </c>
       <c r="E27" s="3">
-        <f>HYPERLINK("mailto:Ronald.Calhoun@asu.edu", "Ronald.Calhoun@asu.edu")</f>
+        <f>HYPERLINK("mailto:ypeet@asu.edu", "ypeet@asu.edu")</f>
         <v/>
       </c>
       <c r="F27" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>fluid dynamics</t>
+          <t>aerospace, fluid mechanics, turbulence</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr"/>
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>Calhoun’s research interests are in fluid dynamics; atmospheric sciences; boundary layer; wind energy and remote sensing.</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="b">
-        <v>1</v>
+          <t>Yulia Peet is an associate professor of aerospace and mechanical engineering in the School for Engineering of Matter, Transport and Energy with the Ira A. Fulton Schools of Engineering at Arizona State University. Her Ph.D. degree is in Aeronautics and Astronautics from Stanford (2006), M.S. and B.S. degrees are from Moscow Institute of Physics and Technology (1999 and 1997). Her previous appoi...</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D. Aeronautics and Astronautics, Stanford University 2006 | M.S. Management, State University Higher School of Economics, Moscow, Russia 2000 | M.S. Aeromechanics and Flight Engineering, Moscow Institute of Physics and Technology, Russia 1999 | B.S. Applied Mathematics and Physics, Moscow Institute of Physics and Technology, Russia 1997</t>
+        </is>
       </c>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/rcalhou", "https://search.asu.edu/profile/rcalhou")</f>
-        <v/>
-      </c>
-      <c r="N27" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ronald%20Calhoun%20Arizona%20State%20University", "Google Scholar Search")</f>
-        <v/>
-      </c>
-      <c r="O27" s="3">
+        <f>HYPERLINK("https://isim.asu.edu", "https://isim.asu.edu")</f>
+        <v/>
+      </c>
+      <c r="N27" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>_6o8MrUAAAAJ</t>
+        </is>
+      </c>
+      <c r="P27" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/ypeet", "https://search.asu.edu/profile/ypeet")</f>
+        <v/>
+      </c>
+      <c r="Q27" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=_6o8MrUAAAAJ", "Scholar (_6o8MrUAAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="R27" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -4321,12 +5932,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Spring Berman</t>
+          <t>Houlong Zhuang</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -4340,49 +5951,56 @@
         </is>
       </c>
       <c r="E28" s="3">
-        <f>HYPERLINK("mailto:Spring.Berman@asu.edu", "Spring.Berman@asu.edu")</f>
+        <f>HYPERLINK("mailto:zhuanghl@asu.edu", "zhuanghl@asu.edu")</f>
         <v/>
       </c>
       <c r="F28" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>optimization</t>
+          <t>aerospace, materials</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Modeling, analysis, control, and optimization of multi-robot systems including robotic swarms; analysis of collective behaviors in biology and biologically-inspired control of distributed systems</t>
+          <t>Quantum simulations Machine learning Quantum computing</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Systems and Control Theory, Mechanical Engineering, Autonomous Technologies, Robotics</t>
+          <t>Artificial Photosynthesis, Chemistry, Computational Physics, Machine Learning, Materials Science, Metals, Nanoscience, Semiconductors</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Dr. Berman directs the Autonomous Collective Systems Laboratory at ASU, which models and analyzes behaviors in biological and engineered collectives and designs control strategies for multi-robot systems.</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>KKup0OgAAAAJ</t>
-        </is>
-      </c>
-      <c r="M28" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/smberma2", "https://search.asu.edu/profile/smberma2")</f>
-        <v/>
-      </c>
-      <c r="N28" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=KKup0OgAAAAJ", "Scholar (KKup0OgAAAAJ)")</f>
-        <v/>
-      </c>
-      <c r="O28" s="3">
+          <t>Dr. Houlong Zhuang is an associate professor in the School for Engineering of Matter, Transport and Energy at ASU. He received his doctorate in materials science and engineering at Cornell University. Prior to ASU, Dr. Zhuang was a postdoctoral researcher at Princeton University. Dr. Zhuang’s current research interests are quantum mechanical simulations, machine learning, and quantum computing.</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>Postdoc, Department of Mechanical and Aerospace Engineering, Princeton University Postdoc, Center for Nanophase Materials Sciences, Oak Ridge National Laboratory Ph.D., Major: Materials Science and Engineering; Minor: Applied Engineering Physics, Cornell University M.S., Major: Materials Science and Engineering; Minor: Applied Engineering Physics, Cornell University M.Phil., Mechanical Engineering, The University of Hong Kong B.Eng., Materials Science and Engineering, Hunan University</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>4yYKCpUAAAAJ</t>
+        </is>
+      </c>
+      <c r="P28" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/hzhuang7", "https://search.asu.edu/profile/hzhuang7")</f>
+        <v/>
+      </c>
+      <c r="Q28" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=4yYKCpUAAAAJ", "Scholar (4yYKCpUAAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="R28" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -4390,12 +6008,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Tianyu Yang</t>
+          <t>Huei-Ping Huang</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -4409,37 +6027,51 @@
         </is>
       </c>
       <c r="E29" s="3">
-        <f>HYPERLINK("mailto:Tianyu.Yang@asu.edu", "Tianyu.Yang@asu.edu")</f>
+        <f>HYPERLINK("mailto:Huei-Ping.Huang@asu.edu", "Huei-Ping.Huang@asu.edu")</f>
         <v/>
       </c>
       <c r="F29" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>heat transfer</t>
+          <t>aerospace, fluid dynamics</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr"/>
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>Yang studies heat transfer, thermal management of electronics, and biomedical devices. She has published multiple research papers in major scientific journals.</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L29" s="2" t="inlineStr"/>
+          <t>Huang's research interests are geophysical and environmental fluid dynamics, numerical simulation of atmospheric and oceanic flows, Earth system remote sensing, and climate change.</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D. University of Illinois-Urbana-Champaign 1997 | M.S. National Taiwan University 1989 | B.S. National Central University,Taiwan 1987</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>ENGRC 359 (Tempe, AZ 85287-6106)</t>
+        </is>
+      </c>
       <c r="M29" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/tyang123", "https://search.asu.edu/profile/tyang123")</f>
-        <v/>
-      </c>
-      <c r="N29" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Tianyu%20Yang%20Arizona%20State%20University", "Google Scholar Search")</f>
-        <v/>
-      </c>
-      <c r="O29" s="3">
+        <f>HYPERLINK("http://www.public.asu.edu/~hhuang38", "http://www.public.asu.edu/~hhuang38")</f>
+        <v/>
+      </c>
+      <c r="N29" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O29" s="2" t="inlineStr"/>
+      <c r="P29" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/hhuang38", "https://search.asu.edu/profile/hhuang38")</f>
+        <v/>
+      </c>
+      <c r="Q29" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Huei-Ping%20Huang%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="R29" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -4447,7 +6079,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Yi Ren</t>
+          <t>Jagannathan Rajagopalan</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -4466,37 +6098,63 @@
         </is>
       </c>
       <c r="E30" s="3">
-        <f>HYPERLINK("mailto:yiren@asu.edu", "yiren@asu.edu")</f>
+        <f>HYPERLINK("mailto:Jagannathan.Rajagopalan@asu.edu", "Jagannathan.Rajagopalan@asu.edu")</f>
         <v/>
       </c>
       <c r="F30" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>optimization</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="inlineStr"/>
+          <t>aerospace, materials</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Synthesis of nanocrystalline materials with tailored microstructures, Mechanics of nanostructured metal and alloy films, MEMS for in situ materials testing, Polymer based micro devices for cell mechanics and biohybrid platforms</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Thin Film Materials, Materials Science, Mechanical Engineering</t>
+        </is>
+      </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>Ren’s current research interests include optimization, product/configuration design, human-computer interaction and machine learning.</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L30" s="2" t="inlineStr"/>
+          <t>Rajagopalan's research focuses on the mechanics of nanoscale materials, cells and biological systems.</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D. Mechanical Science and Engineering, University of Illinois at Urbana-Champaign, Urbana, IL 2009 | M.Tech. Mechanical Engineering, Indian Institute of Technology Madras, Chennai, India 2004 | B.Tech. Mechanical Engineering, Indian Institute of Technology Madras, Chennai, India 2004</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>ENGRC 355 (Tempe, AZ 85287-6106)</t>
+        </is>
+      </c>
       <c r="M30" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/yren32", "https://search.asu.edu/profile/yren32")</f>
-        <v/>
-      </c>
-      <c r="N30" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Yi%20Ren%20Arizona%20State%20University", "Google Scholar Search")</f>
-        <v/>
-      </c>
-      <c r="O30" s="3">
+        <f>HYPERLINK("http://faculty.engineering.asu.edu/jagan/", "http://faculty.engineering.asu.edu/jagan/")</f>
+        <v/>
+      </c>
+      <c r="N30" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>ClqRIhIAAAAJ</t>
+        </is>
+      </c>
+      <c r="P30" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/jrajago1", "https://search.asu.edu/profile/jrajago1")</f>
+        <v/>
+      </c>
+      <c r="Q30" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=ClqRIhIAAAAJ", "Scholar (ClqRIhIAAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="R30" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -4504,12 +6162,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Yongming Liu</t>
+          <t>Konrad Rykaczewski</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -4523,41 +6181,51 @@
         </is>
       </c>
       <c r="E31" s="3">
-        <f>HYPERLINK("mailto:Yongming.Liu@asu.edu", "Yongming.Liu@asu.edu")</f>
+        <f>HYPERLINK("mailto:konradr@asu.edu", "konradr@asu.edu")</f>
         <v/>
       </c>
       <c r="F31" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>uncertainty quantification</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>Yongming Liu is a professor of aerospace and mechanical engineering with the School for Engineering of Matter, Transport and Energy at Arizona State University. Fatigue and fracture of engineering materials and structures, probabilistic computational mechanics, risk assessment and management, multi-physics damage modeling and structural durability, multi-scale uncertainty quantification and propagation, imaging-based experimental testing, diagnostics and prognostics</t>
-        </is>
-      </c>
+          <t>materials, thermal</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>Liu heads the Prognostic Analysis and Reliability Assessment Laboratory (PARA). He joined ASU in 2012.</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="b">
-        <v>1</v>
+          <t>Rykaczewski's research focuses on development of soft thermal materials and system as well as studying human thermal exposure in extreme heat.</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D. Mechanical Engineering, Georgia Institute of Technology 2009 | M.S. Mechanical Engineering, Georgia Institute of Technology 2007 | B.S. Mechanical Engineering, Georgia Institute of Technology 2005</t>
+        </is>
       </c>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/yliu35", "https://search.asu.edu/profile/yliu35")</f>
-        <v/>
-      </c>
-      <c r="N31" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Yongming%20Liu%20Arizona%20State%20University", "Google Scholar Search")</f>
-        <v/>
-      </c>
-      <c r="O31" s="3">
+        <f>HYPERLINK("http://faculty.engineering.asu.edu/konrad/", "http://faculty.engineering.asu.edu/konrad/")</f>
+        <v/>
+      </c>
+      <c r="N31" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>SWeAf4UAAAAJ</t>
+        </is>
+      </c>
+      <c r="P31" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/krykacze", "https://search.asu.edu/profile/krykacze")</f>
+        <v/>
+      </c>
+      <c r="Q31" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=SWeAf4UAAAAJ", "Scholar (SWeAf4UAAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="R31" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -4565,12 +6233,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Aikaterini Stefanaki</t>
+          <t>Minglei Qu</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Associate Teaching Professor</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -4584,29 +6252,52 @@
         </is>
       </c>
       <c r="E32" s="3">
-        <f>HYPERLINK("mailto:astefan9@asu.edu", "astefan9@asu.edu")</f>
+        <f>HYPERLINK("mailto:minglei.qu@asu.edu", "minglei.qu@asu.edu")</f>
         <v/>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>composites, materials</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Metal additive manufacturing, in-situ synchrotron X-ray and neutron characterization, non-equilibrium phase transformation, metal matrix composites. Selected Publications M. Qu , J. Yuan, Q. Guo, A. Nabaa, L. I. Escano, J. Huang, Q. Li, L. Chen. Achieving uniformly refined grain structure in metal additive manufacturing: Experimental demonstration and analytical model development. Additive Manufacturing 108 (2025) 104805. M. Qu , D. Yu, J. Yuan, L. Chen, K. An, Y. Chen. Multi-stage load partitioning in additively manufactured Al6061+TiC nanocomposite characterized by in-situ neutron diffraction. Additive Manufacturing, 96 (2024) 104584. M. Qu , J. Yuan, A. Nabaa, J. Huang, C. A. Chuang, L. Chen. Melting and solidification dynamics during laser additive manufacturing of reaction-based metal matrix composites uncovered by in-situ synchrotron X-ray diffraction. Acta Materialia , 271 (2024) 119875. M. Qu , Q. Guo, L. I. Escano, A. Nabaa, S. M. H. Hojjatzadeh, Z. A. Young, L. Chen. Controlling process instability for defect lean metal additive manufacturing. Nature Communications , 13 (2022) 1079. M. Qu , Q. Guo, L. I. Escano, A. Nabaa, K. Fezzaa, L. Chen. Nanoparticle-enabled increase of energy efficiency during laser metal additive manufacturing. Additive Manufacturing , 60 (2022) 103242. M. Qu , Q.Guo, L. I. Escano, J. Yuan, S. J. Clark, K. Fezzaa, L. Chen. Controlling melt flow by nanoparticles to eliminate surface wave induced surface fluctuation. Additive Manufacturing , 59 (2022) 103081.</t>
+        </is>
+      </c>
       <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr"/>
-      <c r="K32" s="2" t="b">
-        <v>0</v>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>Minglei Qu is an Assistant Professor of Mechanical Engineering and a graduate faculty of Materials Science and Engineering in the School for Engineering of Matter, Transport and Energy at ASU. His research lies at the intersection of metal additive manufacturing, in-situ characterization, and materials science. By utilizing advanced in-situ characterization tools, including synchrotron X-ray im...</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>PhD. Mechanical Engineering, University of Wisconsin-Madison 2023</t>
+        </is>
       </c>
       <c r="L32" s="2" t="inlineStr"/>
-      <c r="M32" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/astefan9", "https://search.asu.edu/profile/astefan9")</f>
-        <v/>
-      </c>
-      <c r="N32" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Aikaterini%20Stefanaki%20Arizona%20State%20University", "Google Scholar Search")</f>
-        <v/>
-      </c>
-      <c r="O32" s="3">
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>9LWNC50AAAAJ</t>
+        </is>
+      </c>
+      <c r="P32" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/mingleiq", "https://search.asu.edu/profile/mingleiq")</f>
+        <v/>
+      </c>
+      <c r="Q32" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=9LWNC50AAAAJ", "Scholar (9LWNC50AAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="R32" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -4614,7 +6305,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Cindy (Xiangjia) Li</t>
+          <t>Qiong Nian</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -4633,45 +6324,59 @@
         </is>
       </c>
       <c r="E33" s="3">
-        <f>HYPERLINK("mailto:xiangjia.li@asu.edu", "xiangjia.li@asu.edu")</f>
+        <f>HYPERLINK("mailto:Qiong.Nian@asu.edu", "Qiong.Nian@asu.edu")</f>
         <v/>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>aerospace, materials</t>
+        </is>
+      </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Biomimetic Additive Manufacturing (3D Printing); Bioinspired Material and Structure Design; Stereolithography; Photopolymerization based 3D Printing; Multi-material and Multi-scale 3D printing; Biofabrication; Biomaterial; Ceramic Printing; Nanocomposite Printing; Physical Field Assisted Printing; 4D Printing; Flexible Sensor; Biomedical Device; Tissue Repair and Regeneration.</t>
+          <t>Nanomanufacturing, additive manufacturing, laser-based material processing, laser matter interaction and physics simulation; inkjet printing of functional materials; and 2D materials fabrication for energy storage and bio-sensors.</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Ceramic Technology, Mechanics of Composite Materials, Mechanical Engineering, Biomimicry, 3D Printing, Additive Manufacturing, Manufacturing Engineering</t>
+          <t>Additive Manufacturing, Manufacturing Engineering, Mechanical Engineering</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>Xiangjia (Cindy) Li is an Associate Professor at Arizona State University. Her research focuses on multiscale, multimaterial additive manufacturing and bioinspired design for functional materials and devices.</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="b">
-        <v>0</v>
+          <t>Nian's research interests include additive manufacturing, laser-based manufacturing and material processing, laser matter interaction and physics simulation, and functional materials for energy storage and bio-sensors.</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D. Manufacturing, Industrial Engineering, Purdue University 2015 | B.Sc. Materials Science and Engineering, University of Science and Technology of China 2009</t>
+        </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>tGQzHJIAAAAJ</t>
+          <t>Campus: Tempe</t>
         </is>
       </c>
       <c r="M33" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/xiangji5", "https://search.asu.edu/profile/xiangji5")</f>
-        <v/>
-      </c>
-      <c r="N33" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=tGQzHJIAAAAJ", "Scholar (tGQzHJIAAAAJ)")</f>
-        <v/>
-      </c>
-      <c r="O33" s="3">
+        <f>HYPERLINK("https://mmmplab.engineering.asu.edu/", "https://mmmplab.engineering.asu.edu/")</f>
+        <v/>
+      </c>
+      <c r="N33" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O33" s="2" t="inlineStr"/>
+      <c r="P33" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/qnian", "https://search.asu.edu/profile/qnian")</f>
+        <v/>
+      </c>
+      <c r="Q33" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Qiong%20Nian%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="R33" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -4679,12 +6384,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Derrick Speaks</t>
+          <t>Ronald Calhoun</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Assistant Teaching Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -4698,29 +6403,51 @@
         </is>
       </c>
       <c r="E34" s="3">
-        <f>HYPERLINK("mailto:Derrick.Speaks@asu.edu", "Derrick.Speaks@asu.edu")</f>
+        <f>HYPERLINK("mailto:Ronald.Calhoun@asu.edu", "Ronald.Calhoun@asu.edu")</f>
         <v/>
       </c>
       <c r="F34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>boundary layer, fluid dynamics</t>
+        </is>
+      </c>
       <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr"/>
-      <c r="K34" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>Calhoun’s research interests are in fluid dynamics; atmospheric sciences; boundary layer; wind energy and remote sensing.</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D. Civil and Environmental Engineering, Stanford University 1998 | Engineer. Civil and Environmental Engineering, Stanford University 1993 | M.S. Civil and Environmental Engineering, Stanford University 1992 | B.S. Symbolic Systems, Stanford University 1989</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>Goldwater 466 (TEMPE, AZ 85287-6106)</t>
+        </is>
+      </c>
       <c r="M34" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/dspeaks2", "https://search.asu.edu/profile/dspeaks2")</f>
-        <v/>
-      </c>
-      <c r="N34" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Derrick%20Speaks%20Arizona%20State%20University", "Google Scholar Search")</f>
-        <v/>
-      </c>
-      <c r="O34" s="3">
+        <f>HYPERLINK("https://windlab.engineering.asu.edu/ronald-calhoun/", "https://windlab.engineering.asu.edu/ronald-calhoun/")</f>
+        <v/>
+      </c>
+      <c r="N34" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O34" s="2" t="inlineStr"/>
+      <c r="P34" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/rcalhou", "https://search.asu.edu/profile/rcalhou")</f>
+        <v/>
+      </c>
+      <c r="Q34" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ronald%20Calhoun%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="R34" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -4728,12 +6455,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Erik Andersen</t>
+          <t>Wanxin Jin</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Faculty Associate</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -4747,29 +6474,55 @@
         </is>
       </c>
       <c r="E35" s="3">
-        <f>HYPERLINK("mailto:Erik.J.Andersen@asu.edu", "Erik.J.Andersen@asu.edu")</f>
+        <f>HYPERLINK("mailto:wjin@asu.edu", "wjin@asu.edu")</f>
         <v/>
       </c>
       <c r="F35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>robot, robotics</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>https://irislab.tech/</t>
+        </is>
+      </c>
       <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr"/>
-      <c r="K35" s="2" t="b">
-        <v>0</v>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>Jin's research includes robotics, control and machine learning, with a focus on the autonomy of robots interacting with humans and objects.</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D., Purdue University 2021 | Master of Science, Harbin Institute of Technology, 2016 | Bachelor of Engineering, Harbin Institute of Technology, 2014</t>
+        </is>
       </c>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/ejande22", "https://search.asu.edu/profile/ejande22")</f>
-        <v/>
-      </c>
-      <c r="N35" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Erik%20Andersen%20Arizona%20State%20University", "Google Scholar Search")</f>
-        <v/>
-      </c>
-      <c r="O35" s="3">
+        <f>HYPERLINK("https://irislab.tech/", "https://irislab.tech/")</f>
+        <v/>
+      </c>
+      <c r="N35" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>SoEC4h4AAAAJ</t>
+        </is>
+      </c>
+      <c r="P35" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/wjin34", "https://search.asu.edu/profile/wjin34")</f>
+        <v/>
+      </c>
+      <c r="Q35" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=SoEC4h4AAAAJ", "Scholar (SoEC4h4AAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="R35" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -4777,12 +6530,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Hamidreza Marvi</t>
+          <t>Yongming Liu</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Professor</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -4796,41 +6549,52 @@
         </is>
       </c>
       <c r="E36" s="3">
-        <f>HYPERLINK("mailto:hmarvi@asu.edu", "hmarvi@asu.edu")</f>
+        <f>HYPERLINK("mailto:Yongming.Liu@asu.edu", "Yongming.Liu@asu.edu")</f>
         <v/>
       </c>
       <c r="F36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>aerospace, materials</t>
+        </is>
+      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Bio-inspired robotics Soft robotics Magnetic micro-robotics Mechanics of animal locomotion</t>
+          <t>Yongming Liu is a professor of aerospace and mechanical engineering with the School for Engineering of Matter, Transport and Energy at Arizona State University. Fatigue and fracture of engineering materials and structures, probabilistic computational mechanics, risk assessment and management, multi-physics damage modeling and structural durability, multi-scale uncertainty quantification and propagation, imaging-based experimental testing, diagnostics and prognostics</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>Marvi would like to develop bio-inspired robotic systems and programmable interfacial structures for search and rescue, exploratory and medical applications.</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="b">
-        <v>0</v>
+          <t>Liu heads the Prognostic Analysis and Reliability Assessment Laboratory (PARA). He joined ASU in 2012.</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D. Civil Engineering, Vanderbilt University 2006 | M.S. Structural Engineering, Tongji University, Shanghai, China 2002 | B.S. Structural Engineering, Tongji University, Shanghai, China 1999</t>
+        </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>00Fepb0AAAAJ</t>
-        </is>
-      </c>
-      <c r="M36" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/hmarvi", "https://search.asu.edu/profile/hmarvi")</f>
-        <v/>
-      </c>
-      <c r="N36" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=00Fepb0AAAAJ", "Scholar (00Fepb0AAAAJ)")</f>
-        <v/>
-      </c>
-      <c r="O36" s="3">
+          <t>ENGRC 409 (Tempe, AZ 85287-6106)</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O36" s="2" t="inlineStr"/>
+      <c r="P36" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/yliu35", "https://search.asu.edu/profile/yliu35")</f>
+        <v/>
+      </c>
+      <c r="Q36" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Yongming%20Liu%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="R36" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -4838,7 +6602,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Hyunglae Lee</t>
+          <t>Cindy (Xiangjia) Li</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -4857,33 +6621,59 @@
         </is>
       </c>
       <c r="E37" s="3">
-        <f>HYPERLINK("mailto:Hyunglae.Lee@asu.edu", "Hyunglae.Lee@asu.edu")</f>
+        <f>HYPERLINK("mailto:xiangjia.li@asu.edu", "xiangjia.li@asu.edu")</f>
         <v/>
       </c>
       <c r="F37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr"/>
-      <c r="I37" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Biomimetic Additive Manufacturing (3D Printing); Bioinspired Material and Structure Design; Stereolithography; Photopolymerization based 3D Printing; Multi-material and Multi-scale 3D printing; Biofabrication; Biomaterial; Ceramic Printing; Nanocomposite Printing; Physical Field Assisted Printing; 4D Printing; Flexible Sensor; Biomedical Device; Tissue Repair and Regeneration.</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Ceramic Technology, Mechanics of Composite Materials, Mechanical Engineering, Biomimicry, 3D Printing, Additive Manufacturing, Manufacturing Engineering</t>
+        </is>
+      </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>Lee's research interests include physical human-robot interaction, neuromuscular control of human movement, robot-aided neurorehabilitation, bio-inspired robotics and system identification for physiological systems.</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="b">
-        <v>0</v>
+          <t>Xiangjia (Cindy) Li is an Associate Professor at Arizona State University. Her research focuses on multiscale, multimaterial additive manufacturing and bioinspired design for functional materials and devices.</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D. in Industrial and Systems Engineering, University of Southern California, 2019 M.S. in Computer Science, University of Southern California, 2019 M.S. in Manufacturing Engineering, Nanjing University of Aeronautics and Astronautics, 2014 B.E. in Mechanical Engineering and Automation, Nanjing University of Aeronautics and Astronautics, 2011</t>
+        </is>
       </c>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/hlee234", "https://search.asu.edu/profile/hlee234")</f>
-        <v/>
-      </c>
-      <c r="N37" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Hyunglae%20Lee%20Arizona%20State%20University", "Google Scholar Search")</f>
-        <v/>
-      </c>
-      <c r="O37" s="3">
+        <f>HYPERLINK("https://www.cindyxjli.com/", "https://www.cindyxjli.com/")</f>
+        <v/>
+      </c>
+      <c r="N37" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>tGQzHJIAAAAJ</t>
+        </is>
+      </c>
+      <c r="P37" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/xiangji5", "https://search.asu.edu/profile/xiangji5")</f>
+        <v/>
+      </c>
+      <c r="Q37" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=tGQzHJIAAAAJ", "Scholar (tGQzHJIAAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="R37" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -4891,12 +6681,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Ivy Chang</t>
+          <t>James Middleton</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Assistant Teaching Professor</t>
+          <t>Professor</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -4910,29 +6700,48 @@
         </is>
       </c>
       <c r="E38" s="3">
-        <f>HYPERLINK("mailto:Ivy.Chang@asu.edu", "Ivy.Chang@asu.edu")</f>
+        <f>HYPERLINK("mailto:jimbo@asu.edu", "jimbo@asu.edu")</f>
         <v/>
       </c>
       <c r="F38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>aerospace</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Student learning of mathematical concepts. Motivation and mathematics learning. Teacher change. Applications of technology to mathematics teaching and learning.</t>
+        </is>
+      </c>
       <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr"/>
-      <c r="K38" s="2" t="b">
-        <v>0</v>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>Middleton’s research interests focus in the following areas where he has published extensively: children’s mathematical thinking; teacher and student motivation in mathematics; and teacher change in mathematics.</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D. Educational Psychology, University of Wisconsin-Madison 1992</t>
+        </is>
       </c>
       <c r="L38" s="2" t="inlineStr"/>
-      <c r="M38" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/iychang", "https://search.asu.edu/profile/iychang")</f>
-        <v/>
-      </c>
-      <c r="N38" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ivy%20Chang%20Arizona%20State%20University", "Google Scholar Search")</f>
-        <v/>
-      </c>
-      <c r="O38" s="3">
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O38" s="2" t="inlineStr"/>
+      <c r="P38" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/jimbo", "https://search.asu.edu/profile/jimbo")</f>
+        <v/>
+      </c>
+      <c r="Q38" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=James%20Middleton%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="R38" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -4940,12 +6749,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>James Middleton</t>
+          <t>Lin Li</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -4959,37 +6768,48 @@
         </is>
       </c>
       <c r="E39" s="3">
-        <f>HYPERLINK("mailto:jimbo@asu.edu", "jimbo@asu.edu")</f>
+        <f>HYPERLINK("mailto:Lin.Li.10@asu.edu", "Lin.Li.10@asu.edu")</f>
         <v/>
       </c>
       <c r="F39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>Student learning of mathematical concepts. Motivation and mathematics learning. Teacher change. Applications of technology to mathematics teaching and learning.</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr"/>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>Middleton’s research interests focus in the following areas where he has published extensively: children’s mathematical thinking; teacher and student motivation in mathematics; and teacher change in mathematics.</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L39" s="2" t="inlineStr"/>
-      <c r="M39" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/jimbo", "https://search.asu.edu/profile/jimbo")</f>
-        <v/>
-      </c>
-      <c r="N39" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=James%20Middleton%20Arizona%20State%20University", "Google Scholar Search")</f>
-        <v/>
-      </c>
-      <c r="O39" s="3">
+          <t>Li uses multiscale material mechanics models, computational and data tools to explore advanced materials for extreme environments.</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>PhD The Ohio State University</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>Campus: Tempe</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O39" s="2" t="inlineStr"/>
+      <c r="P39" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/linli25", "https://search.asu.edu/profile/linli25")</f>
+        <v/>
+      </c>
+      <c r="Q39" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Lin%20Li%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="R39" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -4997,12 +6817,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Jiefeng Sun</t>
+          <t>Marc Mignolet</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Professor</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -5016,45 +6836,44 @@
         </is>
       </c>
       <c r="E40" s="3">
-        <f>HYPERLINK("mailto:Jiefeng.Sun@asu.edu", "Jiefeng.Sun@asu.edu")</f>
+        <f>HYPERLINK("mailto:marc.mignolet@asu.edu", "marc.mignolet@asu.edu")</f>
         <v/>
       </c>
       <c r="F40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>Hire students to conduct research https://sunroboticslab.github.io</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>Autonomous Technologies, Control Systems, Mechanical Engineering, Robotics</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>aerospace</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>Sun's research focuses on the design, dynamics, and control of soft robots and artificial muscles</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>fjUoHOsAAAAJ</t>
-        </is>
-      </c>
-      <c r="M40" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/jsun165", "https://search.asu.edu/profile/jsun165")</f>
-        <v/>
-      </c>
-      <c r="N40" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=fjUoHOsAAAAJ", "Scholar (fjUoHOsAAAAJ)")</f>
-        <v/>
-      </c>
-      <c r="O40" s="3">
+          <t>Mignolet's research interests include structural dynamics, vibrations, modeling of uncertainty in structures and stochastic multiscale analyses.</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D. Rice University 1987</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O40" s="2" t="inlineStr"/>
+      <c r="P40" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/marc03", "https://search.asu.edu/profile/marc03")</f>
+        <v/>
+      </c>
+      <c r="Q40" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Marc%20Mignolet%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="R40" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -5062,12 +6881,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Joshua Wilbur</t>
+          <t>Pedro Peralta</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Associate Teaching Professor</t>
+          <t>Professor</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -5081,29 +6900,47 @@
         </is>
       </c>
       <c r="E41" s="3">
-        <f>HYPERLINK("mailto:Joshua.Wilbur@asu.edu", "Joshua.Wilbur@asu.edu")</f>
+        <f>HYPERLINK("mailto:pperalta@asu.edu", "pperalta@asu.edu")</f>
         <v/>
       </c>
       <c r="F41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
       <c r="H41" s="2" t="inlineStr"/>
       <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr"/>
-      <c r="K41" s="2" t="b">
-        <v>0</v>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>Peralta's research focuses on mechanics of materials, fatigue and fracture of metallic alloys, dynamic and shock loading of metallic and intermetallic materials.</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D. Materials Science and Engineering, University of Pennsylvania | M.S. Mechanical Engineering and Applied Mechanics, University of Pennsylvania | Bachelor’s degree. Mechanical Engineering, Universidad Simón Bolívar, Caracas, Venezuela</t>
+        </is>
       </c>
       <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/jdwilbu1", "https://search.asu.edu/profile/jdwilbu1")</f>
-        <v/>
-      </c>
-      <c r="N41" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Joshua%20Wilbur%20Arizona%20State%20University", "Google Scholar Search")</f>
-        <v/>
-      </c>
-      <c r="O41" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/pperalta/", "https://faculty.engineering.asu.edu/pperalta/")</f>
+        <v/>
+      </c>
+      <c r="N41" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O41" s="2" t="inlineStr"/>
+      <c r="P41" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/pperalta", "https://search.asu.edu/profile/pperalta")</f>
+        <v/>
+      </c>
+      <c r="Q41" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Pedro%20Peralta%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="R41" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -5111,7 +6948,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Konrad Rykaczewski</t>
+          <t>Wonmo Kang</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -5130,37 +6967,63 @@
         </is>
       </c>
       <c r="E42" s="3">
-        <f>HYPERLINK("mailto:konradr@asu.edu", "konradr@asu.edu")</f>
+        <f>HYPERLINK("mailto:Wonmo.Kang@asu.edu", "Wonmo.Kang@asu.edu")</f>
         <v/>
       </c>
       <c r="F42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Mechanics of Composite Materials, Micro and Nanoscale Bioengineering, Nanotechnology, Thin Film Materials</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Mechanics of Composite Materials, Micro and Nanoscale Bioengineering, Nanotechnology, Thin Film Materials</t>
+        </is>
+      </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>Rykaczewski's research focuses on development of soft thermal materials and system as well as studying human thermal exposure in extreme heat.</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="b">
-        <v>0</v>
+          <t>Kang's current research interests include functional materials for energy/manufacturing applications and biomaterials/biomechanics for injury and wound healing mechanisms.</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D. Mechanical Science and Engineering, University of Illinois at Urbana-Champaign 2012</t>
+        </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>SWeAf4UAAAAJ</t>
+          <t>Campus: Tempe</t>
         </is>
       </c>
       <c r="M42" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/krykacze", "https://search.asu.edu/profile/krykacze")</f>
-        <v/>
-      </c>
-      <c r="N42" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=SWeAf4UAAAAJ", "Scholar (SWeAf4UAAAAJ)")</f>
-        <v/>
-      </c>
-      <c r="O42" s="3">
+        <f>HYPERLINK("https://wonmokang3.wixsite.com/website", "https://wonmokang3.wixsite.com/website")</f>
+        <v/>
+      </c>
+      <c r="N42" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>bHyyOTAAAAAJ</t>
+        </is>
+      </c>
+      <c r="P42" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/wkang16", "https://search.asu.edu/profile/wkang16")</f>
+        <v/>
+      </c>
+      <c r="Q42" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=bHyyOTAAAAAJ", "Scholar (bHyyOTAAAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="R42" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -5168,12 +7031,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Leila Ladani</t>
+          <t>Yi Ren</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -5187,41 +7050,48 @@
         </is>
       </c>
       <c r="E43" s="3">
-        <f>HYPERLINK("mailto:ladani@asu.edu", "ladani@asu.edu")</f>
+        <f>HYPERLINK("mailto:yiren@asu.edu", "yiren@asu.edu")</f>
         <v/>
       </c>
       <c r="F43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>Manufacturing process simulation and modeling and experiments Additive manufacturing Micro/nano manufacturing Microelectronic packaging Application of AI in manufacturing Mechanic of metallic materials Materials characterization Fatigue and damage modeling and simulation</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>Additive Manufacturing, Manufacturing Engineering</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>aerospace</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr"/>
+      <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>Dr. Ladani is a Professor of Mechanical and Aerospace Engineering at Arizona State University.</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L43" s="2" t="inlineStr"/>
-      <c r="M43" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/ljannesa", "https://search.asu.edu/profile/ljannesa")</f>
-        <v/>
-      </c>
-      <c r="N43" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Leila%20Ladani%20Arizona%20State%20University", "Google Scholar Search")</f>
-        <v/>
-      </c>
-      <c r="O43" s="3">
+          <t>Ren’s current research interests include optimization, product/configuration design, human-computer interaction and machine learning.</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D. Mechanical Engineering, University of Michigan 2011 | M.S. Mechanical Engineering, University of Michigan 2009 | B.S. Automative Engineering, Tsinghua University, China 2007</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>GWC 464 (Tempe, AZ 85287-6106)</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O43" s="2" t="inlineStr"/>
+      <c r="P43" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/yren32", "https://search.asu.edu/profile/yren32")</f>
+        <v/>
+      </c>
+      <c r="Q43" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Yi%20Ren%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="R43" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -5229,12 +7099,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Lin Li</t>
+          <t>Derrick Speaks</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Assistant Teaching Professor</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -5248,7 +7118,7 @@
         </is>
       </c>
       <c r="E44" s="3">
-        <f>HYPERLINK("mailto:Lin.Li.10@asu.edu", "Lin.Li.10@asu.edu")</f>
+        <f>HYPERLINK("mailto:Derrick.Speaks@asu.edu", "Derrick.Speaks@asu.edu")</f>
         <v/>
       </c>
       <c r="F44" s="2" t="n">
@@ -5257,24 +7127,23 @@
       <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr"/>
       <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>Li uses multiscale material mechanics models, computational and data tools to explore advanced materials for extreme environments.</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="b">
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L44" s="2" t="inlineStr"/>
-      <c r="M44" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/linli25", "https://search.asu.edu/profile/linli25")</f>
-        <v/>
-      </c>
-      <c r="N44" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Lin%20Li%20Arizona%20State%20University", "Google Scholar Search")</f>
-        <v/>
-      </c>
-      <c r="O44" s="3">
+      <c r="O44" s="2" t="inlineStr"/>
+      <c r="P44" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/dspeaks2", "https://search.asu.edu/profile/dspeaks2")</f>
+        <v/>
+      </c>
+      <c r="Q44" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Derrick%20Speaks%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="R44" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -5282,7 +7151,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Marc Mignolet</t>
+          <t>Erik Andersen</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -5301,7 +7170,7 @@
         </is>
       </c>
       <c r="E45" s="3">
-        <f>HYPERLINK("mailto:marc.mignolet@asu.edu", "marc.mignolet@asu.edu")</f>
+        <f>HYPERLINK("mailto:Erik.J.Andersen@asu.edu", "Erik.J.Andersen@asu.edu")</f>
         <v/>
       </c>
       <c r="F45" s="2" t="n">
@@ -5310,24 +7179,31 @@
       <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr"/>
       <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>Mignolet's research interests include structural dynamics, vibrations, modeling of uncertainty in structures and stochastic multiscale analyses.</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="b">
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>Ph.D. in Mechanical Engineering 2022 - University of Utah B.S./M.S.in Mechanical Engineering 2018 - University of Utah</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>Campus: Otherus</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L45" s="2" t="inlineStr"/>
-      <c r="M45" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/marc03", "https://search.asu.edu/profile/marc03")</f>
-        <v/>
-      </c>
-      <c r="N45" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Marc%20Mignolet%20Arizona%20State%20University", "Google Scholar Search")</f>
-        <v/>
-      </c>
-      <c r="O45" s="3">
+      <c r="O45" s="2" t="inlineStr"/>
+      <c r="P45" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/ejande22", "https://search.asu.edu/profile/ejande22")</f>
+        <v/>
+      </c>
+      <c r="Q45" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Erik%20Andersen%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="R45" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -5335,12 +7211,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Patrick Phelan</t>
+          <t>Ivy Chang</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Professor</t>
+          <t>Assistant Teaching Professor</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -5354,41 +7230,32 @@
         </is>
       </c>
       <c r="E46" s="3">
-        <f>HYPERLINK("mailto:phelan@asu.edu", "phelan@asu.edu")</f>
+        <f>HYPERLINK("mailto:Ivy.Chang@asu.edu", "Ivy.Chang@asu.edu")</f>
         <v/>
       </c>
       <c r="F46" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>Thermal engineering, sustainable energy systems, energy management, sustainable cooling systems.</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>Building Technology, Solar Energy Systems, Energy Efficiency Technologies, Mechanical Engineering</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>Phelan researches and teaches in the area of sustainable energy, thermal transport and thermal management.</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="b">
+      <c r="H46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L46" s="2" t="inlineStr"/>
-      <c r="M46" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/pphelan", "https://search.asu.edu/profile/pphelan")</f>
-        <v/>
-      </c>
-      <c r="N46" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Patrick%20Phelan%20Arizona%20State%20University", "Google Scholar Search")</f>
-        <v/>
-      </c>
-      <c r="O46" s="3">
+      <c r="O46" s="2" t="inlineStr"/>
+      <c r="P46" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/iychang", "https://search.asu.edu/profile/iychang")</f>
+        <v/>
+      </c>
+      <c r="Q46" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ivy%20Chang%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="R46" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -5396,12 +7263,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Pedro Peralta</t>
+          <t>Joshua Wilbur</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Professor</t>
+          <t>Associate Teaching Professor</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -5415,7 +7282,7 @@
         </is>
       </c>
       <c r="E47" s="3">
-        <f>HYPERLINK("mailto:pperalta@asu.edu", "pperalta@asu.edu")</f>
+        <f>HYPERLINK("mailto:Joshua.Wilbur@asu.edu", "Joshua.Wilbur@asu.edu")</f>
         <v/>
       </c>
       <c r="F47" s="2" t="n">
@@ -5424,24 +7291,23 @@
       <c r="G47" s="2" t="inlineStr"/>
       <c r="H47" s="2" t="inlineStr"/>
       <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>Peralta's research focuses on mechanics of materials, fatigue and fracture of metallic alloys, dynamic and shock loading of metallic and intermetallic materials.</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="b">
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L47" s="2" t="inlineStr"/>
-      <c r="M47" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/pperalta", "https://search.asu.edu/profile/pperalta")</f>
-        <v/>
-      </c>
-      <c r="N47" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Pedro%20Peralta%20Arizona%20State%20University", "Google Scholar Search")</f>
-        <v/>
-      </c>
-      <c r="O47" s="3">
+      <c r="O47" s="2" t="inlineStr"/>
+      <c r="P47" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/jdwilbu1", "https://search.asu.edu/profile/jdwilbu1")</f>
+        <v/>
+      </c>
+      <c r="Q47" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Joshua%20Wilbur%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="R47" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -5449,12 +7315,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Qiong Nian</t>
+          <t>Ricardo Cruz Lozano</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Assistant Teaching Professor</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -5468,41 +7334,32 @@
         </is>
       </c>
       <c r="E48" s="3">
-        <f>HYPERLINK("mailto:Qiong.Nian@asu.edu", "Qiong.Nian@asu.edu")</f>
+        <f>HYPERLINK("mailto:Ricardo.Cruz.Lozano@asu.edu", "Ricardo.Cruz.Lozano@asu.edu")</f>
         <v/>
       </c>
       <c r="F48" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>Nanomanufacturing, additive manufacturing, laser-based material processing, laser matter interaction and physics simulation; inkjet printing of functional materials; and 2D materials fabrication for energy storage and bio-sensors.</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>Additive Manufacturing, Manufacturing Engineering, Mechanical Engineering</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>Nian's research interests include additive manufacturing, laser-based manufacturing and material processing, laser matter interaction and physics simulation, and functional materials for energy storage and bio-sensors.</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="b">
+      <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L48" s="2" t="inlineStr"/>
-      <c r="M48" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/qnian", "https://search.asu.edu/profile/qnian")</f>
-        <v/>
-      </c>
-      <c r="N48" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Qiong%20Nian%20Arizona%20State%20University", "Google Scholar Search")</f>
-        <v/>
-      </c>
-      <c r="O48" s="3">
+      <c r="O48" s="2" t="inlineStr"/>
+      <c r="P48" s="3">
+        <f>HYPERLINK("https://search.asu.edu/profile/rcruzloz", "https://search.asu.edu/profile/rcruzloz")</f>
+        <v/>
+      </c>
+      <c r="Q48" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ricardo%20Cruz%20Lozano%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="R48" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -5510,12 +7367,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Ricardo Cruz Lozano</t>
+          <t>Srinivas Chakravarthi Kosaraju</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Assistant Teaching Professor</t>
+          <t>Teaching Professor</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -5529,7 +7386,7 @@
         </is>
       </c>
       <c r="E49" s="3">
-        <f>HYPERLINK("mailto:Ricardo.Cruz.Lozano@asu.edu", "Ricardo.Cruz.Lozano@asu.edu")</f>
+        <f>HYPERLINK("mailto:Srinivas.Kosaraju@asu.edu", "Srinivas.Kosaraju@asu.edu")</f>
         <v/>
       </c>
       <c r="F49" s="2" t="n">
@@ -5539,308 +7396,26 @@
       <c r="H49" s="2" t="inlineStr"/>
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr"/>
-      <c r="K49" s="2" t="b">
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>Campus: Tempe</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L49" s="2" t="inlineStr"/>
-      <c r="M49" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/rcruzloz", "https://search.asu.edu/profile/rcruzloz")</f>
-        <v/>
-      </c>
-      <c r="N49" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ricardo%20Cruz%20Lozano%20Arizona%20State%20University", "Google Scholar Search")</f>
-        <v/>
-      </c>
-      <c r="O49" s="3">
-        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>Sridhar Seetharaman</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>Professor</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Aerospace &amp; Mechanical Engineering</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>Arizona State University</t>
-        </is>
-      </c>
-      <c r="E50" s="3">
-        <f>HYPERLINK("mailto:seetharaman@asu.edu", "seetharaman@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr"/>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>Seetharaman's is the director of EPIXC. His research and teaching interests lie in metals and ceramics. He is also engaged in developing materials for harsh conditions.</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L50" s="2" t="inlineStr"/>
-      <c r="M50" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/sseeth11", "https://search.asu.edu/profile/sseeth11")</f>
-        <v/>
-      </c>
-      <c r="N50" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Sridhar%20Seetharaman%20Arizona%20State%20University", "Google Scholar Search")</f>
-        <v/>
-      </c>
-      <c r="O50" s="3">
-        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>Srinivas Chakravarthi Kosaraju</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>Teaching Professor</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>Aerospace &amp; Mechanical Engineering</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>Arizona State University</t>
-        </is>
-      </c>
-      <c r="E51" s="3">
-        <f>HYPERLINK("mailto:Srinivas.Kosaraju@asu.edu", "Srinivas.Kosaraju@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr"/>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr"/>
-      <c r="K51" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L51" s="2" t="inlineStr"/>
-      <c r="M51" s="3">
+      <c r="O49" s="2" t="inlineStr"/>
+      <c r="P49" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/skosara2", "https://search.asu.edu/profile/skosara2")</f>
         <v/>
       </c>
-      <c r="N51" s="3">
+      <c r="Q49" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Srinivas%20Chakravarthi%20Kosaraju%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="O51" s="3">
-        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>Wanxin Jin</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>Assistant Professor</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>Aerospace &amp; Mechanical Engineering</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>Arizona State University</t>
-        </is>
-      </c>
-      <c r="E52" s="3">
-        <f>HYPERLINK("mailto:wjin@asu.edu", "wjin@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>https://irislab.tech/</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>Jin's research includes robotics, control and machine learning, with a focus on the autonomy of robots interacting with humans and objects.</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>SoEC4h4AAAAJ</t>
-        </is>
-      </c>
-      <c r="M52" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/wjin34", "https://search.asu.edu/profile/wjin34")</f>
-        <v/>
-      </c>
-      <c r="N52" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=SoEC4h4AAAAJ", "Scholar (SoEC4h4AAAAJ)")</f>
-        <v/>
-      </c>
-      <c r="O52" s="3">
-        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>Wonmo Kang</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>Associate Professor</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Aerospace &amp; Mechanical Engineering</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>Arizona State University</t>
-        </is>
-      </c>
-      <c r="E53" s="3">
-        <f>HYPERLINK("mailto:Wonmo.Kang@asu.edu", "Wonmo.Kang@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>Mechanics of Composite Materials, Micro and Nanoscale Bioengineering, Nanotechnology, Thin Film Materials</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>Mechanics of Composite Materials, Micro and Nanoscale Bioengineering, Nanotechnology, Thin Film Materials</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>Kang's current research interests include functional materials for energy/manufacturing applications and biomaterials/biomechanics for injury and wound healing mechanisms.</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>bHyyOTAAAAAJ</t>
-        </is>
-      </c>
-      <c r="M53" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/wkang16", "https://search.asu.edu/profile/wkang16")</f>
-        <v/>
-      </c>
-      <c r="N53" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=bHyyOTAAAAAJ", "Scholar (bHyyOTAAAAAJ)")</f>
-        <v/>
-      </c>
-      <c r="O53" s="3">
-        <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>Zhe Xu</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>Assistant Professor</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Aerospace &amp; Mechanical Engineering</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>Arizona State University</t>
-        </is>
-      </c>
-      <c r="E54" s="3">
-        <f>HYPERLINK("mailto:xzhe1@asu.edu", "xzhe1@asu.edu")</f>
-        <v/>
-      </c>
-      <c r="F54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>The research interests include control theory, machine learning, formal methods and autonomous systems.</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence, Control Systems, Electric Power and Energy Systems, Machine Learning, Robotics, Systems and Control Theory</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>My research interests include control theory, formal methods, and machine learning (including reinforcement learning), with applications on autonomous systems and cyber-physical systems.</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L54" s="2" t="inlineStr"/>
-      <c r="M54" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/xzhe1", "https://search.asu.edu/profile/xzhe1")</f>
-        <v/>
-      </c>
-      <c r="N54" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Zhe%20Xu%20Arizona%20State%20University", "Google Scholar Search")</f>
-        <v/>
-      </c>
-      <c r="O54" s="3">
+      <c r="R49" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -5849,216 +7424,222 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N7" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N8" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N11" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N12" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N28" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N32" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N33" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N34" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N35" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N36" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N37" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N38" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N39" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N40" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N41" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N42" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N43" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N44" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M45" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N45" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N46" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M47" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N47" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M48" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N48" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M49" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N49" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M50" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N50" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M51" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N51" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M52" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N52" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O52" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M53" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N53" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O53" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M54" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N54" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O54" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R2" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P3" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R3" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P4" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q4" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R4" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P5" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q5" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R5" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P6" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q6" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R6" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P7" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R7" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P8" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R8" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P9" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R9" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P10" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R10" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R11" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P12" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R12" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R13" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P14" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R14" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P15" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R15" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P16" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R16" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P17" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q17" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R17" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P18" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q18" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R18" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q19" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R19" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P20" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q20" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R20" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P21" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q21" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R21" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P22" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q22" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R22" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P23" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q23" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R23" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P24" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q24" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R24" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P25" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q25" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R25" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P26" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q26" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R26" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P27" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q27" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R27" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P28" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q28" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R28" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P29" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q29" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R29" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P30" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q30" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R30" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P31" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q31" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R31" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P32" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q32" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R32" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P33" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q33" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R33" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P34" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q34" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R34" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P35" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q35" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R35" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P36" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q36" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R36" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P37" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q37" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R37" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P38" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q38" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R38" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P39" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q39" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R39" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P40" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q40" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R40" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P41" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q41" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R41" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P42" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q42" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R42" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P43" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q43" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R43" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P44" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q44" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R44" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P45" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q45" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R45" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P46" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q46" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R46" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P47" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q47" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R47" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P48" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q48" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R48" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P49" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q49" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R49" r:id="rId218"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/universities_wise/arizona_state_university/asu_aerospace_mechanical_faculty.xlsx
+++ b/universities_wise/arizona_state_university/asu_aerospace_mechanical_faculty.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R43"/>
+  <dimension ref="A1:S43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -469,13 +469,14 @@
     <col width="65" customWidth="1" min="9" max="9"/>
     <col width="65" customWidth="1" min="10" max="10"/>
     <col width="65" customWidth="1" min="11" max="11"/>
-    <col width="46" customWidth="1" min="12" max="12"/>
-    <col width="49" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="49" customWidth="1" min="16" max="16"/>
-    <col width="32" customWidth="1" min="17" max="17"/>
-    <col width="49" customWidth="1" min="18" max="18"/>
+    <col width="65" customWidth="1" min="12" max="12"/>
+    <col width="46" customWidth="1" min="13" max="13"/>
+    <col width="49" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="49" customWidth="1" min="17" max="17"/>
+    <col width="32" customWidth="1" min="18" max="18"/>
+    <col width="49" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -536,35 +537,40 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>Lab / Research Group Name</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>Office Location</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Lab / Personal Website</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Is Field Match</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Scholar ID</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Profile URL</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Google Scholar URL</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Directory URL</t>
         </is>
@@ -573,7 +579,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Liping Wang</t>
+          <t>Mohamed Houssem Kasbaoui</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -592,55 +598,52 @@
         </is>
       </c>
       <c r="E2" s="3">
-        <f>HYPERLINK("mailto:Liping.Wang@asu.edu", "Liping.Wang@asu.edu")</f>
+        <f>HYPERLINK("mailto:houssem.kasbaoui@asu.edu", "houssem.kasbaoui@asu.edu")</f>
         <v/>
       </c>
       <c r="F2" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>aerospace, guidance, heat transfer, materials, metamaterials, radiation, thermal</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Nanoscale heat transfer, metamaterials, plasmonics, and nanophotonics with an emphasis on solar thermal energy harvesting using plasmonic-enhanced light trapping for photovolatics, as well as near-field enhancement and spectral control of radiation for thermophotovoltaic energy conversion. Other research interests involve electronic cooling, MEMS, and bio-sensing.</t>
-        </is>
-      </c>
+          <t>aerospace, cfd, computational fluid dynamics, dns, fluid dynamics, fluid-structure interaction, multiphase flow, turbulent</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Wang research interests include selective control of thermal emission/absorption using meta-materials for energy harvesting and near-field radiation heat transfer enhancement between meta-materials for thermophotovoltaics.</t>
+          <t>Kasbaoui's research interests include computational fluid dynamics, numerical methods, and massively parallel simulations of multiphase and particle-laden flows for environmental and aerospace applications.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Ph.D. Mechanical Engineering, Georgia Institute of Technology 2011 | M.S. Refrigeration and Cryogenic Engineering, Shanghai Institute of Technical Physics, Chinese  Academy of Sciences 2007 | B.E. Thermal Science and Energy Engineering, University of Science and Technology of China 2004</t>
+          <t>Ph.D.  Aerospace Engineering, Cornell University, 2017 | M.Sc.  Aerospace Engineering, Cornell University, 2015 | M.Sc.  Theoretical Physics, Université Paris-Sud, 2014 | Diplôme d'Ingénieur , Ecole Centrale Paris, 2013 | B.Sc.  Theoretical Physics, Université Paris-Sud, 2011</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>ENGRC 327 (Tempe, AZ 85287-6106)</t>
-        </is>
-      </c>
-      <c r="M2" s="3">
-        <f>HYPERLINK("http://faculty.engineering.asu.edu/lpwang", "http://faculty.engineering.asu.edu/lpwang")</f>
-        <v/>
-      </c>
-      <c r="N2" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/lwang78", "https://search.asu.edu/profile/lwang78")</f>
-        <v/>
-      </c>
+          <t>Multiphase Flow and Fluid-Structure Interaction Group</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="3">
+        <f>HYPERLINK("https://kasbaoui.bitbucket.io", "https://kasbaoui.bitbucket.io")</f>
+        <v/>
+      </c>
+      <c r="O2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P2" s="2" t="inlineStr"/>
       <c r="Q2" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Liping%20Wang%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <f>HYPERLINK("https://search.asu.edu/profile/mkasbaou", "https://search.asu.edu/profile/mkasbaou")</f>
         <v/>
       </c>
       <c r="R2" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Mohamed%20Houssem%20Kasbaoui%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="S2" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -648,7 +651,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Mohamed Houssem Kasbaoui</t>
+          <t>Liping Wang</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -667,7 +670,7 @@
         </is>
       </c>
       <c r="E3" s="3">
-        <f>HYPERLINK("mailto:houssem.kasbaoui@asu.edu", "houssem.kasbaoui@asu.edu")</f>
+        <f>HYPERLINK("mailto:Liping.Wang@asu.edu", "Liping.Wang@asu.edu")</f>
         <v/>
       </c>
       <c r="F3" s="2" t="n">
@@ -675,43 +678,52 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>aerospace, cfd, computational fluid dynamics, dns, fluid dynamics, multiphase flow, turbulent</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
+          <t>aerospace, guidance, heat transfer, materials, metamaterials, radiation, thermal</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Nanoscale heat transfer, metamaterials, plasmonics, and nanophotonics with an emphasis on solar thermal energy harvesting using plasmonic-enhanced light trapping for photovolatics, as well as near-field enhancement and spectral control of radiation for thermophotovoltaic energy conversion. Other research interests involve electronic cooling, MEMS, and bio-sensing.</t>
+        </is>
+      </c>
       <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Kasbaoui's research interests include computational fluid dynamics, numerical methods, and massively parallel simulations of multiphase and particle-laden flows for environmental and aerospace applications.</t>
+          <t>Wang research interests include selective control of thermal emission/absorption using meta-materials for energy harvesting and near-field radiation heat transfer enhancement between meta-materials for thermophotovoltaics.</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Ph.D.  Aerospace Engineering, Cornell University, 2017 | M.Sc.  Aerospace Engineering, Cornell University, 2015 | M.Sc.  Theoretical Physics, Université Paris-Sud, 2014 | Diplôme d'Ingénieur , Ecole Centrale Paris, 2013 | B.Sc.  Theoretical Physics, Université Paris-Sud, 2011</t>
+          <t>Ph.D. Mechanical Engineering, Georgia Institute of Technology 2011 | M.S. Refrigeration and Cryogenic Engineering, Shanghai Institute of Technical Physics, Chinese  Academy of Sciences 2007 | B.E. Thermal Science and Energy Engineering, University of Science and Technology of China 2004</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Campus: Tempe</t>
-        </is>
-      </c>
-      <c r="M3" s="3">
-        <f>HYPERLINK("https://kasbaoui.bitbucket.io", "https://kasbaoui.bitbucket.io")</f>
-        <v/>
-      </c>
-      <c r="N3" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/mkasbaou", "https://search.asu.edu/profile/mkasbaou")</f>
-        <v/>
-      </c>
+          <t>Nanoscale Thermal Radiation Lab</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>ENGRC 327 (Tempe, AZ 85287-6106)</t>
+        </is>
+      </c>
+      <c r="N3" s="3">
+        <f>HYPERLINK("http://faculty.engineering.asu.edu/lpwang", "http://faculty.engineering.asu.edu/lpwang")</f>
+        <v/>
+      </c>
+      <c r="O3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P3" s="2" t="inlineStr"/>
       <c r="Q3" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Mohamed%20Houssem%20Kasbaoui%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <f>HYPERLINK("https://search.asu.edu/profile/lwang78", "https://search.asu.edu/profile/lwang78")</f>
         <v/>
       </c>
       <c r="R3" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Liping%20Wang%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="S3" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -767,26 +779,31 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>Computational Mechanics Lab</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
           <t>ENGRC 353 (Tempe, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="M4" s="3">
+      <c r="N4" s="3">
         <f>HYPERLINK("http://sparky.fulton.asu.edu/oswald/", "http://sparky.fulton.asu.edu/oswald/")</f>
         <v/>
       </c>
-      <c r="N4" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O4" s="2" t="inlineStr"/>
-      <c r="P4" s="3">
+      <c r="O4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/joswald1", "https://search.asu.edu/profile/joswald1")</f>
         <v/>
       </c>
-      <c r="Q4" s="3">
+      <c r="R4" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Jay%20Oswald%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="R4" s="3">
+      <c r="S4" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -846,30 +863,31 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Campus: Tempe</t>
-        </is>
-      </c>
-      <c r="M5" s="3">
+          <t>Sun Robotics Lab</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="3">
         <f>HYPERLINK("https://sunroboticslab.github.io", "https://sunroboticslab.github.io")</f>
         <v/>
       </c>
-      <c r="N5" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>fjUoHOsAAAAJ</t>
         </is>
       </c>
-      <c r="P5" s="3">
+      <c r="Q5" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/jsun165", "https://search.asu.edu/profile/jsun165")</f>
         <v/>
       </c>
-      <c r="Q5" s="3">
+      <c r="R5" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=fjUoHOsAAAAJ", "Scholar (fjUoHOsAAAAJ)")</f>
         <v/>
       </c>
-      <c r="R5" s="3">
+      <c r="S5" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -921,23 +939,24 @@
       </c>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>xT-lX9sAAAAJ</t>
         </is>
       </c>
-      <c r="P6" s="3">
+      <c r="Q6" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/asuchen", "https://search.asu.edu/profile/asuchen")</f>
         <v/>
       </c>
-      <c r="Q6" s="3">
+      <c r="R6" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=xT-lX9sAAAAJ", "Scholar (xT-lX9sAAAAJ)")</f>
         <v/>
       </c>
-      <c r="R6" s="3">
+      <c r="S6" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -993,23 +1012,24 @@
       </c>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>DKc-AgcAAAAJ</t>
         </is>
       </c>
-      <c r="P7" s="3">
+      <c r="Q7" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/kramesh2", "https://search.asu.edu/profile/kramesh2")</f>
         <v/>
       </c>
-      <c r="Q7" s="3">
+      <c r="R7" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=DKc-AgcAAAAJ", "Scholar (DKc-AgcAAAAJ)")</f>
         <v/>
       </c>
-      <c r="R7" s="3">
+      <c r="S7" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1017,7 +1037,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Leixin Ma</t>
+          <t>Kunal Garg</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -1036,7 +1056,7 @@
         </is>
       </c>
       <c r="E8" s="3">
-        <f>HYPERLINK("mailto:Leixin.Ma@asu.edu", "Leixin.Ma@asu.edu")</f>
+        <f>HYPERLINK("mailto:kgarg24@asu.edu", "kgarg24@asu.edu")</f>
         <v/>
       </c>
       <c r="F8" s="2" t="n">
@@ -1044,51 +1064,60 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>aerodynamics, aerospace, fluid-structure interaction, fluids, materials, robot</t>
+          <t>aerospace, autonomous, control theory, motion planning, robot, robotics</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Aerodynamics, Dynamical Systems, Machine Learning, Mechanics of Composite Materials</t>
+          <t>Distributed multi-agent motion planning and control, Provably safe control design using machine learning-based certificates, Foundation models in complex robotic tasks, Failure prediction from limited demonstrations, Human-robot interaction.</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Aerodynamics, Dynamical Systems, Machine Learning, Mechanics of Composite Materials</t>
+          <t>Control Systems, Dynamical Systems, Machine Learning, Nonlinear Dynamical Systems, Robotics</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Leixin Ma's career goal is a data-driven and physically consistent approach to modeling and designing programmable smart structures and robots, especially under complex fluid flow conditions.</t>
+          <t>Garg's research interests include control synthesis for multi-agent coordination using control theory and machine learning.</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Ph.D. in Mechanical Engineering, Massachusetts Institute of Technology, 2021 S.M. in Mechanical Engineering, Massachusetts Institute of Technology, 2017 B.S.E. in Naval Architecture and Ocean Engineering, Shanghai Jiao Tong University, 2015</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="3">
-        <f>HYPERLINK("https://sites.google.com/view/oasislabasu", "https://sites.google.com/view/oasislabasu")</f>
-        <v/>
-      </c>
-      <c r="N8" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>2xQTOc0AAAAJ</t>
-        </is>
-      </c>
-      <c r="P8" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/leixinma", "https://search.asu.edu/profile/leixinma")</f>
-        <v/>
+          <t>PhD. Aerospace Engineering, University of Michigan, Ann Arbor, 2021 MS. Aerospace Engineering, University of Michigan, Ann Arbor, 2019 BTech. Aerospace Engineering, Indian Institute of Technology, Bombay, 2016</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Safe and Autonomous Robotics (STAR) Lab</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>551 E Tyler Mall ERC 475 (Tempe, AZ 85281)</t>
+        </is>
+      </c>
+      <c r="N8" s="3">
+        <f>HYPERLINK("https://sites.google.com/asu.edu/kunalgarg/", "https://sites.google.com/asu.edu/kunalgarg/")</f>
+        <v/>
+      </c>
+      <c r="O8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>vs3pl-8AAAAJ</t>
+        </is>
       </c>
       <c r="Q8" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=2xQTOc0AAAAJ", "Scholar (2xQTOc0AAAAJ)")</f>
+        <f>HYPERLINK("https://search.asu.edu/profile/kgarg24", "https://search.asu.edu/profile/kgarg24")</f>
         <v/>
       </c>
       <c r="R8" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=vs3pl-8AAAAJ", "Scholar (vs3pl-8AAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="S8" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1096,7 +1125,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Gokul Pathikonda</t>
+          <t>Leixin Ma</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1115,59 +1144,64 @@
         </is>
       </c>
       <c r="E9" s="3">
-        <f>HYPERLINK("mailto:Gokul.Pathikonda@asu.edu", "Gokul.Pathikonda@asu.edu")</f>
+        <f>HYPERLINK("mailto:Leixin.Ma@asu.edu", "Leixin.Ma@asu.edu")</f>
         <v/>
       </c>
       <c r="F9" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>aerodynamics, aerospace, reacting flow, turbulence, turbulent</t>
+          <t>aerodynamics, aerospace, fluid-structure interaction, fluids, materials, robot</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Aerodynamics, Aerospace Engineering, Mechanical Engineering</t>
+          <t>Aerodynamics, Dynamical Systems, Machine Learning, Mechanics of Composite Materials</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Aerodynamics, Aerospace Engineering, Mechanical Engineering</t>
+          <t>Aerodynamics, Dynamical Systems, Machine Learning, Mechanics of Composite Materials</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Dr. Pathikonda studies turbulent fluid flows to understand natural and engineering phenomena using lab experiments. His expertise is in complex (reacting) mixing, high Re-flows, laser-based &amp; spectroscopic techniques, etc.</t>
+          <t>Leixin Ma's career goal is a data-driven and physically consistent approach to modeling and designing programmable smart structures and robots, especially under complex fluid flow conditions.</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Ph. D. Theoretical and Applied Mechanics, University of Illinois, Urbana Champaign, 2017 | MS Aerospace Engineering, University of Illinois, Urbana Champaign, 2013 | B. Tech. Mechanical Engineering, National Institute of Technology, Warangal, 2009</t>
+          <t>Ph.D. in Mechanical Engineering, Massachusetts Institute of Technology, 2021 S.M. in Mechanical Engineering, Massachusetts Institute of Technology, 2017 B.S.E. in Naval Architecture and Ocean Engineering, Shanghai Jiao Tong University, 2015</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>551 E Tyler Mall ERC 479 (Tempe, AZ 85281)</t>
-        </is>
-      </c>
-      <c r="M9" s="3">
-        <f>HYPERLINK("https://faculty.engineering.asu.edu/cmat/", "https://faculty.engineering.asu.edu/cmat/")</f>
-        <v/>
-      </c>
-      <c r="N9" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O9" s="2" t="inlineStr"/>
-      <c r="P9" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/gpathiko", "https://search.asu.edu/profile/gpathiko")</f>
-        <v/>
+          <t>Optimization, Autonomy, and Soft Intelligence Systems (OASIS) Lab</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="3">
+        <f>HYPERLINK("https://sites.google.com/view/oasislabasu", "https://sites.google.com/view/oasislabasu")</f>
+        <v/>
+      </c>
+      <c r="O9" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>2xQTOc0AAAAJ</t>
+        </is>
       </c>
       <c r="Q9" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Gokul%20Pathikonda%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <f>HYPERLINK("https://search.asu.edu/profile/leixinma", "https://search.asu.edu/profile/leixinma")</f>
         <v/>
       </c>
       <c r="R9" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=2xQTOc0AAAAJ", "Scholar (2xQTOc0AAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="S9" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1175,7 +1209,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Kunal Garg</t>
+          <t>Gokul Pathikonda</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1194,7 +1228,7 @@
         </is>
       </c>
       <c r="E10" s="3">
-        <f>HYPERLINK("mailto:kgarg24@asu.edu", "kgarg24@asu.edu")</f>
+        <f>HYPERLINK("mailto:Gokul.Pathikonda@asu.edu", "Gokul.Pathikonda@asu.edu")</f>
         <v/>
       </c>
       <c r="F10" s="2" t="n">
@@ -1202,55 +1236,52 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>aerospace, control theory, motion planning, robot, robotics</t>
+          <t>aerodynamics, aerospace, reacting flow, turbulence, turbulent</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Distributed multi-agent motion planning and control, Provably safe control design using machine learning-based certificates, Foundation models in complex robotic tasks, Failure prediction from limited demonstrations, Human-robot interaction.</t>
+          <t>Aerodynamics, Aerospace Engineering, Mechanical Engineering</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Control Systems, Dynamical Systems, Machine Learning, Nonlinear Dynamical Systems, Robotics</t>
+          <t>Aerodynamics, Aerospace Engineering, Mechanical Engineering</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Garg's research interests include control synthesis for multi-agent coordination using control theory and machine learning.</t>
+          <t>Dr. Pathikonda studies turbulent fluid flows to understand natural and engineering phenomena using lab experiments. His expertise is in complex (reacting) mixing, high Re-flows, laser-based &amp; spectroscopic techniques, etc.</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>PhD. Aerospace Engineering, University of Michigan, Ann Arbor, 2021 MS. Aerospace Engineering, University of Michigan, Ann Arbor, 2019 BTech. Aerospace Engineering, Indian Institute of Technology, Bombay, 2016</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>551 E Tyler Mall ERC 475 (Tempe, AZ 85281)</t>
-        </is>
-      </c>
-      <c r="M10" s="3">
-        <f>HYPERLINK("https://sites.google.com/asu.edu/kunalgarg/", "https://sites.google.com/asu.edu/kunalgarg/")</f>
-        <v/>
-      </c>
-      <c r="N10" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>vs3pl-8AAAAJ</t>
-        </is>
-      </c>
-      <c r="P10" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/kgarg24", "https://search.asu.edu/profile/kgarg24")</f>
-        <v/>
-      </c>
+          <t>Ph. D. Theoretical and Applied Mechanics, University of Illinois, Urbana Champaign, 2017 | MS Aerospace Engineering, University of Illinois, Urbana Champaign, 2013 | B. Tech. Mechanical Engineering, National Institute of Technology, Warangal, 2009</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>551 E Tyler Mall ERC 479 (Tempe, AZ 85281)</t>
+        </is>
+      </c>
+      <c r="N10" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/cmat/", "https://faculty.engineering.asu.edu/cmat/")</f>
+        <v/>
+      </c>
+      <c r="O10" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
       <c r="Q10" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=vs3pl-8AAAAJ", "Scholar (vs3pl-8AAAAJ)")</f>
+        <f>HYPERLINK("https://search.asu.edu/profile/gpathiko", "https://search.asu.edu/profile/gpathiko")</f>
         <v/>
       </c>
       <c r="R10" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Gokul%20Pathikonda%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="S10" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1300,25 +1331,30 @@
           <t>PhD in Mechanical Engineering, University of Technology (RWTH) Aachen, Germany 2001 | Diploma. Mechanical and Aerospace Engineering, University of Technology (RWTH) Aachen, Germany 1995</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>Computational Multiphase Physics Laboratory</t>
+        </is>
+      </c>
       <c r="M11" s="2" t="inlineStr"/>
-      <c r="N11" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>yv6aCW8AAAAJ</t>
         </is>
       </c>
-      <c r="P11" s="3">
+      <c r="Q11" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/mherrma1", "https://search.asu.edu/profile/mherrma1")</f>
         <v/>
       </c>
-      <c r="Q11" s="3">
+      <c r="R11" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=yv6aCW8AAAAJ", "Scholar (yv6aCW8AAAAJ)")</f>
         <v/>
       </c>
-      <c r="R11" s="3">
+      <c r="S11" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1376,28 +1412,33 @@
           <t>Ph.D. Mechanical Engineering and Applied Mechanics, University of Pennsylvania 2010 | M.S.E. Mechanical Engineering and Applied Mechanics, University of Pennsylvania 2008 | B.S.E. Mechanical and Aerospace Engineering, Princeton University 2005 | Certificate. Robotics and Intelligent Systems, Princeton University 2005</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="3">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>Autonomous Collective Systems (ACS) Laboratory</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="3">
         <f>HYPERLINK("http://faculty.engineering.asu.edu/acs/", "http://faculty.engineering.asu.edu/acs/")</f>
         <v/>
       </c>
-      <c r="N12" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>KKup0OgAAAAJ</t>
         </is>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/smberma2", "https://search.asu.edu/profile/smberma2")</f>
         <v/>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=KKup0OgAAAAJ", "Scholar (KKup0OgAAAAJ)")</f>
         <v/>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1455,28 +1496,29 @@
           <t>Ph.D Degree at the  Department of Electrical, Computer, and Systems Engineering  at  Rensselaer Polytechnic Institute  in 2018 | Master's Degree at the  School of electrical and information engineering  at  Tianjin University  in 2014 | Bachelor's Degree at the  School of electrical and information engineering  at  Tianjin University  in 2011</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="M13" s="3">
+      <c r="N13" s="3">
         <f>HYPERLINK("https://sites.google.com/site/zhexudavid00710/research?authuser=0", "https://sites.google.com/site/zhexudavid00710/research?authuser=0")</f>
         <v/>
       </c>
-      <c r="N13" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O13" s="2" t="inlineStr"/>
-      <c r="P13" s="3">
+      <c r="O13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/xzhe1", "https://search.asu.edu/profile/xzhe1")</f>
         <v/>
       </c>
-      <c r="Q13" s="3">
+      <c r="R13" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Zhe%20Xu%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="R13" s="3">
+      <c r="S13" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1528,19 +1570,20 @@
       </c>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr"/>
-      <c r="N14" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O14" s="2" t="inlineStr"/>
-      <c r="P14" s="3">
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/jkim520", "https://search.asu.edu/profile/jkim520")</f>
         <v/>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Jeonglae%20Kim%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1598,24 +1641,29 @@
           <t>Ph.D. Aeronautics and Astronautics, Stanford University 2006 | Bachelor's degree. Physics, University of Texas-Austin 1999 | Bachelor's degree. Aerospace Engineering, University of Texas-Austin 1999</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="3">
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>Cybernetic Systems and Controls Laboratory (CSCL)</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="3">
         <f>HYPERLINK("http://control.asu.edu/", "http://control.asu.edu/")</f>
         <v/>
       </c>
-      <c r="N15" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O15" s="2" t="inlineStr"/>
-      <c r="P15" s="3">
+      <c r="O15" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/mpeet", "https://search.asu.edu/profile/mpeet")</f>
         <v/>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Matthew%20Peet%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1674,27 +1722,28 @@
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="3">
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="3">
         <f>HYPERLINK("http://wang.faculty.asu.edu/", "http://wang.faculty.asu.edu/")</f>
         <v/>
       </c>
-      <c r="N16" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>LaUdx9gAAAAJ</t>
         </is>
       </c>
-      <c r="P16" s="3">
+      <c r="Q16" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/rywang", "https://search.asu.edu/profile/rywang")</f>
         <v/>
       </c>
-      <c r="Q16" s="3">
+      <c r="R16" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=LaUdx9gAAAAJ", "Scholar (LaUdx9gAAAAJ)")</f>
         <v/>
       </c>
-      <c r="R16" s="3">
+      <c r="S16" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1753,23 +1802,24 @@
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="3">
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="3">
         <f>HYPERLINK("http://RESEARCHGATE.net/profile/Ryan_Milcarek", "http://RESEARCHGATE.net/profile/Ryan_Milcarek")</f>
         <v/>
       </c>
-      <c r="N17" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O17" s="2" t="inlineStr"/>
-      <c r="P17" s="3">
+      <c r="O17" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/rjmilcar", "https://search.asu.edu/profile/rjmilcar")</f>
         <v/>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ryan%20Milcarek%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1819,25 +1869,26 @@
           <t>Ph.D. Aerospace Engineering, University of Michigan-Ann Arbor | M.S.E. Aerospace Engineering, University of Michigan-Ann Arbor | B.S. Aeronautical and Astronautical Engineering, The Ohio State University-Columbus</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>ENGRC 377 (TEMPE, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr"/>
-      <c r="N18" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O18" s="2" t="inlineStr"/>
-      <c r="P18" s="3">
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/attwl", "https://search.asu.edu/profile/attwl")</f>
         <v/>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=T.-W.%20Lee%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1889,19 +1940,20 @@
       </c>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr"/>
-      <c r="N19" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O19" s="2" t="inlineStr"/>
-      <c r="P19" s="3">
+      <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/tyang123", "https://search.asu.edu/profile/tyang123")</f>
         <v/>
       </c>
-      <c r="Q19" s="3">
+      <c r="R19" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Tianyu%20Yang%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="R19" s="3">
+      <c r="S19" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1953,27 +2005,28 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>ENGRC 427 (TEMPE, AZ 85287-6106)</t>
+          <t>Adaptive Intelligent Materials &amp; Systems (AIMS) Center</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>w3fU9E0AAAAJ</t>
         </is>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/chattopa", "https://search.asu.edu/profile/chattopa")</f>
         <v/>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=w3fU9E0AAAAJ", "Scholar (w3fU9E0AAAAJ)")</f>
         <v/>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2031,29 +2084,30 @@
           <t>PhD Johns Hopkins University</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
         <is>
           <t>HRx2lJQAAAAJ</t>
         </is>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/adscotti", "https://search.asu.edu/profile/adscotti")</f>
         <v/>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=HRx2lJQAAAAJ", "Scholar (HRx2lJQAAAAJ)")</f>
         <v/>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2109,30 +2163,35 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
+          <t>3D Energy Lab</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
           <t>551 E Tyler Mall ERC 363 (Tempe, AZ 85281)</t>
         </is>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <f>HYPERLINK("http://sites.google.com/view/3denergy", "http://sites.google.com/view/3denergy")</f>
         <v/>
       </c>
-      <c r="N22" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>fs2d97sAAAAJ</t>
         </is>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/bkwon2", "https://search.asu.edu/profile/bkwon2")</f>
         <v/>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=fs2d97sAAAAJ", "Scholar (fs2d97sAAAAJ)")</f>
         <v/>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2186,28 +2245,33 @@
           <t>Ph.D. Mechanical Engineering, Georgia Institute of Technology, Atlanta 2013 | M.S. Mechanical Engineering, Clemson University, SC 2009 | M.S. Biomedical Engineering, Sharif University of Technology, Tehran, Iran 2007 | B.S. Mechanical Engineering, Iran University of Science and Technology, Tehran 2004</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr"/>
-      <c r="M23" s="3">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>Bio-Inspired Robotics, Technology, and Healthcare Laboratory (BIRTH Lab)</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="3">
         <f>HYPERLINK("http://birth.asu.edu", "http://birth.asu.edu")</f>
         <v/>
       </c>
-      <c r="N23" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>00Fepb0AAAAJ</t>
         </is>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/hmarvi", "https://search.asu.edu/profile/hmarvi")</f>
         <v/>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=00Fepb0AAAAJ", "Scholar (00Fepb0AAAAJ)")</f>
         <v/>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2257,28 +2321,29 @@
           <t>B.S. Mechanical and Aerospace Engineering, Seoul National University (2002) M.S. Mechanical and Aerospace Engineering, Seoul National University (2004) Ph.D Mechanical Engineering, Massachusetts Institute of Technology (2013)</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/hlee", "https://faculty.engineering.asu.edu/hlee")</f>
         <v/>
       </c>
-      <c r="N24" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O24" s="2" t="inlineStr"/>
-      <c r="P24" s="3">
+      <c r="O24" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P24" s="2" t="inlineStr"/>
+      <c r="Q24" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/hlee234", "https://search.asu.edu/profile/hlee234")</f>
         <v/>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Hyunglae%20Lee%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2336,24 +2401,29 @@
           <t>PhD. Mechanical Engineering, University of Maryland-College Park 2007 | M.S. Mechanical Engineering, University of Maryland-College Park 2005 | PhD. Student, Mechanical Engineering, Isfahan University of Technology, Iran 2001-2002 | M.S. Mechanical Engineering, Isfahan University of Technology, Iran 2001 | B.S. Mechanical Engineering, Isfahan University of Technology, Iran 1999</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr"/>
-      <c r="M25" s="3">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>Manufacturing and Advanced Materials Characterization (MAGIC) Lab</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="3">
         <f>HYPERLINK("https://magic.asu.edu/", "https://magic.asu.edu/")</f>
         <v/>
       </c>
-      <c r="N25" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O25" s="2" t="inlineStr"/>
-      <c r="P25" s="3">
+      <c r="O25" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P25" s="2" t="inlineStr"/>
+      <c r="Q25" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/ljannesa", "https://search.asu.edu/profile/ljannesa")</f>
         <v/>
       </c>
-      <c r="Q25" s="3">
+      <c r="R25" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Leila%20Ladani%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="R25" s="3">
+      <c r="S25" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2411,25 +2481,26 @@
           <t>Postdoctoral Fellow, Tokyo Institute of Technology, Japan 1990-1992 | Ph.D. Mechanical Engineering, University of California, Berkeley 1990 | M.S. Mechanical Engineering, Massachusetts Institute of Technology 1987 | B. S. Mechanical Engineering, Tulane University, New Orleans, LA 1985</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>ENGRC 463 (TEMPE, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr"/>
-      <c r="N26" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O26" s="2" t="inlineStr"/>
-      <c r="P26" s="3">
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P26" s="2" t="inlineStr"/>
+      <c r="Q26" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/pphelan", "https://search.asu.edu/profile/pphelan")</f>
         <v/>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Patrick%20Phelan%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2479,28 +2550,33 @@
           <t>Ph.D. Aeronautics and Astronautics, Stanford University 2006 | M.S. Management, State University Higher School of Economics, Moscow, Russia 2000 | M.S. Aeromechanics and Flight Engineering, Moscow Institute of Physics and Technology, Russia 1999 | B.S. Applied Mathematics and Physics, Moscow Institute of Physics and Technology, Russia 1997</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr"/>
-      <c r="M27" s="3">
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>Interdisciplinary Simulation and Modeling (ISiM) Lab</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="3">
         <f>HYPERLINK("https://isim.asu.edu", "https://isim.asu.edu")</f>
         <v/>
       </c>
-      <c r="N27" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
+      <c r="O27" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
         <is>
           <t>_6o8MrUAAAAJ</t>
         </is>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/ypeet", "https://search.asu.edu/profile/ypeet")</f>
         <v/>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=_6o8MrUAAAAJ", "Scholar (_6o8MrUAAAAJ)")</f>
         <v/>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2558,25 +2634,34 @@
           <t>Postdoc, Department of Mechanical and Aerospace Engineering, Princeton University Postdoc, Center for Nanophase Materials Sciences, Oak Ridge National Laboratory Ph.D., Major: Materials Science and Engineering; Minor: Applied Engineering Physics, Cornell University M.S., Major: Materials Science and Engineering; Minor: Applied Engineering Physics, Cornell University M.Phil., Mechanical Engineering, The University of Hong Kong B.Eng., Materials Science and Engineering, Hunan University</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="2" t="inlineStr"/>
-      <c r="N28" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>Computational Materials Science and Design Lab</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>Campus: Tempe</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
         <is>
           <t>4yYKCpUAAAAJ</t>
         </is>
       </c>
-      <c r="P28" s="3">
+      <c r="Q28" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/hzhuang7", "https://search.asu.edu/profile/hzhuang7")</f>
         <v/>
       </c>
-      <c r="Q28" s="3">
+      <c r="R28" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=4yYKCpUAAAAJ", "Scholar (4yYKCpUAAAAJ)")</f>
         <v/>
       </c>
-      <c r="R28" s="3">
+      <c r="S28" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2626,28 +2711,29 @@
           <t>Ph.D. University of Illinois-Urbana-Champaign 1997 | M.S. National Taiwan University 1989 | B.S. National Central University,Taiwan 1987</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>ENGRC 359 (Tempe, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <f>HYPERLINK("http://www.public.asu.edu/~hhuang38", "http://www.public.asu.edu/~hhuang38")</f>
         <v/>
       </c>
-      <c r="N29" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O29" s="2" t="inlineStr"/>
-      <c r="P29" s="3">
+      <c r="O29" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P29" s="2" t="inlineStr"/>
+      <c r="Q29" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/hhuang38", "https://search.asu.edu/profile/hhuang38")</f>
         <v/>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Huei-Ping%20Huang%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2707,30 +2793,35 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
+          <t>Nanomechanics Laboratory</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
           <t>ENGRC 355 (Tempe, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="M30" s="3">
+      <c r="N30" s="3">
         <f>HYPERLINK("http://faculty.engineering.asu.edu/jagan/", "http://faculty.engineering.asu.edu/jagan/")</f>
         <v/>
       </c>
-      <c r="N30" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
+      <c r="O30" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
         <is>
           <t>ClqRIhIAAAAJ</t>
         </is>
       </c>
-      <c r="P30" s="3">
+      <c r="Q30" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/jrajago1", "https://search.asu.edu/profile/jrajago1")</f>
         <v/>
       </c>
-      <c r="Q30" s="3">
+      <c r="R30" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=ClqRIhIAAAAJ", "Scholar (ClqRIhIAAAAJ)")</f>
         <v/>
       </c>
-      <c r="R30" s="3">
+      <c r="S30" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2780,28 +2871,33 @@
           <t>Ph.D. Mechanical Engineering, Georgia Institute of Technology 2009 | M.S. Mechanical Engineering, Georgia Institute of Technology 2007 | B.S. Mechanical Engineering, Georgia Institute of Technology 2005</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr"/>
-      <c r="M31" s="3">
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>Nano-Bio-Thermal Engineering Laboratory</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="3">
         <f>HYPERLINK("http://faculty.engineering.asu.edu/konrad/", "http://faculty.engineering.asu.edu/konrad/")</f>
         <v/>
       </c>
-      <c r="N31" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
+      <c r="O31" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
         <is>
           <t>SWeAf4UAAAAJ</t>
         </is>
       </c>
-      <c r="P31" s="3">
+      <c r="Q31" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/krykacze", "https://search.asu.edu/profile/krykacze")</f>
         <v/>
       </c>
-      <c r="Q31" s="3">
+      <c r="R31" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=SWeAf4UAAAAJ", "Scholar (SWeAf4UAAAAJ)")</f>
         <v/>
       </c>
-      <c r="R31" s="3">
+      <c r="S31" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2857,23 +2953,24 @@
       </c>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr"/>
-      <c r="N32" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
         <is>
           <t>9LWNC50AAAAJ</t>
         </is>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/mingleiq", "https://search.asu.edu/profile/mingleiq")</f>
         <v/>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=9LWNC50AAAAJ", "Scholar (9LWNC50AAAAJ)")</f>
         <v/>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2931,28 +3028,29 @@
           <t>Ph.D. Manufacturing, Industrial Engineering, Purdue University 2015 | B.Sc. Materials Science and Engineering, University of Science and Technology of China 2009</t>
         </is>
       </c>
-      <c r="L33" s="2" t="inlineStr">
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <f>HYPERLINK("https://mmmplab.engineering.asu.edu/", "https://mmmplab.engineering.asu.edu/")</f>
         <v/>
       </c>
-      <c r="N33" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O33" s="2" t="inlineStr"/>
-      <c r="P33" s="3">
+      <c r="O33" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P33" s="2" t="inlineStr"/>
+      <c r="Q33" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/qnian", "https://search.asu.edu/profile/qnian")</f>
         <v/>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Qiong%20Nian%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -3004,26 +3102,31 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
+          <t>Wind Energy and Atmospheric Boundary Layer Lab</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
           <t>Goldwater 466 (TEMPE, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="M34" s="3">
+      <c r="N34" s="3">
         <f>HYPERLINK("https://windlab.engineering.asu.edu/ronald-calhoun/", "https://windlab.engineering.asu.edu/ronald-calhoun/")</f>
         <v/>
       </c>
-      <c r="N34" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O34" s="2" t="inlineStr"/>
-      <c r="P34" s="3">
+      <c r="O34" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P34" s="2" t="inlineStr"/>
+      <c r="Q34" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/rcalhou", "https://search.asu.edu/profile/rcalhou")</f>
         <v/>
       </c>
-      <c r="Q34" s="3">
+      <c r="R34" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ronald%20Calhoun%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="R34" s="3">
+      <c r="S34" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -3077,28 +3180,33 @@
           <t>Ph.D., Purdue University 2021 | Master of Science, Harbin Institute of Technology, 2016 | Bachelor of Engineering, Harbin Institute of Technology, 2014</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr"/>
-      <c r="M35" s="3">
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>Intelligent Robotics and Interactive Systems Lab (IRIS Lab)</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="3">
         <f>HYPERLINK("https://irislab.tech/", "https://irislab.tech/")</f>
         <v/>
       </c>
-      <c r="N35" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
+      <c r="O35" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
         <is>
           <t>SoEC4h4AAAAJ</t>
         </is>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/wjin34", "https://search.asu.edu/profile/wjin34")</f>
         <v/>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=SoEC4h4AAAAJ", "Scholar (SoEC4h4AAAAJ)")</f>
         <v/>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -3154,23 +3262,28 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
+          <t>Prognostics and Health Management (PHM) Lab</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
           <t>ENGRC 409 (Tempe, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="M36" s="2" t="inlineStr"/>
-      <c r="N36" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O36" s="2" t="inlineStr"/>
-      <c r="P36" s="3">
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P36" s="2" t="inlineStr"/>
+      <c r="Q36" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/yliu35", "https://search.asu.edu/profile/yliu35")</f>
         <v/>
       </c>
-      <c r="Q36" s="3">
+      <c r="R36" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Yongming%20Liu%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="R36" s="3">
+      <c r="S36" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -3228,28 +3341,33 @@
           <t>Ph.D. in Industrial and Systems Engineering, University of Southern California, 2019 M.S. in Computer Science, University of Southern California, 2019 M.S. in Manufacturing Engineering, Nanjing University of Aeronautics and Astronautics, 2014 B.E. in Mechanical Engineering and Automation, Nanjing University of Aeronautics and Astronautics, 2011</t>
         </is>
       </c>
-      <c r="L37" s="2" t="inlineStr"/>
-      <c r="M37" s="3">
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>Advanced Manufacturing and Bio-inspired Design Lab</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="3">
         <f>HYPERLINK("https://www.cindyxjli.com/", "https://www.cindyxjli.com/")</f>
         <v/>
       </c>
-      <c r="N37" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
+      <c r="O37" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
         <is>
           <t>tGQzHJIAAAAJ</t>
         </is>
       </c>
-      <c r="P37" s="3">
+      <c r="Q37" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/xiangji5", "https://search.asu.edu/profile/xiangji5")</f>
         <v/>
       </c>
-      <c r="Q37" s="3">
+      <c r="R37" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=tGQzHJIAAAAJ", "Scholar (tGQzHJIAAAAJ)")</f>
         <v/>
       </c>
-      <c r="R37" s="3">
+      <c r="S37" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -3304,20 +3422,25 @@
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr"/>
-      <c r="M38" s="2" t="inlineStr"/>
-      <c r="N38" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O38" s="2" t="inlineStr"/>
-      <c r="P38" s="3">
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>ENGRC 381 (TEMPE, AZ 85287-6106)</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P38" s="2" t="inlineStr"/>
+      <c r="Q38" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/jimbo", "https://search.asu.edu/profile/jimbo")</f>
         <v/>
       </c>
-      <c r="Q38" s="3">
+      <c r="R38" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=James%20Middleton%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="R38" s="3">
+      <c r="S38" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -3367,25 +3490,26 @@
           <t>PhD The Ohio State University</t>
         </is>
       </c>
-      <c r="L39" s="2" t="inlineStr">
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="M39" s="2" t="inlineStr"/>
-      <c r="N39" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O39" s="2" t="inlineStr"/>
-      <c r="P39" s="3">
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P39" s="2" t="inlineStr"/>
+      <c r="Q39" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/linli25", "https://search.asu.edu/profile/linli25")</f>
         <v/>
       </c>
-      <c r="Q39" s="3">
+      <c r="R39" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Lin%20Li%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="R39" s="3">
+      <c r="S39" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -3436,20 +3560,25 @@
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr"/>
-      <c r="M40" s="2" t="inlineStr"/>
-      <c r="N40" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O40" s="2" t="inlineStr"/>
-      <c r="P40" s="3">
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>ENGRC 411 (TEMPE, AZ 85287-6106)</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P40" s="2" t="inlineStr"/>
+      <c r="Q40" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/marc03", "https://search.asu.edu/profile/marc03")</f>
         <v/>
       </c>
-      <c r="Q40" s="3">
+      <c r="R40" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Marc%20Mignolet%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="R40" s="3">
+      <c r="S40" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -3500,23 +3629,24 @@
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr"/>
-      <c r="M41" s="3">
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/pperalta/", "https://faculty.engineering.asu.edu/pperalta/")</f>
         <v/>
       </c>
-      <c r="N41" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O41" s="2" t="inlineStr"/>
-      <c r="P41" s="3">
+      <c r="O41" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P41" s="2" t="inlineStr"/>
+      <c r="Q41" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/pperalta", "https://search.asu.edu/profile/pperalta")</f>
         <v/>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Pedro%20Peralta%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -3574,32 +3704,33 @@
           <t>Ph.D. Mechanical Science and Engineering, University of Illinois at Urbana-Champaign 2012</t>
         </is>
       </c>
-      <c r="L42" s="2" t="inlineStr">
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <f>HYPERLINK("https://wonmokang3.wixsite.com/website", "https://wonmokang3.wixsite.com/website")</f>
         <v/>
       </c>
-      <c r="N42" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
+      <c r="O42" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
         <is>
           <t>bHyyOTAAAAAJ</t>
         </is>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/wkang16", "https://search.asu.edu/profile/wkang16")</f>
         <v/>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=bHyyOTAAAAAJ", "Scholar (bHyyOTAAAAAJ)")</f>
         <v/>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -3649,25 +3780,22 @@
           <t>Ph.D. Mechanical Engineering, University of Michigan 2011 | M.S. Mechanical Engineering, University of Michigan 2009 | B.S. Automative Engineering, Tsinghua University, China 2007</t>
         </is>
       </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>GWC 464 (Tempe, AZ 85287-6106)</t>
-        </is>
-      </c>
+      <c r="L43" s="2" t="inlineStr"/>
       <c r="M43" s="2" t="inlineStr"/>
-      <c r="N43" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O43" s="2" t="inlineStr"/>
-      <c r="P43" s="3">
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P43" s="2" t="inlineStr"/>
+      <c r="Q43" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/yren32", "https://search.asu.edu/profile/yren32")</f>
         <v/>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Yi%20Ren%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -3675,199 +3803,199 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P2" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R2" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R2" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S2" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P3" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R3" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R3" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S3" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P4" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q4" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R4" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q4" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R4" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S4" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P5" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q5" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R5" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q5" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R5" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S5" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P6" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q6" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R6" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q6" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R6" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S6" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P7" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R7" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R7" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S7" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P8" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R8" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N8" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R8" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S8" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P9" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R9" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R9" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P10" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R10" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R10" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S10" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R11" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R11" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S11" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P12" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R12" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N12" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R12" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S12" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R13" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R13" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S13" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P14" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R14" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R14" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S14" r:id="rId61"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P15" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R15" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R15" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S15" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P16" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R16" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R16" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S16" r:id="rId71"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P17" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q17" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R17" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q17" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R17" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S17" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P18" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q18" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R18" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q18" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R18" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S18" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q19" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R19" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q19" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R19" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S19" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P20" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q20" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R20" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q20" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R20" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S20" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P21" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q21" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R21" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q21" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R21" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S21" r:id="rId92"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P22" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q22" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R22" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q22" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R22" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S22" r:id="rId97"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P23" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q23" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R23" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q23" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R23" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S23" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P24" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q24" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R24" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q24" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R24" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S24" r:id="rId107"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P25" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q25" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R25" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q25" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R25" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S25" r:id="rId112"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P26" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q26" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R26" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q26" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R26" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S26" r:id="rId116"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P27" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q27" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R27" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q27" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R27" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S27" r:id="rId121"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P28" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q28" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R28" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q28" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R28" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S28" r:id="rId125"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P29" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q29" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R29" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q29" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R29" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S29" r:id="rId130"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P30" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q30" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R30" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q30" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R30" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S30" r:id="rId135"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P31" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q31" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R31" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q31" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R31" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S31" r:id="rId140"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P32" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q32" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R32" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q32" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R32" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S32" r:id="rId144"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P33" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q33" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R33" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N33" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q33" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R33" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S33" r:id="rId149"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P34" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q34" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R34" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N34" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q34" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R34" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S34" r:id="rId154"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P35" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q35" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R35" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N35" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q35" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R35" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S35" r:id="rId159"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P36" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q36" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R36" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q36" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R36" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S36" r:id="rId163"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P37" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q37" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R37" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N37" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q37" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R37" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S37" r:id="rId168"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P38" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q38" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R38" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q38" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R38" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S38" r:id="rId172"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P39" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q39" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R39" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q39" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R39" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S39" r:id="rId176"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P40" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q40" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R40" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q40" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R40" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S40" r:id="rId180"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P41" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q41" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R41" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N41" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q41" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R41" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S41" r:id="rId185"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P42" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q42" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R42" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N42" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q42" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R42" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S42" r:id="rId190"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P43" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q43" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R43" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q43" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R43" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S43" r:id="rId194"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3879,7 +4007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R49"/>
+  <dimension ref="A1:S49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3893,13 +4021,14 @@
     <col width="65" customWidth="1" min="9" max="9"/>
     <col width="65" customWidth="1" min="10" max="10"/>
     <col width="65" customWidth="1" min="11" max="11"/>
-    <col width="46" customWidth="1" min="12" max="12"/>
-    <col width="49" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="49" customWidth="1" min="16" max="16"/>
-    <col width="32" customWidth="1" min="17" max="17"/>
-    <col width="49" customWidth="1" min="18" max="18"/>
+    <col width="65" customWidth="1" min="12" max="12"/>
+    <col width="46" customWidth="1" min="13" max="13"/>
+    <col width="49" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="49" customWidth="1" min="17" max="17"/>
+    <col width="32" customWidth="1" min="18" max="18"/>
+    <col width="49" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3960,35 +4089,40 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>Lab / Research Group Name</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>Office Location</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Lab / Personal Website</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Is Field Match</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Scholar ID</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Profile URL</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Google Scholar URL</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Directory URL</t>
         </is>
@@ -3997,7 +4131,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Liping Wang</t>
+          <t>Mohamed Houssem Kasbaoui</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -4016,55 +4150,52 @@
         </is>
       </c>
       <c r="E2" s="3">
-        <f>HYPERLINK("mailto:Liping.Wang@asu.edu", "Liping.Wang@asu.edu")</f>
+        <f>HYPERLINK("mailto:houssem.kasbaoui@asu.edu", "houssem.kasbaoui@asu.edu")</f>
         <v/>
       </c>
       <c r="F2" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>aerospace, guidance, heat transfer, materials, metamaterials, radiation, thermal</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Nanoscale heat transfer, metamaterials, plasmonics, and nanophotonics with an emphasis on solar thermal energy harvesting using plasmonic-enhanced light trapping for photovolatics, as well as near-field enhancement and spectral control of radiation for thermophotovoltaic energy conversion. Other research interests involve electronic cooling, MEMS, and bio-sensing.</t>
-        </is>
-      </c>
+          <t>aerospace, cfd, computational fluid dynamics, dns, fluid dynamics, fluid-structure interaction, multiphase flow, turbulent</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Wang research interests include selective control of thermal emission/absorption using meta-materials for energy harvesting and near-field radiation heat transfer enhancement between meta-materials for thermophotovoltaics.</t>
+          <t>Kasbaoui's research interests include computational fluid dynamics, numerical methods, and massively parallel simulations of multiphase and particle-laden flows for environmental and aerospace applications.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Ph.D. Mechanical Engineering, Georgia Institute of Technology 2011 | M.S. Refrigeration and Cryogenic Engineering, Shanghai Institute of Technical Physics, Chinese  Academy of Sciences 2007 | B.E. Thermal Science and Energy Engineering, University of Science and Technology of China 2004</t>
+          <t>Ph.D.  Aerospace Engineering, Cornell University, 2017 | M.Sc.  Aerospace Engineering, Cornell University, 2015 | M.Sc.  Theoretical Physics, Université Paris-Sud, 2014 | Diplôme d'Ingénieur , Ecole Centrale Paris, 2013 | B.Sc.  Theoretical Physics, Université Paris-Sud, 2011</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>ENGRC 327 (Tempe, AZ 85287-6106)</t>
-        </is>
-      </c>
-      <c r="M2" s="3">
-        <f>HYPERLINK("http://faculty.engineering.asu.edu/lpwang", "http://faculty.engineering.asu.edu/lpwang")</f>
-        <v/>
-      </c>
-      <c r="N2" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/lwang78", "https://search.asu.edu/profile/lwang78")</f>
-        <v/>
-      </c>
+          <t>Multiphase Flow and Fluid-Structure Interaction Group</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="3">
+        <f>HYPERLINK("https://kasbaoui.bitbucket.io", "https://kasbaoui.bitbucket.io")</f>
+        <v/>
+      </c>
+      <c r="O2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P2" s="2" t="inlineStr"/>
       <c r="Q2" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Liping%20Wang%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <f>HYPERLINK("https://search.asu.edu/profile/mkasbaou", "https://search.asu.edu/profile/mkasbaou")</f>
         <v/>
       </c>
       <c r="R2" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Mohamed%20Houssem%20Kasbaoui%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="S2" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -4072,7 +4203,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Mohamed Houssem Kasbaoui</t>
+          <t>Liping Wang</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -4091,7 +4222,7 @@
         </is>
       </c>
       <c r="E3" s="3">
-        <f>HYPERLINK("mailto:houssem.kasbaoui@asu.edu", "houssem.kasbaoui@asu.edu")</f>
+        <f>HYPERLINK("mailto:Liping.Wang@asu.edu", "Liping.Wang@asu.edu")</f>
         <v/>
       </c>
       <c r="F3" s="2" t="n">
@@ -4099,43 +4230,52 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>aerospace, cfd, computational fluid dynamics, dns, fluid dynamics, multiphase flow, turbulent</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
+          <t>aerospace, guidance, heat transfer, materials, metamaterials, radiation, thermal</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Nanoscale heat transfer, metamaterials, plasmonics, and nanophotonics with an emphasis on solar thermal energy harvesting using plasmonic-enhanced light trapping for photovolatics, as well as near-field enhancement and spectral control of radiation for thermophotovoltaic energy conversion. Other research interests involve electronic cooling, MEMS, and bio-sensing.</t>
+        </is>
+      </c>
       <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Kasbaoui's research interests include computational fluid dynamics, numerical methods, and massively parallel simulations of multiphase and particle-laden flows for environmental and aerospace applications.</t>
+          <t>Wang research interests include selective control of thermal emission/absorption using meta-materials for energy harvesting and near-field radiation heat transfer enhancement between meta-materials for thermophotovoltaics.</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Ph.D.  Aerospace Engineering, Cornell University, 2017 | M.Sc.  Aerospace Engineering, Cornell University, 2015 | M.Sc.  Theoretical Physics, Université Paris-Sud, 2014 | Diplôme d'Ingénieur , Ecole Centrale Paris, 2013 | B.Sc.  Theoretical Physics, Université Paris-Sud, 2011</t>
+          <t>Ph.D. Mechanical Engineering, Georgia Institute of Technology 2011 | M.S. Refrigeration and Cryogenic Engineering, Shanghai Institute of Technical Physics, Chinese  Academy of Sciences 2007 | B.E. Thermal Science and Energy Engineering, University of Science and Technology of China 2004</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Campus: Tempe</t>
-        </is>
-      </c>
-      <c r="M3" s="3">
-        <f>HYPERLINK("https://kasbaoui.bitbucket.io", "https://kasbaoui.bitbucket.io")</f>
-        <v/>
-      </c>
-      <c r="N3" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/mkasbaou", "https://search.asu.edu/profile/mkasbaou")</f>
-        <v/>
-      </c>
+          <t>Nanoscale Thermal Radiation Lab</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>ENGRC 327 (Tempe, AZ 85287-6106)</t>
+        </is>
+      </c>
+      <c r="N3" s="3">
+        <f>HYPERLINK("http://faculty.engineering.asu.edu/lpwang", "http://faculty.engineering.asu.edu/lpwang")</f>
+        <v/>
+      </c>
+      <c r="O3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P3" s="2" t="inlineStr"/>
       <c r="Q3" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Mohamed%20Houssem%20Kasbaoui%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <f>HYPERLINK("https://search.asu.edu/profile/lwang78", "https://search.asu.edu/profile/lwang78")</f>
         <v/>
       </c>
       <c r="R3" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Liping%20Wang%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="S3" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -4191,26 +4331,31 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>Computational Mechanics Lab</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
           <t>ENGRC 353 (Tempe, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="M4" s="3">
+      <c r="N4" s="3">
         <f>HYPERLINK("http://sparky.fulton.asu.edu/oswald/", "http://sparky.fulton.asu.edu/oswald/")</f>
         <v/>
       </c>
-      <c r="N4" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O4" s="2" t="inlineStr"/>
-      <c r="P4" s="3">
+      <c r="O4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/joswald1", "https://search.asu.edu/profile/joswald1")</f>
         <v/>
       </c>
-      <c r="Q4" s="3">
+      <c r="R4" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Jay%20Oswald%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="R4" s="3">
+      <c r="S4" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -4270,30 +4415,31 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Campus: Tempe</t>
-        </is>
-      </c>
-      <c r="M5" s="3">
+          <t>Sun Robotics Lab</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="3">
         <f>HYPERLINK("https://sunroboticslab.github.io", "https://sunroboticslab.github.io")</f>
         <v/>
       </c>
-      <c r="N5" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>fjUoHOsAAAAJ</t>
         </is>
       </c>
-      <c r="P5" s="3">
+      <c r="Q5" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/jsun165", "https://search.asu.edu/profile/jsun165")</f>
         <v/>
       </c>
-      <c r="Q5" s="3">
+      <c r="R5" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=fjUoHOsAAAAJ", "Scholar (fjUoHOsAAAAJ)")</f>
         <v/>
       </c>
-      <c r="R5" s="3">
+      <c r="S5" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -4345,23 +4491,24 @@
       </c>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>xT-lX9sAAAAJ</t>
         </is>
       </c>
-      <c r="P6" s="3">
+      <c r="Q6" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/asuchen", "https://search.asu.edu/profile/asuchen")</f>
         <v/>
       </c>
-      <c r="Q6" s="3">
+      <c r="R6" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=xT-lX9sAAAAJ", "Scholar (xT-lX9sAAAAJ)")</f>
         <v/>
       </c>
-      <c r="R6" s="3">
+      <c r="S6" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -4417,23 +4564,24 @@
       </c>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>DKc-AgcAAAAJ</t>
         </is>
       </c>
-      <c r="P7" s="3">
+      <c r="Q7" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/kramesh2", "https://search.asu.edu/profile/kramesh2")</f>
         <v/>
       </c>
-      <c r="Q7" s="3">
+      <c r="R7" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=DKc-AgcAAAAJ", "Scholar (DKc-AgcAAAAJ)")</f>
         <v/>
       </c>
-      <c r="R7" s="3">
+      <c r="S7" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -4441,7 +4589,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Leixin Ma</t>
+          <t>Kunal Garg</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -4460,7 +4608,7 @@
         </is>
       </c>
       <c r="E8" s="3">
-        <f>HYPERLINK("mailto:Leixin.Ma@asu.edu", "Leixin.Ma@asu.edu")</f>
+        <f>HYPERLINK("mailto:kgarg24@asu.edu", "kgarg24@asu.edu")</f>
         <v/>
       </c>
       <c r="F8" s="2" t="n">
@@ -4468,51 +4616,60 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>aerodynamics, aerospace, fluid-structure interaction, fluids, materials, robot</t>
+          <t>aerospace, autonomous, control theory, motion planning, robot, robotics</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Aerodynamics, Dynamical Systems, Machine Learning, Mechanics of Composite Materials</t>
+          <t>Distributed multi-agent motion planning and control, Provably safe control design using machine learning-based certificates, Foundation models in complex robotic tasks, Failure prediction from limited demonstrations, Human-robot interaction.</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Aerodynamics, Dynamical Systems, Machine Learning, Mechanics of Composite Materials</t>
+          <t>Control Systems, Dynamical Systems, Machine Learning, Nonlinear Dynamical Systems, Robotics</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Leixin Ma's career goal is a data-driven and physically consistent approach to modeling and designing programmable smart structures and robots, especially under complex fluid flow conditions.</t>
+          <t>Garg's research interests include control synthesis for multi-agent coordination using control theory and machine learning.</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Ph.D. in Mechanical Engineering, Massachusetts Institute of Technology, 2021 S.M. in Mechanical Engineering, Massachusetts Institute of Technology, 2017 B.S.E. in Naval Architecture and Ocean Engineering, Shanghai Jiao Tong University, 2015</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="3">
-        <f>HYPERLINK("https://sites.google.com/view/oasislabasu", "https://sites.google.com/view/oasislabasu")</f>
-        <v/>
-      </c>
-      <c r="N8" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>2xQTOc0AAAAJ</t>
-        </is>
-      </c>
-      <c r="P8" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/leixinma", "https://search.asu.edu/profile/leixinma")</f>
-        <v/>
+          <t>PhD. Aerospace Engineering, University of Michigan, Ann Arbor, 2021 MS. Aerospace Engineering, University of Michigan, Ann Arbor, 2019 BTech. Aerospace Engineering, Indian Institute of Technology, Bombay, 2016</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Safe and Autonomous Robotics (STAR) Lab</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>551 E Tyler Mall ERC 475 (Tempe, AZ 85281)</t>
+        </is>
+      </c>
+      <c r="N8" s="3">
+        <f>HYPERLINK("https://sites.google.com/asu.edu/kunalgarg/", "https://sites.google.com/asu.edu/kunalgarg/")</f>
+        <v/>
+      </c>
+      <c r="O8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>vs3pl-8AAAAJ</t>
+        </is>
       </c>
       <c r="Q8" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=2xQTOc0AAAAJ", "Scholar (2xQTOc0AAAAJ)")</f>
+        <f>HYPERLINK("https://search.asu.edu/profile/kgarg24", "https://search.asu.edu/profile/kgarg24")</f>
         <v/>
       </c>
       <c r="R8" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=vs3pl-8AAAAJ", "Scholar (vs3pl-8AAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="S8" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -4520,7 +4677,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Gokul Pathikonda</t>
+          <t>Leixin Ma</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -4539,59 +4696,64 @@
         </is>
       </c>
       <c r="E9" s="3">
-        <f>HYPERLINK("mailto:Gokul.Pathikonda@asu.edu", "Gokul.Pathikonda@asu.edu")</f>
+        <f>HYPERLINK("mailto:Leixin.Ma@asu.edu", "Leixin.Ma@asu.edu")</f>
         <v/>
       </c>
       <c r="F9" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>aerodynamics, aerospace, reacting flow, turbulence, turbulent</t>
+          <t>aerodynamics, aerospace, fluid-structure interaction, fluids, materials, robot</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Aerodynamics, Aerospace Engineering, Mechanical Engineering</t>
+          <t>Aerodynamics, Dynamical Systems, Machine Learning, Mechanics of Composite Materials</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Aerodynamics, Aerospace Engineering, Mechanical Engineering</t>
+          <t>Aerodynamics, Dynamical Systems, Machine Learning, Mechanics of Composite Materials</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Dr. Pathikonda studies turbulent fluid flows to understand natural and engineering phenomena using lab experiments. His expertise is in complex (reacting) mixing, high Re-flows, laser-based &amp; spectroscopic techniques, etc.</t>
+          <t>Leixin Ma's career goal is a data-driven and physically consistent approach to modeling and designing programmable smart structures and robots, especially under complex fluid flow conditions.</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Ph. D. Theoretical and Applied Mechanics, University of Illinois, Urbana Champaign, 2017 | MS Aerospace Engineering, University of Illinois, Urbana Champaign, 2013 | B. Tech. Mechanical Engineering, National Institute of Technology, Warangal, 2009</t>
+          <t>Ph.D. in Mechanical Engineering, Massachusetts Institute of Technology, 2021 S.M. in Mechanical Engineering, Massachusetts Institute of Technology, 2017 B.S.E. in Naval Architecture and Ocean Engineering, Shanghai Jiao Tong University, 2015</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>551 E Tyler Mall ERC 479 (Tempe, AZ 85281)</t>
-        </is>
-      </c>
-      <c r="M9" s="3">
-        <f>HYPERLINK("https://faculty.engineering.asu.edu/cmat/", "https://faculty.engineering.asu.edu/cmat/")</f>
-        <v/>
-      </c>
-      <c r="N9" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O9" s="2" t="inlineStr"/>
-      <c r="P9" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/gpathiko", "https://search.asu.edu/profile/gpathiko")</f>
-        <v/>
+          <t>Optimization, Autonomy, and Soft Intelligence Systems (OASIS) Lab</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="3">
+        <f>HYPERLINK("https://sites.google.com/view/oasislabasu", "https://sites.google.com/view/oasislabasu")</f>
+        <v/>
+      </c>
+      <c r="O9" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>2xQTOc0AAAAJ</t>
+        </is>
       </c>
       <c r="Q9" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Gokul%20Pathikonda%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <f>HYPERLINK("https://search.asu.edu/profile/leixinma", "https://search.asu.edu/profile/leixinma")</f>
         <v/>
       </c>
       <c r="R9" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=2xQTOc0AAAAJ", "Scholar (2xQTOc0AAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="S9" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -4599,7 +4761,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Kunal Garg</t>
+          <t>Gokul Pathikonda</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -4618,7 +4780,7 @@
         </is>
       </c>
       <c r="E10" s="3">
-        <f>HYPERLINK("mailto:kgarg24@asu.edu", "kgarg24@asu.edu")</f>
+        <f>HYPERLINK("mailto:Gokul.Pathikonda@asu.edu", "Gokul.Pathikonda@asu.edu")</f>
         <v/>
       </c>
       <c r="F10" s="2" t="n">
@@ -4626,55 +4788,52 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>aerospace, control theory, motion planning, robot, robotics</t>
+          <t>aerodynamics, aerospace, reacting flow, turbulence, turbulent</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Distributed multi-agent motion planning and control, Provably safe control design using machine learning-based certificates, Foundation models in complex robotic tasks, Failure prediction from limited demonstrations, Human-robot interaction.</t>
+          <t>Aerodynamics, Aerospace Engineering, Mechanical Engineering</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Control Systems, Dynamical Systems, Machine Learning, Nonlinear Dynamical Systems, Robotics</t>
+          <t>Aerodynamics, Aerospace Engineering, Mechanical Engineering</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Garg's research interests include control synthesis for multi-agent coordination using control theory and machine learning.</t>
+          <t>Dr. Pathikonda studies turbulent fluid flows to understand natural and engineering phenomena using lab experiments. His expertise is in complex (reacting) mixing, high Re-flows, laser-based &amp; spectroscopic techniques, etc.</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>PhD. Aerospace Engineering, University of Michigan, Ann Arbor, 2021 MS. Aerospace Engineering, University of Michigan, Ann Arbor, 2019 BTech. Aerospace Engineering, Indian Institute of Technology, Bombay, 2016</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>551 E Tyler Mall ERC 475 (Tempe, AZ 85281)</t>
-        </is>
-      </c>
-      <c r="M10" s="3">
-        <f>HYPERLINK("https://sites.google.com/asu.edu/kunalgarg/", "https://sites.google.com/asu.edu/kunalgarg/")</f>
-        <v/>
-      </c>
-      <c r="N10" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>vs3pl-8AAAAJ</t>
-        </is>
-      </c>
-      <c r="P10" s="3">
-        <f>HYPERLINK("https://search.asu.edu/profile/kgarg24", "https://search.asu.edu/profile/kgarg24")</f>
-        <v/>
-      </c>
+          <t>Ph. D. Theoretical and Applied Mechanics, University of Illinois, Urbana Champaign, 2017 | MS Aerospace Engineering, University of Illinois, Urbana Champaign, 2013 | B. Tech. Mechanical Engineering, National Institute of Technology, Warangal, 2009</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>551 E Tyler Mall ERC 479 (Tempe, AZ 85281)</t>
+        </is>
+      </c>
+      <c r="N10" s="3">
+        <f>HYPERLINK("https://faculty.engineering.asu.edu/cmat/", "https://faculty.engineering.asu.edu/cmat/")</f>
+        <v/>
+      </c>
+      <c r="O10" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
       <c r="Q10" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=vs3pl-8AAAAJ", "Scholar (vs3pl-8AAAAJ)")</f>
+        <f>HYPERLINK("https://search.asu.edu/profile/gpathiko", "https://search.asu.edu/profile/gpathiko")</f>
         <v/>
       </c>
       <c r="R10" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Gokul%20Pathikonda%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="S10" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -4724,25 +4883,30 @@
           <t>PhD in Mechanical Engineering, University of Technology (RWTH) Aachen, Germany 2001 | Diploma. Mechanical and Aerospace Engineering, University of Technology (RWTH) Aachen, Germany 1995</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>Computational Multiphase Physics Laboratory</t>
+        </is>
+      </c>
       <c r="M11" s="2" t="inlineStr"/>
-      <c r="N11" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>yv6aCW8AAAAJ</t>
         </is>
       </c>
-      <c r="P11" s="3">
+      <c r="Q11" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/mherrma1", "https://search.asu.edu/profile/mherrma1")</f>
         <v/>
       </c>
-      <c r="Q11" s="3">
+      <c r="R11" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=yv6aCW8AAAAJ", "Scholar (yv6aCW8AAAAJ)")</f>
         <v/>
       </c>
-      <c r="R11" s="3">
+      <c r="S11" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -4800,28 +4964,33 @@
           <t>Ph.D. Mechanical Engineering and Applied Mechanics, University of Pennsylvania 2010 | M.S.E. Mechanical Engineering and Applied Mechanics, University of Pennsylvania 2008 | B.S.E. Mechanical and Aerospace Engineering, Princeton University 2005 | Certificate. Robotics and Intelligent Systems, Princeton University 2005</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="3">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>Autonomous Collective Systems (ACS) Laboratory</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="3">
         <f>HYPERLINK("http://faculty.engineering.asu.edu/acs/", "http://faculty.engineering.asu.edu/acs/")</f>
         <v/>
       </c>
-      <c r="N12" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>KKup0OgAAAAJ</t>
         </is>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/smberma2", "https://search.asu.edu/profile/smberma2")</f>
         <v/>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=KKup0OgAAAAJ", "Scholar (KKup0OgAAAAJ)")</f>
         <v/>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -4879,28 +5048,29 @@
           <t>Ph.D Degree at the  Department of Electrical, Computer, and Systems Engineering  at  Rensselaer Polytechnic Institute  in 2018 | Master's Degree at the  School of electrical and information engineering  at  Tianjin University  in 2014 | Bachelor's Degree at the  School of electrical and information engineering  at  Tianjin University  in 2011</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="M13" s="3">
+      <c r="N13" s="3">
         <f>HYPERLINK("https://sites.google.com/site/zhexudavid00710/research?authuser=0", "https://sites.google.com/site/zhexudavid00710/research?authuser=0")</f>
         <v/>
       </c>
-      <c r="N13" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O13" s="2" t="inlineStr"/>
-      <c r="P13" s="3">
+      <c r="O13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/xzhe1", "https://search.asu.edu/profile/xzhe1")</f>
         <v/>
       </c>
-      <c r="Q13" s="3">
+      <c r="R13" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Zhe%20Xu%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="R13" s="3">
+      <c r="S13" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -4952,19 +5122,20 @@
       </c>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr"/>
-      <c r="N14" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O14" s="2" t="inlineStr"/>
-      <c r="P14" s="3">
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/jkim520", "https://search.asu.edu/profile/jkim520")</f>
         <v/>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Jeonglae%20Kim%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -5022,24 +5193,29 @@
           <t>Ph.D. Aeronautics and Astronautics, Stanford University 2006 | Bachelor's degree. Physics, University of Texas-Austin 1999 | Bachelor's degree. Aerospace Engineering, University of Texas-Austin 1999</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="3">
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>Cybernetic Systems and Controls Laboratory (CSCL)</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="3">
         <f>HYPERLINK("http://control.asu.edu/", "http://control.asu.edu/")</f>
         <v/>
       </c>
-      <c r="N15" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O15" s="2" t="inlineStr"/>
-      <c r="P15" s="3">
+      <c r="O15" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/mpeet", "https://search.asu.edu/profile/mpeet")</f>
         <v/>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Matthew%20Peet%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -5098,27 +5274,28 @@
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="3">
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="3">
         <f>HYPERLINK("http://wang.faculty.asu.edu/", "http://wang.faculty.asu.edu/")</f>
         <v/>
       </c>
-      <c r="N16" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>LaUdx9gAAAAJ</t>
         </is>
       </c>
-      <c r="P16" s="3">
+      <c r="Q16" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/rywang", "https://search.asu.edu/profile/rywang")</f>
         <v/>
       </c>
-      <c r="Q16" s="3">
+      <c r="R16" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=LaUdx9gAAAAJ", "Scholar (LaUdx9gAAAAJ)")</f>
         <v/>
       </c>
-      <c r="R16" s="3">
+      <c r="S16" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -5177,23 +5354,24 @@
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="3">
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="3">
         <f>HYPERLINK("http://RESEARCHGATE.net/profile/Ryan_Milcarek", "http://RESEARCHGATE.net/profile/Ryan_Milcarek")</f>
         <v/>
       </c>
-      <c r="N17" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O17" s="2" t="inlineStr"/>
-      <c r="P17" s="3">
+      <c r="O17" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/rjmilcar", "https://search.asu.edu/profile/rjmilcar")</f>
         <v/>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ryan%20Milcarek%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -5243,25 +5421,26 @@
           <t>Ph.D. Aerospace Engineering, University of Michigan-Ann Arbor | M.S.E. Aerospace Engineering, University of Michigan-Ann Arbor | B.S. Aeronautical and Astronautical Engineering, The Ohio State University-Columbus</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>ENGRC 377 (TEMPE, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr"/>
-      <c r="N18" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O18" s="2" t="inlineStr"/>
-      <c r="P18" s="3">
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/attwl", "https://search.asu.edu/profile/attwl")</f>
         <v/>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=T.-W.%20Lee%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -5313,19 +5492,20 @@
       </c>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr"/>
-      <c r="N19" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O19" s="2" t="inlineStr"/>
-      <c r="P19" s="3">
+      <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/tyang123", "https://search.asu.edu/profile/tyang123")</f>
         <v/>
       </c>
-      <c r="Q19" s="3">
+      <c r="R19" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Tianyu%20Yang%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="R19" s="3">
+      <c r="S19" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -5377,27 +5557,28 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>ENGRC 427 (TEMPE, AZ 85287-6106)</t>
+          <t>Adaptive Intelligent Materials &amp; Systems (AIMS) Center</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>w3fU9E0AAAAJ</t>
         </is>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/chattopa", "https://search.asu.edu/profile/chattopa")</f>
         <v/>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=w3fU9E0AAAAJ", "Scholar (w3fU9E0AAAAJ)")</f>
         <v/>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -5455,29 +5636,30 @@
           <t>PhD Johns Hopkins University</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
         <is>
           <t>HRx2lJQAAAAJ</t>
         </is>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/adscotti", "https://search.asu.edu/profile/adscotti")</f>
         <v/>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=HRx2lJQAAAAJ", "Scholar (HRx2lJQAAAAJ)")</f>
         <v/>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -5533,30 +5715,35 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
+          <t>3D Energy Lab</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
           <t>551 E Tyler Mall ERC 363 (Tempe, AZ 85281)</t>
         </is>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <f>HYPERLINK("http://sites.google.com/view/3denergy", "http://sites.google.com/view/3denergy")</f>
         <v/>
       </c>
-      <c r="N22" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>fs2d97sAAAAJ</t>
         </is>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/bkwon2", "https://search.asu.edu/profile/bkwon2")</f>
         <v/>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=fs2d97sAAAAJ", "Scholar (fs2d97sAAAAJ)")</f>
         <v/>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -5610,28 +5797,33 @@
           <t>Ph.D. Mechanical Engineering, Georgia Institute of Technology, Atlanta 2013 | M.S. Mechanical Engineering, Clemson University, SC 2009 | M.S. Biomedical Engineering, Sharif University of Technology, Tehran, Iran 2007 | B.S. Mechanical Engineering, Iran University of Science and Technology, Tehran 2004</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr"/>
-      <c r="M23" s="3">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>Bio-Inspired Robotics, Technology, and Healthcare Laboratory (BIRTH Lab)</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="3">
         <f>HYPERLINK("http://birth.asu.edu", "http://birth.asu.edu")</f>
         <v/>
       </c>
-      <c r="N23" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>00Fepb0AAAAJ</t>
         </is>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/hmarvi", "https://search.asu.edu/profile/hmarvi")</f>
         <v/>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=00Fepb0AAAAJ", "Scholar (00Fepb0AAAAJ)")</f>
         <v/>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -5681,28 +5873,29 @@
           <t>B.S. Mechanical and Aerospace Engineering, Seoul National University (2002) M.S. Mechanical and Aerospace Engineering, Seoul National University (2004) Ph.D Mechanical Engineering, Massachusetts Institute of Technology (2013)</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/hlee", "https://faculty.engineering.asu.edu/hlee")</f>
         <v/>
       </c>
-      <c r="N24" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O24" s="2" t="inlineStr"/>
-      <c r="P24" s="3">
+      <c r="O24" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P24" s="2" t="inlineStr"/>
+      <c r="Q24" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/hlee234", "https://search.asu.edu/profile/hlee234")</f>
         <v/>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Hyunglae%20Lee%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -5760,24 +5953,29 @@
           <t>PhD. Mechanical Engineering, University of Maryland-College Park 2007 | M.S. Mechanical Engineering, University of Maryland-College Park 2005 | PhD. Student, Mechanical Engineering, Isfahan University of Technology, Iran 2001-2002 | M.S. Mechanical Engineering, Isfahan University of Technology, Iran 2001 | B.S. Mechanical Engineering, Isfahan University of Technology, Iran 1999</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr"/>
-      <c r="M25" s="3">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>Manufacturing and Advanced Materials Characterization (MAGIC) Lab</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="3">
         <f>HYPERLINK("https://magic.asu.edu/", "https://magic.asu.edu/")</f>
         <v/>
       </c>
-      <c r="N25" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O25" s="2" t="inlineStr"/>
-      <c r="P25" s="3">
+      <c r="O25" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P25" s="2" t="inlineStr"/>
+      <c r="Q25" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/ljannesa", "https://search.asu.edu/profile/ljannesa")</f>
         <v/>
       </c>
-      <c r="Q25" s="3">
+      <c r="R25" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Leila%20Ladani%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="R25" s="3">
+      <c r="S25" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -5835,25 +6033,26 @@
           <t>Postdoctoral Fellow, Tokyo Institute of Technology, Japan 1990-1992 | Ph.D. Mechanical Engineering, University of California, Berkeley 1990 | M.S. Mechanical Engineering, Massachusetts Institute of Technology 1987 | B. S. Mechanical Engineering, Tulane University, New Orleans, LA 1985</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>ENGRC 463 (TEMPE, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr"/>
-      <c r="N26" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O26" s="2" t="inlineStr"/>
-      <c r="P26" s="3">
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P26" s="2" t="inlineStr"/>
+      <c r="Q26" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/pphelan", "https://search.asu.edu/profile/pphelan")</f>
         <v/>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Patrick%20Phelan%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -5903,28 +6102,33 @@
           <t>Ph.D. Aeronautics and Astronautics, Stanford University 2006 | M.S. Management, State University Higher School of Economics, Moscow, Russia 2000 | M.S. Aeromechanics and Flight Engineering, Moscow Institute of Physics and Technology, Russia 1999 | B.S. Applied Mathematics and Physics, Moscow Institute of Physics and Technology, Russia 1997</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr"/>
-      <c r="M27" s="3">
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>Interdisciplinary Simulation and Modeling (ISiM) Lab</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="3">
         <f>HYPERLINK("https://isim.asu.edu", "https://isim.asu.edu")</f>
         <v/>
       </c>
-      <c r="N27" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
+      <c r="O27" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
         <is>
           <t>_6o8MrUAAAAJ</t>
         </is>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/ypeet", "https://search.asu.edu/profile/ypeet")</f>
         <v/>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=_6o8MrUAAAAJ", "Scholar (_6o8MrUAAAAJ)")</f>
         <v/>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -5982,25 +6186,34 @@
           <t>Postdoc, Department of Mechanical and Aerospace Engineering, Princeton University Postdoc, Center for Nanophase Materials Sciences, Oak Ridge National Laboratory Ph.D., Major: Materials Science and Engineering; Minor: Applied Engineering Physics, Cornell University M.S., Major: Materials Science and Engineering; Minor: Applied Engineering Physics, Cornell University M.Phil., Mechanical Engineering, The University of Hong Kong B.Eng., Materials Science and Engineering, Hunan University</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="2" t="inlineStr"/>
-      <c r="N28" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>Computational Materials Science and Design Lab</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>Campus: Tempe</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
         <is>
           <t>4yYKCpUAAAAJ</t>
         </is>
       </c>
-      <c r="P28" s="3">
+      <c r="Q28" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/hzhuang7", "https://search.asu.edu/profile/hzhuang7")</f>
         <v/>
       </c>
-      <c r="Q28" s="3">
+      <c r="R28" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=4yYKCpUAAAAJ", "Scholar (4yYKCpUAAAAJ)")</f>
         <v/>
       </c>
-      <c r="R28" s="3">
+      <c r="S28" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -6050,28 +6263,29 @@
           <t>Ph.D. University of Illinois-Urbana-Champaign 1997 | M.S. National Taiwan University 1989 | B.S. National Central University,Taiwan 1987</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>ENGRC 359 (Tempe, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <f>HYPERLINK("http://www.public.asu.edu/~hhuang38", "http://www.public.asu.edu/~hhuang38")</f>
         <v/>
       </c>
-      <c r="N29" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O29" s="2" t="inlineStr"/>
-      <c r="P29" s="3">
+      <c r="O29" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P29" s="2" t="inlineStr"/>
+      <c r="Q29" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/hhuang38", "https://search.asu.edu/profile/hhuang38")</f>
         <v/>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Huei-Ping%20Huang%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -6131,30 +6345,35 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
+          <t>Nanomechanics Laboratory</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
           <t>ENGRC 355 (Tempe, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="M30" s="3">
+      <c r="N30" s="3">
         <f>HYPERLINK("http://faculty.engineering.asu.edu/jagan/", "http://faculty.engineering.asu.edu/jagan/")</f>
         <v/>
       </c>
-      <c r="N30" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
+      <c r="O30" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
         <is>
           <t>ClqRIhIAAAAJ</t>
         </is>
       </c>
-      <c r="P30" s="3">
+      <c r="Q30" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/jrajago1", "https://search.asu.edu/profile/jrajago1")</f>
         <v/>
       </c>
-      <c r="Q30" s="3">
+      <c r="R30" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=ClqRIhIAAAAJ", "Scholar (ClqRIhIAAAAJ)")</f>
         <v/>
       </c>
-      <c r="R30" s="3">
+      <c r="S30" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -6204,28 +6423,33 @@
           <t>Ph.D. Mechanical Engineering, Georgia Institute of Technology 2009 | M.S. Mechanical Engineering, Georgia Institute of Technology 2007 | B.S. Mechanical Engineering, Georgia Institute of Technology 2005</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr"/>
-      <c r="M31" s="3">
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>Nano-Bio-Thermal Engineering Laboratory</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="3">
         <f>HYPERLINK("http://faculty.engineering.asu.edu/konrad/", "http://faculty.engineering.asu.edu/konrad/")</f>
         <v/>
       </c>
-      <c r="N31" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
+      <c r="O31" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
         <is>
           <t>SWeAf4UAAAAJ</t>
         </is>
       </c>
-      <c r="P31" s="3">
+      <c r="Q31" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/krykacze", "https://search.asu.edu/profile/krykacze")</f>
         <v/>
       </c>
-      <c r="Q31" s="3">
+      <c r="R31" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=SWeAf4UAAAAJ", "Scholar (SWeAf4UAAAAJ)")</f>
         <v/>
       </c>
-      <c r="R31" s="3">
+      <c r="S31" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -6281,23 +6505,24 @@
       </c>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr"/>
-      <c r="N32" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
         <is>
           <t>9LWNC50AAAAJ</t>
         </is>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/mingleiq", "https://search.asu.edu/profile/mingleiq")</f>
         <v/>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=9LWNC50AAAAJ", "Scholar (9LWNC50AAAAJ)")</f>
         <v/>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -6355,28 +6580,29 @@
           <t>Ph.D. Manufacturing, Industrial Engineering, Purdue University 2015 | B.Sc. Materials Science and Engineering, University of Science and Technology of China 2009</t>
         </is>
       </c>
-      <c r="L33" s="2" t="inlineStr">
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <f>HYPERLINK("https://mmmplab.engineering.asu.edu/", "https://mmmplab.engineering.asu.edu/")</f>
         <v/>
       </c>
-      <c r="N33" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O33" s="2" t="inlineStr"/>
-      <c r="P33" s="3">
+      <c r="O33" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P33" s="2" t="inlineStr"/>
+      <c r="Q33" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/qnian", "https://search.asu.edu/profile/qnian")</f>
         <v/>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Qiong%20Nian%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -6428,26 +6654,31 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
+          <t>Wind Energy and Atmospheric Boundary Layer Lab</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
           <t>Goldwater 466 (TEMPE, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="M34" s="3">
+      <c r="N34" s="3">
         <f>HYPERLINK("https://windlab.engineering.asu.edu/ronald-calhoun/", "https://windlab.engineering.asu.edu/ronald-calhoun/")</f>
         <v/>
       </c>
-      <c r="N34" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O34" s="2" t="inlineStr"/>
-      <c r="P34" s="3">
+      <c r="O34" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P34" s="2" t="inlineStr"/>
+      <c r="Q34" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/rcalhou", "https://search.asu.edu/profile/rcalhou")</f>
         <v/>
       </c>
-      <c r="Q34" s="3">
+      <c r="R34" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ronald%20Calhoun%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="R34" s="3">
+      <c r="S34" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -6501,28 +6732,33 @@
           <t>Ph.D., Purdue University 2021 | Master of Science, Harbin Institute of Technology, 2016 | Bachelor of Engineering, Harbin Institute of Technology, 2014</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr"/>
-      <c r="M35" s="3">
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>Intelligent Robotics and Interactive Systems Lab (IRIS Lab)</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="3">
         <f>HYPERLINK("https://irislab.tech/", "https://irislab.tech/")</f>
         <v/>
       </c>
-      <c r="N35" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
+      <c r="O35" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
         <is>
           <t>SoEC4h4AAAAJ</t>
         </is>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/wjin34", "https://search.asu.edu/profile/wjin34")</f>
         <v/>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=SoEC4h4AAAAJ", "Scholar (SoEC4h4AAAAJ)")</f>
         <v/>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -6578,23 +6814,28 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
+          <t>Prognostics and Health Management (PHM) Lab</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
           <t>ENGRC 409 (Tempe, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="M36" s="2" t="inlineStr"/>
-      <c r="N36" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O36" s="2" t="inlineStr"/>
-      <c r="P36" s="3">
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P36" s="2" t="inlineStr"/>
+      <c r="Q36" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/yliu35", "https://search.asu.edu/profile/yliu35")</f>
         <v/>
       </c>
-      <c r="Q36" s="3">
+      <c r="R36" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Yongming%20Liu%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="R36" s="3">
+      <c r="S36" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -6652,28 +6893,33 @@
           <t>Ph.D. in Industrial and Systems Engineering, University of Southern California, 2019 M.S. in Computer Science, University of Southern California, 2019 M.S. in Manufacturing Engineering, Nanjing University of Aeronautics and Astronautics, 2014 B.E. in Mechanical Engineering and Automation, Nanjing University of Aeronautics and Astronautics, 2011</t>
         </is>
       </c>
-      <c r="L37" s="2" t="inlineStr"/>
-      <c r="M37" s="3">
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>Advanced Manufacturing and Bio-inspired Design Lab</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="3">
         <f>HYPERLINK("https://www.cindyxjli.com/", "https://www.cindyxjli.com/")</f>
         <v/>
       </c>
-      <c r="N37" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
+      <c r="O37" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
         <is>
           <t>tGQzHJIAAAAJ</t>
         </is>
       </c>
-      <c r="P37" s="3">
+      <c r="Q37" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/xiangji5", "https://search.asu.edu/profile/xiangji5")</f>
         <v/>
       </c>
-      <c r="Q37" s="3">
+      <c r="R37" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=tGQzHJIAAAAJ", "Scholar (tGQzHJIAAAAJ)")</f>
         <v/>
       </c>
-      <c r="R37" s="3">
+      <c r="S37" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -6728,20 +6974,25 @@
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr"/>
-      <c r="M38" s="2" t="inlineStr"/>
-      <c r="N38" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O38" s="2" t="inlineStr"/>
-      <c r="P38" s="3">
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>ENGRC 381 (TEMPE, AZ 85287-6106)</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P38" s="2" t="inlineStr"/>
+      <c r="Q38" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/jimbo", "https://search.asu.edu/profile/jimbo")</f>
         <v/>
       </c>
-      <c r="Q38" s="3">
+      <c r="R38" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=James%20Middleton%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="R38" s="3">
+      <c r="S38" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -6791,25 +7042,26 @@
           <t>PhD The Ohio State University</t>
         </is>
       </c>
-      <c r="L39" s="2" t="inlineStr">
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="M39" s="2" t="inlineStr"/>
-      <c r="N39" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O39" s="2" t="inlineStr"/>
-      <c r="P39" s="3">
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P39" s="2" t="inlineStr"/>
+      <c r="Q39" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/linli25", "https://search.asu.edu/profile/linli25")</f>
         <v/>
       </c>
-      <c r="Q39" s="3">
+      <c r="R39" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Lin%20Li%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="R39" s="3">
+      <c r="S39" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -6860,20 +7112,25 @@
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr"/>
-      <c r="M40" s="2" t="inlineStr"/>
-      <c r="N40" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O40" s="2" t="inlineStr"/>
-      <c r="P40" s="3">
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>ENGRC 411 (TEMPE, AZ 85287-6106)</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P40" s="2" t="inlineStr"/>
+      <c r="Q40" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/marc03", "https://search.asu.edu/profile/marc03")</f>
         <v/>
       </c>
-      <c r="Q40" s="3">
+      <c r="R40" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Marc%20Mignolet%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="R40" s="3">
+      <c r="S40" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -6924,23 +7181,24 @@
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr"/>
-      <c r="M41" s="3">
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/pperalta/", "https://faculty.engineering.asu.edu/pperalta/")</f>
         <v/>
       </c>
-      <c r="N41" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O41" s="2" t="inlineStr"/>
-      <c r="P41" s="3">
+      <c r="O41" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P41" s="2" t="inlineStr"/>
+      <c r="Q41" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/pperalta", "https://search.asu.edu/profile/pperalta")</f>
         <v/>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Pedro%20Peralta%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -6998,32 +7256,33 @@
           <t>Ph.D. Mechanical Science and Engineering, University of Illinois at Urbana-Champaign 2012</t>
         </is>
       </c>
-      <c r="L42" s="2" t="inlineStr">
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <f>HYPERLINK("https://wonmokang3.wixsite.com/website", "https://wonmokang3.wixsite.com/website")</f>
         <v/>
       </c>
-      <c r="N42" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
+      <c r="O42" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
         <is>
           <t>bHyyOTAAAAAJ</t>
         </is>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/wkang16", "https://search.asu.edu/profile/wkang16")</f>
         <v/>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=bHyyOTAAAAAJ", "Scholar (bHyyOTAAAAAJ)")</f>
         <v/>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -7073,25 +7332,22 @@
           <t>Ph.D. Mechanical Engineering, University of Michigan 2011 | M.S. Mechanical Engineering, University of Michigan 2009 | B.S. Automative Engineering, Tsinghua University, China 2007</t>
         </is>
       </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>GWC 464 (Tempe, AZ 85287-6106)</t>
-        </is>
-      </c>
+      <c r="L43" s="2" t="inlineStr"/>
       <c r="M43" s="2" t="inlineStr"/>
-      <c r="N43" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O43" s="2" t="inlineStr"/>
-      <c r="P43" s="3">
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P43" s="2" t="inlineStr"/>
+      <c r="Q43" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/yren32", "https://search.asu.edu/profile/yren32")</f>
         <v/>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Yi%20Ren%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -7131,19 +7387,20 @@
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr"/>
       <c r="M44" s="2" t="inlineStr"/>
-      <c r="N44" s="2" t="b">
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="O44" s="2" t="inlineStr"/>
-      <c r="P44" s="3">
+      <c r="P44" s="2" t="inlineStr"/>
+      <c r="Q44" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/dspeaks2", "https://search.asu.edu/profile/dspeaks2")</f>
         <v/>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Derrick%20Speaks%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -7185,25 +7442,26 @@
           <t>Ph.D. in Mechanical Engineering 2022 - University of Utah B.S./M.S.in Mechanical Engineering 2018 - University of Utah</t>
         </is>
       </c>
-      <c r="L45" s="2" t="inlineStr">
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
         <is>
           <t>Campus: Otherus</t>
         </is>
       </c>
-      <c r="M45" s="2" t="inlineStr"/>
-      <c r="N45" s="2" t="b">
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="O45" s="2" t="inlineStr"/>
-      <c r="P45" s="3">
+      <c r="P45" s="2" t="inlineStr"/>
+      <c r="Q45" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/ejande22", "https://search.asu.edu/profile/ejande22")</f>
         <v/>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Erik%20Andersen%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -7243,19 +7501,20 @@
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr"/>
       <c r="M46" s="2" t="inlineStr"/>
-      <c r="N46" s="2" t="b">
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="O46" s="2" t="inlineStr"/>
-      <c r="P46" s="3">
+      <c r="P46" s="2" t="inlineStr"/>
+      <c r="Q46" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/iychang", "https://search.asu.edu/profile/iychang")</f>
         <v/>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ivy%20Chang%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -7295,19 +7554,20 @@
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr"/>
       <c r="M47" s="2" t="inlineStr"/>
-      <c r="N47" s="2" t="b">
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="O47" s="2" t="inlineStr"/>
-      <c r="P47" s="3">
+      <c r="P47" s="2" t="inlineStr"/>
+      <c r="Q47" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/jdwilbu1", "https://search.asu.edu/profile/jdwilbu1")</f>
         <v/>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Joshua%20Wilbur%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -7347,19 +7607,20 @@
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr"/>
       <c r="M48" s="2" t="inlineStr"/>
-      <c r="N48" s="2" t="b">
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="O48" s="2" t="inlineStr"/>
-      <c r="P48" s="3">
+      <c r="P48" s="2" t="inlineStr"/>
+      <c r="Q48" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/rcruzloz", "https://search.asu.edu/profile/rcruzloz")</f>
         <v/>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ricardo%20Cruz%20Lozano%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -7397,25 +7658,26 @@
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
-      <c r="L49" s="2" t="inlineStr">
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="M49" s="2" t="inlineStr"/>
-      <c r="N49" s="2" t="b">
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="O49" s="2" t="inlineStr"/>
-      <c r="P49" s="3">
+      <c r="P49" s="2" t="inlineStr"/>
+      <c r="Q49" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/skosara2", "https://search.asu.edu/profile/skosara2")</f>
         <v/>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Srinivas%20Chakravarthi%20Kosaraju%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -7423,223 +7685,223 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P2" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R2" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R2" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S2" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P3" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R3" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R3" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S3" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P4" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q4" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R4" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q4" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R4" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S4" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P5" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q5" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R5" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q5" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R5" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S5" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P6" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q6" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R6" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q6" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R6" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S6" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P7" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R7" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R7" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S7" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P8" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R8" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N8" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R8" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S8" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P9" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R9" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R9" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P10" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R10" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R10" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S10" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R11" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R11" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S11" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P12" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R12" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N12" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R12" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S12" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R13" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R13" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S13" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P14" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R14" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R14" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S14" r:id="rId61"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P15" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R15" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R15" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S15" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P16" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R16" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R16" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S16" r:id="rId71"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P17" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q17" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R17" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q17" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R17" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S17" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P18" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q18" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R18" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q18" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R18" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S18" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q19" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R19" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q19" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R19" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S19" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P20" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q20" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R20" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q20" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R20" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S20" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P21" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q21" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R21" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q21" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R21" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S21" r:id="rId92"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P22" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q22" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R22" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q22" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R22" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S22" r:id="rId97"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P23" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q23" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R23" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q23" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R23" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S23" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P24" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q24" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R24" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q24" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R24" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S24" r:id="rId107"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P25" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q25" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R25" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q25" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R25" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S25" r:id="rId112"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P26" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q26" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R26" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q26" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R26" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S26" r:id="rId116"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P27" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q27" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R27" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q27" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R27" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S27" r:id="rId121"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P28" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q28" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R28" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q28" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R28" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S28" r:id="rId125"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P29" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q29" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R29" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q29" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R29" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S29" r:id="rId130"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P30" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q30" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R30" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q30" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R30" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S30" r:id="rId135"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P31" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q31" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R31" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q31" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R31" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S31" r:id="rId140"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P32" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q32" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R32" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q32" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R32" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S32" r:id="rId144"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P33" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q33" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R33" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N33" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q33" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R33" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S33" r:id="rId149"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P34" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q34" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R34" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N34" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q34" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R34" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S34" r:id="rId154"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P35" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q35" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R35" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N35" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q35" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R35" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S35" r:id="rId159"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P36" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q36" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R36" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q36" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R36" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S36" r:id="rId163"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P37" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q37" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R37" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N37" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q37" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R37" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S37" r:id="rId168"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P38" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q38" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R38" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q38" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R38" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S38" r:id="rId172"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P39" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q39" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R39" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q39" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R39" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S39" r:id="rId176"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P40" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q40" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R40" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q40" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R40" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S40" r:id="rId180"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P41" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q41" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R41" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N41" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q41" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R41" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S41" r:id="rId185"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P42" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q42" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R42" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N42" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q42" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R42" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S42" r:id="rId190"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P43" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q43" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R43" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q43" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R43" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S43" r:id="rId194"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P44" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q44" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R44" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q44" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R44" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S44" r:id="rId198"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P45" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q45" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R45" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q45" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R45" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S45" r:id="rId202"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P46" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q46" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R46" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q46" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R46" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S46" r:id="rId206"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P47" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q47" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R47" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q47" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R47" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S47" r:id="rId210"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P48" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q48" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R48" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q48" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R48" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S48" r:id="rId214"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P49" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q49" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R49" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q49" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R49" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S49" r:id="rId218"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/universities_wise/arizona_state_university/asu_aerospace_mechanical_faculty.xlsx
+++ b/universities_wise/arizona_state_university/asu_aerospace_mechanical_faculty.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S43"/>
+  <dimension ref="A1:X43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -470,13 +470,18 @@
     <col width="65" customWidth="1" min="10" max="10"/>
     <col width="65" customWidth="1" min="11" max="11"/>
     <col width="65" customWidth="1" min="12" max="12"/>
-    <col width="46" customWidth="1" min="13" max="13"/>
-    <col width="49" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="49" customWidth="1" min="17" max="17"/>
-    <col width="32" customWidth="1" min="18" max="18"/>
+    <col width="65" customWidth="1" min="13" max="13"/>
+    <col width="53" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="65" customWidth="1" min="16" max="16"/>
+    <col width="56" customWidth="1" min="17" max="17"/>
+    <col width="46" customWidth="1" min="18" max="18"/>
     <col width="49" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="49" customWidth="1" min="22" max="22"/>
+    <col width="32" customWidth="1" min="23" max="23"/>
+    <col width="49" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,35 +547,60 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>Actively Hiring / Openings</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Target Skills / Prerequisites</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Funding Sponsors</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Software / Code Repo</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Latest Project / Highlight</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>Office Location</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Lab / Personal Website</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Is Field Match</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Scholar ID</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Profile URL</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Google Scholar URL</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Directory URL</t>
         </is>
@@ -627,23 +657,44 @@
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="3">
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>CFD</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>AFOSR</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>https://bitbucket.org/krgasu/leap/downloads/leap-v0.8.2.tar.gz, https://bitbucket.org/krgasu/leap/src/master</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>School for Engineering of Matter, Transport &amp; Energy</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr"/>
+      <c r="S2" s="3">
         <f>HYPERLINK("https://kasbaoui.bitbucket.io", "https://kasbaoui.bitbucket.io")</f>
         <v/>
       </c>
-      <c r="O2" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="3">
+      <c r="T2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U2" s="2" t="inlineStr"/>
+      <c r="V2" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/mkasbaou", "https://search.asu.edu/profile/mkasbaou")</f>
         <v/>
       </c>
-      <c r="R2" s="3">
+      <c r="W2" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Mohamed%20Houssem%20Kasbaoui%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="S2" s="3">
+      <c r="X2" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -704,26 +755,43 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
+          <t>Multiple UG/MS research positions available for Fall 2024 (volunteer) and Spring/Summer 2025 (possible FURI / MORE support)</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr"/>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>NASA, NSF</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>News&amp;Awards</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
           <t>ENGRC 327 (Tempe, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="N3" s="3">
+      <c r="S3" s="3">
         <f>HYPERLINK("http://faculty.engineering.asu.edu/lpwang", "http://faculty.engineering.asu.edu/lpwang")</f>
         <v/>
       </c>
-      <c r="O3" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="3">
+      <c r="T3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U3" s="2" t="inlineStr"/>
+      <c r="V3" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/lwang78", "https://search.asu.edu/profile/lwang78")</f>
         <v/>
       </c>
-      <c r="R3" s="3">
+      <c r="W3" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Liping%20Wang%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="S3" s="3">
+      <c r="X3" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -782,28 +850,33 @@
           <t>Computational Mechanics Lab</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>ENGRC 353 (Tempe, AZ 85287-6106)</t>
-        </is>
-      </c>
-      <c r="N4" s="3">
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>Multiscale polymer analysis</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr"/>
+      <c r="S4" s="3">
         <f>HYPERLINK("http://sparky.fulton.asu.edu/oswald/", "http://sparky.fulton.asu.edu/oswald/")</f>
         <v/>
       </c>
-      <c r="O4" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="3">
+      <c r="T4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U4" s="2" t="inlineStr"/>
+      <c r="V4" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/joswald1", "https://search.asu.edu/profile/joswald1")</f>
         <v/>
       </c>
-      <c r="R4" s="3">
+      <c r="W4" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Jay%20Oswald%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="S4" s="3">
+      <c r="X4" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -866,28 +939,45 @@
           <t>Sun Robotics Lab</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="3">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Dec 19, 2025 We have two openings for fully supported summer interns through SURI program at ASU</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>Mission and Core Values</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>Campus: Tempe</t>
+        </is>
+      </c>
+      <c r="S5" s="3">
         <f>HYPERLINK("https://sunroboticslab.github.io", "https://sunroboticslab.github.io")</f>
         <v/>
       </c>
-      <c r="O5" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
         <is>
           <t>fjUoHOsAAAAJ</t>
         </is>
       </c>
-      <c r="Q5" s="3">
+      <c r="V5" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/jsun165", "https://search.asu.edu/profile/jsun165")</f>
         <v/>
       </c>
-      <c r="R5" s="3">
+      <c r="W5" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=fjUoHOsAAAAJ", "Scholar (fjUoHOsAAAAJ)")</f>
         <v/>
       </c>
-      <c r="S5" s="3">
+      <c r="X5" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -940,23 +1030,32 @@
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>ENGRC 361 (TEMPE, AZ 85287-6106)</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
         <is>
           <t>xT-lX9sAAAAJ</t>
         </is>
       </c>
-      <c r="Q6" s="3">
+      <c r="V6" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/asuchen", "https://search.asu.edu/profile/asuchen")</f>
         <v/>
       </c>
-      <c r="R6" s="3">
+      <c r="W6" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=xT-lX9sAAAAJ", "Scholar (xT-lX9sAAAAJ)")</f>
         <v/>
       </c>
-      <c r="S6" s="3">
+      <c r="X6" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1013,23 +1112,28 @@
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr"/>
       <c r="N7" s="2" t="inlineStr"/>
-      <c r="O7" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr"/>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>DKc-AgcAAAAJ</t>
         </is>
       </c>
-      <c r="Q7" s="3">
+      <c r="V7" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/kramesh2", "https://search.asu.edu/profile/kramesh2")</f>
         <v/>
       </c>
-      <c r="R7" s="3">
+      <c r="W7" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=DKc-AgcAAAAJ", "Scholar (DKc-AgcAAAAJ)")</f>
         <v/>
       </c>
-      <c r="S7" s="3">
+      <c r="X7" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1094,30 +1198,43 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
+          <t>Actively seeking graduate students (see bio/lab link)</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>Python, PyTorch, ROS, ROS2, C/C++, Linear Algebra</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
           <t>551 E Tyler Mall ERC 475 (Tempe, AZ 85281)</t>
         </is>
       </c>
-      <c r="N8" s="3">
+      <c r="S8" s="3">
         <f>HYPERLINK("https://sites.google.com/asu.edu/kunalgarg/", "https://sites.google.com/asu.edu/kunalgarg/")</f>
         <v/>
       </c>
-      <c r="O8" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
         <is>
           <t>vs3pl-8AAAAJ</t>
         </is>
       </c>
-      <c r="Q8" s="3">
+      <c r="V8" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/kgarg24", "https://search.asu.edu/profile/kgarg24")</f>
         <v/>
       </c>
-      <c r="R8" s="3">
+      <c r="W8" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=vs3pl-8AAAAJ", "Scholar (vs3pl-8AAAAJ)")</f>
         <v/>
       </c>
-      <c r="S8" s="3">
+      <c r="X8" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1180,28 +1297,45 @@
           <t>Optimization, Autonomy, and Soft Intelligence Systems (OASIS) Lab</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="3">
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>Actively recruiting / Openings mentioned on lab site</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr"/>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>Ocean and Soft Intelligent Structure Interaction Lab</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>ERC 485 (Tempe, AZ 85287)</t>
+        </is>
+      </c>
+      <c r="S9" s="3">
         <f>HYPERLINK("https://sites.google.com/view/oasislabasu", "https://sites.google.com/view/oasislabasu")</f>
         <v/>
       </c>
-      <c r="O9" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="T9" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>2xQTOc0AAAAJ</t>
         </is>
       </c>
-      <c r="Q9" s="3">
+      <c r="V9" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/leixinma", "https://search.asu.edu/profile/leixinma")</f>
         <v/>
       </c>
-      <c r="R9" s="3">
+      <c r="W9" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=2xQTOc0AAAAJ", "Scholar (2xQTOc0AAAAJ)")</f>
         <v/>
       </c>
-      <c r="S9" s="3">
+      <c r="X9" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1260,28 +1394,37 @@
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>Want to be part of CMAT Lab?</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>551 E Tyler Mall ERC 479 (Tempe, AZ 85281)</t>
         </is>
       </c>
-      <c r="N10" s="3">
+      <c r="S10" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/cmat/", "https://faculty.engineering.asu.edu/cmat/")</f>
         <v/>
       </c>
-      <c r="O10" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P10" s="2" t="inlineStr"/>
-      <c r="Q10" s="3">
+      <c r="T10" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U10" s="2" t="inlineStr"/>
+      <c r="V10" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/gpathiko", "https://search.asu.edu/profile/gpathiko")</f>
         <v/>
       </c>
-      <c r="R10" s="3">
+      <c r="W10" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Gokul%20Pathikonda%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="S10" s="3">
+      <c r="X10" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1338,23 +1481,28 @@
       </c>
       <c r="M11" s="2" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr"/>
-      <c r="O11" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr"/>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
         <is>
           <t>yv6aCW8AAAAJ</t>
         </is>
       </c>
-      <c r="Q11" s="3">
+      <c r="V11" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/mherrma1", "https://search.asu.edu/profile/mherrma1")</f>
         <v/>
       </c>
-      <c r="R11" s="3">
+      <c r="W11" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=yv6aCW8AAAAJ", "Scholar (yv6aCW8AAAAJ)")</f>
         <v/>
       </c>
-      <c r="S11" s="3">
+      <c r="X11" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1418,27 +1566,36 @@
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr"/>
-      <c r="N12" s="3">
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>ENGRC 375 (Tempe, AZ 85287-6106)</t>
+        </is>
+      </c>
+      <c r="S12" s="3">
         <f>HYPERLINK("http://faculty.engineering.asu.edu/acs/", "http://faculty.engineering.asu.edu/acs/")</f>
         <v/>
       </c>
-      <c r="O12" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>KKup0OgAAAAJ</t>
         </is>
       </c>
-      <c r="Q12" s="3">
+      <c r="V12" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/smberma2", "https://search.asu.edu/profile/smberma2")</f>
         <v/>
       </c>
-      <c r="R12" s="3">
+      <c r="W12" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=KKup0OgAAAAJ", "Scholar (KKup0OgAAAAJ)")</f>
         <v/>
       </c>
-      <c r="S12" s="3">
+      <c r="X12" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1497,28 +1654,33 @@
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr"/>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="N13" s="3">
+      <c r="S13" s="3">
         <f>HYPERLINK("https://sites.google.com/site/zhexudavid00710/research?authuser=0", "https://sites.google.com/site/zhexudavid00710/research?authuser=0")</f>
         <v/>
       </c>
-      <c r="O13" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P13" s="2" t="inlineStr"/>
-      <c r="Q13" s="3">
+      <c r="T13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U13" s="2" t="inlineStr"/>
+      <c r="V13" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/xzhe1", "https://search.asu.edu/profile/xzhe1")</f>
         <v/>
       </c>
-      <c r="R13" s="3">
+      <c r="W13" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Zhe%20Xu%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="S13" s="3">
+      <c r="X13" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1571,19 +1733,24 @@
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr"/>
-      <c r="O14" s="2" t="b">
-        <v>1</v>
-      </c>
+      <c r="O14" s="2" t="inlineStr"/>
       <c r="P14" s="2" t="inlineStr"/>
-      <c r="Q14" s="3">
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U14" s="2" t="inlineStr"/>
+      <c r="V14" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/jkim520", "https://search.asu.edu/profile/jkim520")</f>
         <v/>
       </c>
-      <c r="R14" s="3">
+      <c r="W14" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Jeonglae%20Kim%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="S14" s="3">
+      <c r="X14" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1647,23 +1814,28 @@
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr"/>
-      <c r="N15" s="3">
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr"/>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="3">
         <f>HYPERLINK("http://control.asu.edu/", "http://control.asu.edu/")</f>
         <v/>
       </c>
-      <c r="O15" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P15" s="2" t="inlineStr"/>
-      <c r="Q15" s="3">
+      <c r="T15" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U15" s="2" t="inlineStr"/>
+      <c r="V15" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/mpeet", "https://search.asu.edu/profile/mpeet")</f>
         <v/>
       </c>
-      <c r="R15" s="3">
+      <c r="W15" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Matthew%20Peet%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="S15" s="3">
+      <c r="X15" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1723,27 +1895,32 @@
       </c>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="3">
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="3">
         <f>HYPERLINK("http://wang.faculty.asu.edu/", "http://wang.faculty.asu.edu/")</f>
         <v/>
       </c>
-      <c r="O16" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>LaUdx9gAAAAJ</t>
         </is>
       </c>
-      <c r="Q16" s="3">
+      <c r="V16" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/rywang", "https://search.asu.edu/profile/rywang")</f>
         <v/>
       </c>
-      <c r="R16" s="3">
+      <c r="W16" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=LaUdx9gAAAAJ", "Scholar (LaUdx9gAAAAJ)")</f>
         <v/>
       </c>
-      <c r="S16" s="3">
+      <c r="X16" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1803,23 +1980,36 @@
       </c>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr"/>
-      <c r="N17" s="3">
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr"/>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>ENGRC 465 (Tempe, AZ 85287)</t>
+        </is>
+      </c>
+      <c r="S17" s="3">
         <f>HYPERLINK("http://RESEARCHGATE.net/profile/Ryan_Milcarek", "http://RESEARCHGATE.net/profile/Ryan_Milcarek")</f>
         <v/>
       </c>
-      <c r="O17" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P17" s="2" t="inlineStr"/>
-      <c r="Q17" s="3">
+      <c r="T17" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>m-Pb6g2pm2UC</t>
+        </is>
+      </c>
+      <c r="V17" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/rjmilcar", "https://search.asu.edu/profile/rjmilcar")</f>
         <v/>
       </c>
-      <c r="R17" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ryan%20Milcarek%20Arizona%20State%20University", "Google Scholar Search")</f>
-        <v/>
-      </c>
-      <c r="S17" s="3">
+      <c r="W17" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=m-Pb6g2pm2UC", "Scholar (m-Pb6g2pm2UC)")</f>
+        <v/>
+      </c>
+      <c r="X17" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1870,25 +2060,30 @@
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr"/>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr">
         <is>
           <t>ENGRC 377 (TEMPE, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="N18" s="2" t="inlineStr"/>
-      <c r="O18" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P18" s="2" t="inlineStr"/>
-      <c r="Q18" s="3">
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U18" s="2" t="inlineStr"/>
+      <c r="V18" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/attwl", "https://search.asu.edu/profile/attwl")</f>
         <v/>
       </c>
-      <c r="R18" s="3">
+      <c r="W18" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=T.-W.%20Lee%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="S18" s="3">
+      <c r="X18" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1941,19 +2136,32 @@
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr"/>
       <c r="N19" s="2" t="inlineStr"/>
-      <c r="O19" s="2" t="b">
-        <v>1</v>
-      </c>
+      <c r="O19" s="2" t="inlineStr"/>
       <c r="P19" s="2" t="inlineStr"/>
-      <c r="Q19" s="3">
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>Campus: Tempe</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>OmBV67MAAAAJ</t>
+        </is>
+      </c>
+      <c r="V19" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/tyang123", "https://search.asu.edu/profile/tyang123")</f>
         <v/>
       </c>
-      <c r="R19" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Tianyu%20Yang%20Arizona%20State%20University", "Google Scholar Search")</f>
-        <v/>
-      </c>
-      <c r="S19" s="3">
+      <c r="W19" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=OmBV67MAAAAJ", "Scholar (OmBV67MAAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="X19" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2010,23 +2218,28 @@
       </c>
       <c r="M20" s="2" t="inlineStr"/>
       <c r="N20" s="2" t="inlineStr"/>
-      <c r="O20" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t>w3fU9E0AAAAJ</t>
         </is>
       </c>
-      <c r="Q20" s="3">
+      <c r="V20" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/chattopa", "https://search.asu.edu/profile/chattopa")</f>
         <v/>
       </c>
-      <c r="R20" s="3">
+      <c r="W20" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=w3fU9E0AAAAJ", "Scholar (w3fU9E0AAAAJ)")</f>
         <v/>
       </c>
-      <c r="S20" s="3">
+      <c r="X20" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2085,29 +2298,34 @@
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr"/>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="N21" s="2" t="inlineStr"/>
-      <c r="O21" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
         <is>
           <t>HRx2lJQAAAAJ</t>
         </is>
       </c>
-      <c r="Q21" s="3">
+      <c r="V21" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/adscotti", "https://search.asu.edu/profile/adscotti")</f>
         <v/>
       </c>
-      <c r="R21" s="3">
+      <c r="W21" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=HRx2lJQAAAAJ", "Scholar (HRx2lJQAAAAJ)")</f>
         <v/>
       </c>
-      <c r="S21" s="3">
+      <c r="X21" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2166,32 +2384,45 @@
           <t>3D Energy Lab</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>NSF</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr"/>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>3D Energy Device Laboratory</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>551 E Tyler Mall ERC 363 (Tempe, AZ 85281)</t>
         </is>
       </c>
-      <c r="N22" s="3">
+      <c r="S22" s="3">
         <f>HYPERLINK("http://sites.google.com/view/3denergy", "http://sites.google.com/view/3denergy")</f>
         <v/>
       </c>
-      <c r="O22" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
         <is>
           <t>fs2d97sAAAAJ</t>
         </is>
       </c>
-      <c r="Q22" s="3">
+      <c r="V22" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/bkwon2", "https://search.asu.edu/profile/bkwon2")</f>
         <v/>
       </c>
-      <c r="R22" s="3">
+      <c r="W22" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=fs2d97sAAAAJ", "Scholar (fs2d97sAAAAJ)")</f>
         <v/>
       </c>
-      <c r="S22" s="3">
+      <c r="X22" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2251,27 +2482,36 @@
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr"/>
-      <c r="N23" s="3">
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr"/>
+      <c r="P23" s="2" t="inlineStr"/>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>Campus: Tempe</t>
+        </is>
+      </c>
+      <c r="S23" s="3">
         <f>HYPERLINK("http://birth.asu.edu", "http://birth.asu.edu")</f>
         <v/>
       </c>
-      <c r="O23" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
+      <c r="T23" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
         <is>
           <t>00Fepb0AAAAJ</t>
         </is>
       </c>
-      <c r="Q23" s="3">
+      <c r="V23" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/hmarvi", "https://search.asu.edu/profile/hmarvi")</f>
         <v/>
       </c>
-      <c r="R23" s="3">
+      <c r="W23" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=00Fepb0AAAAJ", "Scholar (00Fepb0AAAAJ)")</f>
         <v/>
       </c>
-      <c r="S23" s="3">
+      <c r="X23" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2322,28 +2562,33 @@
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr"/>
-      <c r="M24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr"/>
+      <c r="P24" s="2" t="inlineStr"/>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="N24" s="3">
+      <c r="S24" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/hlee", "https://faculty.engineering.asu.edu/hlee")</f>
         <v/>
       </c>
-      <c r="O24" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P24" s="2" t="inlineStr"/>
-      <c r="Q24" s="3">
+      <c r="T24" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/hlee234", "https://search.asu.edu/profile/hlee234")</f>
         <v/>
       </c>
-      <c r="R24" s="3">
+      <c r="W24" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Hyunglae%20Lee%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="S24" s="3">
+      <c r="X24" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2407,23 +2652,28 @@
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr"/>
-      <c r="N25" s="3">
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr"/>
+      <c r="P25" s="2" t="inlineStr"/>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="3">
         <f>HYPERLINK("https://magic.asu.edu/", "https://magic.asu.edu/")</f>
         <v/>
       </c>
-      <c r="O25" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P25" s="2" t="inlineStr"/>
-      <c r="Q25" s="3">
+      <c r="T25" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/ljannesa", "https://search.asu.edu/profile/ljannesa")</f>
         <v/>
       </c>
-      <c r="R25" s="3">
+      <c r="W25" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Leila%20Ladani%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="S25" s="3">
+      <c r="X25" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2482,25 +2732,30 @@
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr"/>
-      <c r="M26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr"/>
+      <c r="P26" s="2" t="inlineStr"/>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr">
         <is>
           <t>ENGRC 463 (TEMPE, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="N26" s="2" t="inlineStr"/>
-      <c r="O26" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P26" s="2" t="inlineStr"/>
-      <c r="Q26" s="3">
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/pphelan", "https://search.asu.edu/profile/pphelan")</f>
         <v/>
       </c>
-      <c r="R26" s="3">
+      <c r="W26" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Patrick%20Phelan%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="S26" s="3">
+      <c r="X26" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2556,27 +2811,32 @@
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr"/>
-      <c r="N27" s="3">
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr"/>
+      <c r="P27" s="2" t="inlineStr"/>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="3">
         <f>HYPERLINK("https://isim.asu.edu", "https://isim.asu.edu")</f>
         <v/>
       </c>
-      <c r="O27" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
+      <c r="T27" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
         <is>
           <t>_6o8MrUAAAAJ</t>
         </is>
       </c>
-      <c r="Q27" s="3">
+      <c r="V27" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/ypeet", "https://search.asu.edu/profile/ypeet")</f>
         <v/>
       </c>
-      <c r="R27" s="3">
+      <c r="W27" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=_6o8MrUAAAAJ", "Scholar (_6o8MrUAAAAJ)")</f>
         <v/>
       </c>
-      <c r="S27" s="3">
+      <c r="X27" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2639,29 +2899,30 @@
           <t>Computational Materials Science and Design Lab</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>Campus: Tempe</t>
-        </is>
-      </c>
+      <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr"/>
-      <c r="O28" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr"/>
+      <c r="P28" s="2" t="inlineStr"/>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
         <is>
           <t>4yYKCpUAAAAJ</t>
         </is>
       </c>
-      <c r="Q28" s="3">
+      <c r="V28" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/hzhuang7", "https://search.asu.edu/profile/hzhuang7")</f>
         <v/>
       </c>
-      <c r="R28" s="3">
+      <c r="W28" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=4yYKCpUAAAAJ", "Scholar (4yYKCpUAAAAJ)")</f>
         <v/>
       </c>
-      <c r="S28" s="3">
+      <c r="X28" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2712,28 +2973,33 @@
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr"/>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>ENGRC 359 (Tempe, AZ 85287-6106)</t>
-        </is>
-      </c>
-      <c r="N29" s="3">
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr"/>
+      <c r="P29" s="2" t="inlineStr"/>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>Log in to www_public</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="3">
         <f>HYPERLINK("http://www.public.asu.edu/~hhuang38", "http://www.public.asu.edu/~hhuang38")</f>
         <v/>
       </c>
-      <c r="O29" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P29" s="2" t="inlineStr"/>
-      <c r="Q29" s="3">
+      <c r="T29" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/hhuang38", "https://search.asu.edu/profile/hhuang38")</f>
         <v/>
       </c>
-      <c r="R29" s="3">
+      <c r="W29" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Huei-Ping%20Huang%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="S29" s="3">
+      <c r="X29" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2796,32 +3062,41 @@
           <t>Nanomechanics Laboratory</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr"/>
+      <c r="P30" s="2" t="inlineStr"/>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>Nanostructured Materials</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
         <is>
           <t>ENGRC 355 (Tempe, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="N30" s="3">
+      <c r="S30" s="3">
         <f>HYPERLINK("http://faculty.engineering.asu.edu/jagan/", "http://faculty.engineering.asu.edu/jagan/")</f>
         <v/>
       </c>
-      <c r="O30" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
+      <c r="T30" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
         <is>
           <t>ClqRIhIAAAAJ</t>
         </is>
       </c>
-      <c r="Q30" s="3">
+      <c r="V30" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/jrajago1", "https://search.asu.edu/profile/jrajago1")</f>
         <v/>
       </c>
-      <c r="R30" s="3">
+      <c r="W30" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=ClqRIhIAAAAJ", "Scholar (ClqRIhIAAAAJ)")</f>
         <v/>
       </c>
-      <c r="S30" s="3">
+      <c r="X30" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2877,27 +3152,36 @@
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr"/>
-      <c r="N31" s="3">
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr"/>
+      <c r="P31" s="2" t="inlineStr"/>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>ENGRC 309 (Tempe, AZ 85287)</t>
+        </is>
+      </c>
+      <c r="S31" s="3">
         <f>HYPERLINK("http://faculty.engineering.asu.edu/konrad/", "http://faculty.engineering.asu.edu/konrad/")</f>
         <v/>
       </c>
-      <c r="O31" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
+      <c r="T31" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
         <is>
           <t>SWeAf4UAAAAJ</t>
         </is>
       </c>
-      <c r="Q31" s="3">
+      <c r="V31" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/krykacze", "https://search.asu.edu/profile/krykacze")</f>
         <v/>
       </c>
-      <c r="R31" s="3">
+      <c r="W31" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=SWeAf4UAAAAJ", "Scholar (SWeAf4UAAAAJ)")</f>
         <v/>
       </c>
-      <c r="S31" s="3">
+      <c r="X31" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2954,23 +3238,32 @@
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr"/>
       <c r="N32" s="2" t="inlineStr"/>
-      <c r="O32" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr"/>
+      <c r="P32" s="2" t="inlineStr"/>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>Campus: Tempe</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
         <is>
           <t>9LWNC50AAAAJ</t>
         </is>
       </c>
-      <c r="Q32" s="3">
+      <c r="V32" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/mingleiq", "https://search.asu.edu/profile/mingleiq")</f>
         <v/>
       </c>
-      <c r="R32" s="3">
+      <c r="W32" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=9LWNC50AAAAJ", "Scholar (9LWNC50AAAAJ)")</f>
         <v/>
       </c>
-      <c r="S32" s="3">
+      <c r="X32" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -3029,28 +3322,33 @@
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr"/>
-      <c r="M33" s="2" t="inlineStr">
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr"/>
+      <c r="P33" s="2" t="inlineStr"/>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="N33" s="3">
+      <c r="S33" s="3">
         <f>HYPERLINK("https://mmmplab.engineering.asu.edu/", "https://mmmplab.engineering.asu.edu/")</f>
         <v/>
       </c>
-      <c r="O33" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P33" s="2" t="inlineStr"/>
-      <c r="Q33" s="3">
+      <c r="T33" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/qnian", "https://search.asu.edu/profile/qnian")</f>
         <v/>
       </c>
-      <c r="R33" s="3">
+      <c r="W33" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Qiong%20Nian%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="S33" s="3">
+      <c r="X33" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -3105,28 +3403,33 @@
           <t>Wind Energy and Atmospheric Boundary Layer Lab</t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr">
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr"/>
+      <c r="P34" s="2" t="inlineStr"/>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr">
         <is>
           <t>Goldwater 466 (TEMPE, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="N34" s="3">
+      <c r="S34" s="3">
         <f>HYPERLINK("https://windlab.engineering.asu.edu/ronald-calhoun/", "https://windlab.engineering.asu.edu/ronald-calhoun/")</f>
         <v/>
       </c>
-      <c r="O34" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P34" s="2" t="inlineStr"/>
-      <c r="Q34" s="3">
+      <c r="T34" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/rcalhou", "https://search.asu.edu/profile/rcalhou")</f>
         <v/>
       </c>
-      <c r="R34" s="3">
+      <c r="W34" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ronald%20Calhoun%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="S34" s="3">
+      <c r="X34" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -3186,27 +3489,48 @@
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr"/>
-      <c r="N35" s="3">
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>NSF</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/asu-iris</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>Recent Updates</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>Campus: Tempe</t>
+        </is>
+      </c>
+      <c r="S35" s="3">
         <f>HYPERLINK("https://irislab.tech/", "https://irislab.tech/")</f>
         <v/>
       </c>
-      <c r="O35" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
+      <c r="T35" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
         <is>
           <t>SoEC4h4AAAAJ</t>
         </is>
       </c>
-      <c r="Q35" s="3">
+      <c r="V35" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/wjin34", "https://search.asu.edu/profile/wjin34")</f>
         <v/>
       </c>
-      <c r="R35" s="3">
+      <c r="W35" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=SoEC4h4AAAAJ", "Scholar (SoEC4h4AAAAJ)")</f>
         <v/>
       </c>
-      <c r="S35" s="3">
+      <c r="X35" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -3265,25 +3589,30 @@
           <t>Prognostics and Health Management (PHM) Lab</t>
         </is>
       </c>
-      <c r="M36" s="2" t="inlineStr">
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr"/>
+      <c r="P36" s="2" t="inlineStr"/>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr">
         <is>
           <t>ENGRC 409 (Tempe, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="N36" s="2" t="inlineStr"/>
-      <c r="O36" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P36" s="2" t="inlineStr"/>
-      <c r="Q36" s="3">
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/yliu35", "https://search.asu.edu/profile/yliu35")</f>
         <v/>
       </c>
-      <c r="R36" s="3">
+      <c r="W36" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Yongming%20Liu%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="S36" s="3">
+      <c r="X36" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -3347,27 +3676,40 @@
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr"/>
-      <c r="N37" s="3">
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>NSF</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr"/>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>Manufacturing</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="3">
         <f>HYPERLINK("https://www.cindyxjli.com/", "https://www.cindyxjli.com/")</f>
         <v/>
       </c>
-      <c r="O37" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
+      <c r="T37" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
         <is>
           <t>tGQzHJIAAAAJ</t>
         </is>
       </c>
-      <c r="Q37" s="3">
+      <c r="V37" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/xiangji5", "https://search.asu.edu/profile/xiangji5")</f>
         <v/>
       </c>
-      <c r="R37" s="3">
+      <c r="W37" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=tGQzHJIAAAAJ", "Scholar (tGQzHJIAAAAJ)")</f>
         <v/>
       </c>
-      <c r="S37" s="3">
+      <c r="X37" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -3422,25 +3764,30 @@
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr"/>
-      <c r="M38" s="2" t="inlineStr">
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr"/>
+      <c r="P38" s="2" t="inlineStr"/>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr">
         <is>
           <t>ENGRC 381 (TEMPE, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="N38" s="2" t="inlineStr"/>
-      <c r="O38" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P38" s="2" t="inlineStr"/>
-      <c r="Q38" s="3">
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/jimbo", "https://search.asu.edu/profile/jimbo")</f>
         <v/>
       </c>
-      <c r="R38" s="3">
+      <c r="W38" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=James%20Middleton%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="S38" s="3">
+      <c r="X38" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -3491,25 +3838,30 @@
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr"/>
-      <c r="M39" s="2" t="inlineStr">
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr"/>
+      <c r="P39" s="2" t="inlineStr"/>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="N39" s="2" t="inlineStr"/>
-      <c r="O39" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P39" s="2" t="inlineStr"/>
-      <c r="Q39" s="3">
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/linli25", "https://search.asu.edu/profile/linli25")</f>
         <v/>
       </c>
-      <c r="R39" s="3">
+      <c r="W39" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Lin%20Li%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="S39" s="3">
+      <c r="X39" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -3560,25 +3912,30 @@
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr"/>
-      <c r="M40" s="2" t="inlineStr">
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr"/>
+      <c r="P40" s="2" t="inlineStr"/>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr">
         <is>
           <t>ENGRC 411 (TEMPE, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="N40" s="2" t="inlineStr"/>
-      <c r="O40" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P40" s="2" t="inlineStr"/>
-      <c r="Q40" s="3">
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/marc03", "https://search.asu.edu/profile/marc03")</f>
         <v/>
       </c>
-      <c r="R40" s="3">
+      <c r="W40" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Marc%20Mignolet%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="S40" s="3">
+      <c r="X40" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -3630,23 +3987,32 @@
       </c>
       <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr"/>
-      <c r="N41" s="3">
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr"/>
+      <c r="P41" s="2" t="inlineStr"/>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>ENGRC 352 (TEMPE, AZ 85287-6106)</t>
+        </is>
+      </c>
+      <c r="S41" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/pperalta/", "https://faculty.engineering.asu.edu/pperalta/")</f>
         <v/>
       </c>
-      <c r="O41" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P41" s="2" t="inlineStr"/>
-      <c r="Q41" s="3">
+      <c r="T41" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/pperalta", "https://search.asu.edu/profile/pperalta")</f>
         <v/>
       </c>
-      <c r="R41" s="3">
+      <c r="W41" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Pedro%20Peralta%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="S41" s="3">
+      <c r="X41" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -3707,30 +4073,47 @@
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr">
         <is>
+          <t>Welcome and we are looking forward to working with Dr</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>NSF, ONR</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr"/>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>Highlighted as a cover in Small</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="N42" s="3">
+      <c r="S42" s="3">
         <f>HYPERLINK("https://wonmokang3.wixsite.com/website", "https://wonmokang3.wixsite.com/website")</f>
         <v/>
       </c>
-      <c r="O42" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
+      <c r="T42" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
         <is>
           <t>bHyyOTAAAAAJ</t>
         </is>
       </c>
-      <c r="Q42" s="3">
+      <c r="V42" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/wkang16", "https://search.asu.edu/profile/wkang16")</f>
         <v/>
       </c>
-      <c r="R42" s="3">
+      <c r="W42" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=bHyyOTAAAAAJ", "Scholar (bHyyOTAAAAAJ)")</f>
         <v/>
       </c>
-      <c r="S42" s="3">
+      <c r="X42" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -3783,19 +4166,28 @@
       <c r="L43" s="2" t="inlineStr"/>
       <c r="M43" s="2" t="inlineStr"/>
       <c r="N43" s="2" t="inlineStr"/>
-      <c r="O43" s="2" t="b">
-        <v>1</v>
-      </c>
+      <c r="O43" s="2" t="inlineStr"/>
       <c r="P43" s="2" t="inlineStr"/>
-      <c r="Q43" s="3">
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>GWC 464 (Tempe, AZ 85287-6106)</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/yren32", "https://search.asu.edu/profile/yren32")</f>
         <v/>
       </c>
-      <c r="R43" s="3">
+      <c r="W43" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Yi%20Ren%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="S43" s="3">
+      <c r="X43" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -3803,199 +4195,199 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R2" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S2" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W2" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X2" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R3" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S3" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S3" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V3" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W3" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X3" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q4" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R4" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S4" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S4" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V4" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W4" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X4" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q5" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R5" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S5" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S5" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V5" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W5" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X5" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q6" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R6" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S6" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V6" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W6" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X6" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R7" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S7" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V7" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W7" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X7" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N8" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R8" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S8" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S8" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V8" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W8" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X8" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R9" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V9" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W9" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X9" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R10" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S10" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S10" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V10" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W10" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X10" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R11" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S11" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V11" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W11" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X11" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N12" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R12" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S12" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S12" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V12" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W12" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X12" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R13" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S13" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S13" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V13" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W13" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X13" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R14" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S14" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V14" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W14" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X14" r:id="rId61"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R15" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S15" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S15" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V15" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W15" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X15" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R16" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S16" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S16" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V16" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W16" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X16" r:id="rId71"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q17" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R17" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S17" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S17" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V17" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W17" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X17" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q18" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R18" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S18" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V18" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W18" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X18" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q19" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R19" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S19" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V19" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W19" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X19" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q20" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R20" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S20" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V20" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W20" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X20" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q21" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R21" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S21" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V21" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W21" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X21" r:id="rId92"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q22" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R22" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S22" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S22" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V22" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W22" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X22" r:id="rId97"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q23" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R23" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S23" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S23" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V23" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W23" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X23" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q24" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R24" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S24" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S24" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V24" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W24" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X24" r:id="rId107"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q25" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R25" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S25" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S25" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V25" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W25" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X25" r:id="rId112"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q26" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R26" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S26" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V26" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W26" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X26" r:id="rId116"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q27" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R27" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S27" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S27" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V27" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W27" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X27" r:id="rId121"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q28" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R28" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S28" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V28" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W28" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X28" r:id="rId125"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q29" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R29" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S29" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S29" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V29" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W29" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X29" r:id="rId130"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q30" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R30" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S30" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S30" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V30" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W30" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X30" r:id="rId135"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q31" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R31" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S31" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S31" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V31" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W31" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X31" r:id="rId140"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q32" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R32" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S32" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V32" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W32" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X32" r:id="rId144"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N33" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q33" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R33" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S33" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S33" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V33" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W33" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X33" r:id="rId149"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N34" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q34" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R34" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S34" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S34" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V34" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W34" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X34" r:id="rId154"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N35" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q35" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R35" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S35" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S35" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V35" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W35" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X35" r:id="rId159"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q36" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R36" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S36" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V36" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W36" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X36" r:id="rId163"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N37" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q37" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R37" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S37" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S37" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V37" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W37" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X37" r:id="rId168"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q38" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R38" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S38" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V38" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W38" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X38" r:id="rId172"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q39" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R39" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S39" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V39" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W39" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X39" r:id="rId176"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q40" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R40" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S40" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V40" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W40" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X40" r:id="rId180"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N41" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q41" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R41" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S41" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S41" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V41" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W41" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X41" r:id="rId185"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N42" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q42" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R42" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S42" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S42" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V42" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W42" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X42" r:id="rId190"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q43" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R43" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S43" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V43" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W43" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X43" r:id="rId194"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4007,7 +4399,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S49"/>
+  <dimension ref="A1:X49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4022,13 +4414,18 @@
     <col width="65" customWidth="1" min="10" max="10"/>
     <col width="65" customWidth="1" min="11" max="11"/>
     <col width="65" customWidth="1" min="12" max="12"/>
-    <col width="46" customWidth="1" min="13" max="13"/>
-    <col width="49" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="49" customWidth="1" min="17" max="17"/>
-    <col width="32" customWidth="1" min="18" max="18"/>
+    <col width="65" customWidth="1" min="13" max="13"/>
+    <col width="53" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="65" customWidth="1" min="16" max="16"/>
+    <col width="56" customWidth="1" min="17" max="17"/>
+    <col width="46" customWidth="1" min="18" max="18"/>
     <col width="49" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="49" customWidth="1" min="22" max="22"/>
+    <col width="32" customWidth="1" min="23" max="23"/>
+    <col width="49" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4094,35 +4491,60 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>Actively Hiring / Openings</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Target Skills / Prerequisites</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Funding Sponsors</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Software / Code Repo</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Latest Project / Highlight</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>Office Location</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Lab / Personal Website</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Is Field Match</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Scholar ID</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Profile URL</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Google Scholar URL</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Directory URL</t>
         </is>
@@ -4179,23 +4601,44 @@
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="3">
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>CFD</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>AFOSR</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>https://bitbucket.org/krgasu/leap/downloads/leap-v0.8.2.tar.gz, https://bitbucket.org/krgasu/leap/src/master</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>School for Engineering of Matter, Transport &amp; Energy</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr"/>
+      <c r="S2" s="3">
         <f>HYPERLINK("https://kasbaoui.bitbucket.io", "https://kasbaoui.bitbucket.io")</f>
         <v/>
       </c>
-      <c r="O2" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="3">
+      <c r="T2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U2" s="2" t="inlineStr"/>
+      <c r="V2" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/mkasbaou", "https://search.asu.edu/profile/mkasbaou")</f>
         <v/>
       </c>
-      <c r="R2" s="3">
+      <c r="W2" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Mohamed%20Houssem%20Kasbaoui%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="S2" s="3">
+      <c r="X2" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -4256,26 +4699,43 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
+          <t>Multiple UG/MS research positions available for Fall 2024 (volunteer) and Spring/Summer 2025 (possible FURI / MORE support)</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr"/>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>NASA, NSF</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>News&amp;Awards</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
           <t>ENGRC 327 (Tempe, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="N3" s="3">
+      <c r="S3" s="3">
         <f>HYPERLINK("http://faculty.engineering.asu.edu/lpwang", "http://faculty.engineering.asu.edu/lpwang")</f>
         <v/>
       </c>
-      <c r="O3" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="3">
+      <c r="T3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U3" s="2" t="inlineStr"/>
+      <c r="V3" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/lwang78", "https://search.asu.edu/profile/lwang78")</f>
         <v/>
       </c>
-      <c r="R3" s="3">
+      <c r="W3" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Liping%20Wang%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="S3" s="3">
+      <c r="X3" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -4334,28 +4794,33 @@
           <t>Computational Mechanics Lab</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>ENGRC 353 (Tempe, AZ 85287-6106)</t>
-        </is>
-      </c>
-      <c r="N4" s="3">
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>Multiscale polymer analysis</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr"/>
+      <c r="S4" s="3">
         <f>HYPERLINK("http://sparky.fulton.asu.edu/oswald/", "http://sparky.fulton.asu.edu/oswald/")</f>
         <v/>
       </c>
-      <c r="O4" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="3">
+      <c r="T4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U4" s="2" t="inlineStr"/>
+      <c r="V4" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/joswald1", "https://search.asu.edu/profile/joswald1")</f>
         <v/>
       </c>
-      <c r="R4" s="3">
+      <c r="W4" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Jay%20Oswald%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="S4" s="3">
+      <c r="X4" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -4418,28 +4883,45 @@
           <t>Sun Robotics Lab</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="3">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Dec 19, 2025 We have two openings for fully supported summer interns through SURI program at ASU</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>Mission and Core Values</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>Campus: Tempe</t>
+        </is>
+      </c>
+      <c r="S5" s="3">
         <f>HYPERLINK("https://sunroboticslab.github.io", "https://sunroboticslab.github.io")</f>
         <v/>
       </c>
-      <c r="O5" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
         <is>
           <t>fjUoHOsAAAAJ</t>
         </is>
       </c>
-      <c r="Q5" s="3">
+      <c r="V5" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/jsun165", "https://search.asu.edu/profile/jsun165")</f>
         <v/>
       </c>
-      <c r="R5" s="3">
+      <c r="W5" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=fjUoHOsAAAAJ", "Scholar (fjUoHOsAAAAJ)")</f>
         <v/>
       </c>
-      <c r="S5" s="3">
+      <c r="X5" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -4492,23 +4974,32 @@
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>ENGRC 361 (TEMPE, AZ 85287-6106)</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
         <is>
           <t>xT-lX9sAAAAJ</t>
         </is>
       </c>
-      <c r="Q6" s="3">
+      <c r="V6" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/asuchen", "https://search.asu.edu/profile/asuchen")</f>
         <v/>
       </c>
-      <c r="R6" s="3">
+      <c r="W6" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=xT-lX9sAAAAJ", "Scholar (xT-lX9sAAAAJ)")</f>
         <v/>
       </c>
-      <c r="S6" s="3">
+      <c r="X6" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -4565,23 +5056,28 @@
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr"/>
       <c r="N7" s="2" t="inlineStr"/>
-      <c r="O7" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr"/>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>DKc-AgcAAAAJ</t>
         </is>
       </c>
-      <c r="Q7" s="3">
+      <c r="V7" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/kramesh2", "https://search.asu.edu/profile/kramesh2")</f>
         <v/>
       </c>
-      <c r="R7" s="3">
+      <c r="W7" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=DKc-AgcAAAAJ", "Scholar (DKc-AgcAAAAJ)")</f>
         <v/>
       </c>
-      <c r="S7" s="3">
+      <c r="X7" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -4646,30 +5142,43 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
+          <t>Actively seeking graduate students (see bio/lab link)</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>Python, PyTorch, ROS, ROS2, C/C++, Linear Algebra</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
           <t>551 E Tyler Mall ERC 475 (Tempe, AZ 85281)</t>
         </is>
       </c>
-      <c r="N8" s="3">
+      <c r="S8" s="3">
         <f>HYPERLINK("https://sites.google.com/asu.edu/kunalgarg/", "https://sites.google.com/asu.edu/kunalgarg/")</f>
         <v/>
       </c>
-      <c r="O8" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
         <is>
           <t>vs3pl-8AAAAJ</t>
         </is>
       </c>
-      <c r="Q8" s="3">
+      <c r="V8" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/kgarg24", "https://search.asu.edu/profile/kgarg24")</f>
         <v/>
       </c>
-      <c r="R8" s="3">
+      <c r="W8" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=vs3pl-8AAAAJ", "Scholar (vs3pl-8AAAAJ)")</f>
         <v/>
       </c>
-      <c r="S8" s="3">
+      <c r="X8" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -4732,28 +5241,45 @@
           <t>Optimization, Autonomy, and Soft Intelligence Systems (OASIS) Lab</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="3">
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>Actively recruiting / Openings mentioned on lab site</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr"/>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>Ocean and Soft Intelligent Structure Interaction Lab</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>ERC 485 (Tempe, AZ 85287)</t>
+        </is>
+      </c>
+      <c r="S9" s="3">
         <f>HYPERLINK("https://sites.google.com/view/oasislabasu", "https://sites.google.com/view/oasislabasu")</f>
         <v/>
       </c>
-      <c r="O9" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="T9" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>2xQTOc0AAAAJ</t>
         </is>
       </c>
-      <c r="Q9" s="3">
+      <c r="V9" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/leixinma", "https://search.asu.edu/profile/leixinma")</f>
         <v/>
       </c>
-      <c r="R9" s="3">
+      <c r="W9" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=2xQTOc0AAAAJ", "Scholar (2xQTOc0AAAAJ)")</f>
         <v/>
       </c>
-      <c r="S9" s="3">
+      <c r="X9" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -4812,28 +5338,37 @@
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>Want to be part of CMAT Lab?</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>551 E Tyler Mall ERC 479 (Tempe, AZ 85281)</t>
         </is>
       </c>
-      <c r="N10" s="3">
+      <c r="S10" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/cmat/", "https://faculty.engineering.asu.edu/cmat/")</f>
         <v/>
       </c>
-      <c r="O10" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P10" s="2" t="inlineStr"/>
-      <c r="Q10" s="3">
+      <c r="T10" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U10" s="2" t="inlineStr"/>
+      <c r="V10" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/gpathiko", "https://search.asu.edu/profile/gpathiko")</f>
         <v/>
       </c>
-      <c r="R10" s="3">
+      <c r="W10" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Gokul%20Pathikonda%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="S10" s="3">
+      <c r="X10" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -4890,23 +5425,28 @@
       </c>
       <c r="M11" s="2" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr"/>
-      <c r="O11" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr"/>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
         <is>
           <t>yv6aCW8AAAAJ</t>
         </is>
       </c>
-      <c r="Q11" s="3">
+      <c r="V11" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/mherrma1", "https://search.asu.edu/profile/mherrma1")</f>
         <v/>
       </c>
-      <c r="R11" s="3">
+      <c r="W11" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=yv6aCW8AAAAJ", "Scholar (yv6aCW8AAAAJ)")</f>
         <v/>
       </c>
-      <c r="S11" s="3">
+      <c r="X11" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -4970,27 +5510,36 @@
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr"/>
-      <c r="N12" s="3">
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>ENGRC 375 (Tempe, AZ 85287-6106)</t>
+        </is>
+      </c>
+      <c r="S12" s="3">
         <f>HYPERLINK("http://faculty.engineering.asu.edu/acs/", "http://faculty.engineering.asu.edu/acs/")</f>
         <v/>
       </c>
-      <c r="O12" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>KKup0OgAAAAJ</t>
         </is>
       </c>
-      <c r="Q12" s="3">
+      <c r="V12" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/smberma2", "https://search.asu.edu/profile/smberma2")</f>
         <v/>
       </c>
-      <c r="R12" s="3">
+      <c r="W12" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=KKup0OgAAAAJ", "Scholar (KKup0OgAAAAJ)")</f>
         <v/>
       </c>
-      <c r="S12" s="3">
+      <c r="X12" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -5049,28 +5598,33 @@
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr"/>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="N13" s="3">
+      <c r="S13" s="3">
         <f>HYPERLINK("https://sites.google.com/site/zhexudavid00710/research?authuser=0", "https://sites.google.com/site/zhexudavid00710/research?authuser=0")</f>
         <v/>
       </c>
-      <c r="O13" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P13" s="2" t="inlineStr"/>
-      <c r="Q13" s="3">
+      <c r="T13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U13" s="2" t="inlineStr"/>
+      <c r="V13" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/xzhe1", "https://search.asu.edu/profile/xzhe1")</f>
         <v/>
       </c>
-      <c r="R13" s="3">
+      <c r="W13" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Zhe%20Xu%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="S13" s="3">
+      <c r="X13" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -5123,19 +5677,24 @@
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr"/>
-      <c r="O14" s="2" t="b">
-        <v>1</v>
-      </c>
+      <c r="O14" s="2" t="inlineStr"/>
       <c r="P14" s="2" t="inlineStr"/>
-      <c r="Q14" s="3">
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U14" s="2" t="inlineStr"/>
+      <c r="V14" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/jkim520", "https://search.asu.edu/profile/jkim520")</f>
         <v/>
       </c>
-      <c r="R14" s="3">
+      <c r="W14" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Jeonglae%20Kim%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="S14" s="3">
+      <c r="X14" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -5199,23 +5758,28 @@
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr"/>
-      <c r="N15" s="3">
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr"/>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="3">
         <f>HYPERLINK("http://control.asu.edu/", "http://control.asu.edu/")</f>
         <v/>
       </c>
-      <c r="O15" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P15" s="2" t="inlineStr"/>
-      <c r="Q15" s="3">
+      <c r="T15" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U15" s="2" t="inlineStr"/>
+      <c r="V15" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/mpeet", "https://search.asu.edu/profile/mpeet")</f>
         <v/>
       </c>
-      <c r="R15" s="3">
+      <c r="W15" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Matthew%20Peet%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="S15" s="3">
+      <c r="X15" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -5275,27 +5839,32 @@
       </c>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="3">
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="3">
         <f>HYPERLINK("http://wang.faculty.asu.edu/", "http://wang.faculty.asu.edu/")</f>
         <v/>
       </c>
-      <c r="O16" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>LaUdx9gAAAAJ</t>
         </is>
       </c>
-      <c r="Q16" s="3">
+      <c r="V16" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/rywang", "https://search.asu.edu/profile/rywang")</f>
         <v/>
       </c>
-      <c r="R16" s="3">
+      <c r="W16" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=LaUdx9gAAAAJ", "Scholar (LaUdx9gAAAAJ)")</f>
         <v/>
       </c>
-      <c r="S16" s="3">
+      <c r="X16" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -5355,23 +5924,36 @@
       </c>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr"/>
-      <c r="N17" s="3">
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr"/>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>ENGRC 465 (Tempe, AZ 85287)</t>
+        </is>
+      </c>
+      <c r="S17" s="3">
         <f>HYPERLINK("http://RESEARCHGATE.net/profile/Ryan_Milcarek", "http://RESEARCHGATE.net/profile/Ryan_Milcarek")</f>
         <v/>
       </c>
-      <c r="O17" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P17" s="2" t="inlineStr"/>
-      <c r="Q17" s="3">
+      <c r="T17" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>m-Pb6g2pm2UC</t>
+        </is>
+      </c>
+      <c r="V17" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/rjmilcar", "https://search.asu.edu/profile/rjmilcar")</f>
         <v/>
       </c>
-      <c r="R17" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ryan%20Milcarek%20Arizona%20State%20University", "Google Scholar Search")</f>
-        <v/>
-      </c>
-      <c r="S17" s="3">
+      <c r="W17" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=m-Pb6g2pm2UC", "Scholar (m-Pb6g2pm2UC)")</f>
+        <v/>
+      </c>
+      <c r="X17" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -5422,25 +6004,30 @@
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr"/>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr">
         <is>
           <t>ENGRC 377 (TEMPE, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="N18" s="2" t="inlineStr"/>
-      <c r="O18" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P18" s="2" t="inlineStr"/>
-      <c r="Q18" s="3">
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U18" s="2" t="inlineStr"/>
+      <c r="V18" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/attwl", "https://search.asu.edu/profile/attwl")</f>
         <v/>
       </c>
-      <c r="R18" s="3">
+      <c r="W18" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=T.-W.%20Lee%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="S18" s="3">
+      <c r="X18" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -5493,19 +6080,32 @@
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr"/>
       <c r="N19" s="2" t="inlineStr"/>
-      <c r="O19" s="2" t="b">
-        <v>1</v>
-      </c>
+      <c r="O19" s="2" t="inlineStr"/>
       <c r="P19" s="2" t="inlineStr"/>
-      <c r="Q19" s="3">
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>Campus: Tempe</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>OmBV67MAAAAJ</t>
+        </is>
+      </c>
+      <c r="V19" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/tyang123", "https://search.asu.edu/profile/tyang123")</f>
         <v/>
       </c>
-      <c r="R19" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Tianyu%20Yang%20Arizona%20State%20University", "Google Scholar Search")</f>
-        <v/>
-      </c>
-      <c r="S19" s="3">
+      <c r="W19" s="3">
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=OmBV67MAAAAJ", "Scholar (OmBV67MAAAAJ)")</f>
+        <v/>
+      </c>
+      <c r="X19" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -5562,23 +6162,28 @@
       </c>
       <c r="M20" s="2" t="inlineStr"/>
       <c r="N20" s="2" t="inlineStr"/>
-      <c r="O20" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t>w3fU9E0AAAAJ</t>
         </is>
       </c>
-      <c r="Q20" s="3">
+      <c r="V20" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/chattopa", "https://search.asu.edu/profile/chattopa")</f>
         <v/>
       </c>
-      <c r="R20" s="3">
+      <c r="W20" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=w3fU9E0AAAAJ", "Scholar (w3fU9E0AAAAJ)")</f>
         <v/>
       </c>
-      <c r="S20" s="3">
+      <c r="X20" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -5637,29 +6242,34 @@
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr"/>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="N21" s="2" t="inlineStr"/>
-      <c r="O21" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
         <is>
           <t>HRx2lJQAAAAJ</t>
         </is>
       </c>
-      <c r="Q21" s="3">
+      <c r="V21" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/adscotti", "https://search.asu.edu/profile/adscotti")</f>
         <v/>
       </c>
-      <c r="R21" s="3">
+      <c r="W21" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=HRx2lJQAAAAJ", "Scholar (HRx2lJQAAAAJ)")</f>
         <v/>
       </c>
-      <c r="S21" s="3">
+      <c r="X21" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -5718,32 +6328,45 @@
           <t>3D Energy Lab</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>NSF</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr"/>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>3D Energy Device Laboratory</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>551 E Tyler Mall ERC 363 (Tempe, AZ 85281)</t>
         </is>
       </c>
-      <c r="N22" s="3">
+      <c r="S22" s="3">
         <f>HYPERLINK("http://sites.google.com/view/3denergy", "http://sites.google.com/view/3denergy")</f>
         <v/>
       </c>
-      <c r="O22" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
         <is>
           <t>fs2d97sAAAAJ</t>
         </is>
       </c>
-      <c r="Q22" s="3">
+      <c r="V22" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/bkwon2", "https://search.asu.edu/profile/bkwon2")</f>
         <v/>
       </c>
-      <c r="R22" s="3">
+      <c r="W22" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=fs2d97sAAAAJ", "Scholar (fs2d97sAAAAJ)")</f>
         <v/>
       </c>
-      <c r="S22" s="3">
+      <c r="X22" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -5803,27 +6426,36 @@
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr"/>
-      <c r="N23" s="3">
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr"/>
+      <c r="P23" s="2" t="inlineStr"/>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>Campus: Tempe</t>
+        </is>
+      </c>
+      <c r="S23" s="3">
         <f>HYPERLINK("http://birth.asu.edu", "http://birth.asu.edu")</f>
         <v/>
       </c>
-      <c r="O23" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
+      <c r="T23" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
         <is>
           <t>00Fepb0AAAAJ</t>
         </is>
       </c>
-      <c r="Q23" s="3">
+      <c r="V23" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/hmarvi", "https://search.asu.edu/profile/hmarvi")</f>
         <v/>
       </c>
-      <c r="R23" s="3">
+      <c r="W23" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=00Fepb0AAAAJ", "Scholar (00Fepb0AAAAJ)")</f>
         <v/>
       </c>
-      <c r="S23" s="3">
+      <c r="X23" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -5874,28 +6506,33 @@
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr"/>
-      <c r="M24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr"/>
+      <c r="P24" s="2" t="inlineStr"/>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="N24" s="3">
+      <c r="S24" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/hlee", "https://faculty.engineering.asu.edu/hlee")</f>
         <v/>
       </c>
-      <c r="O24" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P24" s="2" t="inlineStr"/>
-      <c r="Q24" s="3">
+      <c r="T24" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/hlee234", "https://search.asu.edu/profile/hlee234")</f>
         <v/>
       </c>
-      <c r="R24" s="3">
+      <c r="W24" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Hyunglae%20Lee%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="S24" s="3">
+      <c r="X24" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -5959,23 +6596,28 @@
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr"/>
-      <c r="N25" s="3">
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr"/>
+      <c r="P25" s="2" t="inlineStr"/>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="3">
         <f>HYPERLINK("https://magic.asu.edu/", "https://magic.asu.edu/")</f>
         <v/>
       </c>
-      <c r="O25" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P25" s="2" t="inlineStr"/>
-      <c r="Q25" s="3">
+      <c r="T25" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/ljannesa", "https://search.asu.edu/profile/ljannesa")</f>
         <v/>
       </c>
-      <c r="R25" s="3">
+      <c r="W25" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Leila%20Ladani%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="S25" s="3">
+      <c r="X25" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -6034,25 +6676,30 @@
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr"/>
-      <c r="M26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr"/>
+      <c r="P26" s="2" t="inlineStr"/>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr">
         <is>
           <t>ENGRC 463 (TEMPE, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="N26" s="2" t="inlineStr"/>
-      <c r="O26" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P26" s="2" t="inlineStr"/>
-      <c r="Q26" s="3">
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/pphelan", "https://search.asu.edu/profile/pphelan")</f>
         <v/>
       </c>
-      <c r="R26" s="3">
+      <c r="W26" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Patrick%20Phelan%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="S26" s="3">
+      <c r="X26" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -6108,27 +6755,32 @@
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr"/>
-      <c r="N27" s="3">
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr"/>
+      <c r="P27" s="2" t="inlineStr"/>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="3">
         <f>HYPERLINK("https://isim.asu.edu", "https://isim.asu.edu")</f>
         <v/>
       </c>
-      <c r="O27" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
+      <c r="T27" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
         <is>
           <t>_6o8MrUAAAAJ</t>
         </is>
       </c>
-      <c r="Q27" s="3">
+      <c r="V27" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/ypeet", "https://search.asu.edu/profile/ypeet")</f>
         <v/>
       </c>
-      <c r="R27" s="3">
+      <c r="W27" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=_6o8MrUAAAAJ", "Scholar (_6o8MrUAAAAJ)")</f>
         <v/>
       </c>
-      <c r="S27" s="3">
+      <c r="X27" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -6191,29 +6843,30 @@
           <t>Computational Materials Science and Design Lab</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>Campus: Tempe</t>
-        </is>
-      </c>
+      <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr"/>
-      <c r="O28" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr"/>
+      <c r="P28" s="2" t="inlineStr"/>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
         <is>
           <t>4yYKCpUAAAAJ</t>
         </is>
       </c>
-      <c r="Q28" s="3">
+      <c r="V28" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/hzhuang7", "https://search.asu.edu/profile/hzhuang7")</f>
         <v/>
       </c>
-      <c r="R28" s="3">
+      <c r="W28" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=4yYKCpUAAAAJ", "Scholar (4yYKCpUAAAAJ)")</f>
         <v/>
       </c>
-      <c r="S28" s="3">
+      <c r="X28" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -6264,28 +6917,33 @@
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr"/>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>ENGRC 359 (Tempe, AZ 85287-6106)</t>
-        </is>
-      </c>
-      <c r="N29" s="3">
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr"/>
+      <c r="P29" s="2" t="inlineStr"/>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>Log in to www_public</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="3">
         <f>HYPERLINK("http://www.public.asu.edu/~hhuang38", "http://www.public.asu.edu/~hhuang38")</f>
         <v/>
       </c>
-      <c r="O29" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P29" s="2" t="inlineStr"/>
-      <c r="Q29" s="3">
+      <c r="T29" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/hhuang38", "https://search.asu.edu/profile/hhuang38")</f>
         <v/>
       </c>
-      <c r="R29" s="3">
+      <c r="W29" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Huei-Ping%20Huang%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="S29" s="3">
+      <c r="X29" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -6348,32 +7006,41 @@
           <t>Nanomechanics Laboratory</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr"/>
+      <c r="P30" s="2" t="inlineStr"/>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>Nanostructured Materials</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
         <is>
           <t>ENGRC 355 (Tempe, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="N30" s="3">
+      <c r="S30" s="3">
         <f>HYPERLINK("http://faculty.engineering.asu.edu/jagan/", "http://faculty.engineering.asu.edu/jagan/")</f>
         <v/>
       </c>
-      <c r="O30" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
+      <c r="T30" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
         <is>
           <t>ClqRIhIAAAAJ</t>
         </is>
       </c>
-      <c r="Q30" s="3">
+      <c r="V30" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/jrajago1", "https://search.asu.edu/profile/jrajago1")</f>
         <v/>
       </c>
-      <c r="R30" s="3">
+      <c r="W30" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=ClqRIhIAAAAJ", "Scholar (ClqRIhIAAAAJ)")</f>
         <v/>
       </c>
-      <c r="S30" s="3">
+      <c r="X30" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -6429,27 +7096,36 @@
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr"/>
-      <c r="N31" s="3">
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr"/>
+      <c r="P31" s="2" t="inlineStr"/>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>ENGRC 309 (Tempe, AZ 85287)</t>
+        </is>
+      </c>
+      <c r="S31" s="3">
         <f>HYPERLINK("http://faculty.engineering.asu.edu/konrad/", "http://faculty.engineering.asu.edu/konrad/")</f>
         <v/>
       </c>
-      <c r="O31" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
+      <c r="T31" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
         <is>
           <t>SWeAf4UAAAAJ</t>
         </is>
       </c>
-      <c r="Q31" s="3">
+      <c r="V31" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/krykacze", "https://search.asu.edu/profile/krykacze")</f>
         <v/>
       </c>
-      <c r="R31" s="3">
+      <c r="W31" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=SWeAf4UAAAAJ", "Scholar (SWeAf4UAAAAJ)")</f>
         <v/>
       </c>
-      <c r="S31" s="3">
+      <c r="X31" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -6506,23 +7182,32 @@
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr"/>
       <c r="N32" s="2" t="inlineStr"/>
-      <c r="O32" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr"/>
+      <c r="P32" s="2" t="inlineStr"/>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>Campus: Tempe</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
         <is>
           <t>9LWNC50AAAAJ</t>
         </is>
       </c>
-      <c r="Q32" s="3">
+      <c r="V32" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/mingleiq", "https://search.asu.edu/profile/mingleiq")</f>
         <v/>
       </c>
-      <c r="R32" s="3">
+      <c r="W32" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=9LWNC50AAAAJ", "Scholar (9LWNC50AAAAJ)")</f>
         <v/>
       </c>
-      <c r="S32" s="3">
+      <c r="X32" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -6581,28 +7266,33 @@
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr"/>
-      <c r="M33" s="2" t="inlineStr">
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr"/>
+      <c r="P33" s="2" t="inlineStr"/>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="N33" s="3">
+      <c r="S33" s="3">
         <f>HYPERLINK("https://mmmplab.engineering.asu.edu/", "https://mmmplab.engineering.asu.edu/")</f>
         <v/>
       </c>
-      <c r="O33" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P33" s="2" t="inlineStr"/>
-      <c r="Q33" s="3">
+      <c r="T33" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/qnian", "https://search.asu.edu/profile/qnian")</f>
         <v/>
       </c>
-      <c r="R33" s="3">
+      <c r="W33" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Qiong%20Nian%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="S33" s="3">
+      <c r="X33" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -6657,28 +7347,33 @@
           <t>Wind Energy and Atmospheric Boundary Layer Lab</t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr">
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr"/>
+      <c r="P34" s="2" t="inlineStr"/>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr">
         <is>
           <t>Goldwater 466 (TEMPE, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="N34" s="3">
+      <c r="S34" s="3">
         <f>HYPERLINK("https://windlab.engineering.asu.edu/ronald-calhoun/", "https://windlab.engineering.asu.edu/ronald-calhoun/")</f>
         <v/>
       </c>
-      <c r="O34" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P34" s="2" t="inlineStr"/>
-      <c r="Q34" s="3">
+      <c r="T34" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/rcalhou", "https://search.asu.edu/profile/rcalhou")</f>
         <v/>
       </c>
-      <c r="R34" s="3">
+      <c r="W34" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ronald%20Calhoun%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="S34" s="3">
+      <c r="X34" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -6738,27 +7433,48 @@
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr"/>
-      <c r="N35" s="3">
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>NSF</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/asu-iris</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>Recent Updates</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>Campus: Tempe</t>
+        </is>
+      </c>
+      <c r="S35" s="3">
         <f>HYPERLINK("https://irislab.tech/", "https://irislab.tech/")</f>
         <v/>
       </c>
-      <c r="O35" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
+      <c r="T35" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
         <is>
           <t>SoEC4h4AAAAJ</t>
         </is>
       </c>
-      <c r="Q35" s="3">
+      <c r="V35" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/wjin34", "https://search.asu.edu/profile/wjin34")</f>
         <v/>
       </c>
-      <c r="R35" s="3">
+      <c r="W35" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=SoEC4h4AAAAJ", "Scholar (SoEC4h4AAAAJ)")</f>
         <v/>
       </c>
-      <c r="S35" s="3">
+      <c r="X35" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -6817,25 +7533,30 @@
           <t>Prognostics and Health Management (PHM) Lab</t>
         </is>
       </c>
-      <c r="M36" s="2" t="inlineStr">
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr"/>
+      <c r="P36" s="2" t="inlineStr"/>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr">
         <is>
           <t>ENGRC 409 (Tempe, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="N36" s="2" t="inlineStr"/>
-      <c r="O36" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P36" s="2" t="inlineStr"/>
-      <c r="Q36" s="3">
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/yliu35", "https://search.asu.edu/profile/yliu35")</f>
         <v/>
       </c>
-      <c r="R36" s="3">
+      <c r="W36" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Yongming%20Liu%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="S36" s="3">
+      <c r="X36" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -6899,27 +7620,40 @@
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr"/>
-      <c r="N37" s="3">
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>NSF</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr"/>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>Manufacturing</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="3">
         <f>HYPERLINK("https://www.cindyxjli.com/", "https://www.cindyxjli.com/")</f>
         <v/>
       </c>
-      <c r="O37" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
+      <c r="T37" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
         <is>
           <t>tGQzHJIAAAAJ</t>
         </is>
       </c>
-      <c r="Q37" s="3">
+      <c r="V37" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/xiangji5", "https://search.asu.edu/profile/xiangji5")</f>
         <v/>
       </c>
-      <c r="R37" s="3">
+      <c r="W37" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=tGQzHJIAAAAJ", "Scholar (tGQzHJIAAAAJ)")</f>
         <v/>
       </c>
-      <c r="S37" s="3">
+      <c r="X37" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -6974,25 +7708,30 @@
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr"/>
-      <c r="M38" s="2" t="inlineStr">
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr"/>
+      <c r="P38" s="2" t="inlineStr"/>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr">
         <is>
           <t>ENGRC 381 (TEMPE, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="N38" s="2" t="inlineStr"/>
-      <c r="O38" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P38" s="2" t="inlineStr"/>
-      <c r="Q38" s="3">
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/jimbo", "https://search.asu.edu/profile/jimbo")</f>
         <v/>
       </c>
-      <c r="R38" s="3">
+      <c r="W38" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=James%20Middleton%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="S38" s="3">
+      <c r="X38" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -7043,25 +7782,30 @@
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr"/>
-      <c r="M39" s="2" t="inlineStr">
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr"/>
+      <c r="P39" s="2" t="inlineStr"/>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="N39" s="2" t="inlineStr"/>
-      <c r="O39" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P39" s="2" t="inlineStr"/>
-      <c r="Q39" s="3">
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/linli25", "https://search.asu.edu/profile/linli25")</f>
         <v/>
       </c>
-      <c r="R39" s="3">
+      <c r="W39" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Lin%20Li%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="S39" s="3">
+      <c r="X39" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -7112,25 +7856,30 @@
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr"/>
-      <c r="M40" s="2" t="inlineStr">
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr"/>
+      <c r="P40" s="2" t="inlineStr"/>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr">
         <is>
           <t>ENGRC 411 (TEMPE, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="N40" s="2" t="inlineStr"/>
-      <c r="O40" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P40" s="2" t="inlineStr"/>
-      <c r="Q40" s="3">
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/marc03", "https://search.asu.edu/profile/marc03")</f>
         <v/>
       </c>
-      <c r="R40" s="3">
+      <c r="W40" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Marc%20Mignolet%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="S40" s="3">
+      <c r="X40" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -7182,23 +7931,32 @@
       </c>
       <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr"/>
-      <c r="N41" s="3">
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr"/>
+      <c r="P41" s="2" t="inlineStr"/>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>ENGRC 352 (TEMPE, AZ 85287-6106)</t>
+        </is>
+      </c>
+      <c r="S41" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/pperalta/", "https://faculty.engineering.asu.edu/pperalta/")</f>
         <v/>
       </c>
-      <c r="O41" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P41" s="2" t="inlineStr"/>
-      <c r="Q41" s="3">
+      <c r="T41" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/pperalta", "https://search.asu.edu/profile/pperalta")</f>
         <v/>
       </c>
-      <c r="R41" s="3">
+      <c r="W41" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Pedro%20Peralta%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="S41" s="3">
+      <c r="X41" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -7259,30 +8017,47 @@
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr">
         <is>
+          <t>Welcome and we are looking forward to working with Dr</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>NSF, ONR</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr"/>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>Highlighted as a cover in Small</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="N42" s="3">
+      <c r="S42" s="3">
         <f>HYPERLINK("https://wonmokang3.wixsite.com/website", "https://wonmokang3.wixsite.com/website")</f>
         <v/>
       </c>
-      <c r="O42" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
+      <c r="T42" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
         <is>
           <t>bHyyOTAAAAAJ</t>
         </is>
       </c>
-      <c r="Q42" s="3">
+      <c r="V42" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/wkang16", "https://search.asu.edu/profile/wkang16")</f>
         <v/>
       </c>
-      <c r="R42" s="3">
+      <c r="W42" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=bHyyOTAAAAAJ", "Scholar (bHyyOTAAAAAJ)")</f>
         <v/>
       </c>
-      <c r="S42" s="3">
+      <c r="X42" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -7335,19 +8110,28 @@
       <c r="L43" s="2" t="inlineStr"/>
       <c r="M43" s="2" t="inlineStr"/>
       <c r="N43" s="2" t="inlineStr"/>
-      <c r="O43" s="2" t="b">
-        <v>1</v>
-      </c>
+      <c r="O43" s="2" t="inlineStr"/>
       <c r="P43" s="2" t="inlineStr"/>
-      <c r="Q43" s="3">
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>GWC 464 (Tempe, AZ 85287-6106)</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/yren32", "https://search.asu.edu/profile/yren32")</f>
         <v/>
       </c>
-      <c r="R43" s="3">
+      <c r="W43" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Yi%20Ren%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="S43" s="3">
+      <c r="X43" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -7388,19 +8172,24 @@
       <c r="L44" s="2" t="inlineStr"/>
       <c r="M44" s="2" t="inlineStr"/>
       <c r="N44" s="2" t="inlineStr"/>
-      <c r="O44" s="2" t="b">
+      <c r="O44" s="2" t="inlineStr"/>
+      <c r="P44" s="2" t="inlineStr"/>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="P44" s="2" t="inlineStr"/>
-      <c r="Q44" s="3">
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/dspeaks2", "https://search.asu.edu/profile/dspeaks2")</f>
         <v/>
       </c>
-      <c r="R44" s="3">
+      <c r="W44" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Derrick%20Speaks%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="S44" s="3">
+      <c r="X44" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -7443,25 +8232,26 @@
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr"/>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>Campus: Otherus</t>
-        </is>
-      </c>
+      <c r="M45" s="2" t="inlineStr"/>
       <c r="N45" s="2" t="inlineStr"/>
-      <c r="O45" s="2" t="b">
+      <c r="O45" s="2" t="inlineStr"/>
+      <c r="P45" s="2" t="inlineStr"/>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="P45" s="2" t="inlineStr"/>
-      <c r="Q45" s="3">
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/ejande22", "https://search.asu.edu/profile/ejande22")</f>
         <v/>
       </c>
-      <c r="R45" s="3">
+      <c r="W45" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Erik%20Andersen%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="S45" s="3">
+      <c r="X45" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -7502,19 +8292,28 @@
       <c r="L46" s="2" t="inlineStr"/>
       <c r="M46" s="2" t="inlineStr"/>
       <c r="N46" s="2" t="inlineStr"/>
-      <c r="O46" s="2" t="b">
+      <c r="O46" s="2" t="inlineStr"/>
+      <c r="P46" s="2" t="inlineStr"/>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>Campus: Tempe</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="P46" s="2" t="inlineStr"/>
-      <c r="Q46" s="3">
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/iychang", "https://search.asu.edu/profile/iychang")</f>
         <v/>
       </c>
-      <c r="R46" s="3">
+      <c r="W46" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ivy%20Chang%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="S46" s="3">
+      <c r="X46" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -7555,19 +8354,24 @@
       <c r="L47" s="2" t="inlineStr"/>
       <c r="M47" s="2" t="inlineStr"/>
       <c r="N47" s="2" t="inlineStr"/>
-      <c r="O47" s="2" t="b">
+      <c r="O47" s="2" t="inlineStr"/>
+      <c r="P47" s="2" t="inlineStr"/>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="P47" s="2" t="inlineStr"/>
-      <c r="Q47" s="3">
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/jdwilbu1", "https://search.asu.edu/profile/jdwilbu1")</f>
         <v/>
       </c>
-      <c r="R47" s="3">
+      <c r="W47" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Joshua%20Wilbur%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="S47" s="3">
+      <c r="X47" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -7608,19 +8412,24 @@
       <c r="L48" s="2" t="inlineStr"/>
       <c r="M48" s="2" t="inlineStr"/>
       <c r="N48" s="2" t="inlineStr"/>
-      <c r="O48" s="2" t="b">
+      <c r="O48" s="2" t="inlineStr"/>
+      <c r="P48" s="2" t="inlineStr"/>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="P48" s="2" t="inlineStr"/>
-      <c r="Q48" s="3">
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/rcruzloz", "https://search.asu.edu/profile/rcruzloz")</f>
         <v/>
       </c>
-      <c r="R48" s="3">
+      <c r="W48" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ricardo%20Cruz%20Lozano%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="S48" s="3">
+      <c r="X48" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -7659,25 +8468,26 @@
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr"/>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>Campus: Tempe</t>
-        </is>
-      </c>
+      <c r="M49" s="2" t="inlineStr"/>
       <c r="N49" s="2" t="inlineStr"/>
-      <c r="O49" s="2" t="b">
+      <c r="O49" s="2" t="inlineStr"/>
+      <c r="P49" s="2" t="inlineStr"/>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="P49" s="2" t="inlineStr"/>
-      <c r="Q49" s="3">
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/skosara2", "https://search.asu.edu/profile/skosara2")</f>
         <v/>
       </c>
-      <c r="R49" s="3">
+      <c r="W49" s="3">
         <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Srinivas%20Chakravarthi%20Kosaraju%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
-      <c r="S49" s="3">
+      <c r="X49" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -7685,223 +8495,223 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R2" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S2" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W2" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X2" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R3" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S3" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S3" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V3" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W3" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X3" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q4" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R4" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S4" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S4" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V4" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W4" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X4" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q5" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R5" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S5" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S5" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V5" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W5" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X5" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q6" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R6" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S6" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V6" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W6" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X6" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R7" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S7" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V7" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W7" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X7" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N8" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R8" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S8" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S8" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V8" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W8" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X8" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R9" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V9" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W9" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X9" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R10" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S10" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S10" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V10" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W10" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X10" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R11" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S11" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V11" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W11" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X11" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N12" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R12" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S12" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S12" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V12" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W12" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X12" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R13" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S13" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S13" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V13" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W13" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X13" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R14" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S14" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V14" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W14" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X14" r:id="rId61"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R15" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S15" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S15" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V15" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W15" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X15" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R16" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S16" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S16" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V16" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W16" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X16" r:id="rId71"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q17" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R17" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S17" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S17" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V17" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W17" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X17" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q18" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R18" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S18" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V18" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W18" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X18" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q19" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R19" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S19" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V19" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W19" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X19" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q20" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R20" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S20" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V20" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W20" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X20" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q21" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R21" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S21" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V21" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W21" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X21" r:id="rId92"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q22" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R22" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S22" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S22" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V22" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W22" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X22" r:id="rId97"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q23" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R23" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S23" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S23" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V23" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W23" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X23" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q24" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R24" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S24" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S24" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V24" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W24" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X24" r:id="rId107"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q25" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R25" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S25" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S25" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V25" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W25" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X25" r:id="rId112"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q26" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R26" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S26" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V26" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W26" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X26" r:id="rId116"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q27" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R27" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S27" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S27" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V27" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W27" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X27" r:id="rId121"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q28" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R28" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S28" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V28" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W28" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X28" r:id="rId125"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q29" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R29" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S29" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S29" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V29" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W29" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X29" r:id="rId130"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q30" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R30" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S30" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S30" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V30" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W30" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X30" r:id="rId135"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q31" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R31" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S31" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S31" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V31" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W31" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X31" r:id="rId140"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q32" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R32" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S32" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V32" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W32" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X32" r:id="rId144"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N33" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q33" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R33" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S33" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S33" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V33" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W33" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X33" r:id="rId149"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N34" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q34" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R34" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S34" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S34" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V34" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W34" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X34" r:id="rId154"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N35" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q35" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R35" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S35" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S35" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V35" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W35" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X35" r:id="rId159"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q36" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R36" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S36" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V36" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W36" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X36" r:id="rId163"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N37" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q37" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R37" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S37" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S37" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V37" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W37" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X37" r:id="rId168"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q38" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R38" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S38" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V38" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W38" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X38" r:id="rId172"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q39" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R39" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S39" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V39" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W39" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X39" r:id="rId176"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q40" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R40" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S40" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V40" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W40" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X40" r:id="rId180"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N41" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q41" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R41" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S41" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S41" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V41" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W41" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X41" r:id="rId185"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N42" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q42" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R42" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S42" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S42" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V42" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W42" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X42" r:id="rId190"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q43" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R43" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S43" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V43" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W43" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X43" r:id="rId194"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q44" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R44" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S44" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V44" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W44" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X44" r:id="rId198"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q45" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R45" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S45" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V45" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W45" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X45" r:id="rId202"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q46" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R46" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S46" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V46" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W46" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X46" r:id="rId206"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q47" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R47" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S47" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V47" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W47" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X47" r:id="rId210"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q48" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R48" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S48" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V48" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W48" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X48" r:id="rId214"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q49" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R49" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S49" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V49" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W49" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X49" r:id="rId218"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/universities_wise/arizona_state_university/asu_aerospace_mechanical_faculty.xlsx
+++ b/universities_wise/arizona_state_university/asu_aerospace_mechanical_faculty.xlsx
@@ -470,8 +470,8 @@
     <col width="49" customWidth="1" min="10" max="10"/>
     <col width="53" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="65" customWidth="1" min="13" max="13"/>
-    <col width="61" customWidth="1" min="14" max="14"/>
+    <col width="49" customWidth="1" min="13" max="13"/>
+    <col width="56" customWidth="1" min="14" max="14"/>
     <col width="65" customWidth="1" min="15" max="15"/>
     <col width="65" customWidth="1" min="16" max="16"/>
     <col width="65" customWidth="1" min="17" max="17"/>
@@ -479,7 +479,7 @@
     <col width="32" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
     <col width="49" customWidth="1" min="21" max="21"/>
-    <col width="46" customWidth="1" min="22" max="22"/>
+    <col width="54" customWidth="1" min="22" max="22"/>
     <col width="18" customWidth="1" min="23" max="23"/>
     <col width="49" customWidth="1" min="24" max="24"/>
   </cols>
@@ -659,10 +659,9 @@
           <t>AFOSR</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>https://bitbucket.org/krgasu/leap/downloads/leap-v0.8.2.tar.gz, https://bitbucket.org/krgasu/leap/src/master</t>
-        </is>
+      <c r="M2" s="3">
+        <f>HYPERLINK("https://bitbucket.org/krgasu/leap/downloads/leap-v0.8.2.tar.gz", "https://bitbucket.org/krgasu/leap/downloads/leap-v0.8.2.tar.gz, https://bitbucket.org/krgasu/leap/src/master")</f>
+        <v/>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
@@ -1055,11 +1054,7 @@
         <f>HYPERLINK("https://search.asu.edu/profile/asuchen", "https://search.asu.edu/profile/asuchen")</f>
         <v/>
       </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>ENGRC 361 (TEMPE, AZ 85287-6106)</t>
-        </is>
-      </c>
+      <c r="V6" s="2" t="inlineStr"/>
       <c r="W6" s="2" t="b">
         <v>1</v>
       </c>
@@ -1335,7 +1330,11 @@
         <f>HYPERLINK("https://search.asu.edu/profile/leixinma", "https://search.asu.edu/profile/leixinma")</f>
         <v/>
       </c>
-      <c r="V9" s="2" t="inlineStr"/>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>ERC 485 (Tempe, AZ 85287)</t>
+        </is>
+      </c>
       <c r="W9" s="2" t="b">
         <v>1</v>
       </c>
@@ -1591,11 +1590,7 @@
         <f>HYPERLINK("https://search.asu.edu/profile/smberma2", "https://search.asu.edu/profile/smberma2")</f>
         <v/>
       </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>ENGRC 375 (Tempe, AZ 85287-6106)</t>
-        </is>
-      </c>
+      <c r="V12" s="2" t="inlineStr"/>
       <c r="W12" s="2" t="b">
         <v>1</v>
       </c>
@@ -1890,11 +1885,7 @@
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>Thermal Energy &amp; Nanomaterials Lab</t>
-        </is>
-      </c>
+      <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>My research group is an interdisciplinary nanoengineering team that focuses on manipulating material properties for thermal energy applications. Some of our focus areas are thermoelectric power generation, thermal storage media, heat transfer, and phonon optics. To achieve our objectives, we custom-design materials using colloidal nanoparticles, chemical precursors, and nanocomposites.</t>
@@ -2005,23 +1996,15 @@
         </is>
       </c>
       <c r="S17" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=m-Pb6g2pm2UC", "Scholar (m-Pb6g2pm2UC)")</f>
-        <v/>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>m-Pb6g2pm2UC</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ryan%20Milcarek%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="T17" s="2" t="inlineStr"/>
       <c r="U17" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/rjmilcar", "https://search.asu.edu/profile/rjmilcar")</f>
         <v/>
       </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>ENGRC 465 (Tempe, AZ 85287)</t>
-        </is>
-      </c>
+      <c r="V17" s="2" t="inlineStr"/>
       <c r="W17" s="2" t="b">
         <v>1</v>
       </c>
@@ -2157,23 +2140,15 @@
         </is>
       </c>
       <c r="S19" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=OmBV67MAAAAJ", "Scholar (OmBV67MAAAAJ)")</f>
-        <v/>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>OmBV67MAAAAJ</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Tianyu%20Yang%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="T19" s="2" t="inlineStr"/>
       <c r="U19" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/tyang123", "https://search.asu.edu/profile/tyang123")</f>
         <v/>
       </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Campus: Tempe</t>
-        </is>
-      </c>
+      <c r="V19" s="2" t="inlineStr"/>
       <c r="W19" s="2" t="b">
         <v>1</v>
       </c>
@@ -2493,11 +2468,7 @@
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr"/>
       <c r="M23" s="2" t="inlineStr"/>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>Latest News</t>
-        </is>
-      </c>
+      <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
           <t>Bio-inspired robotics Soft robotics Magnetic micro-robotics Mechanics of animal locomotion</t>
@@ -2527,11 +2498,7 @@
         <f>HYPERLINK("https://search.asu.edu/profile/hmarvi", "https://search.asu.edu/profile/hmarvi")</f>
         <v/>
       </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Campus: Tempe</t>
-        </is>
-      </c>
+      <c r="V23" s="2" t="inlineStr"/>
       <c r="W23" s="2" t="b">
         <v>1</v>
       </c>
@@ -2661,17 +2628,9 @@
         <v/>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>NSF</t>
-        </is>
-      </c>
+      <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr"/>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>Advancing manufacturing innovation</t>
-        </is>
-      </c>
+      <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
           <t>Manufacturing process simulation and modeling and experiments Additive manufacturing Micro/nano manufacturing Microelectronic packaging Application of AI in manufacturing Mechanic of metallic materials Materials characterization Fatigue and damage modeling and simulation</t>
@@ -2701,7 +2660,11 @@
         <f>HYPERLINK("https://search.asu.edu/profile/ljannesa", "https://search.asu.edu/profile/ljannesa")</f>
         <v/>
       </c>
-      <c r="V25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>ISTB4, ROOM 379 781 S Terrace Rd (Tempe, AZ 85287)</t>
+        </is>
+      </c>
       <c r="W25" s="2" t="b">
         <v>1</v>
       </c>
@@ -2864,7 +2827,11 @@
         <f>HYPERLINK("https://search.asu.edu/profile/ypeet", "https://search.asu.edu/profile/ypeet")</f>
         <v/>
       </c>
-      <c r="V27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>ENGRC 379 (Tempe, AZ 85287-6106)</t>
+        </is>
+      </c>
       <c r="W27" s="2" t="b">
         <v>1</v>
       </c>
@@ -3344,17 +3311,9 @@
         <v/>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>NSF</t>
-        </is>
-      </c>
+      <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr"/>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>Multi-scale Manufacturing Material Processing Lab (MMMPL)</t>
-        </is>
-      </c>
+      <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
           <t>Nanomanufacturing, additive manufacturing, laser-based material processing, laser matter interaction and physics simulation; inkjet printing of functional materials; and 2D materials fabrication for energy storage and bio-sensors.</t>
@@ -3441,17 +3400,9 @@
         <v/>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>DOE, NASA</t>
-        </is>
-      </c>
+      <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr"/>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>Environmental Remote SensingGroup</t>
-        </is>
-      </c>
+      <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr"/>
       <c r="P34" s="2" t="inlineStr"/>
       <c r="Q34" s="2" t="inlineStr">
@@ -3535,10 +3486,9 @@
           <t>NSF</t>
         </is>
       </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/asu-iris</t>
-        </is>
+      <c r="M35" s="3">
+        <f>HYPERLINK("https://github.com/asu-iris", "https://github.com/asu-iris")</f>
+        <v/>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
@@ -3574,7 +3524,11 @@
         <f>HYPERLINK("https://search.asu.edu/profile/wjin34", "https://search.asu.edu/profile/wjin34")</f>
         <v/>
       </c>
-      <c r="V35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>Campus: Tempe</t>
+        </is>
+      </c>
       <c r="W35" s="2" t="b">
         <v>1</v>
       </c>
@@ -3753,7 +3707,11 @@
         <f>HYPERLINK("https://search.asu.edu/profile/xiangji5", "https://search.asu.edu/profile/xiangji5")</f>
         <v/>
       </c>
-      <c r="V37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>ERC457 551 E Tyler Mall (Tempe, AZ 85281)</t>
+        </is>
+      </c>
       <c r="W37" s="2" t="b">
         <v>1</v>
       </c>
@@ -3827,11 +3785,7 @@
         <f>HYPERLINK("https://search.asu.edu/profile/jimbo", "https://search.asu.edu/profile/jimbo")</f>
         <v/>
       </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t>ENGRC 381 (TEMPE, AZ 85287-6106)</t>
-        </is>
-      </c>
+      <c r="V38" s="2" t="inlineStr"/>
       <c r="W38" s="2" t="b">
         <v>1</v>
       </c>
@@ -3975,11 +3929,7 @@
         <f>HYPERLINK("https://search.asu.edu/profile/marc03", "https://search.asu.edu/profile/marc03")</f>
         <v/>
       </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>ENGRC 411 (TEMPE, AZ 85287-6106)</t>
-        </is>
-      </c>
+      <c r="V40" s="2" t="inlineStr"/>
       <c r="W40" s="2" t="b">
         <v>1</v>
       </c>
@@ -4240,198 +4190,200 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S2" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U2" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X2" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S3" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U3" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X3" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S4" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U4" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X4" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S5" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U5" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X5" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S6" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U6" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X6" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S7" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U7" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X7" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S8" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U8" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X8" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U9" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X9" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S10" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U10" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X10" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S11" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U11" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X11" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S12" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U12" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X12" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S13" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U13" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X13" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S14" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U14" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X14" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S15" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U15" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X15" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S16" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U16" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X16" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S17" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U17" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X17" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S18" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U18" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X18" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S19" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U19" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X19" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S20" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U20" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X20" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S21" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U21" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X21" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S22" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U22" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X22" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S23" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U23" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X23" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S24" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U24" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X24" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S25" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U25" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X25" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S26" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U26" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X26" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S27" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U27" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X27" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S28" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U28" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X28" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S29" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U29" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X29" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S30" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U30" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X30" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S31" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U31" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X31" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S32" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U32" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X32" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S33" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U33" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X33" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S34" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U34" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X34" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S35" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U35" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X35" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S36" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U36" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X36" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S37" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U37" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X37" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S38" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U38" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X38" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S39" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U39" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X39" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S40" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U40" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X40" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S41" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U41" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X41" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S42" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U42" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X42" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S43" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U43" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X43" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S2" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U2" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X2" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S3" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U3" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X3" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S4" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U4" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X4" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S5" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U5" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X5" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S6" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U6" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X6" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S7" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U7" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X7" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S8" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U8" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X8" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U9" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X9" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S10" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U10" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X10" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S11" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U11" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X11" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S12" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U12" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X12" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S13" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U13" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X13" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S14" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U14" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X14" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S15" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U15" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X15" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S16" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U16" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X16" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S17" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U17" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X17" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S18" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U18" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X18" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S19" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U19" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X19" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S20" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U20" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X20" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S21" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U21" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X21" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S22" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U22" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X22" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S23" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U23" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X23" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S24" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U24" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X24" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S25" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U25" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X25" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S26" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U26" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X26" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S27" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U27" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X27" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S28" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U28" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X28" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S29" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U29" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X29" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S30" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U30" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X30" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S31" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U31" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X31" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S32" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U32" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X32" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S33" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U33" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X33" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S34" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U34" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X34" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S35" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U35" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X35" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S36" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U36" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X36" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S37" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U37" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X37" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S38" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U38" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X38" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S39" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U39" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X39" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S40" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U40" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X40" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S41" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U41" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X41" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S42" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U42" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X42" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S43" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U43" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X43" r:id="rId196"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4458,8 +4410,8 @@
     <col width="49" customWidth="1" min="10" max="10"/>
     <col width="53" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="65" customWidth="1" min="13" max="13"/>
-    <col width="61" customWidth="1" min="14" max="14"/>
+    <col width="49" customWidth="1" min="13" max="13"/>
+    <col width="56" customWidth="1" min="14" max="14"/>
     <col width="65" customWidth="1" min="15" max="15"/>
     <col width="65" customWidth="1" min="16" max="16"/>
     <col width="65" customWidth="1" min="17" max="17"/>
@@ -4467,7 +4419,7 @@
     <col width="32" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
     <col width="49" customWidth="1" min="21" max="21"/>
-    <col width="46" customWidth="1" min="22" max="22"/>
+    <col width="54" customWidth="1" min="22" max="22"/>
     <col width="18" customWidth="1" min="23" max="23"/>
     <col width="49" customWidth="1" min="24" max="24"/>
   </cols>
@@ -4647,10 +4599,9 @@
           <t>AFOSR</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>https://bitbucket.org/krgasu/leap/downloads/leap-v0.8.2.tar.gz, https://bitbucket.org/krgasu/leap/src/master</t>
-        </is>
+      <c r="M2" s="3">
+        <f>HYPERLINK("https://bitbucket.org/krgasu/leap/downloads/leap-v0.8.2.tar.gz", "https://bitbucket.org/krgasu/leap/downloads/leap-v0.8.2.tar.gz, https://bitbucket.org/krgasu/leap/src/master")</f>
+        <v/>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
@@ -5043,11 +4994,7 @@
         <f>HYPERLINK("https://search.asu.edu/profile/asuchen", "https://search.asu.edu/profile/asuchen")</f>
         <v/>
       </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>ENGRC 361 (TEMPE, AZ 85287-6106)</t>
-        </is>
-      </c>
+      <c r="V6" s="2" t="inlineStr"/>
       <c r="W6" s="2" t="b">
         <v>1</v>
       </c>
@@ -5323,7 +5270,11 @@
         <f>HYPERLINK("https://search.asu.edu/profile/leixinma", "https://search.asu.edu/profile/leixinma")</f>
         <v/>
       </c>
-      <c r="V9" s="2" t="inlineStr"/>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>ERC 485 (Tempe, AZ 85287)</t>
+        </is>
+      </c>
       <c r="W9" s="2" t="b">
         <v>1</v>
       </c>
@@ -5579,11 +5530,7 @@
         <f>HYPERLINK("https://search.asu.edu/profile/smberma2", "https://search.asu.edu/profile/smberma2")</f>
         <v/>
       </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>ENGRC 375 (Tempe, AZ 85287-6106)</t>
-        </is>
-      </c>
+      <c r="V12" s="2" t="inlineStr"/>
       <c r="W12" s="2" t="b">
         <v>1</v>
       </c>
@@ -5878,11 +5825,7 @@
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>Thermal Energy &amp; Nanomaterials Lab</t>
-        </is>
-      </c>
+      <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>My research group is an interdisciplinary nanoengineering team that focuses on manipulating material properties for thermal energy applications. Some of our focus areas are thermoelectric power generation, thermal storage media, heat transfer, and phonon optics. To achieve our objectives, we custom-design materials using colloidal nanoparticles, chemical precursors, and nanocomposites.</t>
@@ -5993,23 +5936,15 @@
         </is>
       </c>
       <c r="S17" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=m-Pb6g2pm2UC", "Scholar (m-Pb6g2pm2UC)")</f>
-        <v/>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>m-Pb6g2pm2UC</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Ryan%20Milcarek%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="T17" s="2" t="inlineStr"/>
       <c r="U17" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/rjmilcar", "https://search.asu.edu/profile/rjmilcar")</f>
         <v/>
       </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>ENGRC 465 (Tempe, AZ 85287)</t>
-        </is>
-      </c>
+      <c r="V17" s="2" t="inlineStr"/>
       <c r="W17" s="2" t="b">
         <v>1</v>
       </c>
@@ -6145,23 +6080,15 @@
         </is>
       </c>
       <c r="S19" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=OmBV67MAAAAJ", "Scholar (OmBV67MAAAAJ)")</f>
-        <v/>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>OmBV67MAAAAJ</t>
-        </is>
-      </c>
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Tianyu%20Yang%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <v/>
+      </c>
+      <c r="T19" s="2" t="inlineStr"/>
       <c r="U19" s="3">
         <f>HYPERLINK("https://search.asu.edu/profile/tyang123", "https://search.asu.edu/profile/tyang123")</f>
         <v/>
       </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Campus: Tempe</t>
-        </is>
-      </c>
+      <c r="V19" s="2" t="inlineStr"/>
       <c r="W19" s="2" t="b">
         <v>1</v>
       </c>
@@ -6481,11 +6408,7 @@
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr"/>
       <c r="M23" s="2" t="inlineStr"/>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>Latest News</t>
-        </is>
-      </c>
+      <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
           <t>Bio-inspired robotics Soft robotics Magnetic micro-robotics Mechanics of animal locomotion</t>
@@ -6515,11 +6438,7 @@
         <f>HYPERLINK("https://search.asu.edu/profile/hmarvi", "https://search.asu.edu/profile/hmarvi")</f>
         <v/>
       </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Campus: Tempe</t>
-        </is>
-      </c>
+      <c r="V23" s="2" t="inlineStr"/>
       <c r="W23" s="2" t="b">
         <v>1</v>
       </c>
@@ -6649,17 +6568,9 @@
         <v/>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>NSF</t>
-        </is>
-      </c>
+      <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr"/>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>Advancing manufacturing innovation</t>
-        </is>
-      </c>
+      <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
           <t>Manufacturing process simulation and modeling and experiments Additive manufacturing Micro/nano manufacturing Microelectronic packaging Application of AI in manufacturing Mechanic of metallic materials Materials characterization Fatigue and damage modeling and simulation</t>
@@ -6689,7 +6600,11 @@
         <f>HYPERLINK("https://search.asu.edu/profile/ljannesa", "https://search.asu.edu/profile/ljannesa")</f>
         <v/>
       </c>
-      <c r="V25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>ISTB4, ROOM 379 781 S Terrace Rd (Tempe, AZ 85287)</t>
+        </is>
+      </c>
       <c r="W25" s="2" t="b">
         <v>1</v>
       </c>
@@ -6852,7 +6767,11 @@
         <f>HYPERLINK("https://search.asu.edu/profile/ypeet", "https://search.asu.edu/profile/ypeet")</f>
         <v/>
       </c>
-      <c r="V27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>ENGRC 379 (Tempe, AZ 85287-6106)</t>
+        </is>
+      </c>
       <c r="W27" s="2" t="b">
         <v>1</v>
       </c>
@@ -7332,17 +7251,9 @@
         <v/>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>NSF</t>
-        </is>
-      </c>
+      <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr"/>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>Multi-scale Manufacturing Material Processing Lab (MMMPL)</t>
-        </is>
-      </c>
+      <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
           <t>Nanomanufacturing, additive manufacturing, laser-based material processing, laser matter interaction and physics simulation; inkjet printing of functional materials; and 2D materials fabrication for energy storage and bio-sensors.</t>
@@ -7429,17 +7340,9 @@
         <v/>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>DOE, NASA</t>
-        </is>
-      </c>
+      <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr"/>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>Environmental Remote SensingGroup</t>
-        </is>
-      </c>
+      <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr"/>
       <c r="P34" s="2" t="inlineStr"/>
       <c r="Q34" s="2" t="inlineStr">
@@ -7523,10 +7426,9 @@
           <t>NSF</t>
         </is>
       </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/asu-iris</t>
-        </is>
+      <c r="M35" s="3">
+        <f>HYPERLINK("https://github.com/asu-iris", "https://github.com/asu-iris")</f>
+        <v/>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
@@ -7562,7 +7464,11 @@
         <f>HYPERLINK("https://search.asu.edu/profile/wjin34", "https://search.asu.edu/profile/wjin34")</f>
         <v/>
       </c>
-      <c r="V35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>Campus: Tempe</t>
+        </is>
+      </c>
       <c r="W35" s="2" t="b">
         <v>1</v>
       </c>
@@ -7741,7 +7647,11 @@
         <f>HYPERLINK("https://search.asu.edu/profile/xiangji5", "https://search.asu.edu/profile/xiangji5")</f>
         <v/>
       </c>
-      <c r="V37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>ERC457 551 E Tyler Mall (Tempe, AZ 85281)</t>
+        </is>
+      </c>
       <c r="W37" s="2" t="b">
         <v>1</v>
       </c>
@@ -7815,11 +7725,7 @@
         <f>HYPERLINK("https://search.asu.edu/profile/jimbo", "https://search.asu.edu/profile/jimbo")</f>
         <v/>
       </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t>ENGRC 381 (TEMPE, AZ 85287-6106)</t>
-        </is>
-      </c>
+      <c r="V38" s="2" t="inlineStr"/>
       <c r="W38" s="2" t="b">
         <v>1</v>
       </c>
@@ -7963,11 +7869,7 @@
         <f>HYPERLINK("https://search.asu.edu/profile/marc03", "https://search.asu.edu/profile/marc03")</f>
         <v/>
       </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>ENGRC 411 (TEMPE, AZ 85287-6106)</t>
-        </is>
-      </c>
+      <c r="V40" s="2" t="inlineStr"/>
       <c r="W40" s="2" t="b">
         <v>1</v>
       </c>
@@ -8273,7 +8175,11 @@
         <f>HYPERLINK("https://search.asu.edu/profile/dspeaks2", "https://search.asu.edu/profile/dspeaks2")</f>
         <v/>
       </c>
-      <c r="V44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>Campus: Tempe</t>
+        </is>
+      </c>
       <c r="W44" s="2" t="b">
         <v>0</v>
       </c>
@@ -8513,7 +8419,11 @@
         <f>HYPERLINK("https://search.asu.edu/profile/rcruzloz", "https://search.asu.edu/profile/rcruzloz")</f>
         <v/>
       </c>
-      <c r="V48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>Campus: Tempe</t>
+        </is>
+      </c>
       <c r="W48" s="2" t="b">
         <v>0</v>
       </c>
@@ -8588,222 +8498,224 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S2" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U2" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X2" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S3" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U3" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X3" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S4" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U4" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X4" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S5" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U5" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X5" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S6" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U6" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X6" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S7" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U7" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X7" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S8" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U8" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X8" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U9" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X9" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S10" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U10" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X10" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S11" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U11" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X11" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S12" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U12" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X12" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S13" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U13" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X13" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S14" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U14" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X14" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S15" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U15" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X15" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S16" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U16" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X16" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S17" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U17" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X17" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S18" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U18" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X18" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S19" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U19" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X19" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S20" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U20" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X20" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S21" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U21" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X21" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S22" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U22" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X22" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S23" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U23" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X23" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S24" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U24" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X24" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S25" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U25" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X25" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S26" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U26" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X26" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S27" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U27" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X27" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S28" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U28" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X28" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S29" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U29" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X29" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S30" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U30" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X30" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S31" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U31" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X31" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S32" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U32" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X32" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S33" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U33" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X33" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S34" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U34" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X34" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S35" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U35" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X35" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S36" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U36" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X36" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S37" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U37" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X37" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S38" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U38" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X38" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S39" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U39" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X39" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S40" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U40" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X40" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S41" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U41" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X41" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S42" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U42" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X42" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S43" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U43" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X43" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S44" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U44" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X44" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S45" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U45" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X45" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C46" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S46" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U46" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X46" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S47" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U47" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X47" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S48" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U48" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X48" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S49" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U49" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X49" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S2" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U2" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X2" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S3" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U3" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X3" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S4" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U4" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X4" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S5" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U5" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X5" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S6" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U6" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X6" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S7" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U7" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X7" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S8" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U8" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X8" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U9" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X9" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S10" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U10" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X10" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S11" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U11" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X11" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S12" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U12" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X12" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S13" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U13" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X13" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S14" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U14" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X14" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S15" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U15" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X15" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S16" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U16" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X16" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S17" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U17" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X17" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S18" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U18" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X18" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S19" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U19" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X19" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S20" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U20" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X20" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S21" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U21" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X21" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S22" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U22" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X22" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S23" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U23" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X23" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S24" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U24" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X24" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S25" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U25" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X25" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S26" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U26" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X26" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S27" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U27" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X27" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S28" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U28" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X28" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S29" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U29" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X29" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S30" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U30" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X30" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S31" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U31" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X31" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S32" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U32" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X32" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S33" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U33" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X33" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S34" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U34" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X34" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S35" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U35" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X35" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S36" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U36" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X36" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S37" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U37" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X37" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S38" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U38" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X38" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S39" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U39" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X39" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S40" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U40" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X40" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S41" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U41" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X41" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S42" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U42" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X42" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S43" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U43" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X43" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S44" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U44" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X44" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S45" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U45" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X45" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C46" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S46" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U46" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X46" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S47" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U47" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X47" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S48" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U48" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X48" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S49" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U49" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X49" r:id="rId220"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/universities_wise/arizona_state_university/asu_aerospace_mechanical_faculty.xlsx
+++ b/universities_wise/arizona_state_university/asu_aerospace_mechanical_faculty.xlsx
@@ -483,7 +483,7 @@
     <col width="20" customWidth="1" min="23" max="23"/>
     <col width="49" customWidth="1" min="24" max="24"/>
     <col width="56" customWidth="1" min="25" max="25"/>
-    <col width="46" customWidth="1" min="26" max="26"/>
+    <col width="54" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
     <col width="49" customWidth="1" min="28" max="28"/>
   </cols>
@@ -672,8 +672,16 @@
           <t>aerospace, cfd, computational fluid dynamics, dns, fluid dynamics, fluid-structure interaction, multiphase flow, turbulent</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Refereed Journal Papers M. H. Kasbaoui and M. Herrmann, A high-fidelity methodology for particle-resolved direct numerical simu...</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>MAE 242: Intro to Fluid Mechanics | MAE 574: Multiphase Flow | MAE 501: Linear Algebra in Engineering</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="2" t="inlineStr"/>
@@ -717,7 +725,11 @@
           <t>School for Engineering of Matter, Transport &amp; Energy</t>
         </is>
       </c>
-      <c r="Z2" s="2" t="inlineStr"/>
+      <c r="Z2" s="2" t="inlineStr">
+        <is>
+          <t>Campus: Tempe</t>
+        </is>
+      </c>
       <c r="AA2" s="2" t="b">
         <v>1</v>
       </c>
@@ -768,7 +780,11 @@
           <t>aerospace, guidance, heat transfer, materials, metamaterials, radiation, thermal</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>One PhD position available for Fall 2024 on AFM based near-field thermal measurement! ($32k/year stipend + tuition + benefit)</t>
+        </is>
+      </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
           <t>MAE 584: Internship | MAE 593: Applied Project | MAE 241: Intro to Thermodynamics</t>
@@ -779,7 +795,11 @@
           <t>2017         AFOSR Young Investigator (YIP) Award,  ASU | 2016         JQSRT/Elsevier Viskanta Young Scientist Award,  ASU</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Please send your CV to Prof</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
           <t>Nanoscale heat transfer, metamaterials, plasmonics, and nanophotonics with an emphasis on solar thermal energy harvesting using plasmonic-enhanced light trapping for photovolatics, as well as near-field enhancement and spectral control of radiation for thermophotovoltaic energy conversion. Other research interests involve electronic cooling, MEMS, and bio-sensing.</t>
@@ -884,7 +904,11 @@
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>If you're interested in joining our group, please email</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>Development of computational mechanics: finite element methods, molecular dynamics, multiscale methods, failure analysis, and material design.</t>
@@ -910,7 +934,11 @@
         <f>HYPERLINK("http://sparky.fulton.asu.edu/oswald/", "http://sparky.fulton.asu.edu/oswald/")</f>
         <v/>
       </c>
-      <c r="U4" s="2" t="inlineStr"/>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>What we're looking for:</t>
+        </is>
+      </c>
       <c r="V4" s="2" t="inlineStr"/>
       <c r="W4" s="2" t="inlineStr"/>
       <c r="X4" s="2" t="inlineStr"/>
@@ -978,10 +1006,22 @@
           <t>aerospace, autonomous, materials, robot, robotics, smart materials</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>2026 Versatile artificial muscles by decoupling anisotropy Eric Weissman, Rohan Khatavkar, and Jiefeng Sun Proceedings of the N...</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>MAE 547: Modeling and Control of Robots | MAE 593: Applied Project | MAE 499: Individualized Instruction</t>
+        </is>
+      </c>
       <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Additionally, they should send an email titled “Prospective Ph</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>Hire students to conduct research https://sunroboticslab.github.io</t>
@@ -1024,7 +1064,11 @@
           <t>Mission and Core Values</t>
         </is>
       </c>
-      <c r="Z5" s="2" t="inlineStr"/>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>Campus: Tempe</t>
+        </is>
+      </c>
       <c r="AA5" s="2" t="b">
         <v>1</v>
       </c>
@@ -1247,7 +1291,11 @@
           <t>aerospace, autonomous, control theory, motion planning, robot, robotics</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Search this site Embedded Files Skip to main content Skip to navigation Kunal Garg Home People Teaching Research Publications K...</t>
+        </is>
+      </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
           <t>MAE 417: System Dynamics and Control II | MAE 593: Applied Project | MAE 598: Special Topics</t>
@@ -1360,10 +1408,22 @@
           <t>aerodynamics, aerospace, fluid-structure interaction, fluids, materials, robot</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>Search this site Embedded Files Skip to main content Skip to navigation OASIS group at ASU Home Research People Publications Ne...</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>MAE 499: Individualized Instruction | MAE 202: Mech.Particles/Rigid Bodies II | MAE 318: System Dynamics and Control I</t>
+        </is>
+      </c>
       <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>Potential candidates with strong backgrounds in fluid-structure interaction, soft robotics , machine learning can send their CV to leixinma@asu</t>
+        </is>
+      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
           <t>Aerodynamics, Dynamical Systems, Machine Learning, Mechanics of Composite Materials</t>
@@ -1406,7 +1466,11 @@
           <t>Ocean and Soft Intelligent Structure Interaction Lab</t>
         </is>
       </c>
-      <c r="Z9" s="2" t="inlineStr"/>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>ERC 485 (Tempe, AZ 85287)</t>
+        </is>
+      </c>
       <c r="AA9" s="2" t="b">
         <v>1</v>
       </c>
@@ -1653,7 +1717,11 @@
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>MAE 318: System Dynamics and Control I | MAE 598: Special Topics | MAE 593: Applied Project</t>
+        </is>
+      </c>
       <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2" t="inlineStr">
@@ -1690,7 +1758,11 @@
       <c r="W12" s="2" t="inlineStr"/>
       <c r="X12" s="2" t="inlineStr"/>
       <c r="Y12" s="2" t="inlineStr"/>
-      <c r="Z12" s="2" t="inlineStr"/>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>ENGRC 375 (Tempe, AZ 85287-6106)</t>
+        </is>
+      </c>
       <c r="AA12" s="2" t="b">
         <v>1</v>
       </c>
@@ -1778,7 +1850,11 @@
         <f>HYPERLINK("https://sites.google.com/site/zhexudavid00710/research?authuser=0", "https://sites.google.com/site/zhexudavid00710/research?authuser=0")</f>
         <v/>
       </c>
-      <c r="U13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>Actively recruiting / Openings mentioned on lab site</t>
+        </is>
+      </c>
       <c r="V13" s="2" t="inlineStr"/>
       <c r="W13" s="2" t="inlineStr"/>
       <c r="X13" s="2" t="inlineStr"/>
@@ -1839,7 +1915,11 @@
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>MAE 242: Intro to Fluid Mechanics | MAE 593: Applied Project | MAE 598: Special Topics</t>
+        </is>
+      </c>
       <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr"/>
@@ -1861,7 +1941,11 @@
       <c r="W14" s="2" t="inlineStr"/>
       <c r="X14" s="2" t="inlineStr"/>
       <c r="Y14" s="2" t="inlineStr"/>
-      <c r="Z14" s="2" t="inlineStr"/>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>Campus: Tempe</t>
+        </is>
+      </c>
       <c r="AA14" s="2" t="b">
         <v>1</v>
       </c>
@@ -2006,7 +2090,11 @@
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>MAE 241: Intro to Thermodynamics | MAE 593: Applied Project | MAE 588: Nanoscale Heat Transfer</t>
+        </is>
+      </c>
       <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
@@ -2039,7 +2127,11 @@
       <c r="W16" s="2" t="inlineStr"/>
       <c r="X16" s="2" t="inlineStr"/>
       <c r="Y16" s="2" t="inlineStr"/>
-      <c r="Z16" s="2" t="inlineStr"/>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>ENGRC 307 (Tempe, AZ 85287-6106)</t>
+        </is>
+      </c>
       <c r="AA16" s="2" t="b">
         <v>1</v>
       </c>
@@ -2255,7 +2347,7 @@
         <v/>
       </c>
       <c r="D19" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=OmBV67MAAAAJ", "Scholar (OmBV67MAAAAJ)")</f>
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Tianyu%20Yang%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2268,11 +2360,7 @@
           <t>Aerospace &amp; Mechanical Engineering</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>OmBV67MAAAAJ</t>
-        </is>
-      </c>
+      <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="3">
         <f>HYPERLINK("mailto:Tianyu.Yang@asu.edu", "Tianyu.Yang@asu.edu")</f>
         <v/>
@@ -2286,11 +2374,7 @@
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>MAE 241: Intro to Thermodynamics</t>
-        </is>
-      </c>
+      <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr"/>
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr"/>
@@ -2312,11 +2396,7 @@
       <c r="W19" s="2" t="inlineStr"/>
       <c r="X19" s="2" t="inlineStr"/>
       <c r="Y19" s="2" t="inlineStr"/>
-      <c r="Z19" s="2" t="inlineStr">
-        <is>
-          <t>Campus: Tempe</t>
-        </is>
-      </c>
+      <c r="Z19" s="2" t="inlineStr"/>
       <c r="AA19" s="2" t="b">
         <v>1</v>
       </c>
@@ -2372,7 +2452,11 @@
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>MAE 557: Mechanics Composite Materials | MAE 494: Special Topics | MAE 521: Structural Optimization</t>
+        </is>
+      </c>
       <c r="M20" s="2" t="inlineStr"/>
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr"/>
@@ -2398,7 +2482,11 @@
       <c r="W20" s="2" t="inlineStr"/>
       <c r="X20" s="2" t="inlineStr"/>
       <c r="Y20" s="2" t="inlineStr"/>
-      <c r="Z20" s="2" t="inlineStr"/>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>ENGRC 427 (TEMPE, AZ 85287-6106)</t>
+        </is>
+      </c>
       <c r="AA20" s="2" t="b">
         <v>1</v>
       </c>
@@ -2547,7 +2635,11 @@
           <t>aerospace, energy systems, heat transfer</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Journal Papers 62. N. Ohashi, J. Deng, L.K. Hwang, P.K. Kang, and B. Kwon, “Physics-Informed Machine Learning for Reconstructin...</t>
+        </is>
+      </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
           <t>MAE 593: Applied Project | MAE 241: Intro to Thermodynamics | MAE 598: Special Topics</t>
@@ -2580,7 +2672,11 @@
         <f>HYPERLINK("http://sites.google.com/view/3denergy", "http://sites.google.com/view/3denergy")</f>
         <v/>
       </c>
-      <c r="U22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>Actively recruiting / Openings mentioned on lab site</t>
+        </is>
+      </c>
       <c r="V22" s="2" t="inlineStr"/>
       <c r="W22" s="2" t="inlineStr">
         <is>
@@ -2652,8 +2748,16 @@
           <t>aerospace, robot, robotics</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr"/>
-      <c r="L23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>Shape-programmable magnetic soft matter,</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>MAE 417: System Dynamics and Control II | MAE 598: Special Topics | MAE 547: Modeling and Control of Robots</t>
+        </is>
+      </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
           <t>KEEN Professorship, The Kern Family Foundation, 2017. | Peebles Award for Graduate Student Research in Adhesion Science, Adhesion Society, 2015.</t>
@@ -2690,7 +2794,11 @@
       <c r="W23" s="2" t="inlineStr"/>
       <c r="X23" s="2" t="inlineStr"/>
       <c r="Y23" s="2" t="inlineStr"/>
-      <c r="Z23" s="2" t="inlineStr"/>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>Campus: Tempe</t>
+        </is>
+      </c>
       <c r="AA23" s="2" t="b">
         <v>1</v>
       </c>
@@ -2827,7 +2935,11 @@
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
-      <c r="L25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>MAE 598: Special Topics | MAE 494: Special Topics | MAE 201: Mech. Particles/Rigid Bodies I</t>
+        </is>
+      </c>
       <c r="M25" s="2" t="inlineStr"/>
       <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr">
@@ -2864,7 +2976,11 @@
       <c r="W25" s="2" t="inlineStr"/>
       <c r="X25" s="2" t="inlineStr"/>
       <c r="Y25" s="2" t="inlineStr"/>
-      <c r="Z25" s="2" t="inlineStr"/>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>ISTB4, ROOM 379 781 S Terrace Rd (Tempe, AZ 85287)</t>
+        </is>
+      </c>
       <c r="AA25" s="2" t="b">
         <v>1</v>
       </c>
@@ -3014,7 +3130,11 @@
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>MAE 215: Intro to Programming in MATLAB | MAE 591: Seminar | MAE 593: Applied Project</t>
+        </is>
+      </c>
       <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr"/>
@@ -3043,7 +3163,11 @@
       <c r="W27" s="2" t="inlineStr"/>
       <c r="X27" s="2" t="inlineStr"/>
       <c r="Y27" s="2" t="inlineStr"/>
-      <c r="Z27" s="2" t="inlineStr"/>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>ENGRC 379 (Tempe, AZ 85287-6106)</t>
+        </is>
+      </c>
       <c r="AA27" s="2" t="b">
         <v>1</v>
       </c>
@@ -3099,7 +3223,11 @@
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>MAE 551: Appl Machine Learn Mech Engr | MAE 451: Appl Machine Learn Mech Engr | MAE 202: Mech.Particles/Rigid Bodies II</t>
+        </is>
+      </c>
       <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
@@ -3133,7 +3261,11 @@
       <c r="W28" s="2" t="inlineStr"/>
       <c r="X28" s="2" t="inlineStr"/>
       <c r="Y28" s="2" t="inlineStr"/>
-      <c r="Z28" s="2" t="inlineStr"/>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>Campus: Tempe</t>
+        </is>
+      </c>
       <c r="AA28" s="2" t="b">
         <v>1</v>
       </c>
@@ -3185,7 +3317,11 @@
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>MAE 502: Partial Diff Equations Engr | MAE 460: Applied Comput Fluid Dynamics | MAE 593: Applied Project</t>
+        </is>
+      </c>
       <c r="M29" s="2" t="inlineStr"/>
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr"/>
@@ -3205,7 +3341,11 @@
         <f>HYPERLINK("http://www.public.asu.edu/~hhuang38", "http://www.public.asu.edu/~hhuang38")</f>
         <v/>
       </c>
-      <c r="U29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>Actively recruiting / Openings mentioned on lab site</t>
+        </is>
+      </c>
       <c r="V29" s="2" t="inlineStr"/>
       <c r="W29" s="2" t="inlineStr"/>
       <c r="X29" s="2" t="inlineStr"/>
@@ -3214,7 +3354,11 @@
           <t>Log in to www_public</t>
         </is>
       </c>
-      <c r="Z29" s="2" t="inlineStr"/>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>ENGRC 359 (Tempe, AZ 85287-6106)</t>
+        </is>
+      </c>
       <c r="AA29" s="2" t="b">
         <v>1</v>
       </c>
@@ -3411,11 +3555,7 @@
       <c r="V31" s="2" t="inlineStr"/>
       <c r="W31" s="2" t="inlineStr"/>
       <c r="X31" s="2" t="inlineStr"/>
-      <c r="Y31" s="2" t="inlineStr">
-        <is>
-          <t>Rykaczewski Lab</t>
-        </is>
-      </c>
+      <c r="Y31" s="2" t="inlineStr"/>
       <c r="Z31" s="2" t="inlineStr">
         <is>
           <t>ENGRC 309 (Tempe, AZ 85287)</t>
@@ -3747,10 +3887,22 @@
           <t>robot, robotics</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr"/>
-      <c r="L35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>Below are selected papers that represent our main research threads. Please visit Publications for the full list. Contact-rich i...</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>MAE 301: Applied Experimental Statistic | MAE 593: Applied Project | MAE 547: Modeling and Control of Robots</t>
+        </is>
+      </c>
       <c r="M35" s="2" t="inlineStr"/>
-      <c r="N35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>If you are interested, please email Dr</t>
+        </is>
+      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
           <t>https://irislab.tech/</t>
@@ -3776,7 +3928,11 @@
         <f>HYPERLINK("https://irislab.tech/", "https://irislab.tech/")</f>
         <v/>
       </c>
-      <c r="U35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>Looking for ASU Undergraduate and Master Students</t>
+        </is>
+      </c>
       <c r="V35" s="2" t="inlineStr"/>
       <c r="W35" s="2" t="inlineStr">
         <is>
@@ -3792,7 +3948,11 @@
           <t>Recent Updates</t>
         </is>
       </c>
-      <c r="Z35" s="2" t="inlineStr"/>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>Campus: Tempe</t>
+        </is>
+      </c>
       <c r="AA35" s="2" t="b">
         <v>1</v>
       </c>
@@ -3937,12 +4097,12 @@
           <t>materials</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr"/>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>MAE 301: Applied Experimental Statistic | MAE 593: Applied Project | MAE 494: Special Topics</t>
-        </is>
-      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>Dylan Joralmon~, Soham Khairnar, Xiangjia Li*, "Rapid Fabrication of Multi-Metal 3D Objects with Adjustable Gradients by Contin...</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
           <t>2026 The J. Orin Edson Entrepreneurship &amp; Innovation Seed Funding Award ASU 2025 1st place Skysong Startup Competition C</t>
@@ -3978,7 +4138,11 @@
         <f>HYPERLINK("https://www.cindyxjli.com/", "https://www.cindyxjli.com/")</f>
         <v/>
       </c>
-      <c r="U37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>Actively recruiting / Openings mentioned on lab site</t>
+        </is>
+      </c>
       <c r="V37" s="2" t="inlineStr"/>
       <c r="W37" s="2" t="inlineStr">
         <is>
@@ -3991,11 +4155,7 @@
           <t>Manufacturing</t>
         </is>
       </c>
-      <c r="Z37" s="2" t="inlineStr">
-        <is>
-          <t>ERC457 551 E Tyler Mall (Tempe, AZ 85281)</t>
-        </is>
-      </c>
+      <c r="Z37" s="2" t="inlineStr"/>
       <c r="AA37" s="2" t="b">
         <v>1</v>
       </c>
@@ -4046,16 +4206,8 @@
           <t>aerospace</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>Journal Articles Middleton, J. A. (in press). Archimedes, Euler, &amp; Nursing Cats: Rethinking the Arithmetic Mean. OnCore,</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>MAE 484: Internship | MAE 301: Applied Experimental Statistic | MAE 394: Special Topics</t>
-        </is>
-      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr"/>
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
@@ -4081,11 +4233,7 @@
       <c r="W38" s="2" t="inlineStr"/>
       <c r="X38" s="2" t="inlineStr"/>
       <c r="Y38" s="2" t="inlineStr"/>
-      <c r="Z38" s="2" t="inlineStr">
-        <is>
-          <t>ENGRC 381 (TEMPE, AZ 85287-6106)</t>
-        </is>
-      </c>
+      <c r="Z38" s="2" t="inlineStr"/>
       <c r="AA38" s="2" t="b">
         <v>1</v>
       </c>
@@ -4219,11 +4367,7 @@
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>MAE 510: Dynamics and Vibrations | MAE 591: Seminar | MAE 394: Special Topics</t>
-        </is>
-      </c>
+      <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr"/>
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr"/>
@@ -4245,11 +4389,7 @@
       <c r="W40" s="2" t="inlineStr"/>
       <c r="X40" s="2" t="inlineStr"/>
       <c r="Y40" s="2" t="inlineStr"/>
-      <c r="Z40" s="2" t="inlineStr">
-        <is>
-          <t>ENGRC 411 (TEMPE, AZ 85287-6106)</t>
-        </is>
-      </c>
+      <c r="Z40" s="2" t="inlineStr"/>
       <c r="AA40" s="2" t="b">
         <v>1</v>
       </c>
@@ -4301,7 +4441,11 @@
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
-      <c r="L41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>MAE 213: Mechanics of Materials | MAE 593: Applied Project | MAE 520: Stress Analysis</t>
+        </is>
+      </c>
       <c r="M41" s="2" t="inlineStr"/>
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr"/>
@@ -4326,7 +4470,11 @@
       <c r="W41" s="2" t="inlineStr"/>
       <c r="X41" s="2" t="inlineStr"/>
       <c r="Y41" s="2" t="inlineStr"/>
-      <c r="Z41" s="2" t="inlineStr"/>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>ENGRC 352 (TEMPE, AZ 85287-6106)</t>
+        </is>
+      </c>
       <c r="AA41" s="2" t="b">
         <v>1</v>
       </c>
@@ -4381,7 +4529,11 @@
           <t>materials</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>top of page This website was built on Wix. Create yours today. Get Started Bio &amp; Nano Lab Home Dr. Kang Lab Members Publication...</t>
+        </is>
+      </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
           <t>MAE 598: Special Topics | MAE 494: Special Topics | MAE 202: Mech.Particles/Rigid Bodies II</t>
@@ -4491,7 +4643,11 @@
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr"/>
-      <c r="L43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>MAE 494: Special Topics | MAE 598: Special Topics | MAE 301: Applied Experimental Statistic</t>
+        </is>
+      </c>
       <c r="M43" s="2" t="inlineStr"/>
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr"/>
@@ -4513,7 +4669,11 @@
       <c r="W43" s="2" t="inlineStr"/>
       <c r="X43" s="2" t="inlineStr"/>
       <c r="Y43" s="2" t="inlineStr"/>
-      <c r="Z43" s="2" t="inlineStr"/>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>GWC 464 (Tempe, AZ 85287-6106)</t>
+        </is>
+      </c>
       <c r="AA43" s="2" t="b">
         <v>1</v>
       </c>
@@ -4759,7 +4919,7 @@
     <col width="20" customWidth="1" min="23" max="23"/>
     <col width="49" customWidth="1" min="24" max="24"/>
     <col width="56" customWidth="1" min="25" max="25"/>
-    <col width="46" customWidth="1" min="26" max="26"/>
+    <col width="54" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
     <col width="49" customWidth="1" min="28" max="28"/>
   </cols>
@@ -4948,8 +5108,16 @@
           <t>aerospace, cfd, computational fluid dynamics, dns, fluid dynamics, fluid-structure interaction, multiphase flow, turbulent</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Refereed Journal Papers M. H. Kasbaoui and M. Herrmann, A high-fidelity methodology for particle-resolved direct numerical simu...</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>MAE 242: Intro to Fluid Mechanics | MAE 574: Multiphase Flow | MAE 501: Linear Algebra in Engineering</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="2" t="inlineStr"/>
@@ -4993,7 +5161,11 @@
           <t>School for Engineering of Matter, Transport &amp; Energy</t>
         </is>
       </c>
-      <c r="Z2" s="2" t="inlineStr"/>
+      <c r="Z2" s="2" t="inlineStr">
+        <is>
+          <t>Campus: Tempe</t>
+        </is>
+      </c>
       <c r="AA2" s="2" t="b">
         <v>1</v>
       </c>
@@ -5044,7 +5216,11 @@
           <t>aerospace, guidance, heat transfer, materials, metamaterials, radiation, thermal</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>One PhD position available for Fall 2024 on AFM based near-field thermal measurement! ($32k/year stipend + tuition + benefit)</t>
+        </is>
+      </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
           <t>MAE 584: Internship | MAE 593: Applied Project | MAE 241: Intro to Thermodynamics</t>
@@ -5055,7 +5231,11 @@
           <t>2017         AFOSR Young Investigator (YIP) Award,  ASU | 2016         JQSRT/Elsevier Viskanta Young Scientist Award,  ASU</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Please send your CV to Prof</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
           <t>Nanoscale heat transfer, metamaterials, plasmonics, and nanophotonics with an emphasis on solar thermal energy harvesting using plasmonic-enhanced light trapping for photovolatics, as well as near-field enhancement and spectral control of radiation for thermophotovoltaic energy conversion. Other research interests involve electronic cooling, MEMS, and bio-sensing.</t>
@@ -5160,7 +5340,11 @@
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>If you're interested in joining our group, please email</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>Development of computational mechanics: finite element methods, molecular dynamics, multiscale methods, failure analysis, and material design.</t>
@@ -5186,7 +5370,11 @@
         <f>HYPERLINK("http://sparky.fulton.asu.edu/oswald/", "http://sparky.fulton.asu.edu/oswald/")</f>
         <v/>
       </c>
-      <c r="U4" s="2" t="inlineStr"/>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>What we're looking for:</t>
+        </is>
+      </c>
       <c r="V4" s="2" t="inlineStr"/>
       <c r="W4" s="2" t="inlineStr"/>
       <c r="X4" s="2" t="inlineStr"/>
@@ -5254,10 +5442,22 @@
           <t>aerospace, autonomous, materials, robot, robotics, smart materials</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>2026 Versatile artificial muscles by decoupling anisotropy Eric Weissman, Rohan Khatavkar, and Jiefeng Sun Proceedings of the N...</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>MAE 547: Modeling and Control of Robots | MAE 593: Applied Project | MAE 499: Individualized Instruction</t>
+        </is>
+      </c>
       <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Additionally, they should send an email titled “Prospective Ph</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>Hire students to conduct research https://sunroboticslab.github.io</t>
@@ -5300,7 +5500,11 @@
           <t>Mission and Core Values</t>
         </is>
       </c>
-      <c r="Z5" s="2" t="inlineStr"/>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>Campus: Tempe</t>
+        </is>
+      </c>
       <c r="AA5" s="2" t="b">
         <v>1</v>
       </c>
@@ -5523,7 +5727,11 @@
           <t>aerospace, autonomous, control theory, motion planning, robot, robotics</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Search this site Embedded Files Skip to main content Skip to navigation Kunal Garg Home People Teaching Research Publications K...</t>
+        </is>
+      </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
           <t>MAE 417: System Dynamics and Control II | MAE 593: Applied Project | MAE 598: Special Topics</t>
@@ -5636,10 +5844,22 @@
           <t>aerodynamics, aerospace, fluid-structure interaction, fluids, materials, robot</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>Search this site Embedded Files Skip to main content Skip to navigation OASIS group at ASU Home Research People Publications Ne...</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>MAE 499: Individualized Instruction | MAE 202: Mech.Particles/Rigid Bodies II | MAE 318: System Dynamics and Control I</t>
+        </is>
+      </c>
       <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>Potential candidates with strong backgrounds in fluid-structure interaction, soft robotics , machine learning can send their CV to leixinma@asu</t>
+        </is>
+      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
           <t>Aerodynamics, Dynamical Systems, Machine Learning, Mechanics of Composite Materials</t>
@@ -5682,7 +5902,11 @@
           <t>Ocean and Soft Intelligent Structure Interaction Lab</t>
         </is>
       </c>
-      <c r="Z9" s="2" t="inlineStr"/>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>ERC 485 (Tempe, AZ 85287)</t>
+        </is>
+      </c>
       <c r="AA9" s="2" t="b">
         <v>1</v>
       </c>
@@ -5929,7 +6153,11 @@
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>MAE 318: System Dynamics and Control I | MAE 598: Special Topics | MAE 593: Applied Project</t>
+        </is>
+      </c>
       <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2" t="inlineStr">
@@ -5966,7 +6194,11 @@
       <c r="W12" s="2" t="inlineStr"/>
       <c r="X12" s="2" t="inlineStr"/>
       <c r="Y12" s="2" t="inlineStr"/>
-      <c r="Z12" s="2" t="inlineStr"/>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>ENGRC 375 (Tempe, AZ 85287-6106)</t>
+        </is>
+      </c>
       <c r="AA12" s="2" t="b">
         <v>1</v>
       </c>
@@ -6054,7 +6286,11 @@
         <f>HYPERLINK("https://sites.google.com/site/zhexudavid00710/research?authuser=0", "https://sites.google.com/site/zhexudavid00710/research?authuser=0")</f>
         <v/>
       </c>
-      <c r="U13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>Actively recruiting / Openings mentioned on lab site</t>
+        </is>
+      </c>
       <c r="V13" s="2" t="inlineStr"/>
       <c r="W13" s="2" t="inlineStr"/>
       <c r="X13" s="2" t="inlineStr"/>
@@ -6115,7 +6351,11 @@
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>MAE 242: Intro to Fluid Mechanics | MAE 593: Applied Project | MAE 598: Special Topics</t>
+        </is>
+      </c>
       <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr"/>
@@ -6137,7 +6377,11 @@
       <c r="W14" s="2" t="inlineStr"/>
       <c r="X14" s="2" t="inlineStr"/>
       <c r="Y14" s="2" t="inlineStr"/>
-      <c r="Z14" s="2" t="inlineStr"/>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>Campus: Tempe</t>
+        </is>
+      </c>
       <c r="AA14" s="2" t="b">
         <v>1</v>
       </c>
@@ -6282,7 +6526,11 @@
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>MAE 241: Intro to Thermodynamics | MAE 593: Applied Project | MAE 588: Nanoscale Heat Transfer</t>
+        </is>
+      </c>
       <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
@@ -6315,7 +6563,11 @@
       <c r="W16" s="2" t="inlineStr"/>
       <c r="X16" s="2" t="inlineStr"/>
       <c r="Y16" s="2" t="inlineStr"/>
-      <c r="Z16" s="2" t="inlineStr"/>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>ENGRC 307 (Tempe, AZ 85287-6106)</t>
+        </is>
+      </c>
       <c r="AA16" s="2" t="b">
         <v>1</v>
       </c>
@@ -6531,7 +6783,7 @@
         <v/>
       </c>
       <c r="D19" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=OmBV67MAAAAJ", "Scholar (OmBV67MAAAAJ)")</f>
+        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Tianyu%20Yang%20Arizona%20State%20University", "Google Scholar Search")</f>
         <v/>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -6544,11 +6796,7 @@
           <t>Aerospace &amp; Mechanical Engineering</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>OmBV67MAAAAJ</t>
-        </is>
-      </c>
+      <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="3">
         <f>HYPERLINK("mailto:Tianyu.Yang@asu.edu", "Tianyu.Yang@asu.edu")</f>
         <v/>
@@ -6562,11 +6810,7 @@
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>MAE 241: Intro to Thermodynamics</t>
-        </is>
-      </c>
+      <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr"/>
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr"/>
@@ -6588,11 +6832,7 @@
       <c r="W19" s="2" t="inlineStr"/>
       <c r="X19" s="2" t="inlineStr"/>
       <c r="Y19" s="2" t="inlineStr"/>
-      <c r="Z19" s="2" t="inlineStr">
-        <is>
-          <t>Campus: Tempe</t>
-        </is>
-      </c>
+      <c r="Z19" s="2" t="inlineStr"/>
       <c r="AA19" s="2" t="b">
         <v>1</v>
       </c>
@@ -6648,7 +6888,11 @@
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>MAE 557: Mechanics Composite Materials | MAE 494: Special Topics | MAE 521: Structural Optimization</t>
+        </is>
+      </c>
       <c r="M20" s="2" t="inlineStr"/>
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr"/>
@@ -6674,7 +6918,11 @@
       <c r="W20" s="2" t="inlineStr"/>
       <c r="X20" s="2" t="inlineStr"/>
       <c r="Y20" s="2" t="inlineStr"/>
-      <c r="Z20" s="2" t="inlineStr"/>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>ENGRC 427 (TEMPE, AZ 85287-6106)</t>
+        </is>
+      </c>
       <c r="AA20" s="2" t="b">
         <v>1</v>
       </c>
@@ -6823,7 +7071,11 @@
           <t>aerospace, energy systems, heat transfer</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Journal Papers 62. N. Ohashi, J. Deng, L.K. Hwang, P.K. Kang, and B. Kwon, “Physics-Informed Machine Learning for Reconstructin...</t>
+        </is>
+      </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
           <t>MAE 593: Applied Project | MAE 241: Intro to Thermodynamics | MAE 598: Special Topics</t>
@@ -6856,7 +7108,11 @@
         <f>HYPERLINK("http://sites.google.com/view/3denergy", "http://sites.google.com/view/3denergy")</f>
         <v/>
       </c>
-      <c r="U22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>Actively recruiting / Openings mentioned on lab site</t>
+        </is>
+      </c>
       <c r="V22" s="2" t="inlineStr"/>
       <c r="W22" s="2" t="inlineStr">
         <is>
@@ -6928,8 +7184,16 @@
           <t>aerospace, robot, robotics</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr"/>
-      <c r="L23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>Shape-programmable magnetic soft matter,</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>MAE 417: System Dynamics and Control II | MAE 598: Special Topics | MAE 547: Modeling and Control of Robots</t>
+        </is>
+      </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
           <t>KEEN Professorship, The Kern Family Foundation, 2017. | Peebles Award for Graduate Student Research in Adhesion Science, Adhesion Society, 2015.</t>
@@ -6966,7 +7230,11 @@
       <c r="W23" s="2" t="inlineStr"/>
       <c r="X23" s="2" t="inlineStr"/>
       <c r="Y23" s="2" t="inlineStr"/>
-      <c r="Z23" s="2" t="inlineStr"/>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>Campus: Tempe</t>
+        </is>
+      </c>
       <c r="AA23" s="2" t="b">
         <v>1</v>
       </c>
@@ -7103,7 +7371,11 @@
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
-      <c r="L25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>MAE 598: Special Topics | MAE 494: Special Topics | MAE 201: Mech. Particles/Rigid Bodies I</t>
+        </is>
+      </c>
       <c r="M25" s="2" t="inlineStr"/>
       <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr">
@@ -7140,7 +7412,11 @@
       <c r="W25" s="2" t="inlineStr"/>
       <c r="X25" s="2" t="inlineStr"/>
       <c r="Y25" s="2" t="inlineStr"/>
-      <c r="Z25" s="2" t="inlineStr"/>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>ISTB4, ROOM 379 781 S Terrace Rd (Tempe, AZ 85287)</t>
+        </is>
+      </c>
       <c r="AA25" s="2" t="b">
         <v>1</v>
       </c>
@@ -7290,7 +7566,11 @@
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>MAE 215: Intro to Programming in MATLAB | MAE 591: Seminar | MAE 593: Applied Project</t>
+        </is>
+      </c>
       <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr"/>
@@ -7319,7 +7599,11 @@
       <c r="W27" s="2" t="inlineStr"/>
       <c r="X27" s="2" t="inlineStr"/>
       <c r="Y27" s="2" t="inlineStr"/>
-      <c r="Z27" s="2" t="inlineStr"/>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>ENGRC 379 (Tempe, AZ 85287-6106)</t>
+        </is>
+      </c>
       <c r="AA27" s="2" t="b">
         <v>1</v>
       </c>
@@ -7375,7 +7659,11 @@
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>MAE 551: Appl Machine Learn Mech Engr | MAE 451: Appl Machine Learn Mech Engr | MAE 202: Mech.Particles/Rigid Bodies II</t>
+        </is>
+      </c>
       <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
@@ -7409,7 +7697,11 @@
       <c r="W28" s="2" t="inlineStr"/>
       <c r="X28" s="2" t="inlineStr"/>
       <c r="Y28" s="2" t="inlineStr"/>
-      <c r="Z28" s="2" t="inlineStr"/>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>Campus: Tempe</t>
+        </is>
+      </c>
       <c r="AA28" s="2" t="b">
         <v>1</v>
       </c>
@@ -7461,7 +7753,11 @@
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>MAE 502: Partial Diff Equations Engr | MAE 460: Applied Comput Fluid Dynamics | MAE 593: Applied Project</t>
+        </is>
+      </c>
       <c r="M29" s="2" t="inlineStr"/>
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr"/>
@@ -7481,7 +7777,11 @@
         <f>HYPERLINK("http://www.public.asu.edu/~hhuang38", "http://www.public.asu.edu/~hhuang38")</f>
         <v/>
       </c>
-      <c r="U29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>Actively recruiting / Openings mentioned on lab site</t>
+        </is>
+      </c>
       <c r="V29" s="2" t="inlineStr"/>
       <c r="W29" s="2" t="inlineStr"/>
       <c r="X29" s="2" t="inlineStr"/>
@@ -7490,7 +7790,11 @@
           <t>Log in to www_public</t>
         </is>
       </c>
-      <c r="Z29" s="2" t="inlineStr"/>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>ENGRC 359 (Tempe, AZ 85287-6106)</t>
+        </is>
+      </c>
       <c r="AA29" s="2" t="b">
         <v>1</v>
       </c>
@@ -7687,11 +7991,7 @@
       <c r="V31" s="2" t="inlineStr"/>
       <c r="W31" s="2" t="inlineStr"/>
       <c r="X31" s="2" t="inlineStr"/>
-      <c r="Y31" s="2" t="inlineStr">
-        <is>
-          <t>Rykaczewski Lab</t>
-        </is>
-      </c>
+      <c r="Y31" s="2" t="inlineStr"/>
       <c r="Z31" s="2" t="inlineStr">
         <is>
           <t>ENGRC 309 (Tempe, AZ 85287)</t>
@@ -8023,10 +8323,22 @@
           <t>robot, robotics</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr"/>
-      <c r="L35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>Below are selected papers that represent our main research threads. Please visit Publications for the full list. Contact-rich i...</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>MAE 301: Applied Experimental Statistic | MAE 593: Applied Project | MAE 547: Modeling and Control of Robots</t>
+        </is>
+      </c>
       <c r="M35" s="2" t="inlineStr"/>
-      <c r="N35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>If you are interested, please email Dr</t>
+        </is>
+      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
           <t>https://irislab.tech/</t>
@@ -8052,7 +8364,11 @@
         <f>HYPERLINK("https://irislab.tech/", "https://irislab.tech/")</f>
         <v/>
       </c>
-      <c r="U35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>Looking for ASU Undergraduate and Master Students</t>
+        </is>
+      </c>
       <c r="V35" s="2" t="inlineStr"/>
       <c r="W35" s="2" t="inlineStr">
         <is>
@@ -8068,7 +8384,11 @@
           <t>Recent Updates</t>
         </is>
       </c>
-      <c r="Z35" s="2" t="inlineStr"/>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>Campus: Tempe</t>
+        </is>
+      </c>
       <c r="AA35" s="2" t="b">
         <v>1</v>
       </c>
@@ -8213,12 +8533,12 @@
           <t>materials</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr"/>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>MAE 301: Applied Experimental Statistic | MAE 593: Applied Project | MAE 494: Special Topics</t>
-        </is>
-      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>Dylan Joralmon~, Soham Khairnar, Xiangjia Li*, "Rapid Fabrication of Multi-Metal 3D Objects with Adjustable Gradients by Contin...</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
           <t>2026 The J. Orin Edson Entrepreneurship &amp; Innovation Seed Funding Award ASU 2025 1st place Skysong Startup Competition C</t>
@@ -8254,7 +8574,11 @@
         <f>HYPERLINK("https://www.cindyxjli.com/", "https://www.cindyxjli.com/")</f>
         <v/>
       </c>
-      <c r="U37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>Actively recruiting / Openings mentioned on lab site</t>
+        </is>
+      </c>
       <c r="V37" s="2" t="inlineStr"/>
       <c r="W37" s="2" t="inlineStr">
         <is>
@@ -8267,11 +8591,7 @@
           <t>Manufacturing</t>
         </is>
       </c>
-      <c r="Z37" s="2" t="inlineStr">
-        <is>
-          <t>ERC457 551 E Tyler Mall (Tempe, AZ 85281)</t>
-        </is>
-      </c>
+      <c r="Z37" s="2" t="inlineStr"/>
       <c r="AA37" s="2" t="b">
         <v>1</v>
       </c>
@@ -8322,16 +8642,8 @@
           <t>aerospace</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>Journal Articles Middleton, J. A. (in press). Archimedes, Euler, &amp; Nursing Cats: Rethinking the Arithmetic Mean. OnCore,</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>MAE 484: Internship | MAE 301: Applied Experimental Statistic | MAE 394: Special Topics</t>
-        </is>
-      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr"/>
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
@@ -8357,11 +8669,7 @@
       <c r="W38" s="2" t="inlineStr"/>
       <c r="X38" s="2" t="inlineStr"/>
       <c r="Y38" s="2" t="inlineStr"/>
-      <c r="Z38" s="2" t="inlineStr">
-        <is>
-          <t>ENGRC 381 (TEMPE, AZ 85287-6106)</t>
-        </is>
-      </c>
+      <c r="Z38" s="2" t="inlineStr"/>
       <c r="AA38" s="2" t="b">
         <v>1</v>
       </c>
@@ -8495,11 +8803,7 @@
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>MAE 510: Dynamics and Vibrations | MAE 591: Seminar | MAE 394: Special Topics</t>
-        </is>
-      </c>
+      <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr"/>
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr"/>
@@ -8521,11 +8825,7 @@
       <c r="W40" s="2" t="inlineStr"/>
       <c r="X40" s="2" t="inlineStr"/>
       <c r="Y40" s="2" t="inlineStr"/>
-      <c r="Z40" s="2" t="inlineStr">
-        <is>
-          <t>ENGRC 411 (TEMPE, AZ 85287-6106)</t>
-        </is>
-      </c>
+      <c r="Z40" s="2" t="inlineStr"/>
       <c r="AA40" s="2" t="b">
         <v>1</v>
       </c>
@@ -8577,7 +8877,11 @@
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
-      <c r="L41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>MAE 213: Mechanics of Materials | MAE 593: Applied Project | MAE 520: Stress Analysis</t>
+        </is>
+      </c>
       <c r="M41" s="2" t="inlineStr"/>
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr"/>
@@ -8602,7 +8906,11 @@
       <c r="W41" s="2" t="inlineStr"/>
       <c r="X41" s="2" t="inlineStr"/>
       <c r="Y41" s="2" t="inlineStr"/>
-      <c r="Z41" s="2" t="inlineStr"/>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>ENGRC 352 (TEMPE, AZ 85287-6106)</t>
+        </is>
+      </c>
       <c r="AA41" s="2" t="b">
         <v>1</v>
       </c>
@@ -8657,7 +8965,11 @@
           <t>materials</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>top of page This website was built on Wix. Create yours today. Get Started Bio &amp; Nano Lab Home Dr. Kang Lab Members Publication...</t>
+        </is>
+      </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
           <t>MAE 598: Special Topics | MAE 494: Special Topics | MAE 202: Mech.Particles/Rigid Bodies II</t>
@@ -8767,7 +9079,11 @@
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr"/>
-      <c r="L43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>MAE 494: Special Topics | MAE 598: Special Topics | MAE 301: Applied Experimental Statistic</t>
+        </is>
+      </c>
       <c r="M43" s="2" t="inlineStr"/>
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr"/>
@@ -8789,7 +9105,11 @@
       <c r="W43" s="2" t="inlineStr"/>
       <c r="X43" s="2" t="inlineStr"/>
       <c r="Y43" s="2" t="inlineStr"/>
-      <c r="Z43" s="2" t="inlineStr"/>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>GWC 464 (Tempe, AZ 85287-6106)</t>
+        </is>
+      </c>
       <c r="AA43" s="2" t="b">
         <v>1</v>
       </c>
@@ -8837,7 +9157,11 @@
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
-      <c r="L44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>MAE 242: Intro to Fluid Mechanics | MAE 301: Applied Experimental Statistic | MAE 241: Intro to Thermodynamics</t>
+        </is>
+      </c>
       <c r="M44" s="2" t="inlineStr"/>
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr"/>
@@ -8851,7 +9175,11 @@
       <c r="W44" s="2" t="inlineStr"/>
       <c r="X44" s="2" t="inlineStr"/>
       <c r="Y44" s="2" t="inlineStr"/>
-      <c r="Z44" s="2" t="inlineStr"/>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>Campus: Tempe</t>
+        </is>
+      </c>
       <c r="AA44" s="2" t="b">
         <v>0</v>
       </c>
@@ -8899,7 +9227,11 @@
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
-      <c r="L45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>MAE 301: Applied Experimental Statistic | MAE 202: Mech.Particles/Rigid Bodies II | MAE 417: System Dynamics and Control II</t>
+        </is>
+      </c>
       <c r="M45" s="2" t="inlineStr"/>
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr"/>
@@ -8917,7 +9249,11 @@
       <c r="W45" s="2" t="inlineStr"/>
       <c r="X45" s="2" t="inlineStr"/>
       <c r="Y45" s="2" t="inlineStr"/>
-      <c r="Z45" s="2" t="inlineStr"/>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>Campus: Otherus</t>
+        </is>
+      </c>
       <c r="AA45" s="2" t="b">
         <v>0</v>
       </c>
@@ -9027,11 +9363,7 @@
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>MAE 241: Intro to Thermodynamics | MAE 215: Intro to Programming in MATLAB | MAE 384: Adv Math Methods for Engineers</t>
-        </is>
-      </c>
+      <c r="L47" s="2" t="inlineStr"/>
       <c r="M47" s="2" t="inlineStr"/>
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr"/>
@@ -9045,11 +9377,7 @@
       <c r="W47" s="2" t="inlineStr"/>
       <c r="X47" s="2" t="inlineStr"/>
       <c r="Y47" s="2" t="inlineStr"/>
-      <c r="Z47" s="2" t="inlineStr">
-        <is>
-          <t>Campus: Tempe</t>
-        </is>
-      </c>
+      <c r="Z47" s="2" t="inlineStr"/>
       <c r="AA47" s="2" t="b">
         <v>0</v>
       </c>
@@ -9097,7 +9425,11 @@
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
-      <c r="L48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>MAE 201: Mech. Particles/Rigid Bodies I | MAE 214: Computer-Aided Engineering I | MAE 202: Mech.Particles/Rigid Bodies II</t>
+        </is>
+      </c>
       <c r="M48" s="2" t="inlineStr"/>
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr"/>
@@ -9111,7 +9443,11 @@
       <c r="W48" s="2" t="inlineStr"/>
       <c r="X48" s="2" t="inlineStr"/>
       <c r="Y48" s="2" t="inlineStr"/>
-      <c r="Z48" s="2" t="inlineStr"/>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>Campus: Tempe</t>
+        </is>
+      </c>
       <c r="AA48" s="2" t="b">
         <v>0</v>
       </c>
@@ -9159,7 +9495,11 @@
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
-      <c r="L49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>MAE 570: Intermediate Thermodynamics | MAE 400: Engineering Profession | MAE 494: Special Topics</t>
+        </is>
+      </c>
       <c r="M49" s="2" t="inlineStr"/>
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr"/>
@@ -9173,7 +9513,11 @@
       <c r="W49" s="2" t="inlineStr"/>
       <c r="X49" s="2" t="inlineStr"/>
       <c r="Y49" s="2" t="inlineStr"/>
-      <c r="Z49" s="2" t="inlineStr"/>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>Campus: Tempe</t>
+        </is>
+      </c>
       <c r="AA49" s="2" t="b">
         <v>0</v>
       </c>

--- a/universities_wise/arizona_state_university/asu_aerospace_mechanical_faculty.xlsx
+++ b/universities_wise/arizona_state_university/asu_aerospace_mechanical_faculty.xlsx
@@ -677,11 +677,7 @@
           <t>Refereed Journal Papers M. H. Kasbaoui and M. Herrmann, A high-fidelity methodology for particle-resolved direct numerical simu...</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>MAE 242: Intro to Fluid Mechanics | MAE 574: Multiphase Flow | MAE 501: Linear Algebra in Engineering</t>
-        </is>
-      </c>
+      <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="2" t="inlineStr"/>
@@ -725,11 +721,7 @@
           <t>School for Engineering of Matter, Transport &amp; Energy</t>
         </is>
       </c>
-      <c r="Z2" s="2" t="inlineStr">
-        <is>
-          <t>Campus: Tempe</t>
-        </is>
-      </c>
+      <c r="Z2" s="2" t="inlineStr"/>
       <c r="AA2" s="2" t="b">
         <v>1</v>
       </c>
@@ -797,7 +789,7 @@
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Please send your CV to Prof</t>
+          <t>Please send your CV to Prof. Wang ( [email protected] ). We will try to get back to you ASAP with possible available positions. Please also send a 2-page statement on describing your previous research experience as well as how your research interests match Prof. Wang’s group’s research themes. | Please send Prof. Wang ( [email protected] ) with your resumes for applications and for more details on the projects.</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
@@ -906,7 +898,7 @@
       <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>If you're interested in joining our group, please email</t>
+          <t>If you're interested in joining our group, please email Prof. Oswald with your CV, research interests, and any supporting materials such as publications or code samples.</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -934,11 +926,7 @@
         <f>HYPERLINK("http://sparky.fulton.asu.edu/oswald/", "http://sparky.fulton.asu.edu/oswald/")</f>
         <v/>
       </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>What we're looking for:</t>
-        </is>
-      </c>
+      <c r="U4" s="2" t="inlineStr"/>
       <c r="V4" s="2" t="inlineStr"/>
       <c r="W4" s="2" t="inlineStr"/>
       <c r="X4" s="2" t="inlineStr"/>
@@ -1019,7 +1007,7 @@
       <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Additionally, they should send an email titled “Prospective Ph</t>
+          <t>To apply, interested candidates should submit an application to Arizona State University via https://webapp4.asu.edu/dgsadmissions/ , specifying their interest in working with Dr. Sun. Additionally, they should send an email titled “Prospective Ph.D. Student” to jiefeng.sun@asu.edu, attaching their CV and a cover letter before submitting their application. | I am seeking multiple highly motivated Master students or undergrads to conduct theses. To apply, interested candidates should fill in this form: https://forms.gle/RCwqu4wkCjhBUoFL7</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -1053,7 +1041,7 @@
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>Dec 19, 2025 We have two openings for fully supported summer interns through SURI program at ASU</t>
+          <t>I am seeking multiple highly motivated Master students or undergrads to conduct theses. To apply, interested candidates should fill in this form: https://forms.gle/RCwqu4wkCjhBUoFL7 | I am a K-12 student/teacher and would like information for a school report, tour, help with my robotics team, a research internship, etc. My students and I are very excited about using robotics as a teaching tool to encourage interest in Science, Technology, Engineering, and Math (STEM) topics. We actively involved in outreach and are have an outreach webpage to answer your questions.</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr"/>
@@ -1421,7 +1409,7 @@
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Potential candidates with strong backgrounds in fluid-structure interaction, soft robotics , machine learning can send their CV to leixinma@asu</t>
+          <t>Undergraduate students : Highly-motivated undergraduate students are encouraged to get in touch. The students are encouraged to apply Fulton Undergraduate Research Initiative (FURI) ( Proposals are due the 3rd Wednesday of every March and October ) , Summer Research Initiative (SURI) etc. No prior research experiences are expected. Email to: leixinma@ asu .edu . | Visiting scholars from different backgrounds are welcome to contact Prof. Ma for projects with mutual interests. Email to: leixinma@asu.edu</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1455,7 +1443,7 @@
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>Actively recruiting / Openings mentioned on lab site</t>
+          <t>More Home Research People Publications News Openings Facility Teaching Resources | Update: We are currently hiring multiple fully-funded graduate students, undergraduate students and visiting scholars! The first year graduate students will be selected as the prestigious Ira A. Fulton fellowship from the ASU School of Engineering.</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr"/>
@@ -1523,7 +1511,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Simultaneous velocity and density measurements of fully developed Rayleigh-Taylor turbulent mixing</t>
+          <t>There is an open post-doctoral opening starting Fall 2025 in experimental turbulence research . All students interested in join...</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1815,7 +1803,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Selected Journal Papers Nasim Baharisangari, Kazuma Hirota, Ruixuan Yan, Agung Julius, Zhe Xu , Weighted Graph-Based Sig</t>
+          <t>Search this site Embedded Files Skip to main content Skip to navigation Home Publications Research Teaching Group Members Outre...</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1850,11 +1838,7 @@
         <f>HYPERLINK("https://sites.google.com/site/zhexudavid00710/research?authuser=0", "https://sites.google.com/site/zhexudavid00710/research?authuser=0")</f>
         <v/>
       </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>Actively recruiting / Openings mentioned on lab site</t>
-        </is>
-      </c>
+      <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr"/>
       <c r="W13" s="2" t="inlineStr"/>
       <c r="X13" s="2" t="inlineStr"/>
@@ -1970,7 +1954,7 @@
         <v/>
       </c>
       <c r="D15" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Matthew%20Peet%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=l7umOqMAAAAJ", "Scholar (l7umOqMAAAAJ)")</f>
         <v/>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1983,7 +1967,11 @@
           <t>Aerospace &amp; Mechanical Engineering</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>l7umOqMAAAAJ</t>
+        </is>
+      </c>
       <c r="H15" s="3">
         <f>HYPERLINK("mailto:mpeet@asu.edu", "mpeet@asu.edu")</f>
         <v/>
@@ -1997,7 +1985,11 @@
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>MAE 593: Applied Project | MAE 318: System Dynamics and Control I | MAE 509: LMI Methods</t>
+        </is>
+      </c>
       <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr">
@@ -2034,7 +2026,11 @@
       <c r="W15" s="2" t="inlineStr"/>
       <c r="X15" s="2" t="inlineStr"/>
       <c r="Y15" s="2" t="inlineStr"/>
-      <c r="Z15" s="2" t="inlineStr"/>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>ENGRC 253 (Tempe, AZ 85287-6106)</t>
+        </is>
+      </c>
       <c r="AA15" s="2" t="b">
         <v>1</v>
       </c>
@@ -2452,11 +2448,7 @@
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>MAE 557: Mechanics Composite Materials | MAE 494: Special Topics | MAE 521: Structural Optimization</t>
-        </is>
-      </c>
+      <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr"/>
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr"/>
@@ -2482,11 +2474,7 @@
       <c r="W20" s="2" t="inlineStr"/>
       <c r="X20" s="2" t="inlineStr"/>
       <c r="Y20" s="2" t="inlineStr"/>
-      <c r="Z20" s="2" t="inlineStr">
-        <is>
-          <t>ENGRC 427 (TEMPE, AZ 85287-6106)</t>
-        </is>
-      </c>
+      <c r="Z20" s="2" t="inlineStr"/>
       <c r="AA20" s="2" t="b">
         <v>1</v>
       </c>
@@ -2672,11 +2660,7 @@
         <f>HYPERLINK("http://sites.google.com/view/3denergy", "http://sites.google.com/view/3denergy")</f>
         <v/>
       </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>Actively recruiting / Openings mentioned on lab site</t>
-        </is>
-      </c>
+      <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr"/>
       <c r="W22" s="2" t="inlineStr">
         <is>
@@ -3317,11 +3301,7 @@
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>MAE 502: Partial Diff Equations Engr | MAE 460: Applied Comput Fluid Dynamics | MAE 593: Applied Project</t>
-        </is>
-      </c>
+      <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr"/>
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr"/>
@@ -3341,11 +3321,7 @@
         <f>HYPERLINK("http://www.public.asu.edu/~hhuang38", "http://www.public.asu.edu/~hhuang38")</f>
         <v/>
       </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>Actively recruiting / Openings mentioned on lab site</t>
-        </is>
-      </c>
+      <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr"/>
       <c r="W29" s="2" t="inlineStr"/>
       <c r="X29" s="2" t="inlineStr"/>
@@ -3354,11 +3330,7 @@
           <t>Log in to www_public</t>
         </is>
       </c>
-      <c r="Z29" s="2" t="inlineStr">
-        <is>
-          <t>ENGRC 359 (Tempe, AZ 85287-6106)</t>
-        </is>
-      </c>
+      <c r="Z29" s="2" t="inlineStr"/>
       <c r="AA29" s="2" t="b">
         <v>1</v>
       </c>
@@ -3900,7 +3872,7 @@
       <c r="M35" s="2" t="inlineStr"/>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>If you are interested, please email Dr</t>
+          <t>If you are interested, please email Dr. Wanxin Jin with your CV, transcript, and a brief description of your research interests. In your email, please mention the topics you are interested in, your relevant background, and whether you are looking for thesis research, independent study, an applied project, hourly research work, or volunteer research experience. | If you are interested, please submit this form: https://forms.gle/Yo5mQcwTrogHTgu77 . If there is a potential fit, you should expect to be contacted within one week; if you do not hear back, please email wjin@asu.edu for follow-up.</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
@@ -3930,7 +3902,7 @@
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>Looking for ASU Undergraduate and Master Students</t>
+          <t>ASU undergraduate and master students are welcome to join IRIS Lab research projects in robotics, embodied AI, vision and perception, robot learning, control, and autonomy. Students interested in a thesis, independent study, or sustained applied research project are especially encouraged to reach out. | If you are interested, please email Dr. Wanxin Jin with your CV, transcript, and a brief description of your research interests. In your email, please mention the topics you are interested in, your relevant background, and whether you are looking for thesis research, independent study, an applied project, hourly research work, or volunteer research experience.</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr"/>
@@ -4102,13 +4074,21 @@
           <t>Dylan Joralmon~, Soham Khairnar, Xiangjia Li*, "Rapid Fabrication of Multi-Metal 3D Objects with Adjustable Gradients by Contin...</t>
         </is>
       </c>
-      <c r="L37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>MAE 301: Applied Experimental Statistic | MAE 593: Applied Project | MAE 494: Special Topics</t>
+        </is>
+      </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
           <t>2026 The J. Orin Edson Entrepreneurship &amp; Innovation Seed Funding Award ASU 2025 1st place Skysong Startup Competition C</t>
         </is>
       </c>
-      <c r="N37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>If you are interested in joining us, please send the full CV (with GPA; working and research experiences; publications) to Prof. Li (email: xiangjia.li AT asu.edu).</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
           <t>Biomimetic Additive Manufacturing (3D Printing); Bioinspired Material and Structure Design; Stereolithography; Photopolymerization based 3D Printing; Multi-material and Multi-scale 3D printing; Biofabrication; Biomaterial; Ceramic Printing; Nanocomposite Printing; Physical Field Assisted Printing; 4D Printing; Flexible Sensor; Biomedical Device; Tissue Repair and Regeneration.</t>
@@ -4140,7 +4120,7 @@
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>Actively recruiting / Openings mentioned on lab site</t>
+          <t>The labMI is looking for creative, motivated and energetic Ph.D., Master and Undergraduate students from diverse science and engineering field!</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr"/>
@@ -4155,7 +4135,11 @@
           <t>Manufacturing</t>
         </is>
       </c>
-      <c r="Z37" s="2" t="inlineStr"/>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>ERC457 551 E Tyler Mall (Tempe, AZ 85281)</t>
+        </is>
+      </c>
       <c r="AA37" s="2" t="b">
         <v>1</v>
       </c>
@@ -4367,7 +4351,11 @@
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
-      <c r="L40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>MAE 510: Dynamics and Vibrations | MAE 591: Seminar | MAE 394: Special Topics</t>
+        </is>
+      </c>
       <c r="M40" s="2" t="inlineStr"/>
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr"/>
@@ -4389,7 +4377,11 @@
       <c r="W40" s="2" t="inlineStr"/>
       <c r="X40" s="2" t="inlineStr"/>
       <c r="Y40" s="2" t="inlineStr"/>
-      <c r="Z40" s="2" t="inlineStr"/>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>ENGRC 411 (TEMPE, AZ 85287-6106)</t>
+        </is>
+      </c>
       <c r="AA40" s="2" t="b">
         <v>1</v>
       </c>
@@ -4572,7 +4564,7 @@
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>Welcome and we are looking forward to working with Dr</t>
+          <t>Actively recruiting / Openings mentioned on lab site</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr"/>
@@ -5113,11 +5105,7 @@
           <t>Refereed Journal Papers M. H. Kasbaoui and M. Herrmann, A high-fidelity methodology for particle-resolved direct numerical simu...</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>MAE 242: Intro to Fluid Mechanics | MAE 574: Multiphase Flow | MAE 501: Linear Algebra in Engineering</t>
-        </is>
-      </c>
+      <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="2" t="inlineStr"/>
@@ -5161,11 +5149,7 @@
           <t>School for Engineering of Matter, Transport &amp; Energy</t>
         </is>
       </c>
-      <c r="Z2" s="2" t="inlineStr">
-        <is>
-          <t>Campus: Tempe</t>
-        </is>
-      </c>
+      <c r="Z2" s="2" t="inlineStr"/>
       <c r="AA2" s="2" t="b">
         <v>1</v>
       </c>
@@ -5233,7 +5217,7 @@
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Please send your CV to Prof</t>
+          <t>Please send your CV to Prof. Wang ( [email protected] ). We will try to get back to you ASAP with possible available positions. Please also send a 2-page statement on describing your previous research experience as well as how your research interests match Prof. Wang’s group’s research themes. | Please send Prof. Wang ( [email protected] ) with your resumes for applications and for more details on the projects.</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
@@ -5342,7 +5326,7 @@
       <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>If you're interested in joining our group, please email</t>
+          <t>If you're interested in joining our group, please email Prof. Oswald with your CV, research interests, and any supporting materials such as publications or code samples.</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -5370,11 +5354,7 @@
         <f>HYPERLINK("http://sparky.fulton.asu.edu/oswald/", "http://sparky.fulton.asu.edu/oswald/")</f>
         <v/>
       </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>What we're looking for:</t>
-        </is>
-      </c>
+      <c r="U4" s="2" t="inlineStr"/>
       <c r="V4" s="2" t="inlineStr"/>
       <c r="W4" s="2" t="inlineStr"/>
       <c r="X4" s="2" t="inlineStr"/>
@@ -5455,7 +5435,7 @@
       <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Additionally, they should send an email titled “Prospective Ph</t>
+          <t>To apply, interested candidates should submit an application to Arizona State University via https://webapp4.asu.edu/dgsadmissions/ , specifying their interest in working with Dr. Sun. Additionally, they should send an email titled “Prospective Ph.D. Student” to jiefeng.sun@asu.edu, attaching their CV and a cover letter before submitting their application. | I am seeking multiple highly motivated Master students or undergrads to conduct theses. To apply, interested candidates should fill in this form: https://forms.gle/RCwqu4wkCjhBUoFL7</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -5489,7 +5469,7 @@
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>Dec 19, 2025 We have two openings for fully supported summer interns through SURI program at ASU</t>
+          <t>I am seeking multiple highly motivated Master students or undergrads to conduct theses. To apply, interested candidates should fill in this form: https://forms.gle/RCwqu4wkCjhBUoFL7 | I am a K-12 student/teacher and would like information for a school report, tour, help with my robotics team, a research internship, etc. My students and I are very excited about using robotics as a teaching tool to encourage interest in Science, Technology, Engineering, and Math (STEM) topics. We actively involved in outreach and are have an outreach webpage to answer your questions.</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr"/>
@@ -5857,7 +5837,7 @@
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Potential candidates with strong backgrounds in fluid-structure interaction, soft robotics , machine learning can send their CV to leixinma@asu</t>
+          <t>Undergraduate students : Highly-motivated undergraduate students are encouraged to get in touch. The students are encouraged to apply Fulton Undergraduate Research Initiative (FURI) ( Proposals are due the 3rd Wednesday of every March and October ) , Summer Research Initiative (SURI) etc. No prior research experiences are expected. Email to: leixinma@ asu .edu . | Visiting scholars from different backgrounds are welcome to contact Prof. Ma for projects with mutual interests. Email to: leixinma@asu.edu</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -5891,7 +5871,7 @@
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>Actively recruiting / Openings mentioned on lab site</t>
+          <t>More Home Research People Publications News Openings Facility Teaching Resources | Update: We are currently hiring multiple fully-funded graduate students, undergraduate students and visiting scholars! The first year graduate students will be selected as the prestigious Ira A. Fulton fellowship from the ASU School of Engineering.</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr"/>
@@ -5959,7 +5939,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Simultaneous velocity and density measurements of fully developed Rayleigh-Taylor turbulent mixing</t>
+          <t>There is an open post-doctoral opening starting Fall 2025 in experimental turbulence research . All students interested in join...</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -6251,7 +6231,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Selected Journal Papers Nasim Baharisangari, Kazuma Hirota, Ruixuan Yan, Agung Julius, Zhe Xu , Weighted Graph-Based Sig</t>
+          <t>Search this site Embedded Files Skip to main content Skip to navigation Home Publications Research Teaching Group Members Outre...</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -6286,11 +6266,7 @@
         <f>HYPERLINK("https://sites.google.com/site/zhexudavid00710/research?authuser=0", "https://sites.google.com/site/zhexudavid00710/research?authuser=0")</f>
         <v/>
       </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>Actively recruiting / Openings mentioned on lab site</t>
-        </is>
-      </c>
+      <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr"/>
       <c r="W13" s="2" t="inlineStr"/>
       <c r="X13" s="2" t="inlineStr"/>
@@ -6406,7 +6382,7 @@
         <v/>
       </c>
       <c r="D15" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Matthew%20Peet%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=l7umOqMAAAAJ", "Scholar (l7umOqMAAAAJ)")</f>
         <v/>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -6419,7 +6395,11 @@
           <t>Aerospace &amp; Mechanical Engineering</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>l7umOqMAAAAJ</t>
+        </is>
+      </c>
       <c r="H15" s="3">
         <f>HYPERLINK("mailto:mpeet@asu.edu", "mpeet@asu.edu")</f>
         <v/>
@@ -6433,7 +6413,11 @@
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>MAE 593: Applied Project | MAE 318: System Dynamics and Control I | MAE 509: LMI Methods</t>
+        </is>
+      </c>
       <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr">
@@ -6470,7 +6454,11 @@
       <c r="W15" s="2" t="inlineStr"/>
       <c r="X15" s="2" t="inlineStr"/>
       <c r="Y15" s="2" t="inlineStr"/>
-      <c r="Z15" s="2" t="inlineStr"/>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>ENGRC 253 (Tempe, AZ 85287-6106)</t>
+        </is>
+      </c>
       <c r="AA15" s="2" t="b">
         <v>1</v>
       </c>
@@ -6888,11 +6876,7 @@
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>MAE 557: Mechanics Composite Materials | MAE 494: Special Topics | MAE 521: Structural Optimization</t>
-        </is>
-      </c>
+      <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr"/>
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr"/>
@@ -6918,11 +6902,7 @@
       <c r="W20" s="2" t="inlineStr"/>
       <c r="X20" s="2" t="inlineStr"/>
       <c r="Y20" s="2" t="inlineStr"/>
-      <c r="Z20" s="2" t="inlineStr">
-        <is>
-          <t>ENGRC 427 (TEMPE, AZ 85287-6106)</t>
-        </is>
-      </c>
+      <c r="Z20" s="2" t="inlineStr"/>
       <c r="AA20" s="2" t="b">
         <v>1</v>
       </c>
@@ -7108,11 +7088,7 @@
         <f>HYPERLINK("http://sites.google.com/view/3denergy", "http://sites.google.com/view/3denergy")</f>
         <v/>
       </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>Actively recruiting / Openings mentioned on lab site</t>
-        </is>
-      </c>
+      <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr"/>
       <c r="W22" s="2" t="inlineStr">
         <is>
@@ -7753,11 +7729,7 @@
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>MAE 502: Partial Diff Equations Engr | MAE 460: Applied Comput Fluid Dynamics | MAE 593: Applied Project</t>
-        </is>
-      </c>
+      <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr"/>
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr"/>
@@ -7777,11 +7749,7 @@
         <f>HYPERLINK("http://www.public.asu.edu/~hhuang38", "http://www.public.asu.edu/~hhuang38")</f>
         <v/>
       </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>Actively recruiting / Openings mentioned on lab site</t>
-        </is>
-      </c>
+      <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr"/>
       <c r="W29" s="2" t="inlineStr"/>
       <c r="X29" s="2" t="inlineStr"/>
@@ -7790,11 +7758,7 @@
           <t>Log in to www_public</t>
         </is>
       </c>
-      <c r="Z29" s="2" t="inlineStr">
-        <is>
-          <t>ENGRC 359 (Tempe, AZ 85287-6106)</t>
-        </is>
-      </c>
+      <c r="Z29" s="2" t="inlineStr"/>
       <c r="AA29" s="2" t="b">
         <v>1</v>
       </c>
@@ -8336,7 +8300,7 @@
       <c r="M35" s="2" t="inlineStr"/>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>If you are interested, please email Dr</t>
+          <t>If you are interested, please email Dr. Wanxin Jin with your CV, transcript, and a brief description of your research interests. In your email, please mention the topics you are interested in, your relevant background, and whether you are looking for thesis research, independent study, an applied project, hourly research work, or volunteer research experience. | If you are interested, please submit this form: https://forms.gle/Yo5mQcwTrogHTgu77 . If there is a potential fit, you should expect to be contacted within one week; if you do not hear back, please email wjin@asu.edu for follow-up.</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
@@ -8366,7 +8330,7 @@
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>Looking for ASU Undergraduate and Master Students</t>
+          <t>ASU undergraduate and master students are welcome to join IRIS Lab research projects in robotics, embodied AI, vision and perception, robot learning, control, and autonomy. Students interested in a thesis, independent study, or sustained applied research project are especially encouraged to reach out. | If you are interested, please email Dr. Wanxin Jin with your CV, transcript, and a brief description of your research interests. In your email, please mention the topics you are interested in, your relevant background, and whether you are looking for thesis research, independent study, an applied project, hourly research work, or volunteer research experience.</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr"/>
@@ -8538,13 +8502,21 @@
           <t>Dylan Joralmon~, Soham Khairnar, Xiangjia Li*, "Rapid Fabrication of Multi-Metal 3D Objects with Adjustable Gradients by Contin...</t>
         </is>
       </c>
-      <c r="L37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>MAE 301: Applied Experimental Statistic | MAE 593: Applied Project | MAE 494: Special Topics</t>
+        </is>
+      </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
           <t>2026 The J. Orin Edson Entrepreneurship &amp; Innovation Seed Funding Award ASU 2025 1st place Skysong Startup Competition C</t>
         </is>
       </c>
-      <c r="N37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>If you are interested in joining us, please send the full CV (with GPA; working and research experiences; publications) to Prof. Li (email: xiangjia.li AT asu.edu).</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
           <t>Biomimetic Additive Manufacturing (3D Printing); Bioinspired Material and Structure Design; Stereolithography; Photopolymerization based 3D Printing; Multi-material and Multi-scale 3D printing; Biofabrication; Biomaterial; Ceramic Printing; Nanocomposite Printing; Physical Field Assisted Printing; 4D Printing; Flexible Sensor; Biomedical Device; Tissue Repair and Regeneration.</t>
@@ -8576,7 +8548,7 @@
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>Actively recruiting / Openings mentioned on lab site</t>
+          <t>The labMI is looking for creative, motivated and energetic Ph.D., Master and Undergraduate students from diverse science and engineering field!</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr"/>
@@ -8591,7 +8563,11 @@
           <t>Manufacturing</t>
         </is>
       </c>
-      <c r="Z37" s="2" t="inlineStr"/>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>ERC457 551 E Tyler Mall (Tempe, AZ 85281)</t>
+        </is>
+      </c>
       <c r="AA37" s="2" t="b">
         <v>1</v>
       </c>
@@ -8803,7 +8779,11 @@
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
-      <c r="L40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>MAE 510: Dynamics and Vibrations | MAE 591: Seminar | MAE 394: Special Topics</t>
+        </is>
+      </c>
       <c r="M40" s="2" t="inlineStr"/>
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr"/>
@@ -8825,7 +8805,11 @@
       <c r="W40" s="2" t="inlineStr"/>
       <c r="X40" s="2" t="inlineStr"/>
       <c r="Y40" s="2" t="inlineStr"/>
-      <c r="Z40" s="2" t="inlineStr"/>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>ENGRC 411 (TEMPE, AZ 85287-6106)</t>
+        </is>
+      </c>
       <c r="AA40" s="2" t="b">
         <v>1</v>
       </c>
@@ -9008,7 +8992,7 @@
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>Welcome and we are looking forward to working with Dr</t>
+          <t>Actively recruiting / Openings mentioned on lab site</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr"/>
@@ -9227,11 +9211,7 @@
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>MAE 301: Applied Experimental Statistic | MAE 202: Mech.Particles/Rigid Bodies II | MAE 417: System Dynamics and Control II</t>
-        </is>
-      </c>
+      <c r="L45" s="2" t="inlineStr"/>
       <c r="M45" s="2" t="inlineStr"/>
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr"/>
@@ -9249,11 +9229,7 @@
       <c r="W45" s="2" t="inlineStr"/>
       <c r="X45" s="2" t="inlineStr"/>
       <c r="Y45" s="2" t="inlineStr"/>
-      <c r="Z45" s="2" t="inlineStr">
-        <is>
-          <t>Campus: Otherus</t>
-        </is>
-      </c>
+      <c r="Z45" s="2" t="inlineStr"/>
       <c r="AA45" s="2" t="b">
         <v>0</v>
       </c>
@@ -9301,7 +9277,11 @@
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
-      <c r="L46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>MAE 318: System Dynamics and Control I | MAE 417: System Dynamics and Control II | MAE 215: Intro to Programming in MATLAB</t>
+        </is>
+      </c>
       <c r="M46" s="2" t="inlineStr"/>
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr"/>
@@ -9315,7 +9295,11 @@
       <c r="W46" s="2" t="inlineStr"/>
       <c r="X46" s="2" t="inlineStr"/>
       <c r="Y46" s="2" t="inlineStr"/>
-      <c r="Z46" s="2" t="inlineStr"/>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>Campus: Tempe</t>
+        </is>
+      </c>
       <c r="AA46" s="2" t="b">
         <v>0</v>
       </c>

--- a/universities_wise/arizona_state_university/asu_aerospace_mechanical_faculty.xlsx
+++ b/universities_wise/arizona_state_university/asu_aerospace_mechanical_faculty.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB43"/>
+  <dimension ref="A1:AC43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -480,12 +480,13 @@
     <col width="49" customWidth="1" min="20" max="20"/>
     <col width="65" customWidth="1" min="21" max="21"/>
     <col width="53" customWidth="1" min="22" max="22"/>
-    <col width="20" customWidth="1" min="23" max="23"/>
-    <col width="49" customWidth="1" min="24" max="24"/>
-    <col width="56" customWidth="1" min="25" max="25"/>
-    <col width="54" customWidth="1" min="26" max="26"/>
-    <col width="18" customWidth="1" min="27" max="27"/>
-    <col width="49" customWidth="1" min="28" max="28"/>
+    <col width="30" customWidth="1" min="23" max="23"/>
+    <col width="20" customWidth="1" min="24" max="24"/>
+    <col width="49" customWidth="1" min="25" max="25"/>
+    <col width="56" customWidth="1" min="26" max="26"/>
+    <col width="65" customWidth="1" min="27" max="27"/>
+    <col width="18" customWidth="1" min="28" max="28"/>
+    <col width="49" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -601,30 +602,35 @@
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
+          <t>Lab Facilities &amp; Equipment</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
           <t>Funding Sponsors</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Software / Code Repo</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Latest Project / Highlight</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Office Location</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Is Field Match</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Directory URL</t>
         </is>
@@ -677,7 +683,11 @@
           <t>Refereed Journal Papers M. H. Kasbaoui and M. Herrmann, A high-fidelity methodology for particle-resolved direct numerical simu...</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>MAE 242: Intro to Fluid Mechanics | MAE 574: Multiphase Flow | MAE 501: Linear Algebra in Engineering</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="2" t="inlineStr"/>
@@ -707,25 +717,30 @@
           <t>CFD</t>
         </is>
       </c>
-      <c r="W2" s="2" t="inlineStr">
+      <c r="W2" s="2" t="inlineStr"/>
+      <c r="X2" s="2" t="inlineStr">
         <is>
           <t>AFOSR</t>
         </is>
       </c>
-      <c r="X2" s="3">
+      <c r="Y2" s="3">
         <f>HYPERLINK("https://bitbucket.org/krgasu/leap/downloads/leap-v0.8.2.tar.gz", "https://bitbucket.org/krgasu/leap/downloads/leap-v0.8.2.tar.gz, https://bitbucket.org/krgasu/leap/src/master")</f>
         <v/>
       </c>
-      <c r="Y2" s="2" t="inlineStr">
+      <c r="Z2" s="2" t="inlineStr">
         <is>
           <t>School for Engineering of Matter, Transport &amp; Energy</t>
         </is>
       </c>
-      <c r="Z2" s="2" t="inlineStr"/>
-      <c r="AA2" s="2" t="b">
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
+          <t>Campus: Tempe</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB2" s="3">
+      <c r="AC2" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -825,24 +840,29 @@
       <c r="V3" s="2" t="inlineStr"/>
       <c r="W3" s="2" t="inlineStr">
         <is>
+          <t>AFM</t>
+        </is>
+      </c>
+      <c r="X3" s="2" t="inlineStr">
+        <is>
           <t>NASA, NSF</t>
         </is>
       </c>
-      <c r="X3" s="2" t="inlineStr"/>
-      <c r="Y3" s="2" t="inlineStr">
+      <c r="Y3" s="2" t="inlineStr"/>
+      <c r="Z3" s="2" t="inlineStr">
         <is>
           <t>News&amp;Awards</t>
         </is>
       </c>
-      <c r="Z3" s="2" t="inlineStr">
+      <c r="AA3" s="2" t="inlineStr">
         <is>
           <t>ENGRC 327 (Tempe, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="b">
+      <c r="AB3" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB3" s="3">
+      <c r="AC3" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -930,20 +950,21 @@
       <c r="V4" s="2" t="inlineStr"/>
       <c r="W4" s="2" t="inlineStr"/>
       <c r="X4" s="2" t="inlineStr"/>
-      <c r="Y4" s="2" t="inlineStr">
+      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr">
         <is>
           <t>Multiscale polymer analysis</t>
         </is>
       </c>
-      <c r="Z4" s="2" t="inlineStr">
+      <c r="AA4" s="2" t="inlineStr">
         <is>
           <t>ENGRC 353 (Tempe, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="b">
+      <c r="AB4" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB4" s="3">
+      <c r="AC4" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1047,20 +1068,21 @@
       <c r="V5" s="2" t="inlineStr"/>
       <c r="W5" s="2" t="inlineStr"/>
       <c r="X5" s="2" t="inlineStr"/>
-      <c r="Y5" s="2" t="inlineStr">
+      <c r="Y5" s="2" t="inlineStr"/>
+      <c r="Z5" s="2" t="inlineStr">
         <is>
           <t>Mission and Core Values</t>
         </is>
       </c>
-      <c r="Z5" s="2" t="inlineStr">
+      <c r="AA5" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="b">
+      <c r="AB5" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB5" s="3">
+      <c r="AC5" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1138,15 +1160,16 @@
       <c r="W6" s="2" t="inlineStr"/>
       <c r="X6" s="2" t="inlineStr"/>
       <c r="Y6" s="2" t="inlineStr"/>
-      <c r="Z6" s="2" t="inlineStr">
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr">
         <is>
           <t>ENGRC 361 (TEMPE, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="b">
+      <c r="AB6" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB6" s="3">
+      <c r="AC6" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1198,7 +1221,11 @@
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>MAE 242: Intro to Fluid Mechanics | MAE 593: Applied Project | MAE 564: Advanced Aerodynamics</t>
+        </is>
+      </c>
       <c r="M7" s="2" t="inlineStr"/>
       <c r="N7" s="2" t="inlineStr"/>
       <c r="O7" s="2" t="inlineStr">
@@ -1225,10 +1252,15 @@
       <c r="X7" s="2" t="inlineStr"/>
       <c r="Y7" s="2" t="inlineStr"/>
       <c r="Z7" s="2" t="inlineStr"/>
-      <c r="AA7" s="2" t="b">
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>Engineering research centre Room 383 551 E Tyler mall (Tempe, AZ 85281)</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB7" s="3">
+      <c r="AC7" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1337,15 +1369,16 @@
       <c r="W8" s="2" t="inlineStr"/>
       <c r="X8" s="2" t="inlineStr"/>
       <c r="Y8" s="2" t="inlineStr"/>
-      <c r="Z8" s="2" t="inlineStr">
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr">
         <is>
           <t>551 E Tyler Mall ERC 475 (Tempe, AZ 85281)</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="b">
+      <c r="AB8" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1447,22 +1480,27 @@
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr"/>
-      <c r="W9" s="2" t="inlineStr"/>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>Towing Tank, FDM</t>
+        </is>
+      </c>
       <c r="X9" s="2" t="inlineStr"/>
-      <c r="Y9" s="2" t="inlineStr">
+      <c r="Y9" s="2" t="inlineStr"/>
+      <c r="Z9" s="2" t="inlineStr">
         <is>
           <t>Ocean and Soft Intelligent Structure Interaction Lab</t>
         </is>
       </c>
-      <c r="Z9" s="2" t="inlineStr">
+      <c r="AA9" s="2" t="inlineStr">
         <is>
           <t>ERC 485 (Tempe, AZ 85287)</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="b">
+      <c r="AB9" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1550,20 +1588,21 @@
       <c r="V10" s="2" t="inlineStr"/>
       <c r="W10" s="2" t="inlineStr"/>
       <c r="X10" s="2" t="inlineStr"/>
-      <c r="Y10" s="2" t="inlineStr">
+      <c r="Y10" s="2" t="inlineStr"/>
+      <c r="Z10" s="2" t="inlineStr">
         <is>
           <t>Want to be part of CMAT Lab?</t>
         </is>
       </c>
-      <c r="Z10" s="2" t="inlineStr">
+      <c r="AA10" s="2" t="inlineStr">
         <is>
           <t>551 E Tyler Mall ERC 479 (Tempe, AZ 85281)</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="b">
+      <c r="AB10" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1645,15 +1684,16 @@
       <c r="W11" s="2" t="inlineStr"/>
       <c r="X11" s="2" t="inlineStr"/>
       <c r="Y11" s="2" t="inlineStr"/>
-      <c r="Z11" s="2" t="inlineStr">
+      <c r="Z11" s="2" t="inlineStr"/>
+      <c r="AA11" s="2" t="inlineStr">
         <is>
           <t>ENGRC 311 (TEMPE, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="b">
+      <c r="AB11" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB11" s="3">
+      <c r="AC11" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1746,15 +1786,16 @@
       <c r="W12" s="2" t="inlineStr"/>
       <c r="X12" s="2" t="inlineStr"/>
       <c r="Y12" s="2" t="inlineStr"/>
-      <c r="Z12" s="2" t="inlineStr">
+      <c r="Z12" s="2" t="inlineStr"/>
+      <c r="AA12" s="2" t="inlineStr">
         <is>
           <t>ENGRC 375 (Tempe, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="b">
+      <c r="AB12" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1843,15 +1884,16 @@
       <c r="W13" s="2" t="inlineStr"/>
       <c r="X13" s="2" t="inlineStr"/>
       <c r="Y13" s="2" t="inlineStr"/>
-      <c r="Z13" s="2" t="inlineStr">
+      <c r="Z13" s="2" t="inlineStr"/>
+      <c r="AA13" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="b">
+      <c r="AB13" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB13" s="3">
+      <c r="AC13" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1925,15 +1967,16 @@
       <c r="W14" s="2" t="inlineStr"/>
       <c r="X14" s="2" t="inlineStr"/>
       <c r="Y14" s="2" t="inlineStr"/>
-      <c r="Z14" s="2" t="inlineStr">
+      <c r="Z14" s="2" t="inlineStr"/>
+      <c r="AA14" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="b">
+      <c r="AB14" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2026,15 +2069,16 @@
       <c r="W15" s="2" t="inlineStr"/>
       <c r="X15" s="2" t="inlineStr"/>
       <c r="Y15" s="2" t="inlineStr"/>
-      <c r="Z15" s="2" t="inlineStr">
+      <c r="Z15" s="2" t="inlineStr"/>
+      <c r="AA15" s="2" t="inlineStr">
         <is>
           <t>ENGRC 253 (Tempe, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="b">
+      <c r="AB15" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2086,11 +2130,7 @@
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>MAE 241: Intro to Thermodynamics | MAE 593: Applied Project | MAE 588: Nanoscale Heat Transfer</t>
-        </is>
-      </c>
+      <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
@@ -2123,15 +2163,12 @@
       <c r="W16" s="2" t="inlineStr"/>
       <c r="X16" s="2" t="inlineStr"/>
       <c r="Y16" s="2" t="inlineStr"/>
-      <c r="Z16" s="2" t="inlineStr">
-        <is>
-          <t>ENGRC 307 (Tempe, AZ 85287-6106)</t>
-        </is>
-      </c>
-      <c r="AA16" s="2" t="b">
+      <c r="Z16" s="2" t="inlineStr"/>
+      <c r="AA16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB16" s="3">
+      <c r="AC16" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2228,15 +2265,16 @@
       <c r="W17" s="2" t="inlineStr"/>
       <c r="X17" s="2" t="inlineStr"/>
       <c r="Y17" s="2" t="inlineStr"/>
-      <c r="Z17" s="2" t="inlineStr">
+      <c r="Z17" s="2" t="inlineStr"/>
+      <c r="AA17" s="2" t="inlineStr">
         <is>
           <t>ENGRC 465 (Tempe, AZ 85287)</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="b">
+      <c r="AB17" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2314,15 +2352,16 @@
       <c r="W18" s="2" t="inlineStr"/>
       <c r="X18" s="2" t="inlineStr"/>
       <c r="Y18" s="2" t="inlineStr"/>
-      <c r="Z18" s="2" t="inlineStr">
+      <c r="Z18" s="2" t="inlineStr"/>
+      <c r="AA18" s="2" t="inlineStr">
         <is>
           <t>ENGRC 377 (TEMPE, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="b">
+      <c r="AB18" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2343,7 +2382,7 @@
         <v/>
       </c>
       <c r="D19" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Tianyu%20Yang%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=OmBV67MAAAAJ", "Scholar (OmBV67MAAAAJ)")</f>
         <v/>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2356,7 +2395,11 @@
           <t>Aerospace &amp; Mechanical Engineering</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>OmBV67MAAAAJ</t>
+        </is>
+      </c>
       <c r="H19" s="3">
         <f>HYPERLINK("mailto:Tianyu.Yang@asu.edu", "Tianyu.Yang@asu.edu")</f>
         <v/>
@@ -2370,7 +2413,11 @@
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>MAE 241: Intro to Thermodynamics</t>
+        </is>
+      </c>
       <c r="M19" s="2" t="inlineStr"/>
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr"/>
@@ -2393,10 +2440,15 @@
       <c r="X19" s="2" t="inlineStr"/>
       <c r="Y19" s="2" t="inlineStr"/>
       <c r="Z19" s="2" t="inlineStr"/>
-      <c r="AA19" s="2" t="b">
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>Campus: Tempe</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB19" s="3">
+      <c r="AC19" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2448,7 +2500,11 @@
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>MAE 557: Mechanics Composite Materials | MAE 494: Special Topics | MAE 521: Structural Optimization</t>
+        </is>
+      </c>
       <c r="M20" s="2" t="inlineStr"/>
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr"/>
@@ -2475,10 +2531,15 @@
       <c r="X20" s="2" t="inlineStr"/>
       <c r="Y20" s="2" t="inlineStr"/>
       <c r="Z20" s="2" t="inlineStr"/>
-      <c r="AA20" s="2" t="b">
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>ENGRC 427 (TEMPE, AZ 85287-6106)</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2564,15 +2625,16 @@
       <c r="W21" s="2" t="inlineStr"/>
       <c r="X21" s="2" t="inlineStr"/>
       <c r="Y21" s="2" t="inlineStr"/>
-      <c r="Z21" s="2" t="inlineStr">
+      <c r="Z21" s="2" t="inlineStr"/>
+      <c r="AA21" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="b">
+      <c r="AB21" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2664,24 +2726,29 @@
       <c r="V22" s="2" t="inlineStr"/>
       <c r="W22" s="2" t="inlineStr">
         <is>
+          <t>3D Printer</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
           <t>NSF</t>
         </is>
       </c>
-      <c r="X22" s="2" t="inlineStr"/>
-      <c r="Y22" s="2" t="inlineStr">
+      <c r="Y22" s="2" t="inlineStr"/>
+      <c r="Z22" s="2" t="inlineStr">
         <is>
           <t>3D Energy Device Laboratory</t>
         </is>
       </c>
-      <c r="Z22" s="2" t="inlineStr">
+      <c r="AA22" s="2" t="inlineStr">
         <is>
           <t>551 E Tyler Mall ERC 363 (Tempe, AZ 85281)</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="b">
+      <c r="AB22" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2778,15 +2845,16 @@
       <c r="W23" s="2" t="inlineStr"/>
       <c r="X23" s="2" t="inlineStr"/>
       <c r="Y23" s="2" t="inlineStr"/>
-      <c r="Z23" s="2" t="inlineStr">
+      <c r="Z23" s="2" t="inlineStr"/>
+      <c r="AA23" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="b">
+      <c r="AB23" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2863,15 +2931,16 @@
       <c r="W24" s="2" t="inlineStr"/>
       <c r="X24" s="2" t="inlineStr"/>
       <c r="Y24" s="2" t="inlineStr"/>
-      <c r="Z24" s="2" t="inlineStr">
+      <c r="Z24" s="2" t="inlineStr"/>
+      <c r="AA24" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="b">
+      <c r="AB24" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2960,15 +3029,16 @@
       <c r="W25" s="2" t="inlineStr"/>
       <c r="X25" s="2" t="inlineStr"/>
       <c r="Y25" s="2" t="inlineStr"/>
-      <c r="Z25" s="2" t="inlineStr">
+      <c r="Z25" s="2" t="inlineStr"/>
+      <c r="AA25" s="2" t="inlineStr">
         <is>
           <t>ISTB4, ROOM 379 781 S Terrace Rd (Tempe, AZ 85287)</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="b">
+      <c r="AB25" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB25" s="3">
+      <c r="AC25" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -3054,15 +3124,16 @@
       <c r="W26" s="2" t="inlineStr"/>
       <c r="X26" s="2" t="inlineStr"/>
       <c r="Y26" s="2" t="inlineStr"/>
-      <c r="Z26" s="2" t="inlineStr">
+      <c r="Z26" s="2" t="inlineStr"/>
+      <c r="AA26" s="2" t="inlineStr">
         <is>
           <t>ENGRC 463 (TEMPE, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="b">
+      <c r="AB26" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -3147,15 +3218,16 @@
       <c r="W27" s="2" t="inlineStr"/>
       <c r="X27" s="2" t="inlineStr"/>
       <c r="Y27" s="2" t="inlineStr"/>
-      <c r="Z27" s="2" t="inlineStr">
+      <c r="Z27" s="2" t="inlineStr"/>
+      <c r="AA27" s="2" t="inlineStr">
         <is>
           <t>ENGRC 379 (Tempe, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="b">
+      <c r="AB27" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -3245,15 +3317,16 @@
       <c r="W28" s="2" t="inlineStr"/>
       <c r="X28" s="2" t="inlineStr"/>
       <c r="Y28" s="2" t="inlineStr"/>
-      <c r="Z28" s="2" t="inlineStr">
+      <c r="Z28" s="2" t="inlineStr"/>
+      <c r="AA28" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="b">
+      <c r="AB28" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB28" s="3">
+      <c r="AC28" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -3301,7 +3374,11 @@
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>MAE 502: Partial Diff Equations Engr | MAE 460: Applied Comput Fluid Dynamics | MAE 593: Applied Project</t>
+        </is>
+      </c>
       <c r="M29" s="2" t="inlineStr"/>
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr"/>
@@ -3325,16 +3402,21 @@
       <c r="V29" s="2" t="inlineStr"/>
       <c r="W29" s="2" t="inlineStr"/>
       <c r="X29" s="2" t="inlineStr"/>
-      <c r="Y29" s="2" t="inlineStr">
+      <c r="Y29" s="2" t="inlineStr"/>
+      <c r="Z29" s="2" t="inlineStr">
         <is>
           <t>Log in to www_public</t>
         </is>
       </c>
-      <c r="Z29" s="2" t="inlineStr"/>
-      <c r="AA29" s="2" t="b">
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>ENGRC 359 (Tempe, AZ 85287-6106)</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -3430,20 +3512,21 @@
       <c r="V30" s="2" t="inlineStr"/>
       <c r="W30" s="2" t="inlineStr"/>
       <c r="X30" s="2" t="inlineStr"/>
-      <c r="Y30" s="2" t="inlineStr">
+      <c r="Y30" s="2" t="inlineStr"/>
+      <c r="Z30" s="2" t="inlineStr">
         <is>
           <t>Nanostructured Materials</t>
         </is>
       </c>
-      <c r="Z30" s="2" t="inlineStr">
+      <c r="AA30" s="2" t="inlineStr">
         <is>
           <t>ENGRC 355 (Tempe, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="b">
+      <c r="AB30" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB30" s="3">
+      <c r="AC30" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -3530,13 +3613,18 @@
       <c r="Y31" s="2" t="inlineStr"/>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>Rykaczewski Lab</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>ENGRC 309 (Tempe, AZ 85287)</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="b">
+      <c r="AB31" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB31" s="3">
+      <c r="AC31" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -3618,15 +3706,16 @@
       <c r="W32" s="2" t="inlineStr"/>
       <c r="X32" s="2" t="inlineStr"/>
       <c r="Y32" s="2" t="inlineStr"/>
-      <c r="Z32" s="2" t="inlineStr">
+      <c r="Z32" s="2" t="inlineStr"/>
+      <c r="AA32" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="b">
+      <c r="AB32" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -3711,15 +3800,16 @@
       <c r="W33" s="2" t="inlineStr"/>
       <c r="X33" s="2" t="inlineStr"/>
       <c r="Y33" s="2" t="inlineStr"/>
-      <c r="Z33" s="2" t="inlineStr">
+      <c r="Z33" s="2" t="inlineStr"/>
+      <c r="AA33" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="b">
+      <c r="AB33" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -3800,15 +3890,16 @@
       <c r="W34" s="2" t="inlineStr"/>
       <c r="X34" s="2" t="inlineStr"/>
       <c r="Y34" s="2" t="inlineStr"/>
-      <c r="Z34" s="2" t="inlineStr">
+      <c r="Z34" s="2" t="inlineStr"/>
+      <c r="AA34" s="2" t="inlineStr">
         <is>
           <t>Goldwater 466 (TEMPE, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="b">
+      <c r="AB34" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB34" s="3">
+      <c r="AC34" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -3906,29 +3997,30 @@
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr"/>
-      <c r="W35" s="2" t="inlineStr">
+      <c r="W35" s="2" t="inlineStr"/>
+      <c r="X35" s="2" t="inlineStr">
         <is>
           <t>NSF</t>
         </is>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <f>HYPERLINK("https://github.com/asu-iris", "https://github.com/asu-iris")</f>
         <v/>
       </c>
-      <c r="Y35" s="2" t="inlineStr">
+      <c r="Z35" s="2" t="inlineStr">
         <is>
           <t>Recent Updates</t>
         </is>
       </c>
-      <c r="Z35" s="2" t="inlineStr">
+      <c r="AA35" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="b">
+      <c r="AB35" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -4010,15 +4102,16 @@
       <c r="W36" s="2" t="inlineStr"/>
       <c r="X36" s="2" t="inlineStr"/>
       <c r="Y36" s="2" t="inlineStr"/>
-      <c r="Z36" s="2" t="inlineStr">
+      <c r="Z36" s="2" t="inlineStr"/>
+      <c r="AA36" s="2" t="inlineStr">
         <is>
           <t>ENGRC 409 (Tempe, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="b">
+      <c r="AB36" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB36" s="3">
+      <c r="AC36" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -4124,26 +4217,27 @@
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr"/>
-      <c r="W37" s="2" t="inlineStr">
+      <c r="W37" s="2" t="inlineStr"/>
+      <c r="X37" s="2" t="inlineStr">
         <is>
           <t>NSF</t>
         </is>
       </c>
-      <c r="X37" s="2" t="inlineStr"/>
-      <c r="Y37" s="2" t="inlineStr">
+      <c r="Y37" s="2" t="inlineStr"/>
+      <c r="Z37" s="2" t="inlineStr">
         <is>
           <t>Manufacturing</t>
         </is>
       </c>
-      <c r="Z37" s="2" t="inlineStr">
+      <c r="AA37" s="2" t="inlineStr">
         <is>
           <t>ERC457 551 E Tyler Mall (Tempe, AZ 85281)</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="b">
+      <c r="AB37" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB37" s="3">
+      <c r="AC37" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -4218,10 +4312,11 @@
       <c r="X38" s="2" t="inlineStr"/>
       <c r="Y38" s="2" t="inlineStr"/>
       <c r="Z38" s="2" t="inlineStr"/>
-      <c r="AA38" s="2" t="b">
+      <c r="AA38" s="2" t="inlineStr"/>
+      <c r="AB38" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB38" s="3">
+      <c r="AC38" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -4295,15 +4390,16 @@
       <c r="W39" s="2" t="inlineStr"/>
       <c r="X39" s="2" t="inlineStr"/>
       <c r="Y39" s="2" t="inlineStr"/>
-      <c r="Z39" s="2" t="inlineStr">
+      <c r="Z39" s="2" t="inlineStr"/>
+      <c r="AA39" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="b">
+      <c r="AB39" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB39" s="3">
+      <c r="AC39" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -4377,15 +4473,16 @@
       <c r="W40" s="2" t="inlineStr"/>
       <c r="X40" s="2" t="inlineStr"/>
       <c r="Y40" s="2" t="inlineStr"/>
-      <c r="Z40" s="2" t="inlineStr">
+      <c r="Z40" s="2" t="inlineStr"/>
+      <c r="AA40" s="2" t="inlineStr">
         <is>
           <t>ENGRC 411 (TEMPE, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="b">
+      <c r="AB40" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB40" s="3">
+      <c r="AC40" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -4462,15 +4559,16 @@
       <c r="W41" s="2" t="inlineStr"/>
       <c r="X41" s="2" t="inlineStr"/>
       <c r="Y41" s="2" t="inlineStr"/>
-      <c r="Z41" s="2" t="inlineStr">
+      <c r="Z41" s="2" t="inlineStr"/>
+      <c r="AA41" s="2" t="inlineStr">
         <is>
           <t>ENGRC 352 (TEMPE, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="b">
+      <c r="AB41" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -4570,24 +4668,29 @@
       <c r="V42" s="2" t="inlineStr"/>
       <c r="W42" s="2" t="inlineStr">
         <is>
+          <t>SEM</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
           <t>NSF, ONR</t>
         </is>
       </c>
-      <c r="X42" s="2" t="inlineStr"/>
-      <c r="Y42" s="2" t="inlineStr">
+      <c r="Y42" s="2" t="inlineStr"/>
+      <c r="Z42" s="2" t="inlineStr">
         <is>
           <t>Highlighted as a cover in Small</t>
         </is>
       </c>
-      <c r="Z42" s="2" t="inlineStr">
+      <c r="AA42" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="b">
+      <c r="AB42" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -4661,15 +4764,16 @@
       <c r="W43" s="2" t="inlineStr"/>
       <c r="X43" s="2" t="inlineStr"/>
       <c r="Y43" s="2" t="inlineStr"/>
-      <c r="Z43" s="2" t="inlineStr">
+      <c r="Z43" s="2" t="inlineStr"/>
+      <c r="AA43" s="2" t="inlineStr">
         <is>
           <t>GWC 464 (Tempe, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="b">
+      <c r="AB43" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -4680,198 +4784,198 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T2" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X2" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y2" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC2" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T3" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB3" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC3" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T4" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB4" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC4" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T5" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB5" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC5" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB6" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC6" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB7" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC7" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T8" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB8" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC8" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T9" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB9" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC9" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T10" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB10" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC10" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB11" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC11" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T12" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB12" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC12" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T13" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB13" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC13" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB14" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC14" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId63"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T15" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB15" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC15" r:id="rId67"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId69"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T16" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB16" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC16" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId73"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId75"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T17" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB17" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC17" r:id="rId77"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId79"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB18" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC18" r:id="rId81"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId82"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId83"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB19" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC19" r:id="rId85"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId87"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB20" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC20" r:id="rId89"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId91"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB21" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC21" r:id="rId93"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId95"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId96"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T22" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB22" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC22" r:id="rId98"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId99"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId100"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId101"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T23" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB23" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC23" r:id="rId103"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId104"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId105"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId106"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T24" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB24" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC24" r:id="rId108"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId109"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId110"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId111"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T25" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB25" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC25" r:id="rId113"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId114"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId115"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB26" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC26" r:id="rId117"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId118"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId119"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T27" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB27" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC27" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId123"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId124"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB28" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC28" r:id="rId126"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId127"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId128"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId129"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T29" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB29" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC29" r:id="rId131"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId132"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId133"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId134"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T30" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB30" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC30" r:id="rId136"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId137"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId138"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId139"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T31" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB31" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC31" r:id="rId141"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId142"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId143"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB32" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC32" r:id="rId145"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId146"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId147"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId148"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T33" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB33" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC33" r:id="rId150"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId151"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId152"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId153"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T34" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB34" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC34" r:id="rId155"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId156"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId157"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId158"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T35" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X35" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB35" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y35" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC35" r:id="rId161"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId162"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId163"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB36" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC36" r:id="rId165"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId166"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId167"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId168"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T37" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB37" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC37" r:id="rId170"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId171"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId172"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB38" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC38" r:id="rId174"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId175"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId176"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB39" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC39" r:id="rId178"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId179"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId180"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB40" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC40" r:id="rId182"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId183"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId184"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId185"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T41" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB41" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC41" r:id="rId187"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId188"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId189"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId190"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T42" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB42" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC42" r:id="rId192"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId193"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId194"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB43" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC43" r:id="rId196"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4883,7 +4987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB49"/>
+  <dimension ref="A1:AC49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4908,12 +5012,13 @@
     <col width="49" customWidth="1" min="20" max="20"/>
     <col width="65" customWidth="1" min="21" max="21"/>
     <col width="53" customWidth="1" min="22" max="22"/>
-    <col width="20" customWidth="1" min="23" max="23"/>
-    <col width="49" customWidth="1" min="24" max="24"/>
-    <col width="56" customWidth="1" min="25" max="25"/>
-    <col width="54" customWidth="1" min="26" max="26"/>
-    <col width="18" customWidth="1" min="27" max="27"/>
-    <col width="49" customWidth="1" min="28" max="28"/>
+    <col width="30" customWidth="1" min="23" max="23"/>
+    <col width="20" customWidth="1" min="24" max="24"/>
+    <col width="49" customWidth="1" min="25" max="25"/>
+    <col width="56" customWidth="1" min="26" max="26"/>
+    <col width="65" customWidth="1" min="27" max="27"/>
+    <col width="18" customWidth="1" min="28" max="28"/>
+    <col width="49" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5029,30 +5134,35 @@
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
+          <t>Lab Facilities &amp; Equipment</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
           <t>Funding Sponsors</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Software / Code Repo</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Latest Project / Highlight</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Office Location</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Is Field Match</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Directory URL</t>
         </is>
@@ -5105,7 +5215,11 @@
           <t>Refereed Journal Papers M. H. Kasbaoui and M. Herrmann, A high-fidelity methodology for particle-resolved direct numerical simu...</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>MAE 242: Intro to Fluid Mechanics | MAE 574: Multiphase Flow | MAE 501: Linear Algebra in Engineering</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="2" t="inlineStr"/>
@@ -5135,25 +5249,30 @@
           <t>CFD</t>
         </is>
       </c>
-      <c r="W2" s="2" t="inlineStr">
+      <c r="W2" s="2" t="inlineStr"/>
+      <c r="X2" s="2" t="inlineStr">
         <is>
           <t>AFOSR</t>
         </is>
       </c>
-      <c r="X2" s="3">
+      <c r="Y2" s="3">
         <f>HYPERLINK("https://bitbucket.org/krgasu/leap/downloads/leap-v0.8.2.tar.gz", "https://bitbucket.org/krgasu/leap/downloads/leap-v0.8.2.tar.gz, https://bitbucket.org/krgasu/leap/src/master")</f>
         <v/>
       </c>
-      <c r="Y2" s="2" t="inlineStr">
+      <c r="Z2" s="2" t="inlineStr">
         <is>
           <t>School for Engineering of Matter, Transport &amp; Energy</t>
         </is>
       </c>
-      <c r="Z2" s="2" t="inlineStr"/>
-      <c r="AA2" s="2" t="b">
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
+          <t>Campus: Tempe</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB2" s="3">
+      <c r="AC2" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -5253,24 +5372,29 @@
       <c r="V3" s="2" t="inlineStr"/>
       <c r="W3" s="2" t="inlineStr">
         <is>
+          <t>AFM</t>
+        </is>
+      </c>
+      <c r="X3" s="2" t="inlineStr">
+        <is>
           <t>NASA, NSF</t>
         </is>
       </c>
-      <c r="X3" s="2" t="inlineStr"/>
-      <c r="Y3" s="2" t="inlineStr">
+      <c r="Y3" s="2" t="inlineStr"/>
+      <c r="Z3" s="2" t="inlineStr">
         <is>
           <t>News&amp;Awards</t>
         </is>
       </c>
-      <c r="Z3" s="2" t="inlineStr">
+      <c r="AA3" s="2" t="inlineStr">
         <is>
           <t>ENGRC 327 (Tempe, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="b">
+      <c r="AB3" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB3" s="3">
+      <c r="AC3" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -5358,20 +5482,21 @@
       <c r="V4" s="2" t="inlineStr"/>
       <c r="W4" s="2" t="inlineStr"/>
       <c r="X4" s="2" t="inlineStr"/>
-      <c r="Y4" s="2" t="inlineStr">
+      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr">
         <is>
           <t>Multiscale polymer analysis</t>
         </is>
       </c>
-      <c r="Z4" s="2" t="inlineStr">
+      <c r="AA4" s="2" t="inlineStr">
         <is>
           <t>ENGRC 353 (Tempe, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="b">
+      <c r="AB4" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB4" s="3">
+      <c r="AC4" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -5475,20 +5600,21 @@
       <c r="V5" s="2" t="inlineStr"/>
       <c r="W5" s="2" t="inlineStr"/>
       <c r="X5" s="2" t="inlineStr"/>
-      <c r="Y5" s="2" t="inlineStr">
+      <c r="Y5" s="2" t="inlineStr"/>
+      <c r="Z5" s="2" t="inlineStr">
         <is>
           <t>Mission and Core Values</t>
         </is>
       </c>
-      <c r="Z5" s="2" t="inlineStr">
+      <c r="AA5" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="b">
+      <c r="AB5" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB5" s="3">
+      <c r="AC5" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -5566,15 +5692,16 @@
       <c r="W6" s="2" t="inlineStr"/>
       <c r="X6" s="2" t="inlineStr"/>
       <c r="Y6" s="2" t="inlineStr"/>
-      <c r="Z6" s="2" t="inlineStr">
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr">
         <is>
           <t>ENGRC 361 (TEMPE, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="b">
+      <c r="AB6" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB6" s="3">
+      <c r="AC6" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -5626,7 +5753,11 @@
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>MAE 242: Intro to Fluid Mechanics | MAE 593: Applied Project | MAE 564: Advanced Aerodynamics</t>
+        </is>
+      </c>
       <c r="M7" s="2" t="inlineStr"/>
       <c r="N7" s="2" t="inlineStr"/>
       <c r="O7" s="2" t="inlineStr">
@@ -5653,10 +5784,15 @@
       <c r="X7" s="2" t="inlineStr"/>
       <c r="Y7" s="2" t="inlineStr"/>
       <c r="Z7" s="2" t="inlineStr"/>
-      <c r="AA7" s="2" t="b">
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>Engineering research centre Room 383 551 E Tyler mall (Tempe, AZ 85281)</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB7" s="3">
+      <c r="AC7" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -5765,15 +5901,16 @@
       <c r="W8" s="2" t="inlineStr"/>
       <c r="X8" s="2" t="inlineStr"/>
       <c r="Y8" s="2" t="inlineStr"/>
-      <c r="Z8" s="2" t="inlineStr">
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr">
         <is>
           <t>551 E Tyler Mall ERC 475 (Tempe, AZ 85281)</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="b">
+      <c r="AB8" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -5875,22 +6012,27 @@
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr"/>
-      <c r="W9" s="2" t="inlineStr"/>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>Towing Tank, FDM</t>
+        </is>
+      </c>
       <c r="X9" s="2" t="inlineStr"/>
-      <c r="Y9" s="2" t="inlineStr">
+      <c r="Y9" s="2" t="inlineStr"/>
+      <c r="Z9" s="2" t="inlineStr">
         <is>
           <t>Ocean and Soft Intelligent Structure Interaction Lab</t>
         </is>
       </c>
-      <c r="Z9" s="2" t="inlineStr">
+      <c r="AA9" s="2" t="inlineStr">
         <is>
           <t>ERC 485 (Tempe, AZ 85287)</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="b">
+      <c r="AB9" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -5978,20 +6120,21 @@
       <c r="V10" s="2" t="inlineStr"/>
       <c r="W10" s="2" t="inlineStr"/>
       <c r="X10" s="2" t="inlineStr"/>
-      <c r="Y10" s="2" t="inlineStr">
+      <c r="Y10" s="2" t="inlineStr"/>
+      <c r="Z10" s="2" t="inlineStr">
         <is>
           <t>Want to be part of CMAT Lab?</t>
         </is>
       </c>
-      <c r="Z10" s="2" t="inlineStr">
+      <c r="AA10" s="2" t="inlineStr">
         <is>
           <t>551 E Tyler Mall ERC 479 (Tempe, AZ 85281)</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="b">
+      <c r="AB10" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -6073,15 +6216,16 @@
       <c r="W11" s="2" t="inlineStr"/>
       <c r="X11" s="2" t="inlineStr"/>
       <c r="Y11" s="2" t="inlineStr"/>
-      <c r="Z11" s="2" t="inlineStr">
+      <c r="Z11" s="2" t="inlineStr"/>
+      <c r="AA11" s="2" t="inlineStr">
         <is>
           <t>ENGRC 311 (TEMPE, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="b">
+      <c r="AB11" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB11" s="3">
+      <c r="AC11" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -6174,15 +6318,16 @@
       <c r="W12" s="2" t="inlineStr"/>
       <c r="X12" s="2" t="inlineStr"/>
       <c r="Y12" s="2" t="inlineStr"/>
-      <c r="Z12" s="2" t="inlineStr">
+      <c r="Z12" s="2" t="inlineStr"/>
+      <c r="AA12" s="2" t="inlineStr">
         <is>
           <t>ENGRC 375 (Tempe, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="b">
+      <c r="AB12" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -6271,15 +6416,16 @@
       <c r="W13" s="2" t="inlineStr"/>
       <c r="X13" s="2" t="inlineStr"/>
       <c r="Y13" s="2" t="inlineStr"/>
-      <c r="Z13" s="2" t="inlineStr">
+      <c r="Z13" s="2" t="inlineStr"/>
+      <c r="AA13" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="b">
+      <c r="AB13" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB13" s="3">
+      <c r="AC13" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -6353,15 +6499,16 @@
       <c r="W14" s="2" t="inlineStr"/>
       <c r="X14" s="2" t="inlineStr"/>
       <c r="Y14" s="2" t="inlineStr"/>
-      <c r="Z14" s="2" t="inlineStr">
+      <c r="Z14" s="2" t="inlineStr"/>
+      <c r="AA14" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="b">
+      <c r="AB14" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -6454,15 +6601,16 @@
       <c r="W15" s="2" t="inlineStr"/>
       <c r="X15" s="2" t="inlineStr"/>
       <c r="Y15" s="2" t="inlineStr"/>
-      <c r="Z15" s="2" t="inlineStr">
+      <c r="Z15" s="2" t="inlineStr"/>
+      <c r="AA15" s="2" t="inlineStr">
         <is>
           <t>ENGRC 253 (Tempe, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="b">
+      <c r="AB15" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -6514,11 +6662,7 @@
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>MAE 241: Intro to Thermodynamics | MAE 593: Applied Project | MAE 588: Nanoscale Heat Transfer</t>
-        </is>
-      </c>
+      <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
@@ -6551,15 +6695,12 @@
       <c r="W16" s="2" t="inlineStr"/>
       <c r="X16" s="2" t="inlineStr"/>
       <c r="Y16" s="2" t="inlineStr"/>
-      <c r="Z16" s="2" t="inlineStr">
-        <is>
-          <t>ENGRC 307 (Tempe, AZ 85287-6106)</t>
-        </is>
-      </c>
-      <c r="AA16" s="2" t="b">
+      <c r="Z16" s="2" t="inlineStr"/>
+      <c r="AA16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB16" s="3">
+      <c r="AC16" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -6656,15 +6797,16 @@
       <c r="W17" s="2" t="inlineStr"/>
       <c r="X17" s="2" t="inlineStr"/>
       <c r="Y17" s="2" t="inlineStr"/>
-      <c r="Z17" s="2" t="inlineStr">
+      <c r="Z17" s="2" t="inlineStr"/>
+      <c r="AA17" s="2" t="inlineStr">
         <is>
           <t>ENGRC 465 (Tempe, AZ 85287)</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="b">
+      <c r="AB17" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -6742,15 +6884,16 @@
       <c r="W18" s="2" t="inlineStr"/>
       <c r="X18" s="2" t="inlineStr"/>
       <c r="Y18" s="2" t="inlineStr"/>
-      <c r="Z18" s="2" t="inlineStr">
+      <c r="Z18" s="2" t="inlineStr"/>
+      <c r="AA18" s="2" t="inlineStr">
         <is>
           <t>ENGRC 377 (TEMPE, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="b">
+      <c r="AB18" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -6771,7 +6914,7 @@
         <v/>
       </c>
       <c r="D19" s="3">
-        <f>HYPERLINK("https://scholar.google.com/citations?view_op=search_authors&amp;mauthors=Tianyu%20Yang%20Arizona%20State%20University", "Google Scholar Search")</f>
+        <f>HYPERLINK("https://scholar.google.com/citations?hl=en&amp;user=OmBV67MAAAAJ", "Scholar (OmBV67MAAAAJ)")</f>
         <v/>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -6784,7 +6927,11 @@
           <t>Aerospace &amp; Mechanical Engineering</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>OmBV67MAAAAJ</t>
+        </is>
+      </c>
       <c r="H19" s="3">
         <f>HYPERLINK("mailto:Tianyu.Yang@asu.edu", "Tianyu.Yang@asu.edu")</f>
         <v/>
@@ -6798,7 +6945,11 @@
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>MAE 241: Intro to Thermodynamics</t>
+        </is>
+      </c>
       <c r="M19" s="2" t="inlineStr"/>
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr"/>
@@ -6821,10 +6972,15 @@
       <c r="X19" s="2" t="inlineStr"/>
       <c r="Y19" s="2" t="inlineStr"/>
       <c r="Z19" s="2" t="inlineStr"/>
-      <c r="AA19" s="2" t="b">
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>Campus: Tempe</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB19" s="3">
+      <c r="AC19" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -6876,7 +7032,11 @@
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>MAE 557: Mechanics Composite Materials | MAE 494: Special Topics | MAE 521: Structural Optimization</t>
+        </is>
+      </c>
       <c r="M20" s="2" t="inlineStr"/>
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr"/>
@@ -6903,10 +7063,15 @@
       <c r="X20" s="2" t="inlineStr"/>
       <c r="Y20" s="2" t="inlineStr"/>
       <c r="Z20" s="2" t="inlineStr"/>
-      <c r="AA20" s="2" t="b">
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>ENGRC 427 (TEMPE, AZ 85287-6106)</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -6992,15 +7157,16 @@
       <c r="W21" s="2" t="inlineStr"/>
       <c r="X21" s="2" t="inlineStr"/>
       <c r="Y21" s="2" t="inlineStr"/>
-      <c r="Z21" s="2" t="inlineStr">
+      <c r="Z21" s="2" t="inlineStr"/>
+      <c r="AA21" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="b">
+      <c r="AB21" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -7092,24 +7258,29 @@
       <c r="V22" s="2" t="inlineStr"/>
       <c r="W22" s="2" t="inlineStr">
         <is>
+          <t>3D Printer</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
           <t>NSF</t>
         </is>
       </c>
-      <c r="X22" s="2" t="inlineStr"/>
-      <c r="Y22" s="2" t="inlineStr">
+      <c r="Y22" s="2" t="inlineStr"/>
+      <c r="Z22" s="2" t="inlineStr">
         <is>
           <t>3D Energy Device Laboratory</t>
         </is>
       </c>
-      <c r="Z22" s="2" t="inlineStr">
+      <c r="AA22" s="2" t="inlineStr">
         <is>
           <t>551 E Tyler Mall ERC 363 (Tempe, AZ 85281)</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="b">
+      <c r="AB22" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -7206,15 +7377,16 @@
       <c r="W23" s="2" t="inlineStr"/>
       <c r="X23" s="2" t="inlineStr"/>
       <c r="Y23" s="2" t="inlineStr"/>
-      <c r="Z23" s="2" t="inlineStr">
+      <c r="Z23" s="2" t="inlineStr"/>
+      <c r="AA23" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="b">
+      <c r="AB23" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -7291,15 +7463,16 @@
       <c r="W24" s="2" t="inlineStr"/>
       <c r="X24" s="2" t="inlineStr"/>
       <c r="Y24" s="2" t="inlineStr"/>
-      <c r="Z24" s="2" t="inlineStr">
+      <c r="Z24" s="2" t="inlineStr"/>
+      <c r="AA24" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="b">
+      <c r="AB24" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -7388,15 +7561,16 @@
       <c r="W25" s="2" t="inlineStr"/>
       <c r="X25" s="2" t="inlineStr"/>
       <c r="Y25" s="2" t="inlineStr"/>
-      <c r="Z25" s="2" t="inlineStr">
+      <c r="Z25" s="2" t="inlineStr"/>
+      <c r="AA25" s="2" t="inlineStr">
         <is>
           <t>ISTB4, ROOM 379 781 S Terrace Rd (Tempe, AZ 85287)</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="b">
+      <c r="AB25" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB25" s="3">
+      <c r="AC25" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -7482,15 +7656,16 @@
       <c r="W26" s="2" t="inlineStr"/>
       <c r="X26" s="2" t="inlineStr"/>
       <c r="Y26" s="2" t="inlineStr"/>
-      <c r="Z26" s="2" t="inlineStr">
+      <c r="Z26" s="2" t="inlineStr"/>
+      <c r="AA26" s="2" t="inlineStr">
         <is>
           <t>ENGRC 463 (TEMPE, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="b">
+      <c r="AB26" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -7575,15 +7750,16 @@
       <c r="W27" s="2" t="inlineStr"/>
       <c r="X27" s="2" t="inlineStr"/>
       <c r="Y27" s="2" t="inlineStr"/>
-      <c r="Z27" s="2" t="inlineStr">
+      <c r="Z27" s="2" t="inlineStr"/>
+      <c r="AA27" s="2" t="inlineStr">
         <is>
           <t>ENGRC 379 (Tempe, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="b">
+      <c r="AB27" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -7673,15 +7849,16 @@
       <c r="W28" s="2" t="inlineStr"/>
       <c r="X28" s="2" t="inlineStr"/>
       <c r="Y28" s="2" t="inlineStr"/>
-      <c r="Z28" s="2" t="inlineStr">
+      <c r="Z28" s="2" t="inlineStr"/>
+      <c r="AA28" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="b">
+      <c r="AB28" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB28" s="3">
+      <c r="AC28" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -7729,7 +7906,11 @@
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>MAE 502: Partial Diff Equations Engr | MAE 460: Applied Comput Fluid Dynamics | MAE 593: Applied Project</t>
+        </is>
+      </c>
       <c r="M29" s="2" t="inlineStr"/>
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr"/>
@@ -7753,16 +7934,21 @@
       <c r="V29" s="2" t="inlineStr"/>
       <c r="W29" s="2" t="inlineStr"/>
       <c r="X29" s="2" t="inlineStr"/>
-      <c r="Y29" s="2" t="inlineStr">
+      <c r="Y29" s="2" t="inlineStr"/>
+      <c r="Z29" s="2" t="inlineStr">
         <is>
           <t>Log in to www_public</t>
         </is>
       </c>
-      <c r="Z29" s="2" t="inlineStr"/>
-      <c r="AA29" s="2" t="b">
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>ENGRC 359 (Tempe, AZ 85287-6106)</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -7858,20 +8044,21 @@
       <c r="V30" s="2" t="inlineStr"/>
       <c r="W30" s="2" t="inlineStr"/>
       <c r="X30" s="2" t="inlineStr"/>
-      <c r="Y30" s="2" t="inlineStr">
+      <c r="Y30" s="2" t="inlineStr"/>
+      <c r="Z30" s="2" t="inlineStr">
         <is>
           <t>Nanostructured Materials</t>
         </is>
       </c>
-      <c r="Z30" s="2" t="inlineStr">
+      <c r="AA30" s="2" t="inlineStr">
         <is>
           <t>ENGRC 355 (Tempe, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="b">
+      <c r="AB30" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB30" s="3">
+      <c r="AC30" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -7958,13 +8145,18 @@
       <c r="Y31" s="2" t="inlineStr"/>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>Rykaczewski Lab</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>ENGRC 309 (Tempe, AZ 85287)</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="b">
+      <c r="AB31" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB31" s="3">
+      <c r="AC31" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -8046,15 +8238,16 @@
       <c r="W32" s="2" t="inlineStr"/>
       <c r="X32" s="2" t="inlineStr"/>
       <c r="Y32" s="2" t="inlineStr"/>
-      <c r="Z32" s="2" t="inlineStr">
+      <c r="Z32" s="2" t="inlineStr"/>
+      <c r="AA32" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="b">
+      <c r="AB32" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -8139,15 +8332,16 @@
       <c r="W33" s="2" t="inlineStr"/>
       <c r="X33" s="2" t="inlineStr"/>
       <c r="Y33" s="2" t="inlineStr"/>
-      <c r="Z33" s="2" t="inlineStr">
+      <c r="Z33" s="2" t="inlineStr"/>
+      <c r="AA33" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="b">
+      <c r="AB33" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -8228,15 +8422,16 @@
       <c r="W34" s="2" t="inlineStr"/>
       <c r="X34" s="2" t="inlineStr"/>
       <c r="Y34" s="2" t="inlineStr"/>
-      <c r="Z34" s="2" t="inlineStr">
+      <c r="Z34" s="2" t="inlineStr"/>
+      <c r="AA34" s="2" t="inlineStr">
         <is>
           <t>Goldwater 466 (TEMPE, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="b">
+      <c r="AB34" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB34" s="3">
+      <c r="AC34" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -8334,29 +8529,30 @@
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr"/>
-      <c r="W35" s="2" t="inlineStr">
+      <c r="W35" s="2" t="inlineStr"/>
+      <c r="X35" s="2" t="inlineStr">
         <is>
           <t>NSF</t>
         </is>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <f>HYPERLINK("https://github.com/asu-iris", "https://github.com/asu-iris")</f>
         <v/>
       </c>
-      <c r="Y35" s="2" t="inlineStr">
+      <c r="Z35" s="2" t="inlineStr">
         <is>
           <t>Recent Updates</t>
         </is>
       </c>
-      <c r="Z35" s="2" t="inlineStr">
+      <c r="AA35" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="b">
+      <c r="AB35" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -8438,15 +8634,16 @@
       <c r="W36" s="2" t="inlineStr"/>
       <c r="X36" s="2" t="inlineStr"/>
       <c r="Y36" s="2" t="inlineStr"/>
-      <c r="Z36" s="2" t="inlineStr">
+      <c r="Z36" s="2" t="inlineStr"/>
+      <c r="AA36" s="2" t="inlineStr">
         <is>
           <t>ENGRC 409 (Tempe, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="b">
+      <c r="AB36" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB36" s="3">
+      <c r="AC36" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -8552,26 +8749,27 @@
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr"/>
-      <c r="W37" s="2" t="inlineStr">
+      <c r="W37" s="2" t="inlineStr"/>
+      <c r="X37" s="2" t="inlineStr">
         <is>
           <t>NSF</t>
         </is>
       </c>
-      <c r="X37" s="2" t="inlineStr"/>
-      <c r="Y37" s="2" t="inlineStr">
+      <c r="Y37" s="2" t="inlineStr"/>
+      <c r="Z37" s="2" t="inlineStr">
         <is>
           <t>Manufacturing</t>
         </is>
       </c>
-      <c r="Z37" s="2" t="inlineStr">
+      <c r="AA37" s="2" t="inlineStr">
         <is>
           <t>ERC457 551 E Tyler Mall (Tempe, AZ 85281)</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="b">
+      <c r="AB37" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB37" s="3">
+      <c r="AC37" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -8646,10 +8844,11 @@
       <c r="X38" s="2" t="inlineStr"/>
       <c r="Y38" s="2" t="inlineStr"/>
       <c r="Z38" s="2" t="inlineStr"/>
-      <c r="AA38" s="2" t="b">
+      <c r="AA38" s="2" t="inlineStr"/>
+      <c r="AB38" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB38" s="3">
+      <c r="AC38" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -8723,15 +8922,16 @@
       <c r="W39" s="2" t="inlineStr"/>
       <c r="X39" s="2" t="inlineStr"/>
       <c r="Y39" s="2" t="inlineStr"/>
-      <c r="Z39" s="2" t="inlineStr">
+      <c r="Z39" s="2" t="inlineStr"/>
+      <c r="AA39" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="b">
+      <c r="AB39" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB39" s="3">
+      <c r="AC39" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -8805,15 +9005,16 @@
       <c r="W40" s="2" t="inlineStr"/>
       <c r="X40" s="2" t="inlineStr"/>
       <c r="Y40" s="2" t="inlineStr"/>
-      <c r="Z40" s="2" t="inlineStr">
+      <c r="Z40" s="2" t="inlineStr"/>
+      <c r="AA40" s="2" t="inlineStr">
         <is>
           <t>ENGRC 411 (TEMPE, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="b">
+      <c r="AB40" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB40" s="3">
+      <c r="AC40" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -8890,15 +9091,16 @@
       <c r="W41" s="2" t="inlineStr"/>
       <c r="X41" s="2" t="inlineStr"/>
       <c r="Y41" s="2" t="inlineStr"/>
-      <c r="Z41" s="2" t="inlineStr">
+      <c r="Z41" s="2" t="inlineStr"/>
+      <c r="AA41" s="2" t="inlineStr">
         <is>
           <t>ENGRC 352 (TEMPE, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="b">
+      <c r="AB41" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -8998,24 +9200,29 @@
       <c r="V42" s="2" t="inlineStr"/>
       <c r="W42" s="2" t="inlineStr">
         <is>
+          <t>SEM</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
           <t>NSF, ONR</t>
         </is>
       </c>
-      <c r="X42" s="2" t="inlineStr"/>
-      <c r="Y42" s="2" t="inlineStr">
+      <c r="Y42" s="2" t="inlineStr"/>
+      <c r="Z42" s="2" t="inlineStr">
         <is>
           <t>Highlighted as a cover in Small</t>
         </is>
       </c>
-      <c r="Z42" s="2" t="inlineStr">
+      <c r="AA42" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="b">
+      <c r="AB42" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -9089,15 +9296,16 @@
       <c r="W43" s="2" t="inlineStr"/>
       <c r="X43" s="2" t="inlineStr"/>
       <c r="Y43" s="2" t="inlineStr"/>
-      <c r="Z43" s="2" t="inlineStr">
+      <c r="Z43" s="2" t="inlineStr"/>
+      <c r="AA43" s="2" t="inlineStr">
         <is>
           <t>GWC 464 (Tempe, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="b">
+      <c r="AB43" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -9159,15 +9367,16 @@
       <c r="W44" s="2" t="inlineStr"/>
       <c r="X44" s="2" t="inlineStr"/>
       <c r="Y44" s="2" t="inlineStr"/>
-      <c r="Z44" s="2" t="inlineStr">
+      <c r="Z44" s="2" t="inlineStr"/>
+      <c r="AA44" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="b">
+      <c r="AB44" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -9211,7 +9420,11 @@
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
-      <c r="L45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>MAE 301: Applied Experimental Statistic | MAE 202: Mech.Particles/Rigid Bodies II | MAE 417: System Dynamics and Control II</t>
+        </is>
+      </c>
       <c r="M45" s="2" t="inlineStr"/>
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr"/>
@@ -9230,10 +9443,15 @@
       <c r="X45" s="2" t="inlineStr"/>
       <c r="Y45" s="2" t="inlineStr"/>
       <c r="Z45" s="2" t="inlineStr"/>
-      <c r="AA45" s="2" t="b">
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>Campus: Otherus</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -9295,15 +9513,16 @@
       <c r="W46" s="2" t="inlineStr"/>
       <c r="X46" s="2" t="inlineStr"/>
       <c r="Y46" s="2" t="inlineStr"/>
-      <c r="Z46" s="2" t="inlineStr">
+      <c r="Z46" s="2" t="inlineStr"/>
+      <c r="AA46" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="b">
+      <c r="AB46" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -9347,7 +9566,11 @@
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
-      <c r="L47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>MAE 241: Intro to Thermodynamics | MAE 215: Intro to Programming in MATLAB | MAE 384: Adv Math Methods for Engineers</t>
+        </is>
+      </c>
       <c r="M47" s="2" t="inlineStr"/>
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr"/>
@@ -9362,10 +9585,15 @@
       <c r="X47" s="2" t="inlineStr"/>
       <c r="Y47" s="2" t="inlineStr"/>
       <c r="Z47" s="2" t="inlineStr"/>
-      <c r="AA47" s="2" t="b">
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>Campus: Tempe</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -9427,15 +9655,16 @@
       <c r="W48" s="2" t="inlineStr"/>
       <c r="X48" s="2" t="inlineStr"/>
       <c r="Y48" s="2" t="inlineStr"/>
-      <c r="Z48" s="2" t="inlineStr">
+      <c r="Z48" s="2" t="inlineStr"/>
+      <c r="AA48" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="b">
+      <c r="AB48" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -9479,11 +9708,7 @@
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>MAE 570: Intermediate Thermodynamics | MAE 400: Engineering Profession | MAE 494: Special Topics</t>
-        </is>
-      </c>
+      <c r="L49" s="2" t="inlineStr"/>
       <c r="M49" s="2" t="inlineStr"/>
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr"/>
@@ -9497,15 +9722,12 @@
       <c r="W49" s="2" t="inlineStr"/>
       <c r="X49" s="2" t="inlineStr"/>
       <c r="Y49" s="2" t="inlineStr"/>
-      <c r="Z49" s="2" t="inlineStr">
-        <is>
-          <t>Campus: Tempe</t>
-        </is>
-      </c>
-      <c r="AA49" s="2" t="b">
+      <c r="Z49" s="2" t="inlineStr"/>
+      <c r="AA49" s="2" t="inlineStr"/>
+      <c r="AB49" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -9516,222 +9738,222 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T2" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X2" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y2" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC2" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T3" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB3" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC3" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T4" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB4" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC4" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T5" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB5" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC5" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB6" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC6" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB7" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC7" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T8" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB8" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC8" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T9" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB9" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC9" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T10" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB10" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC10" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB11" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC11" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T12" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB12" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC12" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T13" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB13" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC13" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB14" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC14" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId63"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T15" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB15" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC15" r:id="rId67"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId69"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T16" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB16" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC16" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId73"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId75"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T17" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB17" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC17" r:id="rId77"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId79"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB18" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC18" r:id="rId81"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId82"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId83"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB19" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC19" r:id="rId85"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId87"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB20" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC20" r:id="rId89"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId91"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB21" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC21" r:id="rId93"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId95"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId96"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T22" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB22" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC22" r:id="rId98"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId99"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId100"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId101"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T23" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB23" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC23" r:id="rId103"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId104"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId105"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId106"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T24" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB24" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC24" r:id="rId108"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId109"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId110"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId111"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T25" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB25" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC25" r:id="rId113"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId114"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId115"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB26" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC26" r:id="rId117"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId118"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId119"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T27" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB27" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC27" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId123"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId124"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB28" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC28" r:id="rId126"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId127"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId128"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId129"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T29" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB29" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC29" r:id="rId131"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId132"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId133"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId134"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T30" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB30" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC30" r:id="rId136"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId137"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId138"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId139"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T31" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB31" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC31" r:id="rId141"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId142"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId143"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB32" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC32" r:id="rId145"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId146"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId147"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId148"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T33" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB33" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC33" r:id="rId150"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId151"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId152"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId153"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T34" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB34" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC34" r:id="rId155"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId156"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId157"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId158"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T35" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X35" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB35" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y35" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC35" r:id="rId161"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId162"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId163"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB36" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC36" r:id="rId165"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId166"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId167"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId168"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T37" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB37" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC37" r:id="rId170"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId171"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId172"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB38" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC38" r:id="rId174"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId175"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId176"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB39" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC39" r:id="rId178"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId179"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId180"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB40" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC40" r:id="rId182"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId183"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId184"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId185"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T41" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB41" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC41" r:id="rId187"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId188"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId189"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId190"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T42" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB42" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC42" r:id="rId192"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId193"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId194"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB43" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC43" r:id="rId196"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" r:id="rId197"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId198"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB44" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC44" r:id="rId200"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="rId201"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId202"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB45" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC45" r:id="rId204"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C46" r:id="rId205"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId206"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB46" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC46" r:id="rId208"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId209"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId210"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB47" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC47" r:id="rId212"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId213"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId214"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB48" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC48" r:id="rId216"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId217"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId218"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB49" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC49" r:id="rId220"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/universities_wise/arizona_state_university/asu_aerospace_mechanical_faculty.xlsx
+++ b/universities_wise/arizona_state_university/asu_aerospace_mechanical_faculty.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC43"/>
+  <dimension ref="A1:AF43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -477,16 +477,19 @@
     <col width="65" customWidth="1" min="17" max="17"/>
     <col width="65" customWidth="1" min="18" max="18"/>
     <col width="65" customWidth="1" min="19" max="19"/>
-    <col width="49" customWidth="1" min="20" max="20"/>
+    <col width="65" customWidth="1" min="20" max="20"/>
     <col width="65" customWidth="1" min="21" max="21"/>
-    <col width="53" customWidth="1" min="22" max="22"/>
-    <col width="30" customWidth="1" min="23" max="23"/>
-    <col width="20" customWidth="1" min="24" max="24"/>
-    <col width="49" customWidth="1" min="25" max="25"/>
-    <col width="56" customWidth="1" min="26" max="26"/>
-    <col width="65" customWidth="1" min="27" max="27"/>
-    <col width="18" customWidth="1" min="28" max="28"/>
-    <col width="49" customWidth="1" min="29" max="29"/>
+    <col width="65" customWidth="1" min="22" max="22"/>
+    <col width="49" customWidth="1" min="23" max="23"/>
+    <col width="65" customWidth="1" min="24" max="24"/>
+    <col width="53" customWidth="1" min="25" max="25"/>
+    <col width="30" customWidth="1" min="26" max="26"/>
+    <col width="20" customWidth="1" min="27" max="27"/>
+    <col width="49" customWidth="1" min="28" max="28"/>
+    <col width="56" customWidth="1" min="29" max="29"/>
+    <col width="65" customWidth="1" min="30" max="30"/>
+    <col width="18" customWidth="1" min="31" max="31"/>
+    <col width="49" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -547,90 +550,105 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>Recent Papers (2024-2026)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Top Cited Papers</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>Courses Taught</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Recent Awards / Honors</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Cold Email / Application Instructions</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Google Scholar Tags</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Research Interests</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Expertise Areas</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Research / Bio Summary</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Education / Degrees</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Lab / Research Group Name</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Lab / Personal Website</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Actively Hiring / Openings</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Target Skills / Prerequisites</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Lab Facilities &amp; Equipment</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Funding Sponsors</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Software / Code Repo</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Latest Project / Highlight</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Office Location</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Is Field Match</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Directory URL</t>
         </is>
@@ -685,62 +703,77 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
+          <t>"Modelling the wall slip in large eddy simulations with immersed boundaries" [Journal of Fluid Mechanics] (2026) | "Dynamics of an oscillatory boundary layer over a sediment bed in Euler–Lagrange simulations" [Journal of Fluid Mechanics] (2025) | "Modeling the wall-slip in large eddy simulations with immersed boundaries" [arXiv (Cornell University)] (2025)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>"Clustering in Euler–Euler and Euler–Lagrange simulations of unbounded homogeneous particle-laden shear" [Journal of Fluid Mechanics] (2018, 40 cites) | "Accelerated decay of a Lamb–Oseen vortex tube laden with inertial particles in Eulerian–Lagrangian simulations" [Journal of Fluid Mechanics] (2022, 22 cites) | "Reynolds number scaling of burning rates in spherical turbulent premixed flames" [Journal of Fluid Mechanics] (2020, 20 cites)</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>MAE 242: Intro to Fluid Mechanics | MAE 574: Multiphase Flow | MAE 501: Linear Algebra in Engineering</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="2" t="inlineStr"/>
       <c r="P2" s="2" t="inlineStr"/>
       <c r="Q2" s="2" t="inlineStr">
         <is>
+          <t>Particle Dynamics in Fluid Flows, Fluid Dynamics and Turbulent Flows, Granular flow and fluidized beds, Aeolian processes and effects, Lattice Boltzmann Simulation Studies</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr"/>
+      <c r="S2" s="2" t="inlineStr"/>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
           <t>Kasbaoui's research interests include computational fluid dynamics, numerical methods, and massively parallel simulations of multiphase and particle-laden flows for environmental and aerospace applications.</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="U2" s="2" t="inlineStr">
         <is>
           <t>Ph.D.  Aerospace Engineering, Cornell University, 2017 | M.Sc.  Aerospace Engineering, Cornell University, 2015 | M.Sc.  Theoretical Physics, Université Paris-Sud, 2014 | Diplôme d'Ingénieur , Ecole Centrale Paris, 2013 | B.Sc.  Theoretical Physics, Université Paris-Sud, 2011</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr">
+      <c r="V2" s="2" t="inlineStr">
         <is>
           <t>Multiphase Flow and Fluid-Structure Interaction Group</t>
         </is>
       </c>
-      <c r="T2" s="3">
+      <c r="W2" s="3">
         <f>HYPERLINK("https://kasbaoui.bitbucket.io", "https://kasbaoui.bitbucket.io")</f>
         <v/>
       </c>
-      <c r="U2" s="2" t="inlineStr"/>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="X2" s="2" t="inlineStr"/>
+      <c r="Y2" s="2" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
-      <c r="W2" s="2" t="inlineStr"/>
-      <c r="X2" s="2" t="inlineStr">
+      <c r="Z2" s="2" t="inlineStr"/>
+      <c r="AA2" s="2" t="inlineStr">
         <is>
           <t>AFOSR</t>
         </is>
       </c>
-      <c r="Y2" s="3">
+      <c r="AB2" s="3">
         <f>HYPERLINK("https://bitbucket.org/krgasu/leap/downloads/leap-v0.8.2.tar.gz", "https://bitbucket.org/krgasu/leap/downloads/leap-v0.8.2.tar.gz, https://bitbucket.org/krgasu/leap/src/master")</f>
         <v/>
       </c>
-      <c r="Z2" s="2" t="inlineStr">
+      <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>School for Engineering of Matter, Transport &amp; Energy</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
+      <c r="AD2" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="b">
+      <c r="AE2" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AC2" s="3">
+      <c r="AF2" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -794,75 +827,90 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
+          <t>"Self-adaptive thermal regulation with broadband variable emittance coatings" [Solar Energy Materials and Solar Cells] (2026) | "A Study on the Integration of Teaching on Borrowing Costs and Financing Costs in International Trade Enterprises Under the Guidance of Ideological and Political Education in the Curriculum" [Educational and Humanities] (2026) | "A Supply-Chain Assessment of Water Resource Allocation in China’s National Water Network and Water-Diversion Projects" [Engineering] (2026)</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>"Perfect selective metamaterial solar absorbers" [Optics Express] (2013, 350 cites) | "Highly efficient selective metamaterial absorber for high-temperature solar thermal energy harvesting" [Solar Energy Materials and Solar Cells] (2015, 302 cites) | "Coherent thermal emission by excitation of magnetic polaritons between periodic strips and a metallic film" [Optics Express] (2008, 260 cites)</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
           <t>MAE 584: Internship | MAE 593: Applied Project | MAE 241: Intro to Thermodynamics</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>2017         AFOSR Young Investigator (YIP) Award,  ASU | 2016         JQSRT/Elsevier Viskanta Young Scientist Award,  ASU</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>Please send your CV to Prof. Wang ( [email protected] ). We will try to get back to you ASAP with possible available positions. Please also send a 2-page statement on describing your previous research experience as well as how your research interests match Prof. Wang’s group’s research themes. | Please send Prof. Wang ( [email protected] ) with your resumes for applications and for more details on the projects.</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>Thermal Radiation and Cooling Technologies, Metamaterials and Metasurfaces Applications, Quantum Electrodynamics and Casimir Effect, Transition Metal Oxide Nanomaterials, Optical properties and cooling technologies in crystalline materials</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
         <is>
           <t>Nanoscale heat transfer, metamaterials, plasmonics, and nanophotonics with an emphasis on solar thermal energy harvesting using plasmonic-enhanced light trapping for photovolatics, as well as near-field enhancement and spectral control of radiation for thermophotovoltaic energy conversion. Other research interests involve electronic cooling, MEMS, and bio-sensing.</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="S3" s="2" t="inlineStr"/>
+      <c r="T3" s="2" t="inlineStr">
         <is>
           <t>Wang research interests include selective control of thermal emission/absorption using meta-materials for energy harvesting and near-field radiation heat transfer enhancement between meta-materials for thermophotovoltaics.</t>
         </is>
       </c>
-      <c r="R3" s="2" t="inlineStr">
+      <c r="U3" s="2" t="inlineStr">
         <is>
           <t>Ph.D. Mechanical Engineering, Georgia Institute of Technology 2011 | M.S. Refrigeration and Cryogenic Engineering, Shanghai Institute of Technical Physics, Chinese  Academy of Sciences 2007 | B.E. Thermal Science and Energy Engineering, University of Science and Technology of China 2004</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr">
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Nanoscale Thermal Radiation Lab</t>
         </is>
       </c>
-      <c r="T3" s="3">
+      <c r="W3" s="3">
         <f>HYPERLINK("http://faculty.engineering.asu.edu/lpwang", "http://faculty.engineering.asu.edu/lpwang")</f>
         <v/>
       </c>
-      <c r="U3" s="2" t="inlineStr">
+      <c r="X3" s="2" t="inlineStr">
         <is>
           <t>Multiple UG/MS research positions available for Fall 2024 (volunteer) and Spring/Summer 2025 (possible FURI / MORE support)</t>
-        </is>
-      </c>
-      <c r="V3" s="2" t="inlineStr"/>
-      <c r="W3" s="2" t="inlineStr">
-        <is>
-          <t>AFM</t>
-        </is>
-      </c>
-      <c r="X3" s="2" t="inlineStr">
-        <is>
-          <t>NASA, NSF</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr"/>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>AFM</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
+          <t>NASA, NSF</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
           <t>News&amp;Awards</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
+      <c r="AD3" s="2" t="inlineStr">
         <is>
           <t>ENGRC 327 (Tempe, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="b">
+      <c r="AE3" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AC3" s="3">
+      <c r="AF3" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -912,59 +960,74 @@
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>"Influence of beam oscillation on keyhole stability and porosity in aluminum laser welding" [Journal of Materials Processing Technology] (2025) | "Influence of Topological Segment Length on the Mechanical Properties of Semicrystalline Polyethylene: A Bias-Controlled Monte Carlo Approach" [Macromolecules] (2025) | "Beam Oscillation Mechanisms for Porosity Reduction in Aluminum Laser Welding for Battery Applications" [SSRN Electronic Journal] (2025)</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>"Aging of microplastics increases their adsorption affinity towards organic contaminants" [Chemosphere] (2022, 351 cites) | "Simultaneous Iterative Boltzmann Inversion for Coarse-Graining of Polyurea" [Macromolecules] (2014, 113 cites) | "A coupled quantum/continuum mechanics study of graphene fracture" [International Journal of Fracture] (2012, 99 cites)</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
           <t>MAE 404: Finite Elements in Engineering | MAE 503: Finite Elements in Engineering | MAE 593: Applied Project</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>If you're interested in joining our group, please email Prof. Oswald with your CV, research interests, and any supporting materials such as publications or code samples.</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>Numerical methods in engineering, Microstructure and mechanical properties, Tribology and Lubrication Engineering, Composite Material Mechanics, Structural Response to Dynamic Loads</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>Development of computational mechanics: finite element methods, molecular dynamics, multiscale methods, failure analysis, and material design.</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr"/>
+      <c r="T4" s="2" t="inlineStr">
         <is>
           <t>Dr. Oswald develops computational and AI-driven methods for advanced manufacturing, including laser welding, automated inspection, robotics, and computational mechanics.</t>
         </is>
       </c>
-      <c r="R4" s="2" t="inlineStr">
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>Ph.D. Mechanical Engineering, Northwestern University, Evanston, IL 2011 | M.S. Mechanical Engineering, Case Western Reserve University, Cleveland, OH 2005 | B.S. Mechanical Engineering, Case Western Reserve University, Cleveland, OH 2004</t>
         </is>
       </c>
-      <c r="S4" s="2" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Computational Mechanics Lab</t>
         </is>
       </c>
-      <c r="T4" s="3">
+      <c r="W4" s="3">
         <f>HYPERLINK("http://sparky.fulton.asu.edu/oswald/", "http://sparky.fulton.asu.edu/oswald/")</f>
         <v/>
       </c>
-      <c r="U4" s="2" t="inlineStr"/>
-      <c r="V4" s="2" t="inlineStr"/>
-      <c r="W4" s="2" t="inlineStr"/>
       <c r="X4" s="2" t="inlineStr"/>
       <c r="Y4" s="2" t="inlineStr"/>
-      <c r="Z4" s="2" t="inlineStr">
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr">
         <is>
           <t>Multiscale polymer analysis</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
+      <c r="AD4" s="2" t="inlineStr">
         <is>
           <t>ENGRC 353 (Tempe, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="b">
+      <c r="AE4" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AC4" s="3">
+      <c r="AF4" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1022,67 +1085,82 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
+          <t>"Real-Time Shape Control of Multi-Segment Soft Robotic Arms Using Koopman Operators with Global and Local Observables" [arXiv (Cornell University)] (2026) | "Impact of a Soft Wearable Back-Support Device on Postural Stability During Trip-Like Perturbations" (2026) | "Improved Postural Stability Using a Lightweight Semi-Active Soft Back Support Device Under Standing Perturbations" [arXiv (Cornell University)] (2026)</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>"Leveraging elastic instabilities for amplified performance: Spine-inspired high-speed and high-force soft robots" [Science Advances] (2020, 497 cites) | "Twisted-and-Coiled Actuators with Free Strokes Enable Soft Robots with Programmable Motions" [Soft Robotics] (2020, 100 cites) | "Embedded shape morphing for morphologically adaptive robots" [Nature Communications] (2023, 97 cites)</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
           <t>MAE 547: Modeling and Control of Robots | MAE 593: Applied Project | MAE 499: Individualized Instruction</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>To apply, interested candidates should submit an application to Arizona State University via https://webapp4.asu.edu/dgsadmissions/ , specifying their interest in working with Dr. Sun. Additionally, they should send an email titled “Prospective Ph.D. Student” to jiefeng.sun@asu.edu, attaching their CV and a cover letter before submitting their application. | I am seeking multiple highly motivated Master students or undergrads to conduct theses. To apply, interested candidates should fill in this form: https://forms.gle/RCwqu4wkCjhBUoFL7</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>Soft Robotics and Applications, Advanced Materials and Mechanics, Advanced Sensor and Energy Harvesting Materials, Prosthetics and Rehabilitation Robotics, Micro and Nano Robotics</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>Hire students to conduct research https://sunroboticslab.github.io</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>Autonomous Technologies, Control Systems, Mechanical Engineering, Robotics</t>
         </is>
       </c>
-      <c r="Q5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
         <is>
           <t>Sun's research focuses on the design, dynamics, and control of soft robots and artificial muscles</t>
         </is>
       </c>
-      <c r="R5" s="2" t="inlineStr">
+      <c r="U5" s="2" t="inlineStr">
         <is>
           <t>Ph.D. in Robotics and Control, Colorado State University, 2022 M.S. in Mechanical Engineering, Dalian University of Technology, 2017 B.S. in Mechanical Engineering, Lanzhou University of Technology, 2014</t>
         </is>
       </c>
-      <c r="S5" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Sun Robotics Lab</t>
         </is>
       </c>
-      <c r="T5" s="3">
+      <c r="W5" s="3">
         <f>HYPERLINK("https://sunroboticslab.github.io", "https://sunroboticslab.github.io")</f>
         <v/>
       </c>
-      <c r="U5" s="2" t="inlineStr">
+      <c r="X5" s="2" t="inlineStr">
         <is>
           <t>I am seeking multiple highly motivated Master students or undergrads to conduct theses. To apply, interested candidates should fill in this form: https://forms.gle/RCwqu4wkCjhBUoFL7 | I am a K-12 student/teacher and would like information for a school report, tour, help with my robotics team, a research internship, etc. My students and I are very excited about using robotics as a teaching tool to encourage interest in Science, Technology, Engineering, and Math (STEM) topics. We actively involved in outreach and are have an outreach webpage to answer your questions.</t>
         </is>
       </c>
-      <c r="V5" s="2" t="inlineStr"/>
-      <c r="W5" s="2" t="inlineStr"/>
-      <c r="X5" s="2" t="inlineStr"/>
       <c r="Y5" s="2" t="inlineStr"/>
-      <c r="Z5" s="2" t="inlineStr">
+      <c r="Z5" s="2" t="inlineStr"/>
+      <c r="AA5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AC5" s="2" t="inlineStr">
         <is>
           <t>Mission and Core Values</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
+      <c r="AD5" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="b">
+      <c r="AE5" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AC5" s="3">
+      <c r="AF5" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1136,40 +1214,55 @@
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
+          <t>"Heterogeneous Feature Knowledge Distillation based on Enhanced Feature Projector Correlation" [Neural Networks] (2025) | "Deep learning and multi-omics reveal programmed cell death-associated diagnostic signatures and prognostic biomarkers in gastric cancer" [Frontiers in Immunology] (2025) | "Research on flexible job shop scheduling based on deep reinforcement learning with transformer-graph neural network" [Journal of Control and Decision] (2025)</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>"Lubricated pipelining: stability of core-annular flow" [Journal of Fluid Mechanics] (1989, 202 cites) | "Lubricated pipelining: stability of core—annular flow. Part 5. Experiments and comparison with theory" [Journal of Fluid Mechanics] (1992, 163 cites) | "Pool-boiling enhancement by novel metallic nanoporous surface" [Experimental Thermal and Fluid Science] (2012, 112 cites)</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
           <t>MAE 242: Intro to Fluid Mechanics | MAE 384: Adv Math Methods for Engineers | MAE 501: Linear Algebra in Engineering</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="2" t="inlineStr"/>
       <c r="P6" s="2" t="inlineStr"/>
       <c r="Q6" s="2" t="inlineStr">
         <is>
+          <t>Fluid Dynamics and Thin Films, Rheology and Fluid Dynamics Studies, Hydraulic Fracturing and Reservoir Analysis, Fluid Dynamics and Turbulent Flows, Drilling and Well Engineering</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
           <t>Chen’s research interests include multiphase flows, drag reduction, airplane de-icing, interfacial instabilities and flow in porous media.</t>
         </is>
       </c>
-      <c r="R6" s="2" t="inlineStr">
+      <c r="U6" s="2" t="inlineStr">
         <is>
           <t>Ph.D. Fluid Mechanics, University of Minnesota 1990 | B.S. Mechanics, Peking University, China 1982</t>
         </is>
       </c>
-      <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr"/>
-      <c r="U6" s="2" t="inlineStr"/>
       <c r="V6" s="2" t="inlineStr"/>
       <c r="W6" s="2" t="inlineStr"/>
       <c r="X6" s="2" t="inlineStr"/>
       <c r="Y6" s="2" t="inlineStr"/>
       <c r="Z6" s="2" t="inlineStr"/>
-      <c r="AA6" s="2" t="inlineStr">
+      <c r="AA6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr">
         <is>
           <t>ENGRC 361 (TEMPE, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="b">
+      <c r="AE6" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AC6" s="3">
+      <c r="AF6" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1221,46 +1314,49 @@
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>MAE 242: Intro to Fluid Mechanics | MAE 593: Applied Project | MAE 564: Advanced Aerodynamics</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr"/>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr"/>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>Unsteady aerodynamics, vortex dynamics, flow control, turbulence, separated flows</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr"/>
-      <c r="Q7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr">
         <is>
           <t>Ramesh's expertise is in unsteady fluid dynamics, vortex dynamics, turbulence and flow control.</t>
         </is>
       </c>
-      <c r="R7" s="2" t="inlineStr">
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>PhD North Carolina State University</t>
         </is>
       </c>
-      <c r="S7" s="2" t="inlineStr"/>
-      <c r="T7" s="2" t="inlineStr"/>
-      <c r="U7" s="2" t="inlineStr"/>
       <c r="V7" s="2" t="inlineStr"/>
       <c r="W7" s="2" t="inlineStr"/>
       <c r="X7" s="2" t="inlineStr"/>
       <c r="Y7" s="2" t="inlineStr"/>
       <c r="Z7" s="2" t="inlineStr"/>
-      <c r="AA7" s="2" t="inlineStr">
+      <c r="AA7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AD7" s="2" t="inlineStr">
         <is>
           <t>Engineering research centre Room 383 551 E Tyler mall (Tempe, AZ 85281)</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="b">
+      <c r="AE7" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AC7" s="3">
+      <c r="AF7" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1318,67 +1414,82 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
+          <t>"Measurement of CP asymmetries in $$ {\overline{B}}^0\to {D}_s^{-}{D}^{+} $$ and $$ {\overline{B}}_s^0\to {D}_s^{-}{D}^{-} $$ decays" [Journal of High Energy Physics] (2026) | "Machine learning techniques for jet reconstruction at LHCb and application to the search for $$ H\to b\overline{b} $$ and $$ H\to c\overline{c} $$ in $$ \sqrt{s}=13 $$ TeV pp collisions" [Journal of High Energy Physics] (2026) | "Improved branching-fraction measurements of $$ {B}_{(s)}^0\to {K}_{\mathrm{S}}^0{h}^{+}h{\prime}^{-} $$ decays and first observation of $$ {B}_s^0\to {K}_{\mathrm{S}}^0{K}^{+}{K}^{-} $$" [Journal of High Energy Physics] (2026)</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>"Unveiling the strong interaction among hadrons at the LHC" [Nature] (2020, 196 cites) | "Multiplicity dependence of light-flavor hadron production in p p collisions at s = 7 TeV" [Physical Review C] (2019, 180 cites) | "The ALICE experiment: a journey through QCD" [The European Physical Journal C] (2024, 165 cites)</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
           <t>MAE 417: System Dynamics and Control II | MAE 593: Applied Project | MAE 598: Special Topics</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>More specific topics that I will be interested in working on are: Multi-agent robotics Team robotics with aerial and ground robots Learning-based methods for safe robotics Optimization-based methods for safe robotic control Reinforcement learning for multi-objective robotic applications Large-Language Models (LLMs) in robotic applications The pre-requisites and background I am looking for are as follows: Strong interests in control, autonomy, and robotics Strong mathematical background in Linear Systems and Linear Algebra, ODEs, Probability, and Calculus Programming efficiency: Python (C/C++ is optional, but will be a good add-on as we will plan to conduct hardware experiments) Hands-on experience with ML packages (PyTorch or JAX) Hands-on experience with ROS or ROS2 Email me your CV along with a one or two-page document on why you are interested in working with me, what topic(s) you are interested in working on, what motivates you to work on those, which of the pre-requisites listed above you meet, and what's your plan for meeting the rest of the requirements</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>Particle physics theoretical and experimental studies, Quantum Chromodynamics and Particle Interactions, High-Energy Particle Collisions Research, Neutrino Physics Research, Dark Matter and Cosmic Phenomena</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>Distributed multi-agent motion planning and control, Provably safe control design using machine learning-based certificates, Foundation models in complex robotic tasks, Failure prediction from limited demonstrations, Human-robot interaction.</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>Control Systems, Dynamical Systems, Machine Learning, Nonlinear Dynamical Systems, Robotics</t>
         </is>
       </c>
-      <c r="Q8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
         <is>
           <t>Garg's research interests include control synthesis for multi-agent coordination using control theory and machine learning.</t>
         </is>
       </c>
-      <c r="R8" s="2" t="inlineStr">
+      <c r="U8" s="2" t="inlineStr">
         <is>
           <t>PhD. Aerospace Engineering, University of Michigan, Ann Arbor, 2021 MS. Aerospace Engineering, University of Michigan, Ann Arbor, 2019 BTech. Aerospace Engineering, Indian Institute of Technology, Bombay, 2016</t>
         </is>
       </c>
-      <c r="S8" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Safe and Autonomous Robotics (STAR) Lab</t>
         </is>
       </c>
-      <c r="T8" s="3">
+      <c r="W8" s="3">
         <f>HYPERLINK("https://sites.google.com/asu.edu/kunalgarg/", "https://sites.google.com/asu.edu/kunalgarg/")</f>
         <v/>
       </c>
-      <c r="U8" s="2" t="inlineStr">
+      <c r="X8" s="2" t="inlineStr">
         <is>
           <t>Actively seeking graduate students (see lab link/instructions)</t>
         </is>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="Y8" s="2" t="inlineStr">
         <is>
           <t>Python, PyTorch, ROS, ROS2, C/C++, Linear Algebra</t>
         </is>
       </c>
-      <c r="W8" s="2" t="inlineStr"/>
-      <c r="X8" s="2" t="inlineStr"/>
-      <c r="Y8" s="2" t="inlineStr"/>
       <c r="Z8" s="2" t="inlineStr"/>
-      <c r="AA8" s="2" t="inlineStr">
+      <c r="AA8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr">
         <is>
           <t>551 E Tyler Mall ERC 475 (Tempe, AZ 85281)</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="b">
+      <c r="AE8" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AF8" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1436,71 +1547,86 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
+          <t>"HGTO: A Unified Graph-Based Physics-Informed Formulation for Structural Topology Optimization" [arXiv (Cornell University)] (2026) | "HGTO: A Unified Graph-Based Physics-Informed Formulation for Structural Topology Optimization" [arXiv (Cornell University)] (2026) | "Graph neural network-based aquaculture net modeling and inference — A frequency domain approach" [Ocean Engineering] (2026)</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>"An investigation into the hydrodynamics of a flexible riser undergoing vortex-induced vibration" [Journal of Fluids and Structures] (2016, 178 cites) | "Theoretical and numerical analysis of bending behavior of unbonded flexible risers" [Marine Structures] (2015, 42 cites) | "Experimental investigation of the response performance of VIV on a flexible riser with helical strakes" [Ships and Offshore Structures] (2014, 39 cites)</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
           <t>MAE 499: Individualized Instruction | MAE 202: Mech.Particles/Rigid Bodies II | MAE 318: System Dynamics and Control I</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr"/>
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>Undergraduate students : Highly-motivated undergraduate students are encouraged to get in touch. The students are encouraged to apply Fulton Undergraduate Research Initiative (FURI) ( Proposals are due the 3rd Wednesday of every March and October ) , Summer Research Initiative (SURI) etc. No prior research experiences are expected. Email to: leixinma@ asu .edu . | Visiting scholars from different backgrounds are welcome to contact Prof. Ma for projects with mutual interests. Email to: leixinma@asu.edu</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>Fluid Dynamics and Vibration Analysis, Vibration and Dynamic Analysis, Wind and Air Flow Studies, Marine Bivalve and Aquaculture Studies, Topology Optimization in Engineering</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>Aerodynamics, Dynamical Systems, Machine Learning, Mechanics of Composite Materials</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
         <is>
           <t>Aerodynamics, Dynamical Systems, Machine Learning, Mechanics of Composite Materials</t>
         </is>
       </c>
-      <c r="Q9" s="2" t="inlineStr">
+      <c r="T9" s="2" t="inlineStr">
         <is>
           <t>Leixin Ma's career goal is a data-driven and physically consistent approach to modeling and designing programmable smart structures and robots, especially under complex fluid flow conditions.</t>
         </is>
       </c>
-      <c r="R9" s="2" t="inlineStr">
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>Ph.D. in Mechanical Engineering, Massachusetts Institute of Technology, 2021 S.M. in Mechanical Engineering, Massachusetts Institute of Technology, 2017 B.S.E. in Naval Architecture and Ocean Engineering, Shanghai Jiao Tong University, 2015</t>
         </is>
       </c>
-      <c r="S9" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Optimization, Autonomy, and Soft Intelligence Systems (OASIS) Lab</t>
         </is>
       </c>
-      <c r="T9" s="3">
+      <c r="W9" s="3">
         <f>HYPERLINK("https://sites.google.com/view/oasislabasu", "https://sites.google.com/view/oasislabasu")</f>
         <v/>
       </c>
-      <c r="U9" s="2" t="inlineStr">
+      <c r="X9" s="2" t="inlineStr">
         <is>
           <t>More Home Research People Publications News Openings Facility Teaching Resources | Update: We are currently hiring multiple fully-funded graduate students, undergraduate students and visiting scholars! The first year graduate students will be selected as the prestigious Ira A. Fulton fellowship from the ASU School of Engineering.</t>
         </is>
       </c>
-      <c r="V9" s="2" t="inlineStr"/>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t>Towing Tank, FDM</t>
-        </is>
-      </c>
-      <c r="X9" s="2" t="inlineStr"/>
       <c r="Y9" s="2" t="inlineStr"/>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>Towing Tank, FDM</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
           <t>Ocean and Soft Intelligent Structure Interaction Lab</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
+      <c r="AD9" s="2" t="inlineStr">
         <is>
           <t>ERC 485 (Tempe, AZ 85287)</t>
         </is>
       </c>
-      <c r="AB9" s="2" t="b">
+      <c r="AE9" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AF9" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1554,55 +1680,70 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
+          <t>"Bleeding flow characteristics downstream of isotropic porous square cylinders" [Journal of Fluid Mechanics] (2026) | "Coherent organisation of passive scalar from a point source in a turbulent boundary layer" [Journal of Fluid Mechanics] (2025) | "Turbulent/non-turbulent interface in Rayleigh–Taylor flows" [Journal of Turbulence] (2025)</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>"Cross-stream stereoscopic particle image velocimetry of a modified turbulent boundary layer over directional surface pattern" [Journal of Fluid Mechanics] (2017, 120 cites) | "The transition to turbulence in shock-driven mixing: effects of Mach number and initial conditions" [Journal of Fluid Mechanics] (2019, 77 cites) | "Numerical analyses of high temperature dense, granular flows coupled to high temperature flow property measurements for solar thermal energy storage" [Solar Energy] (2020, 25 cites)</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
           <t>MAE 575: Turbulence | MAE 593: Applied Project | MAE 499: Individualized Instruction</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr"/>
-      <c r="N10" s="2" t="inlineStr"/>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>Fluid Dynamics and Turbulent Flows, Particle Dynamics in Fluid Flows, Laser-Plasma Interactions and Diagnostics, Wind and Air Flow Studies, Combustion and flame dynamics</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>Aerodynamics, Aerospace Engineering, Mechanical Engineering</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>Aerodynamics, Aerospace Engineering, Mechanical Engineering</t>
         </is>
       </c>
-      <c r="Q10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
         <is>
           <t>Dr. Pathikonda studies turbulent fluid flows to understand natural and engineering phenomena using lab experiments. His expertise is in complex (reacting) mixing, high Re-flows, laser-based &amp; spectroscopic techniques, etc.</t>
         </is>
       </c>
-      <c r="R10" s="2" t="inlineStr">
+      <c r="U10" s="2" t="inlineStr">
         <is>
           <t>Ph. D. Theoretical and Applied Mechanics, University of Illinois, Urbana Champaign, 2017 | MS Aerospace Engineering, University of Illinois, Urbana Champaign, 2013 | B. Tech. Mechanical Engineering, National Institute of Technology, Warangal, 2009</t>
         </is>
       </c>
-      <c r="S10" s="2" t="inlineStr"/>
-      <c r="T10" s="3">
+      <c r="V10" s="2" t="inlineStr"/>
+      <c r="W10" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/cmat/", "https://faculty.engineering.asu.edu/cmat/")</f>
         <v/>
       </c>
-      <c r="U10" s="2" t="inlineStr"/>
-      <c r="V10" s="2" t="inlineStr"/>
-      <c r="W10" s="2" t="inlineStr"/>
       <c r="X10" s="2" t="inlineStr"/>
       <c r="Y10" s="2" t="inlineStr"/>
-      <c r="Z10" s="2" t="inlineStr">
+      <c r="Z10" s="2" t="inlineStr"/>
+      <c r="AA10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
         <is>
           <t>Want to be part of CMAT Lab?</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
+      <c r="AD10" s="2" t="inlineStr">
         <is>
           <t>551 E Tyler Mall ERC 479 (Tempe, AZ 85281)</t>
         </is>
       </c>
-      <c r="AB10" s="2" t="b">
+      <c r="AE10" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AF10" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1656,44 +1797,59 @@
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
+          <t>"A high-fidelity methodology for particle-resolved direct numerical simulations" [International Journal of Multiphase Flow] (2025) | "BPS2025 - Liquid nano-sheet sample delivery for femtosecond solution X-ray scattering" [Biophysical Journal] (2025) | "Characterization of the forcing and sub-filter scale terms in the volume-filtering immersed boundary method" [Journal of Computational Physics] (2025)</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>"Modeling Primary Atomization" [Annual Review of Fluid Mechanics] (2008, 440 cites) | "A balanced force refined level set grid method for two-phase flows on unstructured flow solver grids" [Journal of Computational Physics] (2007, 316 cites) | "A parallel Eulerian interface tracking/Lagrangian point particle multi-scale coupling procedure" [Journal of Computational Physics] (2009, 235 cites)</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
           <t>MAE 384: Adv Math Methods for Engineers | MAE 484: Internship | MAE 561: Computational Fluid Dynamics</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr"/>
-      <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr"/>
       <c r="P11" s="2" t="inlineStr"/>
       <c r="Q11" s="2" t="inlineStr">
         <is>
+          <t>Fluid Dynamics and Heat Transfer, Fluid Dynamics and Turbulent Flows, Particle Dynamics in Fluid Flows, Combustion and flame dynamics, Computational Fluid Dynamics and Aerodynamics</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
           <t>Herrmann's research interests include fluid mechanics, modeling and numerical simulation of multiphase flows with a focus on turbulent atomization processes, and numerical methods for discontinuous interfaces.</t>
         </is>
       </c>
-      <c r="R11" s="2" t="inlineStr">
+      <c r="U11" s="2" t="inlineStr">
         <is>
           <t>PhD in Mechanical Engineering, University of Technology (RWTH) Aachen, Germany 2001 | Diploma. Mechanical and Aerospace Engineering, University of Technology (RWTH) Aachen, Germany 1995</t>
         </is>
       </c>
-      <c r="S11" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Computational Multiphase Physics Laboratory</t>
         </is>
       </c>
-      <c r="T11" s="2" t="inlineStr"/>
-      <c r="U11" s="2" t="inlineStr"/>
-      <c r="V11" s="2" t="inlineStr"/>
       <c r="W11" s="2" t="inlineStr"/>
       <c r="X11" s="2" t="inlineStr"/>
       <c r="Y11" s="2" t="inlineStr"/>
       <c r="Z11" s="2" t="inlineStr"/>
-      <c r="AA11" s="2" t="inlineStr">
+      <c r="AA11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AD11" s="2" t="inlineStr">
         <is>
           <t>ENGRC 311 (TEMPE, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="AB11" s="2" t="b">
+      <c r="AE11" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AC11" s="3">
+      <c r="AF11" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1747,55 +1903,70 @@
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
+          <t>"Robust optimal density control of robotic swarms" [Automatica] (2025) | "A Survey on Small-Scale Testbeds for Connected and Automated Vehicles and Robot Swarms: A Guide for Creating a New Testbed [Survey]" [IEEE Robotics &amp; Automation Magazine] (2024) | "PathFinder: Attention-Driven Dynamic Non-Line-of-Sight Tracking with a Mobile Robot" (2024)</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>"Optimized Stochastic Policies for Task Allocation in Swarms of Robots" [IEEE Transactions on Robotics] (2009, 259 cites) | "Highly stretchable self-sensing actuator based on conductive photothermally-responsive hydrogel" [Materials Today] (2021, 221 cites) | "Experimental Study and Modeling of Group Retrieval in Ants as an Approach to Collective Transport in Swarm Robotic Systems" [Proceedings of the IEEE] (2011, 110 cites)</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
           <t>MAE 318: System Dynamics and Control I | MAE 598: Special Topics | MAE 593: Applied Project</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr"/>
-      <c r="N12" s="2" t="inlineStr"/>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>Distributed Control Multi-Agent Systems, Modular Robots and Swarm Intelligence, Mathematical and Theoretical Epidemiology and Ecology Models, Gene Regulatory Network Analysis, Micro and Nano Robotics</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>Modeling, analysis, control, and optimization of multi-robot systems including robotic swarms; analysis of collective behaviors in biology and biologically-inspired control of distributed systems</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>Systems and Control Theory, Mechanical Engineering, Autonomous Technologies, Robotics</t>
         </is>
       </c>
-      <c r="Q12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
         <is>
           <t>Dr. Berman directs the Autonomous Collective Systems Laboratory at ASU, which models and analyzes behaviors in biological and engineered collectives and designs control strategies for multi-robot systems.</t>
         </is>
       </c>
-      <c r="R12" s="2" t="inlineStr">
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>Ph.D. Mechanical Engineering and Applied Mechanics, University of Pennsylvania 2010 | M.S.E. Mechanical Engineering and Applied Mechanics, University of Pennsylvania 2008 | B.S.E. Mechanical and Aerospace Engineering, Princeton University 2005 | Certificate. Robotics and Intelligent Systems, Princeton University 2005</t>
         </is>
       </c>
-      <c r="S12" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Autonomous Collective Systems (ACS) Laboratory</t>
         </is>
       </c>
-      <c r="T12" s="3">
+      <c r="W12" s="3">
         <f>HYPERLINK("http://faculty.engineering.asu.edu/acs/", "http://faculty.engineering.asu.edu/acs/")</f>
         <v/>
       </c>
-      <c r="U12" s="2" t="inlineStr"/>
-      <c r="V12" s="2" t="inlineStr"/>
-      <c r="W12" s="2" t="inlineStr"/>
       <c r="X12" s="2" t="inlineStr"/>
       <c r="Y12" s="2" t="inlineStr"/>
       <c r="Z12" s="2" t="inlineStr"/>
-      <c r="AA12" s="2" t="inlineStr">
+      <c r="AA12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AD12" s="2" t="inlineStr">
         <is>
           <t>ENGRC 375 (Tempe, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="AB12" s="2" t="b">
+      <c r="AE12" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AF12" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1849,51 +2020,66 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
+          <t>"A comprehensive CFD lifecycle dataset for marine vessel hydrodynamics" [Scientific Data] (2026) | "Current-Biased Informed RRT* for USV Path Planning in Flow Fields" (2026) | "Inferring Causal Graph Temporal Logic Formulas to Expedite Reinforcement Learning in Temporally Extended Tasks" [arXiv (Cornell University)] (2026)</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>"The oyster genome reveals stress adaptation and complexity of shell formation" [Nature] (2012, 2316 cites) | "The pearl oyster Pinctada fucata martensii genome and multi-omic analyses provide insights into biomineralization" [GigaScience] (2017, 232 cites) | "Dynamics of microbial communities, texture and flavor in Suan zuo yu during fermentation" [Food Chemistry] (2020, 120 cites)</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
           <t>MAE 506: Adv Sys Model, Dynamic, Contrl | MAE 318: System Dynamics and Control I | MAE 593: Applied Project</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr"/>
-      <c r="N13" s="2" t="inlineStr"/>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr"/>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>Marine Bivalve and Aquaculture Studies, Magnesium Alloys: Properties and Applications, Aluminum Alloys Composites Properties, Calcium Carbonate Crystallization and Inhibition, Meat and Animal Product Quality</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>The research interests include control theory, machine learning, formal methods and autonomous systems.</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>Artificial Intelligence, Control Systems, Electric Power and Energy Systems, Machine Learning, Robotics, Systems and Control Theory</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
         <is>
           <t>My research interests include control theory, formal methods, and machine learning (including reinforcement learning), with applications on autonomous systems and cyber-physical systems.</t>
         </is>
       </c>
-      <c r="R13" s="2" t="inlineStr">
+      <c r="U13" s="2" t="inlineStr">
         <is>
           <t>Ph.D Degree at the  Department of Electrical, Computer, and Systems Engineering  at  Rensselaer Polytechnic Institute  in 2018 | Master's Degree at the  School of electrical and information engineering  at  Tianjin University  in 2014 | Bachelor's Degree at the  School of electrical and information engineering  at  Tianjin University  in 2011</t>
         </is>
       </c>
-      <c r="S13" s="2" t="inlineStr"/>
-      <c r="T13" s="3">
+      <c r="V13" s="2" t="inlineStr"/>
+      <c r="W13" s="3">
         <f>HYPERLINK("https://sites.google.com/site/zhexudavid00710/research?authuser=0", "https://sites.google.com/site/zhexudavid00710/research?authuser=0")</f>
         <v/>
       </c>
-      <c r="U13" s="2" t="inlineStr"/>
-      <c r="V13" s="2" t="inlineStr"/>
-      <c r="W13" s="2" t="inlineStr"/>
       <c r="X13" s="2" t="inlineStr"/>
       <c r="Y13" s="2" t="inlineStr"/>
       <c r="Z13" s="2" t="inlineStr"/>
-      <c r="AA13" s="2" t="inlineStr">
+      <c r="AA13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AD13" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="b">
+      <c r="AE13" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AC13" s="3">
+      <c r="AF13" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -1941,42 +2127,53 @@
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>"Adjoint-based control of loud events in a turbulent jet" [Journal of Fluid Mechanics] (2014, 46 cites) | "LES Investigation of a Mach 1.3 Jet With and Without Plasma Actuators" [47th AIAA Aerospace Sciences Meeting including The New Horizons Forum and Aerospace Exposition] (2009, 38 cites) | "A High-Order, Overset-Mesh Algorithm for Adjoint-Based Optimization for Aeroacoustics Control" (2010, 21 cites)</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>MAE 242: Intro to Fluid Mechanics | MAE 593: Applied Project | MAE 598: Special Topics</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr"/>
-      <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr"/>
       <c r="P14" s="2" t="inlineStr"/>
       <c r="Q14" s="2" t="inlineStr">
         <is>
+          <t>Aerodynamics and Acoustics in Jet Flows, Fluid Dynamics and Turbulent Flows, Computational Fluid Dynamics and Aerodynamics, Combustion and flame dynamics, Acoustic Wave Phenomena Research</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
           <t>Kim's research interests include large-eddy simulation of high-speed turbulent flows with multi-physics, aeroacoustics, flow control and optimization.</t>
         </is>
       </c>
-      <c r="R14" s="2" t="inlineStr">
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>Ph.D. Theoretical and Applied Mechanics, University of Illinois at Urbana-Champaign | M.S. Mechanical and Aerospace Engineering, Seoul National University, South Korea | B.S. Mechanical and Aerospace Engineering, Seoul National University, South Korea</t>
         </is>
       </c>
-      <c r="S14" s="2" t="inlineStr"/>
-      <c r="T14" s="2" t="inlineStr"/>
-      <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" s="2" t="inlineStr"/>
       <c r="W14" s="2" t="inlineStr"/>
       <c r="X14" s="2" t="inlineStr"/>
       <c r="Y14" s="2" t="inlineStr"/>
       <c r="Z14" s="2" t="inlineStr"/>
-      <c r="AA14" s="2" t="inlineStr">
+      <c r="AA14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AD14" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="AB14" s="2" t="b">
+      <c r="AE14" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AF14" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2030,55 +2227,70 @@
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
+          <t>"Lyapunov Functions can Exactly Quantify Rate Performance of Nonlinear Differential Equations" [arXiv (Cornell University)] (2026) | "Lyapunov Functions can Exactly Quantify Rate Performance of Nonlinear Differential Equations" [arXiv (Cornell University)] (2026) | "Hierarchical Stability and Lyapunov Conditions for Linear PDEs" [IEEE Control Systems Letters] (2026)</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>"Highly stretchable self-sensing actuator based on conductive photothermally-responsive hydrogel" [Materials Today] (2021, 221 cites) | "Positive Forms and Stability of Linear Time-Delay Systems" [SIAM Journal on Control and Optimization] (2009, 98 cites) | "Exponentially Stable Nonlinear Systems Have Polynomial Lyapunov Functions on Bounded Regions" [IEEE Transactions on Automatic Control] (2009, 76 cites)</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
           <t>MAE 593: Applied Project | MAE 318: System Dynamics and Control I | MAE 509: LMI Methods</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr"/>
-      <c r="O15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr"/>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>Stability and Control of Uncertain Systems, Stability and Controllability of Differential Equations, Control Systems and Identification, Numerical methods for differential equations, Advanced Optimization Algorithms Research</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
         <is>
           <t>The intersection of computer science and control including convex optimization, artificial intelligence, and manipulation of delayed and PDE systems. The understanding and regulation of complex dynamical systems such as the motion of plasma in nuclear fusion reactors, autoregulation in the human immune response, and the motion of spacecraft in orbit.</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr">
+      <c r="S15" s="2" t="inlineStr">
         <is>
           <t>Control Systems, Dynamical Systems Theory, Aerospace Engineering, Algorithm Development, Dynamical Systems, Nonlinear Dynamical Systems, Mathematical and System Dynamics Modeling, Immunology</t>
         </is>
       </c>
-      <c r="Q15" s="2" t="inlineStr">
+      <c r="T15" s="2" t="inlineStr">
         <is>
           <t>Peet's current research interests are in the role of computation as it is applied to the understanding and control of complex and large-scale systems.</t>
         </is>
       </c>
-      <c r="R15" s="2" t="inlineStr">
+      <c r="U15" s="2" t="inlineStr">
         <is>
           <t>Ph.D. Aeronautics and Astronautics, Stanford University 2006 | Bachelor's degree. Physics, University of Texas-Austin 1999 | Bachelor's degree. Aerospace Engineering, University of Texas-Austin 1999</t>
         </is>
       </c>
-      <c r="S15" s="2" t="inlineStr">
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Cybernetic Systems and Controls Laboratory (CSCL)</t>
         </is>
       </c>
-      <c r="T15" s="3">
+      <c r="W15" s="3">
         <f>HYPERLINK("http://control.asu.edu/", "http://control.asu.edu/")</f>
         <v/>
       </c>
-      <c r="U15" s="2" t="inlineStr"/>
-      <c r="V15" s="2" t="inlineStr"/>
-      <c r="W15" s="2" t="inlineStr"/>
       <c r="X15" s="2" t="inlineStr"/>
       <c r="Y15" s="2" t="inlineStr"/>
       <c r="Z15" s="2" t="inlineStr"/>
-      <c r="AA15" s="2" t="inlineStr">
+      <c r="AA15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr"/>
+      <c r="AD15" s="2" t="inlineStr">
         <is>
           <t>ENGRC 253 (Tempe, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="AB15" s="2" t="b">
+      <c r="AE15" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AF15" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2130,45 +2342,68 @@
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr"/>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>"Thermal conductivity trends across cadmium sulfide nanoparticle sizes – from colloidal nanocrystals down to magic-sized clusters" [Chemical Physics] (2026) | "BACQ - Application-Oriented Benchmarks for Quantum Computing" [Communications in computer and information science] (2026) | "Thermal Radiative Properties of Tungsten-Doped Vanadium Dioxide Thin Films Fabricated in an Extremely Low-Oxygen Furnace Environment" [International Journal of Thermophysics] (2025)</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>"Real-time hand-tracking with a color glove" [ACM Transactions on Graphics] (2009, 610 cites) | "Enhanced Thermopower in PbSe Nanocrystal Quantum Dot Superlattices" [Nano Letters] (2008, 257 cites) | "Oxide‐Mediated Formation of Chemically Stable Tungsten–Liquid Metal Mixtures for Enhanced Thermal Interfaces" [Advanced Materials] (2019, 192 cites)</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>MAE 241: Intro to Thermodynamics | MAE 593: Applied Project | MAE 588: Nanoscale Heat Transfer</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>Thermal properties of materials, Quantum Dots Synthesis And Properties, Advanced Thermoelectric Materials and Devices, Chalcogenide Semiconductor Thin Films, Thermal Radiation and Cooling Technologies</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>My research group is an interdisciplinary nanoengineering team that focuses on manipulating material properties for thermal energy applications. Some of our focus areas are thermoelectric power generation, thermal storage media, heat transfer, and phonon optics. To achieve our objectives, we custom-design materials using colloidal nanoparticles, chemical precursors, and nanocomposites.</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>Mechanical Engineering, Energy, Renewable Energy, Energy and Sustainability, Clean Energy, Energy Efficiency Technologies, Materials Science and Engineering, Chemical Engineering, Nanoengineering, Nanoscience, Nanotechnology, Solid State Physics, Thin Film Materials, Semiconductors, Chemistry, Physics</t>
         </is>
       </c>
-      <c r="Q16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
         <is>
           <t>Wang's research interests include thermal energy conversion, storage, and transport in nanostructured materials; thermoelectric power generation; thermal storage media; heat transfer, and phonon optics</t>
         </is>
       </c>
-      <c r="R16" s="2" t="inlineStr">
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>Ph.D. Mechanical Engineering, University of California-Berkeley 2008 | M.S. Mechanical Engineering, University of California-Berkeley 2005 | B.S. Mechanical Engineering, University of California-Los Angeles 2003</t>
         </is>
       </c>
-      <c r="S16" s="2" t="inlineStr"/>
-      <c r="T16" s="3">
+      <c r="V16" s="2" t="inlineStr"/>
+      <c r="W16" s="3">
         <f>HYPERLINK("http://wang.faculty.asu.edu/", "http://wang.faculty.asu.edu/")</f>
         <v/>
       </c>
-      <c r="U16" s="2" t="inlineStr"/>
-      <c r="V16" s="2" t="inlineStr"/>
-      <c r="W16" s="2" t="inlineStr"/>
       <c r="X16" s="2" t="inlineStr"/>
       <c r="Y16" s="2" t="inlineStr"/>
       <c r="Z16" s="2" t="inlineStr"/>
       <c r="AA16" s="2" t="inlineStr"/>
-      <c r="AB16" s="2" t="b">
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr"/>
+      <c r="AD16" s="2" t="inlineStr">
+        <is>
+          <t>ENGRC 307 (Tempe, AZ 85287-6106)</t>
+        </is>
+      </c>
+      <c r="AE16" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AC16" s="3">
+      <c r="AF16" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2226,55 +2461,70 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
+          <t>"Multi-year assessment of energy storage capacity for a carbon-neutral grid in Arizona and the impact of wind energy integration" [Renewable Energy] (2026) | "Analysis of gas turbines with diffusion, premixed and rich-quench-lean combustor designs utilizing ternary CH4/H2/NH3 fuel blends" [Energy Conversion and Management] (2026) | "Micro-scale thermal partial oxidation reformer and integrated solid oxide fuel cell operating with jet fuel" [Journal of Power Sources] (2026)</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>"A review of energy storage technologies for demand-side management in industrial facilities" [Journal of Cleaner Production] (2021, 100 cites) | "Techno-Economic Assessment of CHP Systems in Wastewater Treatment Plants" [Environments] (2020, 78 cites) | "Thermodynamic and emission analysis of a hydrogen/methane fueled gas turbine" [Energy Conversion and Management X] (2023, 50 cites)</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
           <t>MAE 593: Applied Project | MAE 436: Combustion | MAE 536: Combustion</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>Outstanding Faculty Mentor, Fulton Schools of Engineering, For the Fulton Forge Student Research programs, 2026 | 1st Place, Student Paper Competition, 2025 ASME IMECE Power Symposium, 2025</t>
         </is>
       </c>
-      <c r="N17" s="2" t="inlineStr"/>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>Advancements in Solid Oxide Fuel Cells, Fuel Cells and Related Materials, Catalytic Processes in Materials Science, Electrocatalysts for Energy Conversion, Catalysis and Oxidation Reactions</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
         <is>
           <t>Energy management and efficiency, energy transition, energy storage, solid oxide fuel cells, partial oxidation, cogeneration, combustion, and synthesis of hydrogen</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
+      <c r="S17" s="2" t="inlineStr">
         <is>
           <t>Ceramics, Electrochemistry, Energy, Energy and Sustainability, Energy Conservation, Energy Economics, Energy Efficiency Technologies, Thin Film Materials</t>
         </is>
       </c>
-      <c r="Q17" s="2" t="inlineStr">
+      <c r="T17" s="2" t="inlineStr">
         <is>
           <t>Milcarek's current research focuses on energy management and efficiency, energy system modeling, energy transition, energy storage, solid oxide fuel cells fabrication and testing, partial oxidation and synthesis of hydrogen.</t>
         </is>
       </c>
-      <c r="R17" s="2" t="inlineStr">
+      <c r="U17" s="2" t="inlineStr">
         <is>
           <t>Ph.D. Mechanical and Aerospace Engineering, College of Engineering and Computer Science, Syracuse University 2018 | M.S. Mechanical and Aerospace Engineering, College of Engineering and Computer Science, Syracuse University 2017 | M.S. Energy Systems Engineering, College of Engineering and Computer Science, Syracuse University 2017 | Certificate of Advanced Study (CAS) Sustainable Enterprise, Martin J. Whitman School of Management, Syracuse University 2017 | Certificate in University Teaching (CUT). Graduate School, Future Professorate Program, Syracuse University 2017 | B.S. Mechanical Engineering; minor: Mathematics (Summa Cum Laude), L.C. Smith College of Engineering and Computer Science, Syracuse University 2014</t>
         </is>
       </c>
-      <c r="S17" s="2" t="inlineStr"/>
-      <c r="T17" s="3">
+      <c r="V17" s="2" t="inlineStr"/>
+      <c r="W17" s="3">
         <f>HYPERLINK("http://RESEARCHGATE.net/profile/Ryan_Milcarek", "http://RESEARCHGATE.net/profile/Ryan_Milcarek")</f>
         <v/>
       </c>
-      <c r="U17" s="2" t="inlineStr"/>
-      <c r="V17" s="2" t="inlineStr"/>
-      <c r="W17" s="2" t="inlineStr"/>
       <c r="X17" s="2" t="inlineStr"/>
       <c r="Y17" s="2" t="inlineStr"/>
       <c r="Z17" s="2" t="inlineStr"/>
-      <c r="AA17" s="2" t="inlineStr">
+      <c r="AA17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr"/>
+      <c r="AD17" s="2" t="inlineStr">
         <is>
           <t>ENGRC 465 (Tempe, AZ 85287)</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="b">
+      <c r="AE17" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AF17" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2326,42 +2576,45 @@
           <t>N Hegde, Taewoo Lee. Laser-induced breakdown spectroscopy for in situ diagnostics of combustion parameters including tem</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>MAE 565: Rocket Propulsion | MAE 593: Applied Project | MAE 570: Intermediate Thermodynamics</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr"/>
-      <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr"/>
       <c r="P18" s="2" t="inlineStr"/>
-      <c r="Q18" s="2" t="inlineStr">
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr">
         <is>
           <t>Lee's areas of expertise include energy system analysis, thermal and fluid process characterization, and fuel property measurements for energy systems.</t>
         </is>
       </c>
-      <c r="R18" s="2" t="inlineStr">
+      <c r="U18" s="2" t="inlineStr">
         <is>
           <t>Ph.D. Aerospace Engineering, University of Michigan-Ann Arbor | M.S.E. Aerospace Engineering, University of Michigan-Ann Arbor | B.S. Aeronautical and Astronautical Engineering, The Ohio State University-Columbus</t>
         </is>
       </c>
-      <c r="S18" s="2" t="inlineStr"/>
-      <c r="T18" s="2" t="inlineStr"/>
-      <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr"/>
       <c r="W18" s="2" t="inlineStr"/>
       <c r="X18" s="2" t="inlineStr"/>
       <c r="Y18" s="2" t="inlineStr"/>
       <c r="Z18" s="2" t="inlineStr"/>
-      <c r="AA18" s="2" t="inlineStr">
+      <c r="AA18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr"/>
+      <c r="AD18" s="2" t="inlineStr">
         <is>
           <t>ENGRC 377 (TEMPE, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="b">
+      <c r="AE18" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AF18" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2415,40 +2668,55 @@
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
+          <t>"Micro‐explosions caused by the reaction of nano‐sized aluminium and polyvinylidene fluoride to promote the micron‐sized aluminium combustion and inhibit its agglomeration" [The Canadian Journal of Chemical Engineering] (2025) | "Canadian Spine SocietyAbstract ID 19. Program Code CPSS01. Pediatric Spine Frailty Index predicts morbidity and mortality in spinal deformity surgeryAbstract ID 99. Program Code CPSS02. Evaluation of biplane radiographic systems for scoliotic patientsAbstract ID 180. Program Code CPSS03. Rate of spinal osteochondromas diagnosed via advanced imaging in pediatric patients with hereditary multiple osteochondromas: a systematic review and meta-analysisAbstract ID 137. Program Code CPSS04. The impact of adverse childhood experiences on fibromyalgia: a systematic review and meta-analysis of case–control studiesAbstract ID 61. Program Code CPSS05. Enhanced recovery pathway for patients with adolescent idiopathic scoliosis undergoing posterior spinal instrumentation and fusion surgery: a matched controlled analysisAbstract ID 193. Program Code CPSS06. Integrated approach to back pain in the adolescent populationAbstract ID 38. Program Code CPSS07. Traumatic spinal cord injury in children and adolescents: a 20-year review from the Hospital for Sick ChildrenAbstract ID 93. Program Code CPSS08. Prevalence and prognosis of scapular pain following surgical treatment of adolescent idiopathic scoliosis: a prospective study to guide preoperative counsellingAbstract ID 150. Program Code CPSS09. Preoperative zoledronate is safe for children with medical complexity undergoing posterior spinal fusion for neuromuscular scoliosisAbstract ID 15. Program Code CPSS10. Allogeneic transfusion is associated with adverse events in idiopathic scoliosis surgeryAbstract ID 56. Program Code A11. Defining the gaps in transitional care to adulthood for patients in pediatric surgical specialties: a scoping reviewAbstract ID 81. Program Code A12. Effect of mixing dissimilar metals on serum metal ion levels following spinal deformity surgeryAbstract ID 184. Program Code A13. Intraoperative neuromonitoring has poor correlation with postoperative neurological deficits in non-cord level adult deformity surgeryAbstract ID 94. Program Code A14. Role of somatosensory evoked potential (SSEP) in enhancing intraoperative neuromonitoring for spinal deformity surgery — results from a prospective multicentre studyAbstract ID 9. Program Code A15. Does fat matter? The association between extension of fusion and paraspinal muscle fat infiltrationAbstract ID 47. Program Code A16. Pelvic incidence to lumbar lordosis association varies by Roussouly morphotypeAbstract ID 102. Program Code A17. Association between rod and fusion mass fractures in adult spinal deformity: a retrospective cohort studyAbstract ID 8. Program Code A18. Design and implementation of a novel morselized bone interbody cage in posterior lumbar spinal fusion: a biomechanical studyAbstract ID 86. Program Code A19. Decompression versus decompression plus fusion for stable degenerative lumbar spondylolisthesis: comparing outcomes using propensity score–matched dataAbstract ID 176. Program Code A20. Reoperation rates for decompression and fusion versus decompression alone for degenerative spondylolisthesis: a comparative analysisAbstract ID 186. Program Code B21. Modic change is not associated with occult discitis or poor clinical outcome among patients treated surgically for lumbar disc herniation: prospective cohort studyAbstract ID 145. Program Code B22. Machine learning–driven clinical and imaging clustering of degenerative lumbar spondylolisthesis: implications for stratified surgical careAbstract ID 68. Program Code B23. Which psychosocial measures are most strongly related to surgical outcomes in patients with degenerative pathology of the spine?Abstract ID 111. Program Code B24. Acceptance and commitment therapy for patients with degenerative spinal disorders and maladaptive psychological processes: an observational studyAbstract ID 128. Program Code B25. Assessing construct validity of the Spine Adverse Events Severity System: impact of adverse event severity grade on longitudinal patient-reported outcomes)Abstract ID 72. Program Code B26. A pilot randomized controlled trial comparing traditional midline versus paramedian approaches to the lumbar spine for elective posterior/transforaminal lumbar interbody fusion proceduresAbstract ID 96. Program Code B27. Uniportal versus biportal endoscopic decompression for the treatment of lumbar spinal stenosis: a systematic review and updated meta-analysisAbstract ID 152. Program Code B28. Why business tools are essential for managing a spine programAbstract ID 172. Program Code B29. Relationship between fatty infiltration, frailty, and outcomes after spinal surgeryAbstract ID 143. Program Code C30. Clinical trajectory and outcomes with surgical intervention for traumatic central cord syndrome: impact of mechanism of injuryAbstract ID 13. Program Code C31. Optimal tracheostomy timing following traumatic complete spinal cord injury: a comparative analysis of ultra-early, early and delayed practiceAbstract ID 123. Program Code C32. Early stabilizatio" [Canadian Journal of Surgery] (2025) | "Enhanced Thermoelectric Performance of GeTe Materials via Compositing Fe 3 O 4 Nanoparticles" [ACS Applied Materials &amp; Interfaces] (2025)</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>"A facile soft-template synthesis of mesoporous polymeric and carbonaceous nanospheres" [Nature Communications] (2013, 1593 cites) | "Lattice plainification advances highly effective SnSe crystalline thermoelectrics" [Science] (2023, 474 cites) | "Yolk–Shell Hybrid Materials with a Periodic Mesoporous Organosilica Shell: Ideal Nanoreactors for Selective Alcohol Oxidation" [Advanced Functional Materials] (2011, 362 cites)</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
           <t>MAE 241: Intro to Thermodynamics</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr"/>
-      <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr"/>
       <c r="P19" s="2" t="inlineStr"/>
       <c r="Q19" s="2" t="inlineStr">
         <is>
+          <t>Advanced Thermoelectric Materials and Devices, Catalytic Processes in Materials Science, Electrocatalysts for Energy Conversion, Chalcogenide Semiconductor Thin Films, Topological Materials and Phenomena</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
           <t>Yang studies heat transfer, thermal management of electronics, and biomedical devices. She has published multiple research papers in major scientific journals.</t>
         </is>
       </c>
-      <c r="R19" s="2" t="inlineStr">
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>PhD. University of Illinois at Urbana Champaign, 2016-2021 | BS. Tsinghua University, China 2012-2016</t>
         </is>
       </c>
-      <c r="S19" s="2" t="inlineStr"/>
-      <c r="T19" s="2" t="inlineStr"/>
-      <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr"/>
       <c r="W19" s="2" t="inlineStr"/>
       <c r="X19" s="2" t="inlineStr"/>
       <c r="Y19" s="2" t="inlineStr"/>
       <c r="Z19" s="2" t="inlineStr"/>
-      <c r="AA19" s="2" t="inlineStr">
+      <c r="AA19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AD19" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="AB19" s="2" t="b">
+      <c r="AE19" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AC19" s="3">
+      <c r="AF19" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2502,44 +2770,59 @@
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
+          <t>"Early Damage Detection in Cinnamoyl‐Functionalized Shape Memory Epoxy Through Mechanochemical Activation" [Journal of Polymer Science] (2026) | "Microstructural Descriptors-Aware Diffusion-Based model for stochastic reconstruction of composite microstructures" [Composite Structures] (2026) | "In Situ Scanning Electron Microscopy Investigation of Flexural and Interlaminar Failure Mechanisms in Carbon Nanotube‐Reinforced Shape Memory Polymer Composites" [Polymer Composites] (2026)</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>"Automated fatigue damage detection and classification technique for composite structures using Lamb waves and deep autoencoder" [Mechanical Systems and Signal Processing] (2021, 141 cites) | "New higher order plate theory in modeling delamination buckling of composite laminates" [AIAA Journal] (1994, 120 cites) | "Real-time anomaly detection framework using a support vector regression for the safety monitoring of commercial aircraft" [Advanced Engineering Informatics] (2020, 112 cites)</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
           <t>MAE 557: Mechanics Composite Materials | MAE 494: Special Topics | MAE 521: Structural Optimization</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr"/>
       <c r="P20" s="2" t="inlineStr"/>
       <c r="Q20" s="2" t="inlineStr">
         <is>
+          <t>Structural Health Monitoring Techniques, Composite Structure Analysis and Optimization, Ultrasonics and Acoustic Wave Propagation, Mechanical Behavior of Composites, Aeroelasticity and Vibration Control</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
           <t>Chattopadhyay is the director of Adaptive Intelligent Materials and Systems (AIMS) Center at ASU. Her research focuses on structural health monitoring and damage prognosis, and multidisciplinary design optimization.</t>
         </is>
       </c>
-      <c r="R20" s="2" t="inlineStr">
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t>Ph. D. Aerospace Engineering, Georgia Institute of Technology | M.S. Aerospace Engineering, Georgia Institute of Technology | B. Tech. Aeronautical Engineering (Honors), Indian Institute of Technology, Kharagpur, India 1980</t>
         </is>
       </c>
-      <c r="S20" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Adaptive Intelligent Materials &amp; Systems (AIMS) Center</t>
         </is>
       </c>
-      <c r="T20" s="2" t="inlineStr"/>
-      <c r="U20" s="2" t="inlineStr"/>
-      <c r="V20" s="2" t="inlineStr"/>
       <c r="W20" s="2" t="inlineStr"/>
       <c r="X20" s="2" t="inlineStr"/>
       <c r="Y20" s="2" t="inlineStr"/>
       <c r="Z20" s="2" t="inlineStr"/>
-      <c r="AA20" s="2" t="inlineStr">
+      <c r="AA20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr"/>
+      <c r="AD20" s="2" t="inlineStr">
         <is>
           <t>ENGRC 427 (TEMPE, AZ 85287-6106)</t>
         </is>
       </c>
-      <c r="AB20" s="2" t="b">
+      <c r="AE20" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AF20" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2593,48 +2876,63 @@
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
+          <t>"A Versatile Laboratory Approach to Reproduce and Analyze Internal Ocean Wave Dynamics" [arXiv (Cornell University)] (2026) | "A Versatile Laboratory Approach to Reproduce and Analyze Internal Ocean Wave Dynamics" [arXiv (Cornell University)] (2026) | "Lagrangian geometry of flows" [Physical Review Fluids] (2026)</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>"The formation and fate of internal waves in the South China Sea" [Nature] (2015, 739 cites) | "Generalized Smagorinsky model for anisotropic grids" [Physics of Fluids A Fluid Dynamics] (1993, 282 cites) | "Numerical simulation of pulsating turbulent channel flow" [Physics of Fluids] (2001, 211 cites)</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
           <t>MAE 501: Linear Algebra in Engineering | MAE 215: Intro to Programming in MATLAB | MAE 202: Mech.Particles/Rigid Bodies II</t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="2" t="inlineStr"/>
-      <c r="O21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr"/>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>Oceanographic and Atmospheric Processes, Fluid Dynamics and Turbulent Flows, Meteorological Phenomena and Simulations, Ocean Waves and Remote Sensing, Climate variability and models</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
         <is>
           <t>Modeling and Simulation, Oceanography, Earth Systems and Climate Science, Modeling, Modeling, Simulation and Cyberinfrastructure, Applied Mathematics</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr">
+      <c r="S21" s="2" t="inlineStr">
         <is>
           <t>Modeling and Simulation, Oceanography, Earth Systems and Climate Science, Modeling, Modeling, Simulation and Cyberinfrastructure, Applied Mathematics</t>
         </is>
       </c>
-      <c r="Q21" s="2" t="inlineStr">
+      <c r="T21" s="2" t="inlineStr">
         <is>
           <t>Scotti's main focus is theoretical, experimental and computational aspects of environmental fluid mechanics.</t>
         </is>
       </c>
-      <c r="R21" s="2" t="inlineStr">
+      <c r="U21" s="2" t="inlineStr">
         <is>
           <t>PhD Johns Hopkins University</t>
         </is>
       </c>
-      <c r="S21" s="2" t="inlineStr"/>
-      <c r="T21" s="2" t="inlineStr"/>
-      <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr"/>
       <c r="W21" s="2" t="inlineStr"/>
       <c r="X21" s="2" t="inlineStr"/>
       <c r="Y21" s="2" t="inlineStr"/>
       <c r="Z21" s="2" t="inlineStr"/>
-      <c r="AA21" s="2" t="inlineStr">
+      <c r="AA21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AD21" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="AB21" s="2" t="b">
+      <c r="AE21" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AF21" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2692,63 +2990,78 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
+          <t>"Physics-informed machine learning for reconstructing three-dimensional velocity fields from two-dimensional concentration fields" [Physics of Fluids] (2026) | "Statistically Equivalent Representative Volume Element Modeling of Carbon Nanotube–Copper Composite Fibers Based on Cross-Sectional Microstructures" [Journal of Engineering Materials and Technology] (2026) | "Physics-informed neural networks with domain decomposition for inferring velocity fields from concentration fields" [AI Thermal Fluids] (2026)</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>"3D printing of shape-conformable thermoelectric materials using all-inorganic Bi2Te3-based inks" [Nature Energy] (2018, 353 cites) | "Machine learning for heat transfer correlations" [International Communications in Heat and Mass Transfer] (2020, 182 cites) | "High-performance shape-engineerable thermoelectric painting" [Nature Communications] (2016, 173 cites)</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
           <t>MAE 593: Applied Project | MAE 241: Intro to Thermodynamics | MAE 598: Special Topics</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr"/>
-      <c r="N22" s="2" t="inlineStr"/>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>Transport phenomena in heat transfer systems Additive manufacturing Data-driven modeling and design</t>
-        </is>
-      </c>
+      <c r="O22" s="2" t="inlineStr"/>
       <c r="P22" s="2" t="inlineStr"/>
       <c r="Q22" s="2" t="inlineStr">
         <is>
+          <t>Advanced Thermoelectric Materials and Devices, Heat Transfer and Optimization, Thermal properties of materials, Thermal Radiation and Cooling Technologies, Heat Transfer Mechanisms</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>Transport phenomena in heat transfer systems Additive manufacturing Data-driven modeling and design</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
           <t>Kwon aims to improve the energy conversion and transport systems through the fundamental insights into transport physics, and by exploiting additive manufacturing and data-driven approaches.</t>
         </is>
       </c>
-      <c r="R22" s="2" t="inlineStr">
+      <c r="U22" s="2" t="inlineStr">
         <is>
           <t>Ph.D. Mechanical Engineering, University of Illinois at Urbana-Champaign 2013 | M.S. Mechanical Engineering, University of Illinois at Urbana-Champaign 2009 | B.S. Mechanical and Aerospace Engineering, Seoul National University 2008</t>
         </is>
       </c>
-      <c r="S22" s="2" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>3D Energy Lab</t>
         </is>
       </c>
-      <c r="T22" s="3">
+      <c r="W22" s="3">
         <f>HYPERLINK("http://sites.google.com/view/3denergy", "http://sites.google.com/view/3denergy")</f>
         <v/>
       </c>
-      <c r="U22" s="2" t="inlineStr"/>
-      <c r="V22" s="2" t="inlineStr"/>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>3D Printer</t>
-        </is>
-      </c>
-      <c r="X22" s="2" t="inlineStr">
-        <is>
-          <t>NSF</t>
-        </is>
-      </c>
+      <c r="X22" s="2" t="inlineStr"/>
       <c r="Y22" s="2" t="inlineStr"/>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>3D Printer</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>NSF</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
           <t>3D Energy Device Laboratory</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
+      <c r="AD22" s="2" t="inlineStr">
         <is>
           <t>551 E Tyler Mall ERC 363 (Tempe, AZ 85281)</t>
         </is>
       </c>
-      <c r="AB22" s="2" t="b">
+      <c r="AE22" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AF22" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2804,57 +3117,60 @@
           <t>Shape-programmable magnetic soft matter,</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>MAE 417: System Dynamics and Control II | MAE 598: Special Topics | MAE 547: Modeling and Control of Robots</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>KEEN Professorship, The Kern Family Foundation, 2017. | Peebles Award for Graduate Student Research in Adhesion Science, Adhesion Society, 2015.</t>
         </is>
       </c>
-      <c r="N23" s="2" t="inlineStr"/>
-      <c r="O23" s="2" t="inlineStr">
+      <c r="P23" s="2" t="inlineStr"/>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr">
         <is>
           <t>Bio-inspired robotics Soft robotics Magnetic micro-robotics Mechanics of animal locomotion</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr"/>
-      <c r="Q23" s="2" t="inlineStr">
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr">
         <is>
           <t>Marvi would like to develop bio-inspired robotic systems and programmable interfacial structures for search and rescue, exploratory and medical applications.</t>
         </is>
       </c>
-      <c r="R23" s="2" t="inlineStr">
+      <c r="U23" s="2" t="inlineStr">
         <is>
           <t>Ph.D. Mechanical Engineering, Georgia Institute of Technology, Atlanta 2013 | M.S. Mechanical Engineering, Clemson University, SC 2009 | M.S. Biomedical Engineering, Sharif University of Technology, Tehran, Iran 2007 | B.S. Mechanical Engineering, Iran University of Science and Technology, Tehran 2004</t>
         </is>
       </c>
-      <c r="S23" s="2" t="inlineStr">
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Bio-Inspired Robotics, Technology, and Healthcare Laboratory (BIRTH Lab)</t>
         </is>
       </c>
-      <c r="T23" s="3">
+      <c r="W23" s="3">
         <f>HYPERLINK("http://birth.asu.edu", "http://birth.asu.edu")</f>
         <v/>
       </c>
-      <c r="U23" s="2" t="inlineStr"/>
-      <c r="V23" s="2" t="inlineStr"/>
-      <c r="W23" s="2" t="inlineStr"/>
       <c r="X23" s="2" t="inlineStr"/>
       <c r="Y23" s="2" t="inlineStr"/>
       <c r="Z23" s="2" t="inlineStr"/>
-      <c r="AA23" s="2" t="inlineStr">
+      <c r="AA23" s="2" t="inlineStr"/>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="AB23" s="2" t="b">
+      <c r="AE23" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AF23" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2904,43 +3220,58 @@
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
+          <t>"Geometric Feature Relationship-Based Knowledge Distillation for Ground Reaction Force Estimation" [Measurement] (2026) | "Consistency and robustness of virtual time-to-contact in assessing postural sway in people with multiple sclerosis" [Gait &amp; Posture] (2026) | "Understanding the Relationship Between Cutaneous Sensation, Balance, and Falls in People With Multiple Sclerosis" [Neurology Report] (2026)</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>"Time-Varying Ankle Mechanical Impedance During Human Locomotion" [IEEE Transactions on Neural Systems and Rehabilitation Engineering] (2014, 169 cites) | "Summary of Human Ankle Mechanical Impedance During Walking" [IEEE Journal of Translational Engineering in Health and Medicine] (2016, 156 cites) | "Multivariable Dynamic Ankle Mechanical Impedance With Active Muscles" [IEEE Transactions on Neural Systems and Rehabilitation Engineering] (2014, 109 cites)</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
           <t>MAE 598: Special Topics | MAE 417: System Dynamics and Control II | MAE 593: Applied Project</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr"/>
-      <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr"/>
       <c r="P24" s="2" t="inlineStr"/>
       <c r="Q24" s="2" t="inlineStr">
         <is>
+          <t>Muscle activation and electromyography studies, Prosthetics and Rehabilitation Robotics, Balance, Gait, and Falls Prevention, Motor Control and Adaptation, Stroke Rehabilitation and Recovery</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
           <t>Lee's research interests include physical human-robot interaction, neuromuscular control of human movement, robot-aided neurorehabilitation, bio-inspired robotics and system identification for physiological systems.</t>
         </is>
       </c>
-      <c r="R24" s="2" t="inlineStr">
+      <c r="U24" s="2" t="inlineStr">
         <is>
           <t>B.S. Mechanical and Aerospace Engineering, Seoul National University (2002) M.S. Mechanical and Aerospace Engineering, Seoul National University (2004) Ph.D Mechanical Engineering, Massachusetts Institute of Technology (2013)</t>
         </is>
       </c>
-      <c r="S24" s="2" t="inlineStr"/>
-      <c r="T24" s="3">
+      <c r="V24" s="2" t="inlineStr"/>
+      <c r="W24" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/hlee", "https://faculty.engineering.asu.edu/hlee")</f>
         <v/>
       </c>
-      <c r="U24" s="2" t="inlineStr"/>
-      <c r="V24" s="2" t="inlineStr"/>
-      <c r="W24" s="2" t="inlineStr"/>
       <c r="X24" s="2" t="inlineStr"/>
       <c r="Y24" s="2" t="inlineStr"/>
       <c r="Z24" s="2" t="inlineStr"/>
-      <c r="AA24" s="2" t="inlineStr">
+      <c r="AA24" s="2" t="inlineStr"/>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr">
         <is>
           <t>Campus: Tempe</t>
         </is>
       </c>
-      <c r="AB24" s="2" t="b">
+      <c r="AE24" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AF24" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -2990,55 +3321,70 @@
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
+          <t>"Theoretical Analysis of the Process Window for Laser Powder-Bed Fusion for Infrared and Green Lasers Using Rosenthal Approximation" [Materials] (2026) | "Evaluation of Solid-State Diffusion Bonded Inconel 718 Mechanical Properties" [Journal of Innovations in Materials and Manufacturing Engineering] (2026) | "Optimization of Fused Deposition Modeling (FDM) Process for Small-Scale PEEK Medical Devices" [Journal of Manufacturing and Materials Processing] (2025)</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>"Review of Powder Bed Fusion Additive Manufacturing for Metals" [Metals] (2021, 182 cites) | "Optimizing quality of additively manufactured Inconel 718 using powder bed laser melting process" [Additive manufacturing] (2016, 150 cites) | "Towards developing multiscale-multiphysics models and their surrogates for digital twins of metal additive manufacturing" [Additive manufacturing] (2021, 143 cites)</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
           <t>MAE 598: Special Topics | MAE 494: Special Topics | MAE 201: Mech. Particles/Rigid Bodies I</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr"/>
-      <c r="N25" s="2" t="inlineStr"/>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr"/>
+      <c r="P25" s="2" t="inlineStr"/>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>Electronic Packaging and Soldering Technologies, Additive Manufacturing and 3D Printing Technologies, Additive Manufacturing Materials and Processes, Aluminum Alloys Composites Properties, Microstructure and mechanical properties</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
         <is>
           <t>Manufacturing process simulation and modeling and experiments Additive manufacturing Micro/nano manufacturing Microelectronic packaging Application of AI in manufacturing Mechanic of metallic materials Materials characterization Fatigue and damage modeling and simulation</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
+      <c r="S25" s="2" t="inlineStr">
         <is>
           <t>Additive Manufacturing, Manufacturing Engineering</t>
         </is>
       </c>
-      <c r="Q25" s="2" t="inlineStr">
+      <c r="T25" s="2" t="inlineStr">
         <is>
           <t>Dr. Ladani is a Professor of Mechanical and Aerospace Engineering at Arizona State University.</t>
         </is>
       </c>
-      <c r="R25" s="2" t="inlineStr">
+      <c r="U25" s="2" t="inlineStr">
         <is>
           <t>PhD. Mechanical Engineering, University of Maryland-College Park 2007 | M.S. Mechanical Engineering, University of Maryland-College Park 2005 | PhD. Student, Mechanical Engineering, Isfahan University of Technology, Iran 2001-2002 | M.S. Mechanical Engineering, Isfahan University of Technology, Iran 2001 | B.S. Mechanical Engineering, Isfahan University of Technology, Iran 1999</t>
         </is>
       </c>
-      <c r="S25" s="2" t="inlineStr">
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Manufacturing and Advanced Materials Characterization (MAGIC) Lab</t>
         </is>
       </c>
-      <c r="T25" s="3">
+      <c r="W25" s="3">
         <f>HYPERLINK("https://magic.asu.edu/", "https://magic.asu.edu/")</f>
         <v/>
       </c>
-      <c r="U25" s="2" t="inlineStr"/>
-      <c r="V25" s="2" t="inlineStr"/>
-      <c r="W25" s="2" t="inlineStr"/>
       <c r="X25" s="2" t="inlineStr"/>
       <c r="Y25" s="2" t="inlineStr"/>
       <c r="Z25" s="2" t="inlineStr"/>
-      <c r="AA25" s="2" t="inlineStr">
+      <c r="AA25" s="2" t="inlineStr"/>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr">
         <is>
           <t>ISTB4, ROOM 379 781 S Terrace Rd (Tempe, AZ 85287)</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="b">
+      <c r="AE25" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="AC25" s="3">
+      <c r="AF25" s="3">
         <f>HYPERLINK("https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/", "https://faculty.engineering.asu.edu/directory/semte/aerospace-and-mechanical-engineering/")</f>
         <v/>
       </c>
@@ -3092,48 +3438,63 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
+          <t>"Dynamic Energy Simulation for a Tiny House Targeting a Net Zero-Energy Building" [Journal of Innovative Science and Engineering (JISE)] (2026) | "Heat Transfer Enhancement with Low-Concentration CuO/Water Nanofluid and Ultrasonic Energy: An Experimental Study" [International Journal of Thermophysics] (2025) | "Performance enhancement of photovoltaic panels using rotating elliptic enclosures filled with phase change material" [Numerical Heat Transfer Part A Applications] (2025)</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>"Recent developments in phase change materials for energy storage applications: A review" [International Journal of Heat and Mass Transfer] (2018, 1518 cites) | "Thermal Conductivity of Nanoscale Colloidal Solutions (Nanofluids)" [Physical Review Letters] (2005, 921 cites) | "Nanofluid-based direct absorption solar collector" [Journal of Renewable and Sustainable Energy] (2010, 879 cites)</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
           <t>MAE 593: Applied Project | MAE 494: Special Topics | MAE 598: Special Topics</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr"/>
-      <c r="N26" s="2" t="inlineStr"/>
-      <c r="O26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr"/>
+      <c r="P26" s="2" t="inlineStr"/>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>Heat Transfer and Optimization, Solar Thermal and Photovoltaic Systems, Nanofluid Flow and Heat Transfer, Solar-Powered Water Purification Methods, Thermal properties of materials</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
         <is>
           <t>Thermal engineering, sustainable energy systems, energy management, sustainable cooling systems.</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
+      <c r="S26" s="2" t="inlineStr">
         <is>
           <t>Building Technology, Solar Energy Systems, Energy Efficiency Technologies, Mechanical Engineering</t>
         </is>
       </c>
-      <c r="Q26" s="2" t="inlineStr">
+      <c r="T26" s="2" t="inlineStr">
         <is>
           <t>Phelan researches and teaches in the area of sustainable energy, thermal transport and thermal management.</t>
         </is>
       </c>
-      <c r="R26" s="2" t="inlineStr">
+      <c r="U26" s="2" t="in